--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC5932-C31F-4B15-9901-C3B4A7AAFD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE1870F-4241-43AD-B147-C8D28C003057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="297">
   <si>
     <t>Nombre</t>
   </si>
@@ -830,6 +830,87 @@
   </si>
   <si>
     <t>La Bat-Familia;Aves de Presa</t>
+  </si>
+  <si>
+    <t>skill_class</t>
+  </si>
+  <si>
+    <t>skill_name</t>
+  </si>
+  <si>
+    <t>skill_info</t>
+  </si>
+  <si>
+    <t>skill_power</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
+    <t>debuff</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>revive</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>skill_trigger</t>
+  </si>
+  <si>
+    <t>Poder+</t>
+  </si>
+  <si>
+    <t>Poder-</t>
+  </si>
+  <si>
+    <t>Curar+</t>
+  </si>
+  <si>
+    <t>Revivir</t>
+  </si>
+  <si>
+    <t>Escudo</t>
+  </si>
+  <si>
+    <t>Aumenta el poder de todos las cartas aliadas en juego.</t>
+  </si>
+  <si>
+    <t>Reduce el poder de todas las cartas enemigas en juego.</t>
+  </si>
+  <si>
+    <t>Cura 500 puntos de salud una carta aliada</t>
+  </si>
+  <si>
+    <t>Revive una carta de tu elección del cementerio y la devuelve al mazo.</t>
+  </si>
+  <si>
+    <t>Aplica un escudo en esta carta, o en una carta aliada.</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>usar</t>
+  </si>
+  <si>
+    <t>aoe</t>
+  </si>
+  <si>
+    <t>poder/2</t>
+  </si>
+  <si>
+    <t>Ataque múltiple</t>
+  </si>
+  <si>
+    <t>Ataca a todas las cartas enemigas enemigos de forma simultanea.</t>
+  </si>
+  <si>
+    <t>Salud</t>
   </si>
 </sst>
 </file>
@@ -920,7 +1001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -951,6 +1032,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1232,20 +1314,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="105.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="42.42578125" customWidth="1"/>
-    <col min="8" max="8" width="71.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="105.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" customWidth="1"/>
+    <col min="9" max="9" width="71.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1253,29 +1339,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J1" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1283,22 +1383,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="3">
+        <v>6000</v>
+      </c>
+      <c r="D2" s="3">
         <v>5000</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M2">
+        <v>500</v>
+      </c>
+      <c r="N2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1306,22 +1424,40 @@
         <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="6" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>281</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M3">
+        <v>500</v>
+      </c>
+      <c r="N3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1329,22 +1465,40 @@
         <v>1</v>
       </c>
       <c r="C4" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D4" s="3">
         <v>4000</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" t="s">
+        <v>287</v>
+      </c>
+      <c r="L4" t="s">
+        <v>276</v>
+      </c>
+      <c r="M4">
+        <v>500</v>
+      </c>
+      <c r="N4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1352,22 +1506,40 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D5" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>283</v>
+      </c>
+      <c r="K5" t="s">
+        <v>288</v>
+      </c>
+      <c r="L5" t="s">
+        <v>277</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -1375,22 +1547,40 @@
         <v>1</v>
       </c>
       <c r="C6" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="3">
         <v>4000</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6" t="s">
+        <v>289</v>
+      </c>
+      <c r="L6" t="s">
+        <v>278</v>
+      </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="N6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -1398,22 +1588,40 @@
         <v>1</v>
       </c>
       <c r="C7" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D7" s="3">
         <v>4000</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>294</v>
+      </c>
+      <c r="K7" t="s">
+        <v>295</v>
+      </c>
+      <c r="L7" t="s">
+        <v>292</v>
+      </c>
+      <c r="M7" t="s">
+        <v>293</v>
+      </c>
+      <c r="N7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
@@ -1421,22 +1629,25 @@
         <v>1</v>
       </c>
       <c r="C8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -1444,22 +1655,25 @@
         <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="6" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -1467,25 +1681,28 @@
         <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
@@ -1493,20 +1710,23 @@
         <v>1</v>
       </c>
       <c r="C11" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="3">
         <v>3000</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1514,22 +1734,25 @@
         <v>1</v>
       </c>
       <c r="C12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="3">
         <v>3000</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>42</v>
       </c>
@@ -1537,20 +1760,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D13" s="3" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
@@ -1558,20 +1784,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D14" s="3">
         <v>2500</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>46</v>
       </c>
@@ -1579,22 +1808,25 @@
         <v>1</v>
       </c>
       <c r="C15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D15" s="3">
         <v>3000</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -1602,22 +1834,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D16" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>52</v>
       </c>
@@ -1625,22 +1860,25 @@
         <v>1</v>
       </c>
       <c r="C17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D17" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
@@ -1648,20 +1886,23 @@
         <v>1</v>
       </c>
       <c r="C18" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D18" s="3" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="10"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>56</v>
       </c>
@@ -1669,20 +1910,23 @@
         <v>1</v>
       </c>
       <c r="C19" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D19" s="3">
         <v>4000</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="10"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
@@ -1690,20 +1934,23 @@
         <v>1</v>
       </c>
       <c r="C20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D20" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="10"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -1711,20 +1958,23 @@
         <v>1</v>
       </c>
       <c r="C21" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D21" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="10"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -1732,20 +1982,23 @@
         <v>1</v>
       </c>
       <c r="C22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D22" s="3">
         <v>3000</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="10"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
@@ -1753,20 +2006,23 @@
         <v>1</v>
       </c>
       <c r="C23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D23" s="3">
         <v>2500</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>66</v>
       </c>
@@ -1774,20 +2030,23 @@
         <v>1</v>
       </c>
       <c r="C24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D24" s="3">
         <v>3000</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="10"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>68</v>
       </c>
@@ -1795,20 +2054,23 @@
         <v>1</v>
       </c>
       <c r="C25" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="3">
         <v>3000</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="10"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
@@ -1816,22 +2078,25 @@
         <v>1</v>
       </c>
       <c r="C26" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="1" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
@@ -1839,22 +2104,25 @@
         <v>1</v>
       </c>
       <c r="C27" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D27" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
@@ -1862,22 +2130,25 @@
         <v>1</v>
       </c>
       <c r="C28" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D28" s="3">
         <v>3000</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>77</v>
       </c>
@@ -1885,22 +2156,25 @@
         <v>1</v>
       </c>
       <c r="C29" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D29" s="3">
         <v>3000</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G29" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>267</v>
       </c>
@@ -1908,22 +2182,25 @@
         <v>1</v>
       </c>
       <c r="C30" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D30" s="3">
         <v>3000</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>79</v>
       </c>
@@ -1931,22 +2208,25 @@
         <v>1</v>
       </c>
       <c r="C31" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D31" s="3">
         <v>2500</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G31" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>81</v>
       </c>
@@ -1954,22 +2234,25 @@
         <v>1</v>
       </c>
       <c r="C32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="D32" s="3">
         <v>2000</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G32" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>84</v>
       </c>
@@ -1977,22 +2260,25 @@
         <v>1</v>
       </c>
       <c r="C33" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D33" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>86</v>
       </c>
@@ -2000,20 +2286,23 @@
         <v>1</v>
       </c>
       <c r="C34" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="6" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D34" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="10"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>88</v>
       </c>
@@ -2021,22 +2310,25 @@
         <v>1</v>
       </c>
       <c r="C35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D35" s="3">
         <v>2500</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G35" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>90</v>
       </c>
@@ -2044,20 +2336,23 @@
         <v>1</v>
       </c>
       <c r="C36" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D36" s="3">
         <v>4000</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="10"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>92</v>
       </c>
@@ -2065,22 +2360,25 @@
         <v>1</v>
       </c>
       <c r="C37" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D37" s="3">
         <v>4000</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G37" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -2088,22 +2386,25 @@
         <v>1</v>
       </c>
       <c r="C38" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D38" s="3">
         <v>4000</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>97</v>
       </c>
@@ -2111,20 +2412,23 @@
         <v>1</v>
       </c>
       <c r="C39" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D39" s="3">
         <v>2500</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="10"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>99</v>
       </c>
@@ -2132,20 +2436,23 @@
         <v>1</v>
       </c>
       <c r="C40" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="1" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D40" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="10"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G40" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
@@ -2153,22 +2460,25 @@
         <v>1</v>
       </c>
       <c r="C41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D41" s="3">
         <v>3000</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G41" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>103</v>
       </c>
@@ -2176,22 +2486,25 @@
         <v>1</v>
       </c>
       <c r="C42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D42" s="3">
         <v>3000</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G42" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>105</v>
       </c>
@@ -2199,22 +2512,25 @@
         <v>1</v>
       </c>
       <c r="C43" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="1" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G43" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>108</v>
       </c>
@@ -2222,22 +2538,25 @@
         <v>1</v>
       </c>
       <c r="C44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="6" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>111</v>
       </c>
@@ -2245,22 +2564,25 @@
         <v>1</v>
       </c>
       <c r="C45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D45" s="3">
         <v>3000</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G45" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>113</v>
       </c>
@@ -2268,22 +2590,25 @@
         <v>1</v>
       </c>
       <c r="C46" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="1" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G46" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>116</v>
       </c>
@@ -2291,20 +2616,23 @@
         <v>1</v>
       </c>
       <c r="C47" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="1" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D47" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="10"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="10"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>118</v>
       </c>
@@ -2312,20 +2640,23 @@
         <v>1</v>
       </c>
       <c r="C48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D48" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F48" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="10"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G48" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="10"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>120</v>
       </c>
@@ -2333,20 +2664,23 @@
         <v>1</v>
       </c>
       <c r="C49" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D49" s="3">
         <v>4000</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="10"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>122</v>
       </c>
@@ -2354,20 +2688,23 @@
         <v>1</v>
       </c>
       <c r="C50" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D50" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D50" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F50" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="10"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G50" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>124</v>
       </c>
@@ -2375,22 +2712,25 @@
         <v>1</v>
       </c>
       <c r="C51" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="1" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D51" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G51" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>127</v>
       </c>
@@ -2398,22 +2738,25 @@
         <v>1</v>
       </c>
       <c r="C52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D52" s="3">
         <v>4000</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F52" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="G52" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>129</v>
       </c>
@@ -2421,20 +2764,23 @@
         <v>1</v>
       </c>
       <c r="C53" s="3">
-        <v>3500</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="1" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D53" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="10"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="10"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>131</v>
       </c>
@@ -2442,22 +2788,25 @@
         <v>1</v>
       </c>
       <c r="C54" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D54" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D54" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G54" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>135</v>
       </c>
@@ -2465,22 +2814,25 @@
         <v>1</v>
       </c>
       <c r="C55" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D55" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D55" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G55" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>138</v>
       </c>
@@ -2488,22 +2840,25 @@
         <v>1</v>
       </c>
       <c r="C56" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D56" s="4">
         <v>5000</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G56" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>259</v>
       </c>
@@ -2511,20 +2866,23 @@
         <v>1</v>
       </c>
       <c r="C57" s="4">
+        <v>6500</v>
+      </c>
+      <c r="D57" s="4">
         <v>5500</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G57" s="4"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>141</v>
       </c>
@@ -2532,22 +2890,25 @@
         <v>1</v>
       </c>
       <c r="C58" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D58" s="4" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D58" s="4">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G58" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>144</v>
       </c>
@@ -2555,22 +2916,25 @@
         <v>1</v>
       </c>
       <c r="C59" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D59" s="4" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D59" s="4">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="F59" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>264</v>
       </c>
@@ -2578,20 +2942,23 @@
         <v>1</v>
       </c>
       <c r="C60" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D60" s="4" t="s">
+        <v>5500</v>
+      </c>
+      <c r="D60" s="4">
+        <v>4500</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G60" s="4"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G60" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>261</v>
       </c>
@@ -2599,20 +2966,23 @@
         <v>1</v>
       </c>
       <c r="C61" s="4">
+        <v>6500</v>
+      </c>
+      <c r="D61" s="4">
         <v>5500</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G61" s="4"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>147</v>
       </c>
@@ -2620,22 +2990,25 @@
         <v>1</v>
       </c>
       <c r="C62" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D62" s="4">
         <v>4000</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G62" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>256</v>
       </c>
@@ -2643,22 +3016,25 @@
         <v>1</v>
       </c>
       <c r="C63" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D63" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D63" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G63" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H63" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>254</v>
       </c>
@@ -2666,22 +3042,25 @@
         <v>1</v>
       </c>
       <c r="C64" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D64" s="4">
         <v>3000</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G64" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>150</v>
       </c>
@@ -2689,20 +3068,23 @@
         <v>1</v>
       </c>
       <c r="C65" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D65" s="4">
         <v>4000</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G65" s="4"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>152</v>
       </c>
@@ -2710,22 +3092,25 @@
         <v>1</v>
       </c>
       <c r="C66" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D66" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D66" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G66" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>155</v>
       </c>
@@ -2733,22 +3118,25 @@
         <v>1</v>
       </c>
       <c r="C67" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D67" s="4">
         <v>3000</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G67" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>158</v>
       </c>
@@ -2756,20 +3144,23 @@
         <v>1</v>
       </c>
       <c r="C68" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D68" s="4">
         <v>2500</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G68" s="4"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>160</v>
       </c>
@@ -2777,22 +3168,25 @@
         <v>1</v>
       </c>
       <c r="C69" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>8</v>
+        <v>4500</v>
+      </c>
+      <c r="D69" s="4">
+        <v>3500</v>
       </c>
       <c r="E69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G69" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H69" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>163</v>
       </c>
@@ -2800,20 +3194,23 @@
         <v>1</v>
       </c>
       <c r="C70" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D70" s="4">
         <v>2000</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G70" s="4"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>165</v>
       </c>
@@ -2821,22 +3218,25 @@
         <v>1</v>
       </c>
       <c r="C71" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D71" s="4">
         <v>2500</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="F71" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G71" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H71" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>168</v>
       </c>
@@ -2844,20 +3244,23 @@
         <v>1</v>
       </c>
       <c r="C72" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D72" s="4">
         <v>2000</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G72" s="4"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G72" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>170</v>
       </c>
@@ -2865,22 +3268,25 @@
         <v>1</v>
       </c>
       <c r="C73" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D73" s="4">
         <v>2000</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="E73" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G73" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>173</v>
       </c>
@@ -2888,22 +3294,25 @@
         <v>1</v>
       </c>
       <c r="C74" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="8" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D74" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G74" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>175</v>
       </c>
@@ -2911,22 +3320,25 @@
         <v>1</v>
       </c>
       <c r="C75" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D75" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D75" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="F75" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G75" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>177</v>
       </c>
@@ -2934,22 +3346,25 @@
         <v>1</v>
       </c>
       <c r="C76" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D76" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D76" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G76" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>180</v>
       </c>
@@ -2957,22 +3372,25 @@
         <v>1</v>
       </c>
       <c r="C77" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D77" s="4">
         <v>3000</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G77" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>182</v>
       </c>
@@ -2980,22 +3398,25 @@
         <v>1</v>
       </c>
       <c r="C78" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>8</v>
+        <v>5500</v>
+      </c>
+      <c r="D78" s="4">
+        <v>4500</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G78" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H78" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>263</v>
       </c>
@@ -3003,22 +3424,25 @@
         <v>1</v>
       </c>
       <c r="C79" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D79" s="4">
         <v>5000</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G79" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>185</v>
       </c>
@@ -3026,22 +3450,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>8</v>
+        <v>5500</v>
+      </c>
+      <c r="D80" s="4">
+        <v>4500</v>
       </c>
       <c r="E80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G80" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H80" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>188</v>
       </c>
@@ -3049,20 +3476,23 @@
         <v>1</v>
       </c>
       <c r="C81" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D81" s="4">
         <v>5000</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G81" s="4"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G81" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>190</v>
       </c>
@@ -3070,20 +3500,23 @@
         <v>1</v>
       </c>
       <c r="C82" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D82" s="4">
         <v>3000</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G82" s="4"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>192</v>
       </c>
@@ -3091,20 +3524,23 @@
         <v>1</v>
       </c>
       <c r="C83" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D83" s="4">
         <v>4000</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G83" s="4"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G83" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>194</v>
       </c>
@@ -3112,22 +3548,25 @@
         <v>1</v>
       </c>
       <c r="C84" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="7" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D84" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G84" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H84" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>196</v>
       </c>
@@ -3135,22 +3574,25 @@
         <v>1</v>
       </c>
       <c r="C85" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D85" s="4">
         <v>3000</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="E85" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="F85" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G85" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>198</v>
       </c>
@@ -3158,20 +3600,23 @@
         <v>1</v>
       </c>
       <c r="C86" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D86" s="4">
         <v>3000</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="E86" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="F86" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G86" s="4"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G86" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>200</v>
       </c>
@@ -3179,20 +3624,23 @@
         <v>1</v>
       </c>
       <c r="C87" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D87" s="4">
         <v>3000</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="E87" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="F87" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G87" s="4"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>202</v>
       </c>
@@ -3200,22 +3648,25 @@
         <v>1</v>
       </c>
       <c r="C88" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D88" s="4">
         <v>4000</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G88" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>205</v>
       </c>
@@ -3223,22 +3674,25 @@
         <v>1</v>
       </c>
       <c r="C89" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D89" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D89" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="F89" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G89" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>208</v>
       </c>
@@ -3246,22 +3700,25 @@
         <v>1</v>
       </c>
       <c r="C90" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D90" s="4">
         <v>4000</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="F90" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G90" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>210</v>
       </c>
@@ -3269,22 +3726,25 @@
         <v>1</v>
       </c>
       <c r="C91" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D91" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D91" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="F91" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G91" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>212</v>
       </c>
@@ -3292,20 +3752,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D92" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D92" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E92" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="F92" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G92" s="4"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>214</v>
       </c>
@@ -3313,22 +3776,25 @@
         <v>1</v>
       </c>
       <c r="C93" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D93" s="4">
         <v>3000</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="E93" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="F93" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G93" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>216</v>
       </c>
@@ -3336,20 +3802,23 @@
         <v>1</v>
       </c>
       <c r="C94" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>8</v>
+        <v>4500</v>
+      </c>
+      <c r="D94" s="4">
+        <v>3500</v>
       </c>
       <c r="E94" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G94" s="4"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>218</v>
       </c>
@@ -3357,22 +3826,25 @@
         <v>1</v>
       </c>
       <c r="C95" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D95" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D95" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="F95" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G95" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>220</v>
       </c>
@@ -3380,22 +3852,25 @@
         <v>1</v>
       </c>
       <c r="C96" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D96" s="4">
         <v>4000</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E96" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G96" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>223</v>
       </c>
@@ -3403,20 +3878,23 @@
         <v>1</v>
       </c>
       <c r="C97" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D97" s="4">
         <v>3000</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="E97" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="F97" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G97" s="4"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G97" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>225</v>
       </c>
@@ -3424,22 +3902,25 @@
         <v>1</v>
       </c>
       <c r="C98" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D98" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D98" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="F98" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G98" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>227</v>
       </c>
@@ -3447,20 +3928,23 @@
         <v>1</v>
       </c>
       <c r="C99" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D99" s="4">
         <v>3000</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E99" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G99" s="4"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G99" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>229</v>
       </c>
@@ -3468,20 +3952,23 @@
         <v>1</v>
       </c>
       <c r="C100" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D100" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D100" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="F100" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G100" s="4"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G100" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>231</v>
       </c>
@@ -3489,20 +3976,23 @@
         <v>1</v>
       </c>
       <c r="C101" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D101" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D101" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="F101" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G101" s="4"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G101" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>233</v>
       </c>
@@ -3510,22 +4000,25 @@
         <v>1</v>
       </c>
       <c r="C102" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D102" s="4">
         <v>4000</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="E102" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="F102" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G102" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H102" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>235</v>
       </c>
@@ -3533,20 +4026,23 @@
         <v>1</v>
       </c>
       <c r="C103" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D103" s="4">
         <v>2500</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="F103" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G103" s="4"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G103" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>237</v>
       </c>
@@ -3554,20 +4050,23 @@
         <v>1</v>
       </c>
       <c r="C104" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D104" s="4">
         <v>3000</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="F104" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G104" s="4"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G104" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>239</v>
       </c>
@@ -3575,20 +4074,23 @@
         <v>1</v>
       </c>
       <c r="C105" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D105" s="4">
         <v>4000</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E105" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G105" s="4"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G105" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>241</v>
       </c>
@@ -3596,20 +4098,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>8</v>
+        <v>4500</v>
+      </c>
+      <c r="D106" s="4">
+        <v>3500</v>
       </c>
       <c r="E106" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G106" s="4"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G106" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>243</v>
       </c>
@@ -3617,20 +4122,23 @@
         <v>1</v>
       </c>
       <c r="C107" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D107" s="4">
         <v>5000</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="E107" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="F107" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G107" s="4"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G107" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>245</v>
       </c>
@@ -3638,22 +4146,25 @@
         <v>1</v>
       </c>
       <c r="C108" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D108" s="4">
         <v>4000</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="E108" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="F108" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F108" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G108" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H108" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>247</v>
       </c>
@@ -3661,20 +4172,23 @@
         <v>1</v>
       </c>
       <c r="C109" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D109" s="4">
         <v>2500</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="E109" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F109" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G109" s="4"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G109" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>249</v>
       </c>
@@ -3682,22 +4196,25 @@
         <v>1</v>
       </c>
       <c r="C110" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>8</v>
+        <v>5500</v>
+      </c>
+      <c r="D110" s="4">
+        <v>4500</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F110" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="G110" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>251</v>
       </c>
@@ -3705,44 +4222,47 @@
         <v>1</v>
       </c>
       <c r="C111" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="5" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D111" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G111" s="4"/>
+      <c r="G111" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H111" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E34" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E35" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E36" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E37" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E38" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E45" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E52" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E80" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E84" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E64" r:id="rId17" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
-    <hyperlink ref="E63" r:id="rId18" xr:uid="{D80AB2AB-AFBA-474C-9099-56659D4F7343}"/>
-    <hyperlink ref="E57" r:id="rId19" xr:uid="{DBFEB124-BE06-49CC-A78E-75F68A01BDE0}"/>
-    <hyperlink ref="E61" r:id="rId20" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
-    <hyperlink ref="E79" r:id="rId21" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
-    <hyperlink ref="E60" r:id="rId22" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
-    <hyperlink ref="E30" r:id="rId23" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F34" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F35" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F36" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F37" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F38" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F45" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F52" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F80" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F84" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F64" r:id="rId17" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
+    <hyperlink ref="F63" r:id="rId18" xr:uid="{D80AB2AB-AFBA-474C-9099-56659D4F7343}"/>
+    <hyperlink ref="F57" r:id="rId19" xr:uid="{DBFEB124-BE06-49CC-A78E-75F68A01BDE0}"/>
+    <hyperlink ref="F61" r:id="rId20" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
+    <hyperlink ref="F79" r:id="rId21" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
+    <hyperlink ref="F60" r:id="rId22" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
+    <hyperlink ref="F30" r:id="rId23" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE1870F-4241-43AD-B147-C8D28C003057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D362B1BA-D3BA-4B0C-A5D6-B40E932C2058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="318">
   <si>
     <t>Nombre</t>
   </si>
@@ -883,9 +883,6 @@
     <t>Reduce el poder de todas las cartas enemigas en juego.</t>
   </si>
   <si>
-    <t>Cura 500 puntos de salud una carta aliada</t>
-  </si>
-  <si>
     <t>Revive una carta de tu elección del cementerio y la devuelve al mazo.</t>
   </si>
   <si>
@@ -911,6 +908,72 @@
   </si>
   <si>
     <t>Salud</t>
+  </si>
+  <si>
+    <t>Cura 500 puntos de salud a la carta aliada elegida</t>
+  </si>
+  <si>
+    <t>heal_all</t>
+  </si>
+  <si>
+    <t>Cura 500 puntos de salud a todos los aliados en juego</t>
+  </si>
+  <si>
+    <t>Curar++</t>
+  </si>
+  <si>
+    <t>bonus_buff</t>
+  </si>
+  <si>
+    <t>bonus_debuff</t>
+  </si>
+  <si>
+    <t>tank</t>
+  </si>
+  <si>
+    <t>salud*2</t>
+  </si>
+  <si>
+    <t>Duplica su salud y reduce su ataque a la mitad</t>
+  </si>
+  <si>
+    <t>Tanque</t>
+  </si>
+  <si>
+    <t>Potenciar Bonus</t>
+  </si>
+  <si>
+    <t>Anular Bonus</t>
+  </si>
+  <si>
+    <t>Potencia +500 el bonus de afiliación aliado que esté activo</t>
+  </si>
+  <si>
+    <t>Anula el bonus activo enemigo mientras esta carta esté en juego.</t>
+  </si>
+  <si>
+    <t>heal_debuff</t>
+  </si>
+  <si>
+    <t>Reduce un 25% la salud actual de los enemigos en juego, mientras esta carta esté activa</t>
+  </si>
+  <si>
+    <t>Debilitador</t>
+  </si>
+  <si>
+    <t>saludEnemigo*0.75</t>
+  </si>
+  <si>
+    <t>extra_attack</t>
+  </si>
+  <si>
+    <t>Ataque Extra</t>
+  </si>
+  <si>
+    <t>poder</t>
+  </si>
+  <si>
+    <t>Al activar esta habilidad, la carta realiza un ataque extra haciendo n de daño.</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1064,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1032,7 +1095,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1325,8 +1387,8 @@
     <col min="8" max="8" width="42.42578125" customWidth="1"/>
     <col min="9" max="9" width="71.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="79.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1339,7 +1401,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1368,10 +1430,10 @@
       <c r="L1" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>279</v>
       </c>
     </row>
@@ -1413,7 +1475,7 @@
         <v>500</v>
       </c>
       <c r="N2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1454,7 +1516,7 @@
         <v>500</v>
       </c>
       <c r="N3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1486,7 +1548,7 @@
         <v>282</v>
       </c>
       <c r="K4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="L4" t="s">
         <v>276</v>
@@ -1495,7 +1557,7 @@
         <v>500</v>
       </c>
       <c r="N4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1527,7 +1589,7 @@
         <v>283</v>
       </c>
       <c r="K5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L5" t="s">
         <v>277</v>
@@ -1536,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1568,7 +1630,7 @@
         <v>284</v>
       </c>
       <c r="K6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L6" t="s">
         <v>278</v>
@@ -1577,7 +1639,7 @@
         <v>1000</v>
       </c>
       <c r="N6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1606,19 +1668,19 @@
         <v>28</v>
       </c>
       <c r="J7" t="s">
+        <v>293</v>
+      </c>
+      <c r="K7" t="s">
         <v>294</v>
       </c>
-      <c r="K7" t="s">
-        <v>295</v>
-      </c>
       <c r="L7" t="s">
+        <v>291</v>
+      </c>
+      <c r="M7" t="s">
         <v>292</v>
       </c>
-      <c r="M7" t="s">
-        <v>293</v>
-      </c>
       <c r="N7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1646,6 +1708,21 @@
       <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="J8" t="s">
+        <v>299</v>
+      </c>
+      <c r="K8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L8" t="s">
+        <v>297</v>
+      </c>
+      <c r="M8">
+        <v>500</v>
+      </c>
+      <c r="N8" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -1672,6 +1749,21 @@
       <c r="H9" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="J9" t="s">
+        <v>306</v>
+      </c>
+      <c r="K9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L9" t="s">
+        <v>300</v>
+      </c>
+      <c r="M9">
+        <v>500</v>
+      </c>
+      <c r="N9" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -1701,6 +1793,18 @@
       <c r="I10" t="s">
         <v>258</v>
       </c>
+      <c r="J10" t="s">
+        <v>307</v>
+      </c>
+      <c r="K10" t="s">
+        <v>309</v>
+      </c>
+      <c r="L10" t="s">
+        <v>301</v>
+      </c>
+      <c r="N10" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -1725,6 +1829,21 @@
         <v>10</v>
       </c>
       <c r="H11" s="10"/>
+      <c r="J11" t="s">
+        <v>305</v>
+      </c>
+      <c r="K11" t="s">
+        <v>304</v>
+      </c>
+      <c r="L11" t="s">
+        <v>302</v>
+      </c>
+      <c r="M11" t="s">
+        <v>303</v>
+      </c>
+      <c r="N11" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -1751,6 +1870,21 @@
       <c r="H12" s="10" t="s">
         <v>41</v>
       </c>
+      <c r="J12" t="s">
+        <v>312</v>
+      </c>
+      <c r="K12" t="s">
+        <v>311</v>
+      </c>
+      <c r="L12" t="s">
+        <v>310</v>
+      </c>
+      <c r="M12" t="s">
+        <v>313</v>
+      </c>
+      <c r="N12" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1775,6 +1909,21 @@
         <v>10</v>
       </c>
       <c r="H13" s="10"/>
+      <c r="J13" t="s">
+        <v>315</v>
+      </c>
+      <c r="K13" t="s">
+        <v>317</v>
+      </c>
+      <c r="L13" t="s">
+        <v>314</v>
+      </c>
+      <c r="M13" t="s">
+        <v>316</v>
+      </c>
+      <c r="N13" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D362B1BA-D3BA-4B0C-A5D6-B40E932C2058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17361BF3-3CB6-47E4-904B-DC77C435187B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1005,7 +1005,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1021,6 +1021,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64DA89"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBAAEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1064,7 +1088,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1095,6 +1119,11 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1102,6 +1131,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCBAAEC"/>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FF64DA89"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1380,12 +1417,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="105.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42.42578125" customWidth="1"/>
-    <col min="9" max="9" width="71.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="79.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1462,19 +1501,19 @@
       <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="13">
         <v>500</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="13" t="s">
         <v>289</v>
       </c>
     </row>
@@ -1503,19 +1542,19 @@
       <c r="H3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="12">
         <v>500</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="12" t="s">
         <v>289</v>
       </c>
     </row>
@@ -1544,19 +1583,19 @@
       <c r="H4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="13">
         <v>500</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="13" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1585,19 +1624,19 @@
       <c r="H5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="M5" s="15">
+        <v>1</v>
+      </c>
+      <c r="N5" s="15" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1626,19 +1665,19 @@
       <c r="H6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="16">
         <v>1000</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="16" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1667,19 +1706,19 @@
       <c r="H7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="12" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1708,19 +1747,19 @@
       <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="13">
         <v>500</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="13" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1749,19 +1788,19 @@
       <c r="H9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="14">
         <v>500</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="14" t="s">
         <v>289</v>
       </c>
     </row>
@@ -1793,16 +1832,17 @@
       <c r="I10" t="s">
         <v>258</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="N10" t="s">
+      <c r="M10" s="15"/>
+      <c r="N10" s="15" t="s">
         <v>289</v>
       </c>
     </row>
@@ -1829,19 +1869,19 @@
         <v>10</v>
       </c>
       <c r="H11" s="10"/>
-      <c r="J11" t="s">
+      <c r="J11" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="16" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1870,19 +1910,19 @@
       <c r="H12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="15" t="s">
         <v>289</v>
       </c>
     </row>
@@ -1909,19 +1949,19 @@
         <v>10</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="J13" t="s">
+      <c r="J13" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="12" t="s">
         <v>290</v>
       </c>
     </row>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17361BF3-3CB6-47E4-904B-DC77C435187B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA14F89F-95D7-4D21-845E-D089CC373CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="318">
   <si>
     <t>Nombre</t>
   </si>
@@ -877,18 +877,9 @@
     <t>Escudo</t>
   </si>
   <si>
-    <t>Aumenta el poder de todos las cartas aliadas en juego.</t>
-  </si>
-  <si>
-    <t>Reduce el poder de todas las cartas enemigas en juego.</t>
-  </si>
-  <si>
     <t>Revive una carta de tu elección del cementerio y la devuelve al mazo.</t>
   </si>
   <si>
-    <t>Aplica un escudo en esta carta, o en una carta aliada.</t>
-  </si>
-  <si>
     <t>auto</t>
   </si>
   <si>
@@ -910,15 +901,9 @@
     <t>Salud</t>
   </si>
   <si>
-    <t>Cura 500 puntos de salud a la carta aliada elegida</t>
-  </si>
-  <si>
     <t>heal_all</t>
   </si>
   <si>
-    <t>Cura 500 puntos de salud a todos los aliados en juego</t>
-  </si>
-  <si>
     <t>Curar++</t>
   </si>
   <si>
@@ -946,9 +931,6 @@
     <t>Anular Bonus</t>
   </si>
   <si>
-    <t>Potencia +500 el bonus de afiliación aliado que esté activo</t>
-  </si>
-  <si>
     <t>Anula el bonus activo enemigo mientras esta carta esté en juego.</t>
   </si>
   <si>
@@ -974,6 +956,24 @@
   </si>
   <si>
     <t>Al activar esta habilidad, la carta realiza un ataque extra haciendo n de daño.</t>
+  </si>
+  <si>
+    <t>Aumenta @skill_power el poder de todos las cartas aliadas en juego.</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder de todas las cartas enemigas en juego.</t>
+  </si>
+  <si>
+    <t>Cura @skill_power puntos de salud a la carta aliada elegida</t>
+  </si>
+  <si>
+    <t>Cura @skill_power puntos de salud a todos los aliados en juego</t>
+  </si>
+  <si>
+    <t>Aplica @skill_power puntos de escudo a esta carta, o a una carta aliada.</t>
+  </si>
+  <si>
+    <t>Potencia @skill_power el bonus de afiliación aliado que esté activo</t>
   </si>
 </sst>
 </file>
@@ -1119,11 +1119,21 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1428,11 +1438,11 @@
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="79.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1476,7 +1486,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1501,23 +1511,24 @@
       <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="K2" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="L2" s="13" t="s">
+      <c r="K2" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="12">
         <v>500</v>
       </c>
-      <c r="N2" s="13" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1542,23 +1553,24 @@
       <c r="H3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="M3" s="13">
+        <v>500</v>
+      </c>
+      <c r="N3" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="M3" s="12">
-        <v>500</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1583,23 +1595,24 @@
       <c r="H4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="K4" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="L4" s="13" t="s">
+      <c r="K4" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="L4" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>500</v>
       </c>
-      <c r="N4" s="13" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1624,23 +1637,24 @@
       <c r="H5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="M5" s="14">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L5" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="M5" s="15">
-        <v>1</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -1665,23 +1679,24 @@
       <c r="H6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="L6" s="16" t="s">
+      <c r="K6" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="15">
         <v>1000</v>
       </c>
-      <c r="N6" s="16" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -1706,23 +1721,24 @@
       <c r="H7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="L7" s="12" t="s">
+      <c r="I7" s="2"/>
+      <c r="J7" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L7" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
@@ -1747,23 +1763,24 @@
       <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="M8" s="13">
+      <c r="I8" s="2"/>
+      <c r="J8" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="M8" s="12">
         <v>500</v>
       </c>
-      <c r="N8" s="13" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N8" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -1788,23 +1805,24 @@
       <c r="H9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="M9" s="14">
+      <c r="I9" s="2"/>
+      <c r="J9" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="M9" s="16">
         <v>500</v>
       </c>
-      <c r="N9" s="14" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N9" s="16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -1829,24 +1847,24 @@
       <c r="H10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J10" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
@@ -1869,23 +1887,24 @@
         <v>10</v>
       </c>
       <c r="H11" s="10"/>
-      <c r="J11" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I11" s="2"/>
+      <c r="J11" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1910,23 +1929,24 @@
       <c r="H12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I12" s="2"/>
+      <c r="J12" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>42</v>
       </c>
@@ -1949,23 +1969,24 @@
         <v>10</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="J13" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="M13" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I13" s="2"/>
+      <c r="J13" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
@@ -1989,7 +2010,7 @@
       </c>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>46</v>
       </c>
@@ -2015,7 +2036,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2041,7 +2062,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>52</v>
       </c>
@@ -2067,7 +2088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
@@ -2091,7 +2112,7 @@
       </c>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>56</v>
       </c>
@@ -2115,7 +2136,7 @@
       </c>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
@@ -2139,7 +2160,7 @@
       </c>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -2163,7 +2184,7 @@
       </c>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2187,7 +2208,7 @@
       </c>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
@@ -2211,7 +2232,7 @@
       </c>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>66</v>
       </c>
@@ -2235,7 +2256,7 @@
       </c>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>68</v>
       </c>
@@ -2259,7 +2280,7 @@
       </c>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
@@ -2285,7 +2306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
@@ -2311,7 +2332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
@@ -2337,7 +2358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>77</v>
       </c>
@@ -2363,7 +2384,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>267</v>
       </c>
@@ -2389,7 +2410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>79</v>
       </c>
@@ -2415,7 +2436,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>81</v>
       </c>
@@ -2441,7 +2462,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>84</v>
       </c>
@@ -2467,7 +2488,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>86</v>
       </c>
@@ -2491,7 +2512,7 @@
       </c>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>88</v>
       </c>
@@ -2517,7 +2538,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>90</v>
       </c>
@@ -2541,7 +2562,7 @@
       </c>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>92</v>
       </c>
@@ -2567,7 +2588,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -2593,7 +2614,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>97</v>
       </c>
@@ -2617,7 +2638,7 @@
       </c>
       <c r="H39" s="10"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>99</v>
       </c>
@@ -2641,7 +2662,7 @@
       </c>
       <c r="H40" s="10"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
@@ -2667,7 +2688,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>103</v>
       </c>
@@ -2693,7 +2714,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>105</v>
       </c>
@@ -2719,7 +2740,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>108</v>
       </c>
@@ -2745,7 +2766,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>111</v>
       </c>
@@ -2771,7 +2792,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>113</v>
       </c>
@@ -2797,7 +2818,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>116</v>
       </c>
@@ -2821,7 +2842,7 @@
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>118</v>
       </c>
@@ -2843,9 +2864,11 @@
       <c r="G48" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="10"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H48" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>120</v>
       </c>
@@ -2869,7 +2892,7 @@
       </c>
       <c r="H49" s="10"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>122</v>
       </c>
@@ -2893,7 +2916,7 @@
       </c>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>124</v>
       </c>
@@ -2919,7 +2942,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>127</v>
       </c>
@@ -2945,7 +2968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>129</v>
       </c>
@@ -2969,7 +2992,7 @@
       </c>
       <c r="H53" s="10"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>131</v>
       </c>
@@ -2995,7 +3018,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>135</v>
       </c>
@@ -3021,7 +3044,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>138</v>
       </c>
@@ -3047,7 +3070,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>259</v>
       </c>
@@ -3071,7 +3094,7 @@
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>141</v>
       </c>
@@ -3097,7 +3120,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>144</v>
       </c>
@@ -3123,7 +3146,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>264</v>
       </c>
@@ -3147,7 +3170,7 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>261</v>
       </c>
@@ -3171,7 +3194,7 @@
       </c>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>147</v>
       </c>
@@ -3197,7 +3220,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>256</v>
       </c>
@@ -3223,7 +3246,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>254</v>
       </c>
@@ -3249,7 +3272,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>150</v>
       </c>
@@ -3273,7 +3296,7 @@
       </c>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>152</v>
       </c>
@@ -3299,7 +3322,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>155</v>
       </c>
@@ -3325,7 +3348,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>158</v>
       </c>
@@ -3349,7 +3372,7 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>160</v>
       </c>
@@ -3375,7 +3398,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>163</v>
       </c>
@@ -3399,7 +3422,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>165</v>
       </c>
@@ -3425,7 +3448,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>168</v>
       </c>
@@ -3449,7 +3472,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>170</v>
       </c>
@@ -3475,7 +3498,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>173</v>
       </c>
@@ -3501,7 +3524,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>175</v>
       </c>
@@ -3527,7 +3550,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>177</v>
       </c>
@@ -3553,7 +3576,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>180</v>
       </c>
@@ -3579,7 +3602,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>182</v>
       </c>
@@ -3605,7 +3628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>263</v>
       </c>
@@ -3631,7 +3654,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>185</v>
       </c>
@@ -3657,7 +3680,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>188</v>
       </c>
@@ -3681,7 +3704,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>190</v>
       </c>
@@ -3705,7 +3728,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>192</v>
       </c>
@@ -3729,7 +3752,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>194</v>
       </c>
@@ -3755,7 +3778,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>196</v>
       </c>
@@ -3781,7 +3804,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>198</v>
       </c>
@@ -3805,7 +3828,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>200</v>
       </c>
@@ -3829,7 +3852,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>202</v>
       </c>
@@ -3855,7 +3878,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>205</v>
       </c>
@@ -3881,7 +3904,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>208</v>
       </c>
@@ -3907,7 +3930,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>210</v>
       </c>
@@ -3933,7 +3956,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>212</v>
       </c>
@@ -3957,7 +3980,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>214</v>
       </c>
@@ -3983,7 +4006,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>216</v>
       </c>
@@ -4007,7 +4030,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>218</v>
       </c>
@@ -4033,7 +4056,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>220</v>
       </c>
@@ -4059,7 +4082,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>223</v>
       </c>
@@ -4083,7 +4106,7 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>225</v>
       </c>
@@ -4109,7 +4132,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>227</v>
       </c>
@@ -4133,7 +4156,7 @@
       </c>
       <c r="H99" s="4"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>229</v>
       </c>
@@ -4157,7 +4180,7 @@
       </c>
       <c r="H100" s="4"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>231</v>
       </c>
@@ -4181,7 +4204,7 @@
       </c>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>233</v>
       </c>
@@ -4207,7 +4230,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>235</v>
       </c>
@@ -4231,7 +4254,7 @@
       </c>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>237</v>
       </c>
@@ -4255,7 +4278,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>239</v>
       </c>
@@ -4279,7 +4302,7 @@
       </c>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>241</v>
       </c>
@@ -4303,7 +4326,7 @@
       </c>
       <c r="H106" s="4"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>243</v>
       </c>
@@ -4327,7 +4350,7 @@
       </c>
       <c r="H107" s="4"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>245</v>
       </c>
@@ -4353,7 +4376,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>247</v>
       </c>
@@ -4377,7 +4400,7 @@
       </c>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>249</v>
       </c>
@@ -4403,7 +4426,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>251</v>
       </c>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA14F89F-95D7-4D21-845E-D089CC373CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09212922-2D36-4F2C-B74E-443F06F43B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09212922-2D36-4F2C-B74E-443F06F43B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4156E30C-11D8-4F27-81D9-040D0138BD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,7 +1522,7 @@
         <v>274</v>
       </c>
       <c r="M2" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N2" s="12" t="s">
         <v>286</v>
@@ -1564,7 +1564,7 @@
         <v>275</v>
       </c>
       <c r="M3" s="13">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>286</v>
@@ -1606,7 +1606,7 @@
         <v>276</v>
       </c>
       <c r="M4" s="12">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N4" s="12" t="s">
         <v>287</v>
@@ -1774,7 +1774,7 @@
         <v>293</v>
       </c>
       <c r="M8" s="12">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>287</v>
@@ -1816,7 +1816,7 @@
         <v>295</v>
       </c>
       <c r="M9" s="16">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="N9" s="16" t="s">
         <v>286</v>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4156E30C-11D8-4F27-81D9-040D0138BD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2A4E2B-157B-47BC-88A1-065B464F043B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="319">
   <si>
     <t>Nombre</t>
   </si>
@@ -974,6 +974,9 @@
   </si>
   <si>
     <t>Potencia @skill_power el bonus de afiliación aliado que esté activo</t>
+  </si>
+  <si>
+    <t>stun</t>
   </si>
 </sst>
 </file>
@@ -1431,10 +1434,10 @@
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="94" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42.42578125" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="55.42578125" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="79.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -2009,6 +2012,9 @@
         <v>10</v>
       </c>
       <c r="H14" s="10"/>
+      <c r="L14" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2A4E2B-157B-47BC-88A1-065B464F043B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B3A3FF-C20F-49A3-A2F6-6732AD3A47C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$203</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="543">
   <si>
     <t>Nombre</t>
   </si>
@@ -88,18 +91,12 @@
     <t>La Liga de la Justicia;La Bat-Familia</t>
   </si>
   <si>
-    <t>Green Lantern</t>
-  </si>
-  <si>
     <t>Magia</t>
   </si>
   <si>
     <t>https://i.pinimg.com/236x/c5/9b/4a/c59b4a39271f81c1a033ced128c41b70.jpg</t>
   </si>
   <si>
-    <t>Green Lantern Corps;La Liga de la Justicia</t>
-  </si>
-  <si>
     <t>Aquaman</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>Red Tornado</t>
   </si>
   <si>
-    <t>https://i.pinimg.com/236x/26/94/03/269403011bc61f2878bf0a130ad62ca2.jpg</t>
-  </si>
-  <si>
     <t>Blue Beetle</t>
   </si>
   <si>
@@ -268,9 +262,6 @@
     <t>Robin</t>
   </si>
   <si>
-    <t>https://i.pinimg.com/236x/ce/48/ca/ce48ca760324c363401d5345154bf46c.jpg</t>
-  </si>
-  <si>
     <t>Los Titanes;La Bat-Familia</t>
   </si>
   <si>
@@ -304,9 +295,6 @@
     <t>https://i.pinimg.com/236x/ec/e6/15/ece615ad3bac4b22aedbaa8d817408f4.jpg</t>
   </si>
   <si>
-    <t>Green Lantern Corps</t>
-  </si>
-  <si>
     <t>John Stewart</t>
   </si>
   <si>
@@ -709,9 +697,6 @@
     <t>https://i.pinimg.com/236x/b1/37/8d/b1378d50def8a7c4a43be1a094f60335.jpg</t>
   </si>
   <si>
-    <t>Star Sapphire</t>
-  </si>
-  <si>
     <t>https://i.pinimg.com/236x/01/d2/4f/01d24f727ff87d7d91c6749676a042fe.jpg</t>
   </si>
   <si>
@@ -793,18 +778,6 @@
     <t>Lyssa Drak</t>
   </si>
   <si>
-    <t>https://i.pinimg.com/736x/fd/fc/fe/fdfcfeaccaa3b2f54adc827692c585e0.jpg</t>
-  </si>
-  <si>
-    <t>https://i.pinimg.com/1200x/39/23/ca/3923ca18eaf31e58a420da6ca064746c.jpg</t>
-  </si>
-  <si>
-    <t>Antimonitor</t>
-  </si>
-  <si>
-    <t>https://static.wikia.nocookie.net/superman/images/e/eb/Mobius.png/revision/latest?cb=20150724204428&amp;path-prefix=es</t>
-  </si>
-  <si>
     <t>Spectre</t>
   </si>
   <si>
@@ -955,9 +928,6 @@
     <t>poder</t>
   </si>
   <si>
-    <t>Al activar esta habilidad, la carta realiza un ataque extra haciendo n de daño.</t>
-  </si>
-  <si>
     <t>Aumenta @skill_power el poder de todos las cartas aliadas en juego.</t>
   </si>
   <si>
@@ -977,6 +947,711 @@
   </si>
   <si>
     <t>stun</t>
+  </si>
+  <si>
+    <t>La Liga de la Justicia;Los Titanes</t>
+  </si>
+  <si>
+    <t>Alan Scott</t>
+  </si>
+  <si>
+    <t>Amethyst</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Atlanna</t>
+  </si>
+  <si>
+    <t>Batwing</t>
+  </si>
+  <si>
+    <t>Beast Boy</t>
+  </si>
+  <si>
+    <t>Big Barda</t>
+  </si>
+  <si>
+    <t>Bumblebee</t>
+  </si>
+  <si>
+    <t>Cyclone</t>
+  </si>
+  <si>
+    <t>Damian Wayne</t>
+  </si>
+  <si>
+    <t>Deadman</t>
+  </si>
+  <si>
+    <t>Guy Gardner</t>
+  </si>
+  <si>
+    <t>Harbinger</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>Jackson Hyde</t>
+  </si>
+  <si>
+    <t>Jay Garrick</t>
+  </si>
+  <si>
+    <t>Kyle Rayner</t>
+  </si>
+  <si>
+    <t>Orion</t>
+  </si>
+  <si>
+    <t>The Question</t>
+  </si>
+  <si>
+    <t>Krypto</t>
+  </si>
+  <si>
+    <t>Metamorpho</t>
+  </si>
+  <si>
+    <t>Midnighter</t>
+  </si>
+  <si>
+    <t>Mister Miracle</t>
+  </si>
+  <si>
+    <t>Pandora</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Simon Baz</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>Stephanie Brown</t>
+  </si>
+  <si>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Vibe</t>
+  </si>
+  <si>
+    <t>Saint Walker</t>
+  </si>
+  <si>
+    <t>Indigo</t>
+  </si>
+  <si>
+    <t>Nubia</t>
+  </si>
+  <si>
+    <t>Yara Flor</t>
+  </si>
+  <si>
+    <t>Hal Jordan</t>
+  </si>
+  <si>
+    <t>Team Arrow</t>
+  </si>
+  <si>
+    <t>Carol Ferris</t>
+  </si>
+  <si>
+    <t>Red Robin</t>
+  </si>
+  <si>
+    <t>Atlantes</t>
+  </si>
+  <si>
+    <t>La Liga de la Justicia;Atlantes</t>
+  </si>
+  <si>
+    <t>Lanterns</t>
+  </si>
+  <si>
+    <t>Green Lantern Corps;Lanterns</t>
+  </si>
+  <si>
+    <t>Green Lantern Corps;La Liga de la Justicia;Lanterns</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/9/95/Green_Lantern_Alan_Scott_0003.jpg</t>
+  </si>
+  <si>
+    <t>https://static.comicvine.com/uploads/original/11132/111329300/6536021-403612ee5d76b45e32b721806fe7a6e6.jpg</t>
+  </si>
+  <si>
+    <t>https://static.dc.com/dc/files/default_images/GalleryChar_1920x1080_2_Arsenal_RHOODO_Cv23_55f8bc0abe7a46.32624707.jpg</t>
+  </si>
+  <si>
+    <t>https://static.dc.com/dc/files/default_images/BLOGroll_LukeFox_620f0f1b1dc727.66202240.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/9b/2c/d0/9b2cd029879f1a21229eb928f1bb50a2.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/d/d0/Birds_of_Prey_Vol_5_8_Textless_Lee_Variant.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/0/0b/Maxine_Hunkel_Prime_Earth_001.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/22/ec/8a/22ec8ad5f4f01b119223f76366cfc34d.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/564x/87/61/24/876124792ee13cf2c96f9dd863a8663e.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/Green_Lantern_%28Guy_Gardner%29.jpg</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/50e1a9ebe4b0395512a0aa60/1373347231497-CK1QZUA6ZX68MXG2XJQ5/331504-199546-harbinger.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/e/e8/Augustus_Freeman_Earth_M_0002.jpg</t>
+  </si>
+  <si>
+    <t>https://www.comicvine.com/a/uploads/original/11115/111156051/7162203-3419251976-6c514.jpg</t>
+  </si>
+  <si>
+    <t>https://comicvine.gamespot.com/a/uploads/scale_medium/11161/111612243/8827494-jaygarrick.jpg</t>
+  </si>
+  <si>
+    <t>https://dcuguide.com/images/d/d8/Green_Lantern_%28Kyle_Rayner%29.png</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/564x/b9/f7/6f/b9f76f2fb59e7882e4e2b935cebf379c.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/f1/09/b7/f109b729282e480b5617602e1d143c56.jpg</t>
+  </si>
+  <si>
+    <t>Dreamer</t>
+  </si>
+  <si>
+    <t>https://static.dc.com/2025-06/2025_06_30_PrideDreamerDCUJourney_Marquee_3x1.jpg?w=1200</t>
+  </si>
+  <si>
+    <t>https://shop.thirdeyecomics.com/cdn/shop/files/dc-comics-comic-books-krypto-the-last-dog-of-krypton-2-of-5-cvr-b-rafael-de-latorre-card-stock-var-76194138865600221-0525dc101-1156846580.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/b/bd/Metamorpho_The_Element_Man_Vol_1_6_Textless_Variant.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/d2/a6/95/d2a6956055b986f53e88715b5e980738.jpg</t>
+  </si>
+  <si>
+    <t>https://static0.srcdn.com/wordpress/wp-content/uploads/2019/05/Mister-Miracle-DC-Comics-Movie.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/e/e0/Trinity_of_Sin_Pandora_Vol_1_1_Textless.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/5/5b/Detective_Comics_Vol_1_1094_Textless_Benjamin_Variant.jpg</t>
+  </si>
+  <si>
+    <t>https://static.dc.com/dc/files/default_images/Char_Gallery_SimonBaz_GLS_Cv55_var_5fa21e7f1b9996.76773719.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/3e/28/3c/3e283c508760a441c5adb23bff84f623.jpg</t>
+  </si>
+  <si>
+    <t>https://static.dc.com/dc/files/default_images/Char_Thumb_Thunder_60244c92b86625.86689759.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/1/19/Justice_League_of_America%27s_Vibe_Vol_1_1_Textless.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/48/22/75/482275b03fdf6d6893ea45933fb726f4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/4b/b6/fb/4bb6fb276428d52d22096e414850b958.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/10/1b/4b/101b4be6ae92fba922e30146a0ae4bc2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/c9/ef/78/c9ef7882800b6e44ecd25fe89a2f11ba.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/44/e7/f2/44e7f21133de8428b75d60580f77ef08.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/82/4d/cf/824dcfa4c26ced733b4a394922cfc722.jpg</t>
+  </si>
+  <si>
+    <t>Omen</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/10/14/7a/10147aedf913d44c14d893c3004c7d86.jpg</t>
+  </si>
+  <si>
+    <t>Artemis</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/ac/e2/31/ace2317eb1ded4485cf8954d1aec1464.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/69/ad/e2/69ade290a5b4b481c19eefcfc4b0d335.jpg</t>
+  </si>
+  <si>
+    <t>Amazo</t>
+  </si>
+  <si>
+    <t>Batman Who Laughs</t>
+  </si>
+  <si>
+    <t>Barbatos</t>
+  </si>
+  <si>
+    <t>Black Mask</t>
+  </si>
+  <si>
+    <t>Bloodsport</t>
+  </si>
+  <si>
+    <t>Carmine Falcone</t>
+  </si>
+  <si>
+    <t>Captain Boomerang</t>
+  </si>
+  <si>
+    <t>Cheshire</t>
+  </si>
+  <si>
+    <t>Deimos</t>
+  </si>
+  <si>
+    <t>Doctor Psycho</t>
+  </si>
+  <si>
+    <t>Giganta</t>
+  </si>
+  <si>
+    <t>Granny Goodness</t>
+  </si>
+  <si>
+    <t>Queen Bee</t>
+  </si>
+  <si>
+    <t>King Shark</t>
+  </si>
+  <si>
+    <t>Maxwell Lord</t>
+  </si>
+  <si>
+    <t>Ocean Master</t>
+  </si>
+  <si>
+    <t>Grail</t>
+  </si>
+  <si>
+    <t>Ratcatcher</t>
+  </si>
+  <si>
+    <t>Simon Stagg</t>
+  </si>
+  <si>
+    <t>Steppenwolf</t>
+  </si>
+  <si>
+    <t>Thinker</t>
+  </si>
+  <si>
+    <t>Telos</t>
+  </si>
+  <si>
+    <t>Vandal Savage</t>
+  </si>
+  <si>
+    <t>Victor Zsasz</t>
+  </si>
+  <si>
+    <t>Veronica Cale</t>
+  </si>
+  <si>
+    <t>Weasel</t>
+  </si>
+  <si>
+    <t>Dex Starr</t>
+  </si>
+  <si>
+    <t>Skallox</t>
+  </si>
+  <si>
+    <t>Zilius Zox</t>
+  </si>
+  <si>
+    <t>Nekron</t>
+  </si>
+  <si>
+    <t>Black Hand</t>
+  </si>
+  <si>
+    <t>Ursa</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Mongul</t>
+  </si>
+  <si>
+    <t>DeSaad</t>
+  </si>
+  <si>
+    <t>Jinx</t>
+  </si>
+  <si>
+    <t>Arthur Light</t>
+  </si>
+  <si>
+    <t>Psimon</t>
+  </si>
+  <si>
+    <t>Mammoth</t>
+  </si>
+  <si>
+    <t>Gizmo</t>
+  </si>
+  <si>
+    <t>Reign</t>
+  </si>
+  <si>
+    <t>Faora</t>
+  </si>
+  <si>
+    <t>Glomulus</t>
+  </si>
+  <si>
+    <t>Mr. Mxyzptlk</t>
+  </si>
+  <si>
+    <t>The Eradicator</t>
+  </si>
+  <si>
+    <t>Manchester Black</t>
+  </si>
+  <si>
+    <t>Brother Blood</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Kalibak</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/b2/54/3e/b2543e2c74ac7e9e3d8c2b64b8ba4b53.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/e9/c6/2e/e9c62e7e97147bf060efc30b258596c9.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/bf/43/81/bf43812f240a031329fed74d9272b533.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/ed/a8/20/eda8204800ebb79c95d100391f084211.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/28/2f/e7/282fe7a1740bd549a5c0eb42bdb0d190.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/73/78/af/7378af3823b10a46ca3237b15e015fa6.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/b9/0f/bf/b90fbf202135f7051d66b03b3cd3061a.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/e4/ec/1f/e4ec1f51bb80086ce73dc4ca04fcb1e3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/ad/69/91/ad69917cae0edb1156df8c7ec47324ed.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/cb/28/6b/cb286b9d6dcd3600789155a487c468ba.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/d6/fa/07/d6fa070f27660bc32d9b0b8cad3c060a.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/3c/7b/9c/3c7b9c1450bd731b6dbc2c987daddc5b.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/b8/ff/6d/b8ff6d771307cdfa3526bf5a55e8d407.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/07/7b/04/077b0409d32d20546af2b67a666d7a0d.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/65/d2/21/65d221b257b9f7c1cfff9f3cedf471d2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/ba/09/ed/ba09edc930740734192019ce474e9306.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/28/e2/3d/28e23d53e28135cc55f8689783fcbb9e.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/17/6b/b3/176bb3fe4da16399c64f245f82b9350a.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/b9/6d/36/b96d3667f619b53a028cca9a6edb04df.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/ee/b0/de/eeb0de7102924c68f0abcf33686ba505.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/v4HJgWx7/grail.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/68/75/be/6875be4fda22938d7c2fb61e03a7e870.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/11/90/f0/1190f05af1dc274668729059e326b6b7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/3b/82/8f/3b828fbcdee3a1766b193b80dc56e251.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/0e/9e/a8/0e9ea82004bc470470cf2280cf0fe027.jpg</t>
+  </si>
+  <si>
+    <t>Fury</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/07/06/ed/0706edbb9485fbed49a0d7bcaf746b20.jpg</t>
+  </si>
+  <si>
+    <t>Apokolips</t>
+  </si>
+  <si>
+    <t>La Sociedad Secreta; Apokolips</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/36/8c/76/368c76bfe98adf77a5b3811f018018de.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/21WVMhWS/unnamed.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/4b/20/ab/4b20ab15035b55571761e82cf886e613.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/0d/dc/ec/0ddcec39da981fb3c8f65b5a5f7a58fd.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/0f/66/51/0f66514a179c6118e769c30f1b21a7a1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/78/02/ea/7802ea2bf9f6ecc9933dba76261a5688.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/1c/78/a9/1c78a9060301f24a6f40f81ab8e9f996.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/7/71/Skallox_004.jpg/revision/latest?cb=20140209033425</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/doblaje/images/7/70/Zilius_Zox.jpg</t>
+  </si>
+  <si>
+    <t>https://i.redd.it/x122na3idciy.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/injusticefanon/images/8/83/Black_Hand_060.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/45/c9/a8/45c9a8ab92d49460ed57a6eb34c715f2.jpg</t>
+  </si>
+  <si>
+    <t>https://comicvine.gamespot.com/a/uploads/scale_medium/6/65423/4013380-ac34non.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/cb/41/eb/cb41ebcbc4c7b02e7362d1e3dc5f3344.jpg</t>
+  </si>
+  <si>
+    <t>https://www.superherodb.com/pictures2/portraits/10/050/10702.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/e/ea/Jinx_DC_Comics_Modern_001.jpg</t>
+  </si>
+  <si>
+    <t>Fearsome Five</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/marvel_dc/images/d/dd/Deathstroke_Vol_4_22_Textless_Variant.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/7/70/Psimon.jpg</t>
+  </si>
+  <si>
+    <t>https://static0.cbrimages.com/wordpress/wp-content/uploads/2019/08/Mammoth-DC-Titans-feature.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/564x/ee/6b/bc/ee6bbcccafcd67284173ab46e229356f.jpg</t>
+  </si>
+  <si>
+    <t>https://comicvine.gamespot.com/a/uploads/scale_medium/4/47635/2168308-1.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wikia.nocookie.net/antagonisten/images/9/91/Faora_Hu-Ul_%28DC%29.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/bRvQ4jWJ/i-loved-this-team-these-characters-were-great-together-v0-lymv5zg4wbqc1.webp</t>
+  </si>
+  <si>
+    <t>Klarion Bleak</t>
+  </si>
+  <si>
+    <t>https://d2thvodm3xyo6j.cloudfront.net/media/2021/04/6bc23d491d4320a3-600x338.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/10/9d/7b/109d7b4f548bc943bbb290f576b437a1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/58/e0/10/58e0106f11a358eb1aa9d3db9180fb40.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/57/3e/69/573e695beefd4e32efdea7d704c62e2d.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/ymMJFFCC/Grid.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/50/dc/5a/50dc5a54a8ede8e63c44bc1da7ce1b4a.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/b5/15/cb/b515cb5f242e1f4aef07b6df97fe6366.jpg</t>
+  </si>
+  <si>
+    <t>Velocistas;JSA</t>
+  </si>
+  <si>
+    <t>Green Lantern Corps;Lanterns;JSA</t>
+  </si>
+  <si>
+    <t>Etrigan</t>
+  </si>
+  <si>
+    <t>Madame Xanadu</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/7a/d2/3f/7ad23fd6bdda9378f5a71d07e516d870.jpg</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/14/cf/90/14cf90c42ccd0737904e7cb0522aded5.jpg</t>
+  </si>
+  <si>
+    <t>Aves de Presa; Team Arrow</t>
+  </si>
+  <si>
+    <t>Thea Queen</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/40/48/8d/40488d6b44958c7432ec995839590f65.jpg</t>
+  </si>
+  <si>
+    <t>JSA; Team Arrow</t>
+  </si>
+  <si>
+    <t>Al activar esta habilidad, la carta realiza un ataque extra haciendo @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Lluvia de Batarangs</t>
+  </si>
+  <si>
+    <t>Visión de calor</t>
+  </si>
+  <si>
+    <t>Constructo protector</t>
+  </si>
+  <si>
+    <t>Inhibidor sónico</t>
+  </si>
+  <si>
+    <t>Tornado de velocidad</t>
+  </si>
+  <si>
+    <t>Gracia de Temiscira</t>
+  </si>
+  <si>
+    <t>Alíento gélido</t>
+  </si>
+  <si>
+    <t>Empalar</t>
+  </si>
+  <si>
+    <t>Aquaman utiliza su tridente en un ataque feroz que inflige @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Manto psíquico</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power puntos de poder a todas las cartas enemigas en juego.</t>
+  </si>
+  <si>
+    <t>Amplificador neuronal</t>
+  </si>
+  <si>
+    <t>Aumenta @skill_power puntos el poder de todos los aliados en juego.</t>
+  </si>
+  <si>
+    <t>Crea un escudo de luz que otorga @skill_power puntos de escudo a si mismo, o a un aliado.</t>
+  </si>
+  <si>
+    <t>Golpea a todos sus enemigos de forma simultanea causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Potencia @skill_power el bonus de afiliación aliado que esté activo.</t>
+  </si>
+  <si>
+    <t>Superman congela a su enemigo, causándole @skill_power puntos de daño.</t>
+  </si>
+  <si>
+    <t>Gas nervioso</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power puntos el poder de todos los enemigos en juego.</t>
+  </si>
+  <si>
+    <t>Dardo paralizante</t>
+  </si>
+  <si>
+    <t>El objetivo enemigo queda aturdido durante @skill_power turnos.</t>
+  </si>
+  <si>
+    <t>Sueño inducido</t>
+  </si>
+  <si>
+    <t>El objetivo cae en un profundo sueño que dura @skill_power turnos.</t>
+  </si>
+  <si>
+    <t>dot</t>
+  </si>
+  <si>
+    <t>Cortes profundos</t>
+  </si>
+  <si>
+    <t>Hiere al objetivo provocandole un sangrado que causa @skill_power de daño durante 3 turnos.</t>
+  </si>
+  <si>
+    <t>life_steal</t>
+  </si>
+  <si>
+    <t>Al dañar a un enemigo, recupera @skill_power puntos de salud.</t>
+  </si>
+  <si>
+    <t>poder*0.25</t>
+  </si>
+  <si>
+    <t>Robo de vida</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1683,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1048,6 +1723,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA675"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1091,7 +1778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1137,6 +1824,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1146,10 +1843,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF64DA89"/>
+      <color rgb="FFFFA675"/>
       <color rgb="FFCBAAEC"/>
       <color rgb="FF99CCFF"/>
       <color rgb="FFFF7C80"/>
-      <color rgb="FF64DA89"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1426,20 +2124,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="94" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="86.140625" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.42578125" customWidth="1"/>
-    <col min="9" max="9" width="55.42578125" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="79.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="74.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.85546875" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -1453,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1471,22 +2169,22 @@
         <v>6</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1500,7 +2198,7 @@
         <v>6000</v>
       </c>
       <c r="D2" s="3">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
@@ -1515,20 +2213,20 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M2" s="12">
-        <v>100</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>286</v>
+      <c r="J2" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1542,7 +2240,7 @@
         <v>5500</v>
       </c>
       <c r="D3" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -1557,20 +2255,20 @@
         <v>14</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="M3" s="13">
-        <v>100</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>286</v>
+      <c r="J3" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="M3" s="16">
+        <v>50</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1584,7 +2282,7 @@
         <v>5000</v>
       </c>
       <c r="D4" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -1599,20 +2297,20 @@
         <v>17</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="M4" s="12">
-        <v>1000</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>287</v>
+      <c r="J4" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1626,7 +2324,7 @@
         <v>4500</v>
       </c>
       <c r="D5" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -1642,24 +2340,22 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="14" t="s">
-        <v>283</v>
+        <v>516</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="M5" s="14">
-        <v>1</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="M5" s="14"/>
       <c r="N5" s="14" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>343</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1668,40 +2364,40 @@
         <v>5000</v>
       </c>
       <c r="D6" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>25</v>
+        <v>351</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="15" t="s">
-        <v>284</v>
+        <v>515</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>316</v>
+        <v>526</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="M6" s="15">
         <v>1000</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1710,40 +2406,40 @@
         <v>5000</v>
       </c>
       <c r="D7" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>28</v>
+        <v>348</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="13" t="s">
-        <v>290</v>
+        <v>520</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -1752,40 +2448,40 @@
         <v>4500</v>
       </c>
       <c r="D8" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>31</v>
+        <v>308</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="12" t="s">
-        <v>294</v>
+        <v>524</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>315</v>
+        <v>525</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="M8" s="12">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1794,40 +2490,40 @@
         <v>5500</v>
       </c>
       <c r="D9" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="M9" s="16">
-        <v>50</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>286</v>
+      <c r="J9" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M9" s="14">
+        <v>100</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1836,40 +2532,40 @@
         <v>5500</v>
       </c>
       <c r="D10" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14" t="s">
-        <v>286</v>
+        <v>34</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -1878,38 +2574,28 @@
         <v>4000</v>
       </c>
       <c r="D11" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>287</v>
-      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1918,40 +2604,30 @@
         <v>4000</v>
       </c>
       <c r="D12" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="N12" s="14" t="s">
-        <v>286</v>
-      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1960,13 +2636,13 @@
         <v>5500</v>
       </c>
       <c r="D13" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>10</v>
@@ -1974,24 +2650,24 @@
       <c r="H13" s="10"/>
       <c r="I13" s="2"/>
       <c r="J13" s="13" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -2000,25 +2676,39 @@
         <v>3500</v>
       </c>
       <c r="D14" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="L14" t="s">
-        <v>318</v>
+      <c r="H14" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -2027,24 +2717,39 @@
         <v>4000</v>
       </c>
       <c r="D15" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>48</v>
+        <v>508</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -2053,24 +2758,37 @@
         <v>4500</v>
       </c>
       <c r="D16" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -2079,24 +2797,39 @@
         <v>4500</v>
       </c>
       <c r="D17" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="M17" s="14">
+        <v>1</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -2105,22 +2838,37 @@
         <v>5500</v>
       </c>
       <c r="D18" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="M18" s="12">
+        <v>750</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -2129,22 +2877,22 @@
         <v>5000</v>
       </c>
       <c r="D19" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2153,22 +2901,22 @@
         <v>4500</v>
       </c>
       <c r="D20" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>59</v>
+        <v>441</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -2177,22 +2925,22 @@
         <v>4500</v>
       </c>
       <c r="D21" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2201,22 +2949,37 @@
         <v>4000</v>
       </c>
       <c r="D22" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="M22" s="19">
+        <v>200</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2225,22 +2988,22 @@
         <v>3500</v>
       </c>
       <c r="D23" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -2249,22 +3012,22 @@
         <v>4000</v>
       </c>
       <c r="D24" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
@@ -2273,22 +3036,22 @@
         <v>4000</v>
       </c>
       <c r="D25" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3">
         <v>1</v>
@@ -2297,24 +3060,39 @@
         <v>4500</v>
       </c>
       <c r="D26" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -2323,24 +3101,39 @@
         <v>4500</v>
       </c>
       <c r="D27" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="M27" s="14">
+        <v>1</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -2349,30 +3142,45 @@
         <v>4000</v>
       </c>
       <c r="D28" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="M28" s="16">
+        <v>50</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
       </c>
       <c r="C29" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D29" s="3">
         <v>3000</v>
@@ -2381,44 +3189,74 @@
         <v>19</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="3">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D30" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H30" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="M30" s="12">
+        <v>100</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
@@ -2427,24 +3265,39 @@
         <v>3500</v>
       </c>
       <c r="D31" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M31" s="14">
+        <v>100</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -2453,24 +3306,39 @@
         <v>3000</v>
       </c>
       <c r="D32" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B33" s="3">
         <v>1</v>
@@ -2479,24 +3347,39 @@
         <v>4500</v>
       </c>
       <c r="D33" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3">
         <v>1</v>
@@ -2505,22 +3388,22 @@
         <v>4500</v>
       </c>
       <c r="D34" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>87</v>
+      <c r="F34" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3">
         <v>1</v>
@@ -2529,24 +3412,24 @@
         <v>3500</v>
       </c>
       <c r="D35" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>89</v>
+      <c r="F35" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B36" s="3">
         <v>1</v>
@@ -2555,22 +3438,39 @@
         <v>5000</v>
       </c>
       <c r="D36" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>91</v>
+        <v>22</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="M36" s="12">
+        <v>750</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
@@ -2579,24 +3479,39 @@
         <v>5000</v>
       </c>
       <c r="D37" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>93</v>
+        <v>19</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="M37" s="16">
+        <v>50</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
@@ -2605,24 +3520,39 @@
         <v>5000</v>
       </c>
       <c r="D38" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>96</v>
+        <v>19</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="M38" s="12">
+        <v>100</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
@@ -2631,22 +3561,37 @@
         <v>3500</v>
       </c>
       <c r="D39" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J39" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="M39" s="19">
+        <v>200</v>
+      </c>
+      <c r="N39" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -2655,22 +3600,22 @@
         <v>5500</v>
       </c>
       <c r="D40" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H40" s="10"/>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B41" s="3">
         <v>1</v>
@@ -2679,24 +3624,24 @@
         <v>4000</v>
       </c>
       <c r="D41" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
@@ -2705,24 +3650,24 @@
         <v>4000</v>
       </c>
       <c r="D42" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B43" s="3">
         <v>1</v>
@@ -2731,24 +3676,39 @@
         <v>4500</v>
       </c>
       <c r="D43" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
@@ -2757,24 +3717,24 @@
         <v>4500</v>
       </c>
       <c r="D44" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>109</v>
+      <c r="F44" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B45" s="3">
         <v>1</v>
@@ -2783,24 +3743,39 @@
         <v>4000</v>
       </c>
       <c r="D45" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>112</v>
+      <c r="F45" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M45" s="15">
+        <v>1000</v>
+      </c>
+      <c r="N45" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
@@ -2809,24 +3784,24 @@
         <v>4500</v>
       </c>
       <c r="D46" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
@@ -2835,22 +3810,22 @@
         <v>5500</v>
       </c>
       <c r="D47" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B48" s="3">
         <v>1</v>
@@ -2859,24 +3834,39 @@
         <v>4500</v>
       </c>
       <c r="D48" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="N48" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B49" s="3">
         <v>1</v>
@@ -2885,22 +3875,22 @@
         <v>5000</v>
       </c>
       <c r="D49" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H49" s="10"/>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
@@ -2909,22 +3899,39 @@
         <v>4500</v>
       </c>
       <c r="D50" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H50" s="10"/>
-    </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="M50" s="12">
+        <v>1000</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
@@ -2933,24 +3940,39 @@
         <v>5500</v>
       </c>
       <c r="D51" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="M51" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
@@ -2959,1432 +3981,1657 @@
         <v>5000</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M52" s="14">
+        <v>100</v>
+      </c>
+      <c r="N52" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B53" s="17">
+        <v>1</v>
+      </c>
+      <c r="C53" s="17">
+        <v>4500</v>
+      </c>
+      <c r="D53" s="17">
+        <v>3500</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L53" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B54" s="17">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="D54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="J54" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L54" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="M54" s="12">
+        <v>1000</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B55" s="17">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3000</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B56" s="17">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3">
+        <v>3500</v>
+      </c>
+      <c r="D56" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B57" s="17">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="3">
-        <v>1</v>
-      </c>
-      <c r="C53" s="3">
+      <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="B58" s="17">
+        <v>1</v>
+      </c>
+      <c r="C58" s="17">
+        <v>3200</v>
+      </c>
+      <c r="D58" s="17">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="17"/>
+    </row>
+    <row r="59" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B59" s="17">
+        <v>1</v>
+      </c>
+      <c r="C59" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D59" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L59" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M59" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="N59" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" s="17">
+        <v>1</v>
+      </c>
+      <c r="C60" s="17">
         <v>4500</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="17"/>
+    </row>
+    <row r="61" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B61" s="17">
+        <v>1</v>
+      </c>
+      <c r="C61" s="17">
         <v>3500</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H53" s="10"/>
-    </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="4">
-        <v>1</v>
-      </c>
-      <c r="C54" s="4">
+      <c r="D61" s="17">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="17"/>
+    </row>
+    <row r="62" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" s="17">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="17"/>
+    </row>
+    <row r="63" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B63" s="17">
+        <v>1</v>
+      </c>
+      <c r="C63" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="B64" s="17">
+        <v>1</v>
+      </c>
+      <c r="C64" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D64" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B65" s="17">
+        <v>1</v>
+      </c>
+      <c r="C65" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="L65" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="N65" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B66" s="17">
+        <v>1</v>
+      </c>
+      <c r="C66" s="17">
+        <v>3000</v>
+      </c>
+      <c r="D66" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="17">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3">
         <v>4500</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D67" s="3">
         <v>3500</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E67" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4">
+      <c r="F67" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B68" s="17">
+        <v>1</v>
+      </c>
+      <c r="C68" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D68" s="17">
+        <v>3000</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="17"/>
+    </row>
+    <row r="69" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="B69" s="17">
+        <v>1</v>
+      </c>
+      <c r="C69" s="17">
         <v>4500</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D69" s="17">
         <v>3500</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" s="17"/>
+    </row>
+    <row r="70" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B70" s="17">
+        <v>1</v>
+      </c>
+      <c r="C70" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D70" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B71" s="17">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3">
+        <v>4500</v>
+      </c>
+      <c r="D71" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="M71" s="12">
+        <v>100</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="B72" s="17">
+        <v>1</v>
+      </c>
+      <c r="C72" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D72" s="17">
+        <v>2500</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="4">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4">
-        <v>6000</v>
-      </c>
-      <c r="D56" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B57" s="4">
-        <v>1</v>
-      </c>
-      <c r="C57" s="4">
-        <v>6500</v>
-      </c>
-      <c r="D57" s="4">
+      <c r="F72" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B73" s="17">
+        <v>1</v>
+      </c>
+      <c r="C73" s="17">
         <v>5500</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B58" s="4">
-        <v>1</v>
-      </c>
-      <c r="C58" s="4">
-        <v>5500</v>
-      </c>
-      <c r="D58" s="4">
-        <v>4500</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="D73" s="17">
+        <v>4000</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="17"/>
+    </row>
+    <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B74" s="17">
+        <v>1</v>
+      </c>
+      <c r="C74" s="17">
+        <v>3000</v>
+      </c>
+      <c r="D74" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B59" s="4">
-        <v>1</v>
-      </c>
-      <c r="C59" s="4">
-        <v>5500</v>
-      </c>
-      <c r="D59" s="4">
-        <v>4500</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4">
-        <v>5500</v>
-      </c>
-      <c r="D60" s="4">
-        <v>4500</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B61" s="4">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4">
-        <v>6500</v>
-      </c>
-      <c r="D61" s="4">
-        <v>5500</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D62" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B63" s="4">
-        <v>1</v>
-      </c>
-      <c r="C63" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D63" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B64" s="4">
-        <v>1</v>
-      </c>
-      <c r="C64" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D64" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B65" s="4">
-        <v>1</v>
-      </c>
-      <c r="C65" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D65" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="4">
-        <v>1</v>
-      </c>
-      <c r="C66" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D66" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" s="4">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D67" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B68" s="4">
-        <v>1</v>
-      </c>
-      <c r="C68" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D68" s="4">
-        <v>2500</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B69" s="4">
-        <v>1</v>
-      </c>
-      <c r="C69" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D69" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B70" s="4">
-        <v>1</v>
-      </c>
-      <c r="C70" s="4">
-        <v>3000</v>
-      </c>
-      <c r="D70" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B71" s="4">
-        <v>1</v>
-      </c>
-      <c r="C71" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D71" s="4">
-        <v>2500</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B72" s="4">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4">
-        <v>3000</v>
-      </c>
-      <c r="D72" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="4">
-        <v>1</v>
-      </c>
-      <c r="C73" s="4">
-        <v>3000</v>
-      </c>
-      <c r="D73" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B74" s="4">
-        <v>1</v>
-      </c>
-      <c r="C74" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D74" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B75" s="4">
+      <c r="F74" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="17"/>
+    </row>
+    <row r="75" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="B75" s="17">
         <v>1</v>
       </c>
       <c r="C75" s="4">
         <v>4500</v>
       </c>
       <c r="D75" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G75" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="B76" s="17">
+        <v>1</v>
+      </c>
+      <c r="C76" s="17">
         <v>3500</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B76" s="4">
-        <v>1</v>
-      </c>
-      <c r="C76" s="4">
+      <c r="D76" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="10"/>
+      <c r="J76" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="K76" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="L76" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="M76" s="19">
+        <v>2</v>
+      </c>
+      <c r="N76" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B77" s="17">
+        <v>1</v>
+      </c>
+      <c r="C77" s="17">
+        <v>3000</v>
+      </c>
+      <c r="D77" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="B78" s="17">
+        <v>1</v>
+      </c>
+      <c r="C78" s="17">
         <v>4500</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D78" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" s="17"/>
+    </row>
+    <row r="79" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B79" s="17">
+        <v>1</v>
+      </c>
+      <c r="C79" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D79" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="17"/>
+    </row>
+    <row r="80" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B80" s="17">
+        <v>1</v>
+      </c>
+      <c r="C80" s="17">
+        <v>4500</v>
+      </c>
+      <c r="D80" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H80" s="17"/>
+    </row>
+    <row r="81" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="B81" s="17">
+        <v>1</v>
+      </c>
+      <c r="C81" s="17">
+        <v>5000</v>
+      </c>
+      <c r="D81" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="J81" s="20" t="s">
+        <v>542</v>
+      </c>
+      <c r="K81" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="L81" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="M81" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="N81" s="20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B82" s="17">
+        <v>1</v>
+      </c>
+      <c r="C82" s="17">
         <v>3500</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B77" s="4">
-        <v>1</v>
-      </c>
-      <c r="C77" s="4">
+      <c r="D82" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" s="17"/>
+    </row>
+    <row r="83" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B83" s="17">
+        <v>1</v>
+      </c>
+      <c r="C83" s="17">
         <v>4000</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D83" s="17">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B84" s="17">
+        <v>1</v>
+      </c>
+      <c r="C84" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D84" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" s="17"/>
+    </row>
+    <row r="85" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="B85" s="17">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3">
         <v>3000</v>
       </c>
-      <c r="E77" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B78" s="4">
-        <v>1</v>
-      </c>
-      <c r="C78" s="4">
-        <v>5500</v>
-      </c>
-      <c r="D78" s="4">
+      <c r="D85" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J85" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="K85" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="L85" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="M85" s="19">
+        <v>2</v>
+      </c>
+      <c r="N85" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B86" s="17">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D86" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="17"/>
+    </row>
+    <row r="87" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="B87" s="17">
+        <v>1</v>
+      </c>
+      <c r="C87" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D87" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="B88" s="17">
+        <v>1</v>
+      </c>
+      <c r="C88" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D88" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="17"/>
+    </row>
+    <row r="89" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B89" s="17">
+        <v>1</v>
+      </c>
+      <c r="C89" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D89" s="17">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" s="17"/>
+      <c r="J89" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="K89" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="L89" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="M89" s="14"/>
+      <c r="N89" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B90" s="17">
+        <v>1</v>
+      </c>
+      <c r="C90" s="17">
+        <v>5000</v>
+      </c>
+      <c r="D90" s="17">
+        <v>3500</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L90" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="M90" s="12">
+        <v>1250</v>
+      </c>
+      <c r="N90" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B91" s="17">
+        <v>1</v>
+      </c>
+      <c r="C91" s="17">
+        <v>4000</v>
+      </c>
+      <c r="D91" s="17">
+        <v>3500</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="L91" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="M91" s="12">
+        <v>750</v>
+      </c>
+      <c r="N91" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B92" s="17">
+        <v>1</v>
+      </c>
+      <c r="C92" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D92" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K92" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L92" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M92" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="N92" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B93" s="17">
+        <v>1</v>
+      </c>
+      <c r="C93" s="3">
         <v>4500</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B79" s="4">
-        <v>1</v>
-      </c>
-      <c r="C79" s="4">
-        <v>6000</v>
-      </c>
-      <c r="D79" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B80" s="4">
-        <v>1</v>
-      </c>
-      <c r="C80" s="4">
-        <v>5500</v>
-      </c>
-      <c r="D80" s="4">
+      <c r="D93" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J93" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="K93" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="L93" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="M93" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="N93" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B94" s="17">
+        <v>1</v>
+      </c>
+      <c r="C94" s="17">
         <v>4500</v>
       </c>
-      <c r="E80" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B81" s="4">
-        <v>1</v>
-      </c>
-      <c r="C81" s="4">
-        <v>6000</v>
-      </c>
-      <c r="D81" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B82" s="4">
-        <v>1</v>
-      </c>
-      <c r="C82" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D82" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B83" s="4">
-        <v>1</v>
-      </c>
-      <c r="C83" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D83" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B84" s="4">
-        <v>1</v>
-      </c>
-      <c r="C84" s="4">
+      <c r="D94" s="17">
+        <v>3500</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="M94" s="12">
+        <v>100</v>
+      </c>
+      <c r="N94" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="3">
+        <v>1</v>
+      </c>
+      <c r="C95" s="3">
         <v>4500</v>
       </c>
-      <c r="D84" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B85" s="4">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D85" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E85" s="4" t="s">
+      <c r="D95" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" s="10"/>
+    </row>
+    <row r="96" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B96" s="4">
+        <v>1</v>
+      </c>
+      <c r="C96" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D96" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B86" s="4">
-        <v>1</v>
-      </c>
-      <c r="C86" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D86" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B87" s="4">
-        <v>1</v>
-      </c>
-      <c r="C87" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D87" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B88" s="4">
-        <v>1</v>
-      </c>
-      <c r="C88" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D88" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B89" s="4">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D89" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B90" s="4">
-        <v>1</v>
-      </c>
-      <c r="C90" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D90" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B91" s="4">
-        <v>1</v>
-      </c>
-      <c r="C91" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D91" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B92" s="4">
-        <v>1</v>
-      </c>
-      <c r="C92" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D92" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B93" s="4">
-        <v>1</v>
-      </c>
-      <c r="C93" s="4">
-        <v>4000</v>
-      </c>
-      <c r="D93" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B94" s="4">
-        <v>1</v>
-      </c>
-      <c r="C94" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D94" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H94" s="4"/>
-    </row>
-    <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="4">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D95" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B96" s="4">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4">
-        <v>5000</v>
-      </c>
-      <c r="D96" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="F96" s="4" t="s">
-        <v>221</v>
+        <v>127</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>222</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="B97" s="4">
         <v>1</v>
       </c>
       <c r="C97" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D97" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H97" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="B98" s="4">
         <v>1</v>
       </c>
       <c r="C98" s="4">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="D98" s="4">
         <v>3500</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>146</v>
+        <v>469</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="B99" s="4">
         <v>1</v>
       </c>
       <c r="C99" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D99" s="4">
         <v>4000</v>
       </c>
-      <c r="D99" s="4">
-        <v>3000</v>
-      </c>
       <c r="E99" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H99" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="B100" s="4">
         <v>1</v>
       </c>
       <c r="C100" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D100" s="4">
         <v>3500</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H100" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="B101" s="4">
         <v>1</v>
       </c>
       <c r="C101" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D101" s="4">
         <v>3500</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B102" s="4">
         <v>1</v>
       </c>
       <c r="C102" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D102" s="4">
         <v>4000</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="B103" s="4">
         <v>1</v>
       </c>
       <c r="C103" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D103" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>236</v>
+        <v>143</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H103" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B104" s="4">
         <v>1</v>
       </c>
       <c r="C104" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D104" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>238</v>
+        <v>501</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H104" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B105" s="4">
         <v>1</v>
       </c>
       <c r="C105" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D105" s="4">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H105" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="B106" s="4">
         <v>1</v>
       </c>
       <c r="C106" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D106" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H106" s="4"/>
     </row>
     <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="B107" s="4">
         <v>1</v>
       </c>
       <c r="C107" s="4">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D107" s="4">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H107" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="B108" s="4">
         <v>1</v>
       </c>
       <c r="C108" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D108" s="4">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>246</v>
+        <v>151</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="B109" s="4">
         <v>1</v>
@@ -4393,70 +5640,2401 @@
         <v>3500</v>
       </c>
       <c r="D109" s="4">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="B110" s="4">
         <v>1</v>
       </c>
       <c r="C110" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D110" s="4">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B111" s="4">
         <v>1</v>
       </c>
       <c r="C111" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D111" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B112" s="4">
+        <v>1</v>
+      </c>
+      <c r="C112" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D112" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" s="4">
+        <v>1</v>
+      </c>
+      <c r="C113" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D113" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B114" s="4">
+        <v>1</v>
+      </c>
+      <c r="C114" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D114" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B115" s="4">
+        <v>1</v>
+      </c>
+      <c r="C115" s="4">
         <v>4500</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D115" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B116" s="4">
+        <v>1</v>
+      </c>
+      <c r="C116" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D116" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B117" s="4">
+        <v>1</v>
+      </c>
+      <c r="C117" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D117" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B118" s="4">
+        <v>1</v>
+      </c>
+      <c r="C118" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D118" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B119" s="4">
+        <v>1</v>
+      </c>
+      <c r="C119" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D119" s="4">
         <v>3500</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H111" s="4"/>
+      <c r="E119" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B120" s="4">
+        <v>1</v>
+      </c>
+      <c r="C120" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D120" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B121" s="4">
+        <v>1</v>
+      </c>
+      <c r="C121" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D121" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B122" s="4">
+        <v>1</v>
+      </c>
+      <c r="C122" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D122" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B123" s="4">
+        <v>1</v>
+      </c>
+      <c r="C123" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D123" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H123" s="4"/>
+    </row>
+    <row r="124" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B124" s="4">
+        <v>1</v>
+      </c>
+      <c r="C124" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D124" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H124" s="4"/>
+    </row>
+    <row r="125" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B125" s="4">
+        <v>1</v>
+      </c>
+      <c r="C125" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D125" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B126" s="4">
+        <v>1</v>
+      </c>
+      <c r="C126" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D126" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B127" s="4">
+        <v>1</v>
+      </c>
+      <c r="C127" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D127" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H127" s="4"/>
+    </row>
+    <row r="128" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B128" s="4">
+        <v>1</v>
+      </c>
+      <c r="C128" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D128" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H128" s="4"/>
+    </row>
+    <row r="129" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B129" s="4">
+        <v>1</v>
+      </c>
+      <c r="C129" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D129" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" s="4">
+        <v>1</v>
+      </c>
+      <c r="C130" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D130" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="4">
+        <v>1</v>
+      </c>
+      <c r="C131" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D131" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B132" s="4">
+        <v>1</v>
+      </c>
+      <c r="C132" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D132" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B133" s="4">
+        <v>1</v>
+      </c>
+      <c r="C133" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D133" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H133" s="4"/>
+    </row>
+    <row r="134" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B134" s="4">
+        <v>1</v>
+      </c>
+      <c r="C134" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D134" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B135" s="4">
+        <v>1</v>
+      </c>
+      <c r="C135" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D135" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H135" s="4"/>
+    </row>
+    <row r="136" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B136" s="4">
+        <v>1</v>
+      </c>
+      <c r="C136" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D136" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B137" s="4">
+        <v>1</v>
+      </c>
+      <c r="C137" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D137" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B138" s="4">
+        <v>1</v>
+      </c>
+      <c r="C138" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D138" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H138" s="4"/>
+    </row>
+    <row r="139" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B139" s="4">
+        <v>1</v>
+      </c>
+      <c r="C139" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D139" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B140" s="4">
+        <v>1</v>
+      </c>
+      <c r="C140" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D140" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H140" s="4"/>
+    </row>
+    <row r="141" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B141" s="4">
+        <v>1</v>
+      </c>
+      <c r="C141" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D141" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B142" s="4">
+        <v>1</v>
+      </c>
+      <c r="C142" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D142" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B143" s="4">
+        <v>1</v>
+      </c>
+      <c r="C143" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D143" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H143" s="4"/>
+    </row>
+    <row r="144" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B144" s="4">
+        <v>1</v>
+      </c>
+      <c r="C144" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D144" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H144" s="4"/>
+    </row>
+    <row r="145" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B145" s="4">
+        <v>1</v>
+      </c>
+      <c r="C145" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D145" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H145" s="4"/>
+    </row>
+    <row r="146" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B146" s="4">
+        <v>1</v>
+      </c>
+      <c r="C146" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D146" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H146" s="4"/>
+    </row>
+    <row r="147" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B147" s="4">
+        <v>1</v>
+      </c>
+      <c r="C147" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D147" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H147" s="4"/>
+    </row>
+    <row r="148" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B148" s="4">
+        <v>1</v>
+      </c>
+      <c r="C148" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D148" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B149" s="4">
+        <v>1</v>
+      </c>
+      <c r="C149" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D149" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H149" s="4"/>
+    </row>
+    <row r="150" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B150" s="4">
+        <v>1</v>
+      </c>
+      <c r="C150" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D150" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B151" s="4">
+        <v>1</v>
+      </c>
+      <c r="C151" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D151" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B152" s="4">
+        <v>1</v>
+      </c>
+      <c r="C152" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D152" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B153" s="4">
+        <v>1</v>
+      </c>
+      <c r="C153" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D153" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H153" s="4"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B154" s="4">
+        <v>1</v>
+      </c>
+      <c r="C154" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D154" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H154" s="4"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B155" s="4">
+        <v>1</v>
+      </c>
+      <c r="C155" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D155" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B156" s="4">
+        <v>1</v>
+      </c>
+      <c r="C156" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D156" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H156" s="4"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B157" s="4">
+        <v>1</v>
+      </c>
+      <c r="C157" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D157" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B158" s="4">
+        <v>1</v>
+      </c>
+      <c r="C158" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D158" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H158" s="4"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B159" s="4">
+        <v>1</v>
+      </c>
+      <c r="C159" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D159" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H159" s="4"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B160" s="4">
+        <v>1</v>
+      </c>
+      <c r="C160" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D160" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H160" s="4"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B161" s="4">
+        <v>1</v>
+      </c>
+      <c r="C161" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D161" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B162" s="4">
+        <v>1</v>
+      </c>
+      <c r="C162" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D162" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B163" s="4">
+        <v>1</v>
+      </c>
+      <c r="C163" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D163" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B164" s="4">
+        <v>1</v>
+      </c>
+      <c r="C164" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D164" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H164" s="4"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B165" s="4">
+        <v>1</v>
+      </c>
+      <c r="C165" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D165" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B166" s="4">
+        <v>1</v>
+      </c>
+      <c r="C166" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D166" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B167" s="4">
+        <v>1</v>
+      </c>
+      <c r="C167" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D167" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H167" s="4"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B168" s="4">
+        <v>1</v>
+      </c>
+      <c r="C168" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D168" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H168" s="4"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B169" s="4">
+        <v>1</v>
+      </c>
+      <c r="C169" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D169" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B170" s="4">
+        <v>1</v>
+      </c>
+      <c r="C170" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D170" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H170" s="4"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B171" s="4">
+        <v>1</v>
+      </c>
+      <c r="C171" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D171" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H171" s="4"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B172" s="4">
+        <v>1</v>
+      </c>
+      <c r="C172" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D172" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B173" s="4">
+        <v>1</v>
+      </c>
+      <c r="C173" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D173" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B174" s="4">
+        <v>1</v>
+      </c>
+      <c r="C174" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D174" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H174" s="4"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B175" s="4">
+        <v>1</v>
+      </c>
+      <c r="C175" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D175" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B176" s="4">
+        <v>1</v>
+      </c>
+      <c r="C176" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D176" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B177" s="4">
+        <v>1</v>
+      </c>
+      <c r="C177" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D177" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H177" s="4"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B178" s="4">
+        <v>1</v>
+      </c>
+      <c r="C178" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D178" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H178" s="4"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B179" s="4">
+        <v>1</v>
+      </c>
+      <c r="C179" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D179" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H179" s="4"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B180" s="4">
+        <v>1</v>
+      </c>
+      <c r="C180" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D180" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B181" s="4">
+        <v>1</v>
+      </c>
+      <c r="C181" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D181" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B182" s="4">
+        <v>1</v>
+      </c>
+      <c r="C182" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D182" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H182" s="4"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B183" s="4">
+        <v>1</v>
+      </c>
+      <c r="C183" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D183" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H183" s="4"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B184" s="4">
+        <v>1</v>
+      </c>
+      <c r="C184" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D184" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H184" s="4"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B185" s="4">
+        <v>1</v>
+      </c>
+      <c r="C185" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D185" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B186" s="4">
+        <v>1</v>
+      </c>
+      <c r="C186" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D186" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B187" s="4">
+        <v>1</v>
+      </c>
+      <c r="C187" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D187" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H187" s="4"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B188" s="4">
+        <v>1</v>
+      </c>
+      <c r="C188" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D188" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H188" s="4"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B189" s="4">
+        <v>1</v>
+      </c>
+      <c r="C189" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D189" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B190" s="4">
+        <v>1</v>
+      </c>
+      <c r="C190" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D190" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B191" s="4">
+        <v>1</v>
+      </c>
+      <c r="C191" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D191" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B192" s="4">
+        <v>1</v>
+      </c>
+      <c r="C192" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D192" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B193" s="4">
+        <v>1</v>
+      </c>
+      <c r="C193" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D193" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B194" s="4">
+        <v>1</v>
+      </c>
+      <c r="C194" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D194" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B195" s="4">
+        <v>1</v>
+      </c>
+      <c r="C195" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D195" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B196" s="4">
+        <v>1</v>
+      </c>
+      <c r="C196" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D196" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H196" s="4"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B197" s="4">
+        <v>1</v>
+      </c>
+      <c r="C197" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D197" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H197" s="4"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B198" s="4">
+        <v>1</v>
+      </c>
+      <c r="C198" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D198" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H198" s="4"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B199" s="4">
+        <v>1</v>
+      </c>
+      <c r="C199" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D199" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B200" s="4">
+        <v>1</v>
+      </c>
+      <c r="C200" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D200" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H200" s="4"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B201" s="4">
+        <v>1</v>
+      </c>
+      <c r="C201" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D201" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H201" s="4"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B202" s="4">
+        <v>1</v>
+      </c>
+      <c r="C202" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D202" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H202" s="4"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B203" s="4">
+        <v>1</v>
+      </c>
+      <c r="C203" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D203" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H203" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N203" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="C204:C1048576 C2:C151">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D204:D1048576 D2:D151">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C152:C203">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D152:D203">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -4472,15 +8050,64 @@
     <hyperlink ref="F38" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="F45" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="F52" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F80" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F84" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F64" r:id="rId17" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
-    <hyperlink ref="F63" r:id="rId18" xr:uid="{D80AB2AB-AFBA-474C-9099-56659D4F7343}"/>
-    <hyperlink ref="F57" r:id="rId19" xr:uid="{DBFEB124-BE06-49CC-A78E-75F68A01BDE0}"/>
-    <hyperlink ref="F61" r:id="rId20" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
-    <hyperlink ref="F79" r:id="rId21" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
-    <hyperlink ref="F60" r:id="rId22" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
-    <hyperlink ref="F30" r:id="rId23" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
+    <hyperlink ref="F121" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F125" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F105" r:id="rId17" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
+    <hyperlink ref="F102" r:id="rId18" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
+    <hyperlink ref="F120" r:id="rId19" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
+    <hyperlink ref="F101" r:id="rId20" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
+    <hyperlink ref="F30" r:id="rId21" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
+    <hyperlink ref="F75" r:id="rId22" xr:uid="{8B8635A9-7759-45CB-8B60-1697B5FF9938}"/>
+    <hyperlink ref="F53" r:id="rId23" xr:uid="{FAF75EE9-F39E-499A-ACD1-703CCBD91506}"/>
+    <hyperlink ref="F54" r:id="rId24" xr:uid="{2164950A-5C4A-4BAF-AC07-2F7A9737DFEC}"/>
+    <hyperlink ref="F56" r:id="rId25" xr:uid="{BF052A87-D28D-498A-B1EA-FE1690026421}"/>
+    <hyperlink ref="F58" r:id="rId26" xr:uid="{F9CA44D9-04E1-4853-A716-0C4B8461E7E3}"/>
+    <hyperlink ref="F59" r:id="rId27" xr:uid="{CEF48322-9FEF-42B8-80E3-C156D6960EFA}"/>
+    <hyperlink ref="F60" r:id="rId28" xr:uid="{9E242468-6AFA-4082-A28D-9F603379284A}"/>
+    <hyperlink ref="F61" r:id="rId29" xr:uid="{53B53022-7F04-4356-89AB-A1D6D0E44E1D}"/>
+    <hyperlink ref="F62" r:id="rId30" xr:uid="{32737A17-5A88-42D3-9917-D15AF2F3D30A}"/>
+    <hyperlink ref="F63" r:id="rId31" xr:uid="{23FBBBA3-B71B-4F35-A195-46068686A97E}"/>
+    <hyperlink ref="F66" r:id="rId32" xr:uid="{85BCBFF2-1705-40EA-8D3B-AF979565D642}"/>
+    <hyperlink ref="F67" r:id="rId33" xr:uid="{BCC1DB2B-68BC-4B96-9513-417AB11F2B1B}"/>
+    <hyperlink ref="F68" r:id="rId34" xr:uid="{9E6AAD18-3138-488D-A868-7FB730F5BB17}"/>
+    <hyperlink ref="F69" r:id="rId35" xr:uid="{463DB458-38B3-4ECC-91DB-620BB39F5391}"/>
+    <hyperlink ref="F70" r:id="rId36" xr:uid="{5D7036FE-3A41-4ACF-ACB9-00D97858C463}"/>
+    <hyperlink ref="F71" r:id="rId37" xr:uid="{5ECDAAD6-3E1B-4010-8EFB-3C9DF194C9CC}"/>
+    <hyperlink ref="F72" r:id="rId38" xr:uid="{617739E3-F193-44FF-B528-F3D6E35CE749}"/>
+    <hyperlink ref="F73" r:id="rId39" xr:uid="{FD3703D3-5B7A-45BB-9D24-6FBC0C499FBC}"/>
+    <hyperlink ref="F74" r:id="rId40" xr:uid="{180D7152-4C97-4266-98EF-A9966CF6CDF2}"/>
+    <hyperlink ref="F76" r:id="rId41" xr:uid="{657F969F-BED2-42A6-9003-4D948CD7F2A1}"/>
+    <hyperlink ref="F77" r:id="rId42" xr:uid="{ADBB78C4-3B40-43A0-AFB7-981A2BE09F36}"/>
+    <hyperlink ref="F78" r:id="rId43" xr:uid="{0ABCDDBA-5DCB-4B1D-A083-756BE1A9F48B}"/>
+    <hyperlink ref="F79" r:id="rId44" xr:uid="{3D8FADFC-D6EE-40EF-88BF-C83781E0F2A4}"/>
+    <hyperlink ref="F80" r:id="rId45" xr:uid="{CE89D81D-1B8D-4BB2-859C-D8CAFCC7C771}"/>
+    <hyperlink ref="F81" r:id="rId46" xr:uid="{505D2889-8F9A-4136-86BA-79FA148AE3EE}"/>
+    <hyperlink ref="F82" r:id="rId47" xr:uid="{62D77DB1-41F9-4AC0-AB00-9FED676B2031}"/>
+    <hyperlink ref="F83" r:id="rId48" xr:uid="{E27CC96D-AD3A-422B-B6E4-D27A569FA83F}"/>
+    <hyperlink ref="F84" r:id="rId49" xr:uid="{78638C2B-28D8-47F6-86D7-0F8BEDA99EAF}"/>
+    <hyperlink ref="F85" r:id="rId50" xr:uid="{C4E200FF-DB24-41AA-81AB-DA6EC53E3642}"/>
+    <hyperlink ref="F86" r:id="rId51" xr:uid="{DC135E9B-677A-4A55-AB2B-6088AB2D6B46}"/>
+    <hyperlink ref="F87" r:id="rId52" xr:uid="{EB517C68-9EA3-4807-BDE0-F0F4AAA6FE95}"/>
+    <hyperlink ref="F88" r:id="rId53" xr:uid="{74B49192-223F-4E7E-B04D-EFA9792905C8}"/>
+    <hyperlink ref="F89" r:id="rId54" xr:uid="{2F88E60D-F40C-4B66-9E13-1E57EC6E3C0B}"/>
+    <hyperlink ref="F90" r:id="rId55" xr:uid="{8F4AA986-2FF9-4F1E-8CF9-EBF1F52D7BE2}"/>
+    <hyperlink ref="F91" r:id="rId56" xr:uid="{5EFF6D3A-DF0C-43E7-ADA2-E8C333F297BE}"/>
+    <hyperlink ref="F94" r:id="rId57" xr:uid="{5D0BCFFB-293D-4BD1-87F9-A1DAA71A217C}"/>
+    <hyperlink ref="F57" r:id="rId58" xr:uid="{AF8617A7-F5F4-48B3-B57C-55EB50611A83}"/>
+    <hyperlink ref="F92" r:id="rId59" xr:uid="{0BE12A25-88E9-40D7-B6CF-F734F050661F}"/>
+    <hyperlink ref="F93" r:id="rId60" xr:uid="{AE4D9A9E-35DF-4056-9001-4A49AC9714AE}"/>
+    <hyperlink ref="F20" r:id="rId61" xr:uid="{BABB0F5C-56BD-4A07-93B3-021E469232CD}"/>
+    <hyperlink ref="F32" r:id="rId62" xr:uid="{61098037-76F4-4673-81EC-2C0BEA11F28D}"/>
+    <hyperlink ref="F152" r:id="rId63" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
+    <hyperlink ref="F153" r:id="rId64" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
+    <hyperlink ref="F154" r:id="rId65" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
+    <hyperlink ref="F155" r:id="rId66" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
+    <hyperlink ref="F158" r:id="rId67" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
+    <hyperlink ref="F159" r:id="rId68" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
+    <hyperlink ref="F160" r:id="rId69" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
+    <hyperlink ref="F182" r:id="rId70" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
+    <hyperlink ref="F184" r:id="rId71" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
+    <hyperlink ref="F203" r:id="rId72" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B3A3FF-C20F-49A3-A2F6-6732AD3A47C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125390B1-8892-4930-9832-C74F3423C2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="761">
   <si>
     <t>Nombre</t>
   </si>
@@ -835,21 +835,6 @@
     <t>skill_trigger</t>
   </si>
   <si>
-    <t>Poder+</t>
-  </si>
-  <si>
-    <t>Poder-</t>
-  </si>
-  <si>
-    <t>Curar+</t>
-  </si>
-  <si>
-    <t>Revivir</t>
-  </si>
-  <si>
-    <t>Escudo</t>
-  </si>
-  <si>
     <t>Revive una carta de tu elección del cementerio y la devuelve al mazo.</t>
   </si>
   <si>
@@ -877,9 +862,6 @@
     <t>heal_all</t>
   </si>
   <si>
-    <t>Curar++</t>
-  </si>
-  <si>
     <t>bonus_buff</t>
   </si>
   <si>
@@ -1501,9 +1483,6 @@
     <t>https://comicvine.gamespot.com/a/uploads/scale_medium/4/47635/2168308-1.jpg</t>
   </si>
   <si>
-    <t>https://static.wikia.nocookie.net/antagonisten/images/9/91/Faora_Hu-Ul_%28DC%29.png</t>
-  </si>
-  <si>
     <t>https://i.ibb.co/bRvQ4jWJ/i-loved-this-team-these-characters-were-great-together-v0-lymv5zg4wbqc1.webp</t>
   </si>
   <si>
@@ -1652,6 +1631,681 @@
   </si>
   <si>
     <t>Robo de vida</t>
+  </si>
+  <si>
+    <t>Golpe de maza nth</t>
+  </si>
+  <si>
+    <t>Hawkgirl golpea con su maza nth causando @skill_power de daño adicional.</t>
+  </si>
+  <si>
+    <t>Furia alada</t>
+  </si>
+  <si>
+    <t>Hawkman se lanza en picado atacando a todos los enemigos con @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Reacción nuclear</t>
+  </si>
+  <si>
+    <t>Firestorm desata una explosión que inflige @skill_power de daño a todos los enemigos.</t>
+  </si>
+  <si>
+    <t>Vientos protectores</t>
+  </si>
+  <si>
+    <t>Genera corrientes de aire que otorgan @skill_power de escudo a todos los aliados.</t>
+  </si>
+  <si>
+    <t>Armadura escarabajo</t>
+  </si>
+  <si>
+    <t>El escarabajo protege a Blue Beetle otorgándole @skill_power de escudo.</t>
+  </si>
+  <si>
+    <t>Impacto subatómico</t>
+  </si>
+  <si>
+    <t>Atom concentra su tamaño para infligir @skill_power de daño extra.</t>
+  </si>
+  <si>
+    <t>Cuerpo elástico</t>
+  </si>
+  <si>
+    <t>Plastic Man absorbe daño y recupera @skill_power puntos de salud.</t>
+  </si>
+  <si>
+    <t>Campo de fuerza</t>
+  </si>
+  <si>
+    <t>Activa su tecnología futura otorgando @skill_power de escudo.</t>
+  </si>
+  <si>
+    <t>Electroshock</t>
+  </si>
+  <si>
+    <t>Lanza una descarga que causa @skill_power de daño durante varios turnos.</t>
+  </si>
+  <si>
+    <t>Venganza implacable</t>
+  </si>
+  <si>
+    <t>Huntress ejecuta un ataque preciso que inflige @skill_power de daño adicional.</t>
+  </si>
+  <si>
+    <t>Energía cuántica</t>
+  </si>
+  <si>
+    <t>Libera energía nuclear golpeando a todos los enemigos con @skill_power.</t>
+  </si>
+  <si>
+    <t>Ejecución táctica</t>
+  </si>
+  <si>
+    <t>Red Hood realiza un disparo crítico que causa @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Luz cósmica</t>
+  </si>
+  <si>
+    <t>Potencia @skill_power el bonus de afiliación aliado activo.</t>
+  </si>
+  <si>
+    <t>Furia amazona</t>
+  </si>
+  <si>
+    <t>Donna Troy ataca con fuerza divina causando @skill_power de daño extra.</t>
+  </si>
+  <si>
+    <t>Entrenamiento amazona</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder de todos los enemigos en juego.</t>
+  </si>
+  <si>
+    <t>Ataque psíquico</t>
+  </si>
+  <si>
+    <t>Debilita a los enemigos reduciendo @skill_power de poder.</t>
+  </si>
+  <si>
+    <t>Rayo mágico</t>
+  </si>
+  <si>
+    <t>Cae un rayo mágico que inflige @skill_power de daño adicional.</t>
+  </si>
+  <si>
+    <t>Disparo certero</t>
+  </si>
+  <si>
+    <t>Lanza una flecha precisa causando @skill_power de daño extra.</t>
+  </si>
+  <si>
+    <t>Fuego de cobertura</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos con múltiples proyectiles causando @skill_power.</t>
+  </si>
+  <si>
+    <t>Bendición atlante</t>
+  </si>
+  <si>
+    <t>Cura @skill_power puntos de salud a todos los aliados.</t>
+  </si>
+  <si>
+    <t>Soporte aéreo</t>
+  </si>
+  <si>
+    <t>Resistencia de Apokolips</t>
+  </si>
+  <si>
+    <t>Duplica su salud y reduce su ataque a la mitad.</t>
+  </si>
+  <si>
+    <t>Descarga bioeléctrica</t>
+  </si>
+  <si>
+    <t>Aturde al enemigo durante @skill_power turnos.</t>
+  </si>
+  <si>
+    <t>Tormenta desatada</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos con @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Asesino entrenado</t>
+  </si>
+  <si>
+    <t>Inflige sangrado causando @skill_power de daño durante varios turnos.</t>
+  </si>
+  <si>
+    <t>Fuego infernal</t>
+  </si>
+  <si>
+    <t>Etrigan lanza llamas demoníacas causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Posesión espiritual</t>
+  </si>
+  <si>
+    <t>Voluntad indomable</t>
+  </si>
+  <si>
+    <t>Aumenta @skill_power el poder de todos los aliados.</t>
+  </si>
+  <si>
+    <t>Luz del monitor</t>
+  </si>
+  <si>
+    <t>Fuerza gravitatoria</t>
+  </si>
+  <si>
+    <t>Inflige un poderoso golpe causando @skill_power de daño extra.</t>
+  </si>
+  <si>
+    <t>Marea creciente</t>
+  </si>
+  <si>
+    <t>Cura @skill_power puntos de salud a un aliado.</t>
+  </si>
+  <si>
+    <t>Imaginación desbordante</t>
+  </si>
+  <si>
+    <t>Otorga @skill_power puntos de escudo a un aliado.</t>
+  </si>
+  <si>
+    <t>Furia de Apokolips</t>
+  </si>
+  <si>
+    <t>Inflige un ataque devastador causando @skill_power de daño extra.</t>
+  </si>
+  <si>
+    <t>Investigación profunda</t>
+  </si>
+  <si>
+    <t>Anula el bonus activo enemigo mientras esté en juego.</t>
+  </si>
+  <si>
+    <t>Amor de Star Sapphire</t>
+  </si>
+  <si>
+    <t>Lealtad kryptoniana</t>
+  </si>
+  <si>
+    <t>Recupera @skill_power puntos de salud al infligir daño.</t>
+  </si>
+  <si>
+    <t>Cuerpo cambiante</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder de todos los enemigos.</t>
+  </si>
+  <si>
+    <t>Análisis de combate</t>
+  </si>
+  <si>
+    <t>Escape imposible</t>
+  </si>
+  <si>
+    <t>Aplica @skill_power puntos de escudo a sí mismo.</t>
+  </si>
+  <si>
+    <t>Luz del día</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder de los enemigos en juego.</t>
+  </si>
+  <si>
+    <t>Constructo defensivo</t>
+  </si>
+  <si>
+    <t>Carga electromagnética</t>
+  </si>
+  <si>
+    <t>Inflige @skill_power de daño a todos los enemigos.</t>
+  </si>
+  <si>
+    <t>Fuerza amazona</t>
+  </si>
+  <si>
+    <t>Golpea al enemigo causando @skill_power de daño adicional.</t>
+  </si>
+  <si>
+    <t>Estrategia táctica</t>
+  </si>
+  <si>
+    <t>Onda vibratoria</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Manipulación lumínica</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder de los enemigos.</t>
+  </si>
+  <si>
+    <t>Juego macabro</t>
+  </si>
+  <si>
+    <t>Hiere al enemigo provocando un sangrado que causa @skill_power de daño durante varios turnos.</t>
+  </si>
+  <si>
+    <t>Estratega supremo</t>
+  </si>
+  <si>
+    <t>Ecuación Anti-Vida</t>
+  </si>
+  <si>
+    <t>Análisis de datos</t>
+  </si>
+  <si>
+    <t>Aumenta @skill_power el poder de todos los aliados en juego.</t>
+  </si>
+  <si>
+    <t>Furia de Shazam</t>
+  </si>
+  <si>
+    <t>Realiza un ataque extra causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Manipulación emocional</t>
+  </si>
+  <si>
+    <t>Ira divina</t>
+  </si>
+  <si>
+    <t>Miedo absoluto</t>
+  </si>
+  <si>
+    <t>Profecía del miedo</t>
+  </si>
+  <si>
+    <t>Resplandor oscuro</t>
+  </si>
+  <si>
+    <t>Aplica @skill_power puntos de escudo a un aliado.</t>
+  </si>
+  <si>
+    <t>Velocidad letal</t>
+  </si>
+  <si>
+    <t>Táctica letal</t>
+  </si>
+  <si>
+    <t>Caos impredecible</t>
+  </si>
+  <si>
+    <t>Robo sigiloso</t>
+  </si>
+  <si>
+    <t>Garra salvaje</t>
+  </si>
+  <si>
+    <t>Hiere al enemigo provocando @skill_power de daño prolongado.</t>
+  </si>
+  <si>
+    <t>Acertijo mental</t>
+  </si>
+  <si>
+    <t>Gas del miedo</t>
+  </si>
+  <si>
+    <t>Red criminal</t>
+  </si>
+  <si>
+    <t>Doble destino</t>
+  </si>
+  <si>
+    <t>Venom desatado</t>
+  </si>
+  <si>
+    <t>Lázaro inmortal</t>
+  </si>
+  <si>
+    <t>Revive una carta del cementerio y la devuelve al mazo.</t>
+  </si>
+  <si>
+    <t>Control vegetal</t>
+  </si>
+  <si>
+    <t>Furia bestial</t>
+  </si>
+  <si>
+    <t>Fuerza kryptoniana</t>
+  </si>
+  <si>
+    <t>Ira descontrolada</t>
+  </si>
+  <si>
+    <t>Poder soviético</t>
+  </si>
+  <si>
+    <t>Evolución infinita</t>
+  </si>
+  <si>
+    <t>Absorción vital</t>
+  </si>
+  <si>
+    <t>Recupera @skill_power puntos de salud al dañar.</t>
+  </si>
+  <si>
+    <t>Cuerpo inmortal</t>
+  </si>
+  <si>
+    <t>Mente dominante</t>
+  </si>
+  <si>
+    <t>Rayo congelante</t>
+  </si>
+  <si>
+    <t>Llamarada intensa</t>
+  </si>
+  <si>
+    <t>Provoca @skill_power de daño prolongado.</t>
+  </si>
+  <si>
+    <t>Reflejo distorsionado</t>
+  </si>
+  <si>
+    <t>Anula el bonus activo enemigo.</t>
+  </si>
+  <si>
+    <t>Distorsión temporal</t>
+  </si>
+  <si>
+    <t>Implantes cibernéticos</t>
+  </si>
+  <si>
+    <t>Aplica @skill_power puntos de escudo.</t>
+  </si>
+  <si>
+    <t>Hechizo oscuro</t>
+  </si>
+  <si>
+    <t>Rabia roja</t>
+  </si>
+  <si>
+    <t>Maestría marcial</t>
+  </si>
+  <si>
+    <t>Disparo letal</t>
+  </si>
+  <si>
+    <t>Masa cambiante</t>
+  </si>
+  <si>
+    <t>Duplica su salud y reduce su ataque.</t>
+  </si>
+  <si>
+    <t>Núcleo kryptonita</t>
+  </si>
+  <si>
+    <t>Reduce @skill_power el poder enemigo.</t>
+  </si>
+  <si>
+    <t>Entidad del miedo</t>
+  </si>
+  <si>
+    <t>Congelación total</t>
+  </si>
+  <si>
+    <t>Ataque oceánico</t>
+  </si>
+  <si>
+    <t>Realiza un ataque extra causando @skill_power.</t>
+  </si>
+  <si>
+    <t>Mordisco bestial</t>
+  </si>
+  <si>
+    <t>Avaricia infinita</t>
+  </si>
+  <si>
+    <t>Recupera @skill_power puntos de salud.</t>
+  </si>
+  <si>
+    <t>Magia caótica</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos con @skill_power.</t>
+  </si>
+  <si>
+    <t>Violencia desatada</t>
+  </si>
+  <si>
+    <t>Manipulación estratégica</t>
+  </si>
+  <si>
+    <t>Anula bonus enemigo.</t>
+  </si>
+  <si>
+    <t>Cazador inmortal</t>
+  </si>
+  <si>
+    <t>Recupera @skill_power de salud al dañar.</t>
+  </si>
+  <si>
+    <t>Grito sónico</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos.</t>
+  </si>
+  <si>
+    <t>Poder demoníaco</t>
+  </si>
+  <si>
+    <t>Furia roja</t>
+  </si>
+  <si>
+    <t>Sobrecarga eléctrica</t>
+  </si>
+  <si>
+    <t>Anti-fuerza</t>
+  </si>
+  <si>
+    <t>Congelación extrema</t>
+  </si>
+  <si>
+    <t>Aturde al enemigo.</t>
+  </si>
+  <si>
+    <t>Adaptación perfecta</t>
+  </si>
+  <si>
+    <t>Amazo copia habilidades enemigas y realiza un ataque extra causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Risa corruptora</t>
+  </si>
+  <si>
+    <t>Oscuridad primordial</t>
+  </si>
+  <si>
+    <t>Arsenal letal</t>
+  </si>
+  <si>
+    <t>Control mafioso</t>
+  </si>
+  <si>
+    <t>Boomerang explosivo</t>
+  </si>
+  <si>
+    <t>Veneno mortal</t>
+  </si>
+  <si>
+    <t>Provoca @skill_power de daño durante varios turnos.</t>
+  </si>
+  <si>
+    <t>Guerra divina</t>
+  </si>
+  <si>
+    <t>Terror mental</t>
+  </si>
+  <si>
+    <t>Golpe colosal</t>
+  </si>
+  <si>
+    <t>Entrenamiento brutal</t>
+  </si>
+  <si>
+    <t>Dominio mental</t>
+  </si>
+  <si>
+    <t>Mordisco salvaje</t>
+  </si>
+  <si>
+    <t>Control absoluto</t>
+  </si>
+  <si>
+    <t>Dominación brutal</t>
+  </si>
+  <si>
+    <t>Furia oceánica</t>
+  </si>
+  <si>
+    <t>Hija de la guerra</t>
+  </si>
+  <si>
+    <t>Realiza un ataque devastador causando @skill_power de daño.</t>
+  </si>
+  <si>
+    <t>Plaga de ratas</t>
+  </si>
+  <si>
+    <t>Mente científica</t>
+  </si>
+  <si>
+    <t>Hacha de guerra</t>
+  </si>
+  <si>
+    <t>Supercálculo</t>
+  </si>
+  <si>
+    <t>Control del multiverso</t>
+  </si>
+  <si>
+    <t>Inmortalidad ancestral</t>
+  </si>
+  <si>
+    <t>Cortes letales</t>
+  </si>
+  <si>
+    <t>Ataque caótico</t>
+  </si>
+  <si>
+    <t>Ira roja</t>
+  </si>
+  <si>
+    <t>Guardián rojo</t>
+  </si>
+  <si>
+    <t>Energía roja</t>
+  </si>
+  <si>
+    <t>Muerte absoluta</t>
+  </si>
+  <si>
+    <t>Resurrección oscura</t>
+  </si>
+  <si>
+    <t>Revive una carta del cementerio.</t>
+  </si>
+  <si>
+    <t>Poder brutal</t>
+  </si>
+  <si>
+    <t>Tortura mental</t>
+  </si>
+  <si>
+    <t>Maldición caótica</t>
+  </si>
+  <si>
+    <t>Fuerza bruta</t>
+  </si>
+  <si>
+    <t>Inventos letales</t>
+  </si>
+  <si>
+    <t>Ataca a todos los enemigos causando @skill_power.</t>
+  </si>
+  <si>
+    <t>Cazadora kryptoniana</t>
+  </si>
+  <si>
+    <t>Guerrera kryptoniana</t>
+  </si>
+  <si>
+    <t>Energía avariciosa</t>
+  </si>
+  <si>
+    <t>Caos dimensional</t>
+  </si>
+  <si>
+    <t>Aturde a todos los enemigos durante @skill_power turnos.</t>
+  </si>
+  <si>
+    <t>Purga kryptoniana</t>
+  </si>
+  <si>
+    <t>Ritual oscuro</t>
+  </si>
+  <si>
+    <t>Control digital</t>
+  </si>
+  <si>
+    <t>Fuerza de Apokolips</t>
+  </si>
+  <si>
+    <t>Magia de resurrección</t>
+  </si>
+  <si>
+    <t>Luz sanadora</t>
+  </si>
+  <si>
+    <t>Grito debilitador</t>
+  </si>
+  <si>
+    <t>Resurreción</t>
+  </si>
+  <si>
+    <t>Estimulador</t>
+  </si>
+  <si>
+    <t>Revitalizar</t>
+  </si>
+  <si>
+    <t>Batería de poder</t>
+  </si>
+  <si>
+    <t>Escudo estático</t>
+  </si>
+  <si>
+    <t>Oleada de vitalidad</t>
+  </si>
+  <si>
+    <t>Aterrorizar</t>
+  </si>
+  <si>
+    <t>Rejuvenecimiento</t>
+  </si>
+  <si>
+    <t>Favor de la velocidad</t>
+  </si>
+  <si>
+    <t>Renovar</t>
+  </si>
+  <si>
+    <t>Luz de sanación</t>
+  </si>
+  <si>
+    <t>Grito de guerra</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/1200x/84/98/f6/8498f6f9f4b218a61bb9773d50aa946b.jpg</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +2337,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1738,6 +2392,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1778,7 +2438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1827,27 +2487,134 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF64DA89"/>
-      <color rgb="FFFFA675"/>
+      <color rgb="FFCC99FF"/>
+      <color rgb="FFFFD253"/>
+      <color rgb="FFFF9F57"/>
+      <color rgb="FFFFCD69"/>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FF82D8B1"/>
+      <color rgb="FF87DFAF"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFFF5050"/>
       <color rgb="FFCBAAEC"/>
-      <color rgb="FF99CCFF"/>
-      <color rgb="FFFF7C80"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2151,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2214,19 +2981,19 @@
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="13" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2255,20 +3022,20 @@
         <v>14</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="16" t="s">
-        <v>518</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>528</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="M3" s="16">
+      <c r="J3" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="M3" s="22">
         <v>50</v>
       </c>
-      <c r="N3" s="16" t="s">
-        <v>276</v>
+      <c r="N3" s="22" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2298,19 +3065,19 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="13" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,22 +3107,22 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="14" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="M5" s="14"/>
       <c r="N5" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -2376,14 +3143,14 @@
         <v>10</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="15" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="L6" s="15" t="s">
         <v>268</v>
@@ -2392,7 +3159,7 @@
         <v>1000</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2418,23 +3185,23 @@
         <v>10</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="13" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2460,14 +3227,14 @@
         <v>10</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="12" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="L8" s="12" t="s">
         <v>264</v>
@@ -2476,7 +3243,7 @@
         <v>100</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2506,10 +3273,10 @@
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="14" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="L9" s="14" t="s">
         <v>265</v>
@@ -2518,7 +3285,7 @@
         <v>100</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2548,19 +3315,19 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="13" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2587,11 +3354,21 @@
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
+      <c r="J11" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -2619,11 +3396,21 @@
         <v>39</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
+      <c r="J12" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -2650,19 +3437,19 @@
       <c r="H13" s="10"/>
       <c r="I13" s="2"/>
       <c r="J13" s="13" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2688,22 +3475,22 @@
         <v>10</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2729,22 +3516,22 @@
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>296</v>
+        <v>747</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2773,17 +3560,17 @@
         <v>49</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="M16" s="14"/>
       <c r="N16" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2812,10 +3599,10 @@
         <v>49</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>273</v>
+        <v>745</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="L17" s="14" t="s">
         <v>267</v>
@@ -2824,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2851,19 +3638,19 @@
       </c>
       <c r="H18" s="10"/>
       <c r="J18" s="12" t="s">
-        <v>284</v>
+        <v>746</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M18" s="12">
         <v>750</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2889,6 +3676,21 @@
         <v>10</v>
       </c>
       <c r="H19" s="10"/>
+      <c r="J19" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -2907,12 +3709,27 @@
         <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="10"/>
+      <c r="J20" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" s="21">
+        <v>1000</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
@@ -2937,6 +3754,21 @@
         <v>10</v>
       </c>
       <c r="H21" s="10"/>
+      <c r="J21" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M21" s="21">
+        <v>1000</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="22" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -2961,20 +3793,20 @@
         <v>10</v>
       </c>
       <c r="H22" s="10"/>
-      <c r="J22" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="M22" s="19">
+      <c r="J22" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="M22" s="18">
         <v>200</v>
       </c>
-      <c r="N22" s="19" t="s">
-        <v>277</v>
+      <c r="N22" s="18" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3000,6 +3832,21 @@
         <v>10</v>
       </c>
       <c r="H23" s="10"/>
+      <c r="J23" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="24" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -3024,6 +3871,21 @@
         <v>10</v>
       </c>
       <c r="H24" s="10"/>
+      <c r="J24" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -3048,6 +3910,21 @@
         <v>10</v>
       </c>
       <c r="H25" s="10"/>
+      <c r="J25" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M25" s="15">
+        <v>1000</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -3075,19 +3952,19 @@
         <v>29</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3116,10 +3993,10 @@
         <v>29</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>273</v>
+        <v>748</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="L27" s="14" t="s">
         <v>267</v>
@@ -3128,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3156,20 +4033,20 @@
       <c r="H28" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J28" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="L28" s="16" t="s">
+      <c r="J28" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="M28" s="16">
+      <c r="K28" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="M28" s="22">
         <v>50</v>
       </c>
-      <c r="N28" s="16" t="s">
-        <v>276</v>
+      <c r="N28" s="22" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,19 +4075,19 @@
         <v>259</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3238,20 +4115,20 @@
       <c r="H30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="L30" s="12" t="s">
+      <c r="J30" s="22" t="s">
+        <v>749</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="L30" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="22">
         <v>100</v>
       </c>
-      <c r="N30" s="12" t="s">
-        <v>276</v>
+      <c r="N30" s="22" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3280,10 +4157,10 @@
         <v>73</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="L31" s="14" t="s">
         <v>265</v>
@@ -3292,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3312,7 +4189,7 @@
         <v>19</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>10</v>
@@ -3321,19 +4198,19 @@
         <v>79</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,19 +4239,19 @@
         <v>34</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M33" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3400,6 +4277,21 @@
         <v>10</v>
       </c>
       <c r="H34" s="10"/>
+      <c r="J34" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="M34" s="18">
+        <v>200</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -3426,6 +4318,21 @@
       <c r="H35" s="10" t="s">
         <v>46</v>
       </c>
+      <c r="J35" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -3453,19 +4360,19 @@
         <v>49</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>284</v>
+        <v>750</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M36" s="12">
         <v>750</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3491,22 +4398,22 @@
         <v>10</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M37" s="16">
         <v>50</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3532,22 +4439,22 @@
         <v>10</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="L38" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>751</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="L38" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="22">
         <v>100</v>
       </c>
-      <c r="N38" s="12" t="s">
-        <v>276</v>
+      <c r="N38" s="22" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3573,20 +4480,20 @@
         <v>10</v>
       </c>
       <c r="H39" s="10"/>
-      <c r="J39" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="K39" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="L39" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="M39" s="19">
+      <c r="J39" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="M39" s="18">
         <v>200</v>
       </c>
-      <c r="N39" s="19" t="s">
-        <v>277</v>
+      <c r="N39" s="18" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3612,6 +4519,21 @@
         <v>10</v>
       </c>
       <c r="H40" s="10"/>
+      <c r="J40" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="41" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
@@ -3638,6 +4560,21 @@
       <c r="H41" s="10" t="s">
         <v>73</v>
       </c>
+      <c r="J41" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
@@ -3664,6 +4601,21 @@
       <c r="H42" s="10" t="s">
         <v>39</v>
       </c>
+      <c r="J42" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="L42" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="M42" s="22">
+        <v>50</v>
+      </c>
+      <c r="N42" s="22" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
@@ -3691,19 +4643,19 @@
         <v>102</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="L43" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3731,6 +4683,21 @@
       <c r="H44" s="10" t="s">
         <v>105</v>
       </c>
+      <c r="J44" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
@@ -3758,10 +4725,10 @@
         <v>102</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>274</v>
+        <v>752</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="L45" s="15" t="s">
         <v>268</v>
@@ -3770,7 +4737,7 @@
         <v>1000</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3798,6 +4765,21 @@
       <c r="H46" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="J46" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M46" s="14">
+        <v>100</v>
+      </c>
+      <c r="N46" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
@@ -3822,6 +4804,21 @@
         <v>10</v>
       </c>
       <c r="H47" s="10"/>
+      <c r="J47" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M47" s="14">
+        <v>100</v>
+      </c>
+      <c r="N47" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
@@ -3846,22 +4843,22 @@
         <v>10</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M48" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N48" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3887,6 +4884,21 @@
         <v>10</v>
       </c>
       <c r="H49" s="10"/>
+      <c r="J49" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="K49" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N49" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
@@ -3911,13 +4923,13 @@
         <v>10</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>272</v>
+        <v>753</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="L50" s="12" t="s">
         <v>266</v>
@@ -3926,7 +4938,7 @@
         <v>1000</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3955,19 +4967,19 @@
         <v>121</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N51" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,10 +5008,10 @@
         <v>34</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>271</v>
+        <v>754</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="L52" s="14" t="s">
         <v>265</v>
@@ -4008,12 +5020,12 @@
         <v>100</v>
       </c>
       <c r="N52" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B53" s="17">
         <v>1</v>
@@ -4028,33 +5040,33 @@
         <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M53" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N53" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B54" s="17">
         <v>1</v>
@@ -4069,17 +5081,17 @@
         <v>22</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H54" s="17"/>
       <c r="J54" s="12" t="s">
-        <v>272</v>
+        <v>755</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="L54" s="12" t="s">
         <v>266</v>
@@ -4088,12 +5100,12 @@
         <v>1000</v>
       </c>
       <c r="N54" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B55" s="17">
         <v>1</v>
@@ -4108,18 +5120,33 @@
         <v>19</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>344</v>
+        <v>338</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M55" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N55" s="13" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B56" s="17">
         <v>1</v>
@@ -4134,18 +5161,33 @@
         <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>344</v>
+        <v>338</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="L56" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="M56" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="N56" s="13" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B57" s="17">
         <v>1</v>
@@ -4160,18 +5202,33 @@
         <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>347</v>
+        <v>341</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="M57" s="12">
+        <v>750</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B58" s="17">
         <v>1</v>
@@ -4186,16 +5243,31 @@
         <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H58" s="17"/>
+      <c r="J58" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M58" s="14">
+        <v>100</v>
+      </c>
+      <c r="N58" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="59" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B59" s="17">
         <v>1</v>
@@ -4210,7 +5282,7 @@
         <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>10</v>
@@ -4219,24 +5291,24 @@
         <v>29</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M59" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B60" s="17">
         <v>1</v>
@@ -4251,16 +5323,31 @@
         <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H60" s="17"/>
+      <c r="J60" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="M60" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="N60" s="15" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="61" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B61" s="17">
         <v>1</v>
@@ -4275,16 +5362,31 @@
         <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H61" s="17"/>
+      <c r="J61" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="M61" s="18">
+        <v>2</v>
+      </c>
+      <c r="N61" s="18" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="62" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B62" s="17">
         <v>1</v>
@@ -4299,16 +5401,31 @@
         <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H62" s="17"/>
+      <c r="J62" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="L62" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="M62" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="N62" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B63" s="17">
         <v>1</v>
@@ -4323,7 +5440,7 @@
         <v>19</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>10</v>
@@ -4331,10 +5448,25 @@
       <c r="H63" s="10" t="s">
         <v>73</v>
       </c>
+      <c r="J63" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="K63" s="18" t="s">
+        <v>584</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="M63" s="18">
+        <v>200</v>
+      </c>
+      <c r="N63" s="18" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B64" s="17">
         <v>1</v>
@@ -4349,7 +5481,7 @@
         <v>22</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>10</v>
@@ -4357,10 +5489,25 @@
       <c r="H64" s="10" t="s">
         <v>49</v>
       </c>
+      <c r="J64" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="L64" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M64" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N64" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="65" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B65" s="17">
         <v>1</v>
@@ -4375,7 +5522,7 @@
         <v>22</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>10</v>
@@ -4384,24 +5531,24 @@
         <v>49</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M65" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="N65" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B66" s="17">
         <v>1</v>
@@ -4416,7 +5563,7 @@
         <v>22</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>10</v>
@@ -4424,10 +5571,25 @@
       <c r="H66" s="10" t="s">
         <v>49</v>
       </c>
+      <c r="J66" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="M66" s="18">
+        <v>2</v>
+      </c>
+      <c r="N66" s="18" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="67" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B67" s="17">
         <v>1</v>
@@ -4442,18 +5604,33 @@
         <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
+      </c>
+      <c r="J67" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="K67" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="L67" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="M67" s="22">
+        <v>100</v>
+      </c>
+      <c r="N67" s="22" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B68" s="17">
         <v>1</v>
@@ -4468,16 +5645,31 @@
         <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H68" s="17"/>
+      <c r="J68" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="K68" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="L68" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="M68" s="12">
+        <v>750</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="69" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B69" s="17">
         <v>1</v>
@@ -4492,16 +5684,31 @@
         <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H69" s="17"/>
+      <c r="J69" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="L69" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M69" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N69" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="70" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B70" s="17">
         <v>1</v>
@@ -4516,18 +5723,33 @@
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>347</v>
+        <v>341</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="K70" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="L70" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="M70" s="12">
+        <v>1000</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B71" s="17">
         <v>1</v>
@@ -4542,19 +5764,19 @@
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>270</v>
+        <v>756</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L71" s="12" t="s">
         <v>264</v>
@@ -4563,12 +5785,12 @@
         <v>100</v>
       </c>
       <c r="N71" s="12" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B72" s="17">
         <v>1</v>
@@ -4583,18 +5805,33 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M72" s="15">
+        <v>1000</v>
+      </c>
+      <c r="N72" s="15" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B73" s="17">
         <v>1</v>
@@ -4609,16 +5846,31 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H73" s="17"/>
+      <c r="J73" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="L73" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M73" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N73" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B74" s="17">
         <v>1</v>
@@ -4633,16 +5885,29 @@
         <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H74" s="17"/>
+      <c r="J74" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="L74" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="75" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B75" s="17">
         <v>1</v>
@@ -4663,12 +5928,27 @@
         <v>10</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>349</v>
+        <v>343</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="M75" s="12">
+        <v>750</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B76" s="17">
         <v>1</v>
@@ -4683,31 +5963,31 @@
         <v>22</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H76" s="10"/>
-      <c r="J76" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="K76" s="19" t="s">
-        <v>535</v>
-      </c>
-      <c r="L76" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="M76" s="19">
+      <c r="J76" s="18" t="s">
+        <v>527</v>
+      </c>
+      <c r="K76" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="L76" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="M76" s="18">
         <v>2</v>
       </c>
-      <c r="N76" s="19" t="s">
-        <v>277</v>
+      <c r="N76" s="18" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B77" s="17">
         <v>1</v>
@@ -4722,7 +6002,7 @@
         <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>10</v>
@@ -4730,10 +6010,25 @@
       <c r="H77" s="10" t="s">
         <v>34</v>
       </c>
+      <c r="J77" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="K77" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="L77" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="M77" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="78" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B78" s="17">
         <v>1</v>
@@ -4748,16 +6043,31 @@
         <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H78" s="17"/>
+      <c r="J78" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="L78" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M78" s="14">
+        <v>100</v>
+      </c>
+      <c r="N78" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="79" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B79" s="17">
         <v>1</v>
@@ -4772,16 +6082,31 @@
         <v>19</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H79" s="17"/>
+      <c r="J79" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="K79" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="L79" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="M79" s="22">
+        <v>100</v>
+      </c>
+      <c r="N79" s="22" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="80" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B80" s="17">
         <v>1</v>
@@ -4796,16 +6121,31 @@
         <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H80" s="17"/>
+      <c r="J80" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="K80" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="L80" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M80" s="21">
+        <v>1000</v>
+      </c>
+      <c r="N80" s="21" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="81" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B81" s="17">
         <v>1</v>
@@ -4820,31 +6160,31 @@
         <v>22</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H81" s="17"/>
-      <c r="J81" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="K81" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="L81" s="20" t="s">
-        <v>539</v>
-      </c>
-      <c r="M81" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="N81" s="20" t="s">
-        <v>276</v>
+      <c r="J81" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="K81" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="L81" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="M81" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="N81" s="19" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B82" s="17">
         <v>1</v>
@@ -4859,16 +6199,31 @@
         <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="17"/>
+      <c r="J82" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="K82" s="23" t="s">
+        <v>610</v>
+      </c>
+      <c r="L82" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="M82" s="23">
+        <v>100</v>
+      </c>
+      <c r="N82" s="23" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="83" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B83" s="17">
         <v>1</v>
@@ -4883,18 +6238,33 @@
         <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
+      </c>
+      <c r="J83" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="K83" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="L83" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M83" s="21">
+        <v>1000</v>
+      </c>
+      <c r="N83" s="21" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B84" s="17">
         <v>1</v>
@@ -4909,16 +6279,31 @@
         <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H84" s="17"/>
+      <c r="J84" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="K84" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="L84" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="M84" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="N84" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="85" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B85" s="17">
         <v>1</v>
@@ -4933,7 +6318,7 @@
         <v>19</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>10</v>
@@ -4941,25 +6326,25 @@
       <c r="H85" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J85" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="K85" s="19" t="s">
-        <v>533</v>
-      </c>
-      <c r="L85" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="M85" s="19">
+      <c r="J85" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="M85" s="18">
         <v>2</v>
       </c>
-      <c r="N85" s="19" t="s">
-        <v>277</v>
+      <c r="N85" s="18" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B86" s="17">
         <v>1</v>
@@ -4974,16 +6359,31 @@
         <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H86" s="17"/>
+      <c r="J86" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="K86" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="L86" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="M86" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="N86" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="87" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B87" s="17">
         <v>1</v>
@@ -4998,7 +6398,7 @@
         <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>10</v>
@@ -5006,10 +6406,23 @@
       <c r="H87" s="10" t="s">
         <v>73</v>
       </c>
+      <c r="J87" s="23" t="s">
+        <v>616</v>
+      </c>
+      <c r="K87" s="23" t="s">
+        <v>600</v>
+      </c>
+      <c r="L87" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="M87" s="23"/>
+      <c r="N87" s="23" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="88" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B88" s="17">
         <v>1</v>
@@ -5024,16 +6437,31 @@
         <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="17"/>
+      <c r="J88" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="K88" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="L88" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="M88" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="N88" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="89" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B89" s="17">
         <v>1</v>
@@ -5048,29 +6476,29 @@
         <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="17"/>
       <c r="J89" s="14" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L89" s="14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="M89" s="14"/>
       <c r="N89" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B90" s="17">
         <v>1</v>
@@ -5085,19 +6513,19 @@
         <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>272</v>
+        <v>757</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="L90" s="12" t="s">
         <v>266</v>
@@ -5106,12 +6534,12 @@
         <v>1250</v>
       </c>
       <c r="N90" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B91" s="17">
         <v>1</v>
@@ -5126,33 +6554,33 @@
         <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>284</v>
+        <v>758</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L91" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M91" s="12">
         <v>750</v>
       </c>
       <c r="N91" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B92" s="17">
         <v>1</v>
@@ -5167,7 +6595,7 @@
         <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>10</v>
@@ -5176,24 +6604,24 @@
         <v>110</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L92" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M92" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N92" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B93" s="17">
         <v>1</v>
@@ -5208,7 +6636,7 @@
         <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>10</v>
@@ -5217,24 +6645,24 @@
         <v>110</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="K93" s="13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="L93" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="M93" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N93" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B94" s="17">
         <v>1</v>
@@ -5249,7 +6677,7 @@
         <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>10</v>
@@ -5258,10 +6686,10 @@
         <v>110</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>270</v>
+        <v>759</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L94" s="12" t="s">
         <v>264</v>
@@ -5270,7 +6698,7 @@
         <v>100</v>
       </c>
       <c r="N94" s="12" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5296,6 +6724,21 @@
         <v>10</v>
       </c>
       <c r="H95" s="10"/>
+      <c r="J95" s="23" t="s">
+        <v>619</v>
+      </c>
+      <c r="K95" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="L95" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="M95" s="23">
+        <v>100</v>
+      </c>
+      <c r="N95" s="23" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="96" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -5322,8 +6765,23 @@
       <c r="H96" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J96" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M96" s="2">
+        <v>200</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>130</v>
       </c>
@@ -5348,8 +6806,21 @@
       <c r="H97" s="4" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J97" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M97" s="2"/>
+      <c r="N97" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>133</v>
       </c>
@@ -5372,10 +6843,25 @@
         <v>128</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M98" s="2">
+        <v>100</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>136</v>
       </c>
@@ -5400,8 +6886,23 @@
       <c r="H99" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J99" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M99" s="2">
+        <v>100</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>139</v>
       </c>
@@ -5426,8 +6927,23 @@
       <c r="H100" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J100" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>254</v>
       </c>
@@ -5450,8 +6966,23 @@
         <v>128</v>
       </c>
       <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J101" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M101" s="2">
+        <v>100</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>251</v>
       </c>
@@ -5474,8 +7005,23 @@
         <v>128</v>
       </c>
       <c r="H102" s="4"/>
-    </row>
-    <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J102" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>142</v>
       </c>
@@ -5500,8 +7046,23 @@
       <c r="H103" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J103" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M103" s="2">
+        <v>100</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>250</v>
       </c>
@@ -5518,7 +7079,7 @@
         <v>22</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>128</v>
@@ -5526,8 +7087,23 @@
       <c r="H104" s="4" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J104" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="M104" s="2">
+        <v>50</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>248</v>
       </c>
@@ -5552,8 +7128,23 @@
       <c r="H105" s="4" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J105" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M105" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>145</v>
       </c>
@@ -5576,8 +7167,23 @@
         <v>128</v>
       </c>
       <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J106" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>147</v>
       </c>
@@ -5602,8 +7208,23 @@
       <c r="H107" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J107" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>150</v>
       </c>
@@ -5628,8 +7249,23 @@
       <c r="H108" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J108" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>153</v>
       </c>
@@ -5652,8 +7288,23 @@
         <v>128</v>
       </c>
       <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J109" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>155</v>
       </c>
@@ -5678,8 +7329,23 @@
       <c r="H110" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J110" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M110" s="2">
+        <v>200</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>158</v>
       </c>
@@ -5702,8 +7368,23 @@
         <v>128</v>
       </c>
       <c r="H111" s="4"/>
-    </row>
-    <row r="112" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J111" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M111" s="2">
+        <v>100</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>160</v>
       </c>
@@ -5728,8 +7409,23 @@
       <c r="H112" s="4" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J112" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M112" s="2">
+        <v>2</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>163</v>
       </c>
@@ -5752,8 +7448,23 @@
         <v>128</v>
       </c>
       <c r="H113" s="4"/>
-    </row>
-    <row r="114" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J113" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="M113" s="2">
+        <v>50</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>165</v>
       </c>
@@ -5778,8 +7489,23 @@
       <c r="H114" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J114" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>168</v>
       </c>
@@ -5804,8 +7530,23 @@
       <c r="H115" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J115" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>170</v>
       </c>
@@ -5830,8 +7571,23 @@
       <c r="H116" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J116" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="M116" s="2">
+        <v>1</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>172</v>
       </c>
@@ -5856,8 +7612,23 @@
       <c r="H117" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J117" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M117" s="2">
+        <v>750</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>175</v>
       </c>
@@ -5882,8 +7653,23 @@
       <c r="H118" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J118" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>177</v>
       </c>
@@ -5908,8 +7694,23 @@
       <c r="H119" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J119" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>253</v>
       </c>
@@ -5934,8 +7735,23 @@
       <c r="H120" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J120" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>180</v>
       </c>
@@ -5960,8 +7776,23 @@
       <c r="H121" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J121" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>183</v>
       </c>
@@ -5984,8 +7815,23 @@
         <v>128</v>
       </c>
       <c r="H122" s="4"/>
-    </row>
-    <row r="123" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J122" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>185</v>
       </c>
@@ -6008,8 +7854,23 @@
         <v>128</v>
       </c>
       <c r="H123" s="4"/>
-    </row>
-    <row r="124" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J123" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>187</v>
       </c>
@@ -6032,8 +7893,23 @@
         <v>128</v>
       </c>
       <c r="H124" s="4"/>
-    </row>
-    <row r="125" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J124" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>189</v>
       </c>
@@ -6058,8 +7934,23 @@
       <c r="H125" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J125" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M125" s="2">
+        <v>100</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>191</v>
       </c>
@@ -6084,8 +7975,23 @@
       <c r="H126" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J126" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M126" s="2">
+        <v>2</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>193</v>
       </c>
@@ -6108,8 +8014,23 @@
         <v>128</v>
       </c>
       <c r="H127" s="4"/>
-    </row>
-    <row r="128" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J127" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M127" s="2">
+        <v>200</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>195</v>
       </c>
@@ -6132,8 +8053,21 @@
         <v>128</v>
       </c>
       <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J128" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M128" s="2"/>
+      <c r="N128" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>197</v>
       </c>
@@ -6158,8 +8092,23 @@
       <c r="H129" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J129" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>200</v>
       </c>
@@ -6184,8 +8133,23 @@
       <c r="H130" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J130" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M130" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>203</v>
       </c>
@@ -6210,8 +8174,23 @@
       <c r="H131" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J131" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M131" s="2">
+        <v>2</v>
+      </c>
+      <c r="N131" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>205</v>
       </c>
@@ -6236,8 +8215,23 @@
       <c r="H132" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J132" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M132" s="2">
+        <v>200</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>207</v>
       </c>
@@ -6260,8 +8254,23 @@
         <v>128</v>
       </c>
       <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J133" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>209</v>
       </c>
@@ -6286,8 +8295,23 @@
       <c r="H134" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J134" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>211</v>
       </c>
@@ -6310,8 +8334,23 @@
         <v>128</v>
       </c>
       <c r="H135" s="4"/>
-    </row>
-    <row r="136" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J135" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>213</v>
       </c>
@@ -6336,8 +8375,23 @@
       <c r="H136" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J136" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M136" s="2">
+        <v>100</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>215</v>
       </c>
@@ -6362,8 +8416,23 @@
       <c r="H137" s="4" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J137" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M137" s="2">
+        <v>100</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>218</v>
       </c>
@@ -6386,8 +8455,23 @@
         <v>128</v>
       </c>
       <c r="H138" s="4"/>
-    </row>
-    <row r="139" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J138" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M138" s="2">
+        <v>2</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>220</v>
       </c>
@@ -6412,8 +8496,23 @@
       <c r="H139" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J139" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>222</v>
       </c>
@@ -6436,8 +8535,23 @@
         <v>128</v>
       </c>
       <c r="H140" s="4"/>
-    </row>
-    <row r="141" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J140" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M140" s="2">
+        <v>200</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>225</v>
       </c>
@@ -6460,8 +8574,23 @@
         <v>128</v>
       </c>
       <c r="H141" s="4"/>
-    </row>
-    <row r="142" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J141" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>227</v>
       </c>
@@ -6486,8 +8615,23 @@
       <c r="H142" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J142" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N142" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>229</v>
       </c>
@@ -6510,8 +8654,23 @@
         <v>128</v>
       </c>
       <c r="H143" s="4"/>
-    </row>
-    <row r="144" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J143" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M143" s="2">
+        <v>200</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>231</v>
       </c>
@@ -6534,8 +8693,21 @@
         <v>128</v>
       </c>
       <c r="H144" s="4"/>
-    </row>
-    <row r="145" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J144" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M144" s="2"/>
+      <c r="N144" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>233</v>
       </c>
@@ -6558,8 +8730,23 @@
         <v>128</v>
       </c>
       <c r="H145" s="4"/>
-    </row>
-    <row r="146" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J145" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>235</v>
       </c>
@@ -6582,8 +8769,23 @@
         <v>128</v>
       </c>
       <c r="H146" s="4"/>
-    </row>
-    <row r="147" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J146" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>237</v>
       </c>
@@ -6606,8 +8808,23 @@
         <v>128</v>
       </c>
       <c r="H147" s="4"/>
-    </row>
-    <row r="148" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J147" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N147" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>239</v>
       </c>
@@ -6632,8 +8849,23 @@
       <c r="H148" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J148" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M148" s="2">
+        <v>200</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>241</v>
       </c>
@@ -6656,8 +8888,23 @@
         <v>128</v>
       </c>
       <c r="H149" s="4"/>
-    </row>
-    <row r="150" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J149" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>243</v>
       </c>
@@ -6682,8 +8929,23 @@
       <c r="H150" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J150" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M150" s="2">
+        <v>100</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>245</v>
       </c>
@@ -6706,10 +8968,25 @@
         <v>128</v>
       </c>
       <c r="H151" s="4"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J151" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="L151" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M151" s="2">
+        <v>2</v>
+      </c>
+      <c r="N151" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B152" s="4">
         <v>1</v>
@@ -6724,16 +9001,31 @@
         <v>19</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H152" s="4"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J152" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B153" s="4">
         <v>1</v>
@@ -6748,16 +9040,31 @@
         <v>19</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H153" s="4"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J153" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M153" s="2">
+        <v>100</v>
+      </c>
+      <c r="N153" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B154" s="4">
         <v>1</v>
@@ -6772,16 +9079,31 @@
         <v>22</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H154" s="4"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J154" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B155" s="4">
         <v>1</v>
@@ -6796,16 +9118,31 @@
         <v>19</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H155" s="4"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J155" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="M155" s="2">
+        <v>50</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B156" s="4">
         <v>1</v>
@@ -6820,16 +9157,31 @@
         <v>19</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H156" s="4"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J156" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B157" s="4">
         <v>1</v>
@@ -6844,16 +9196,31 @@
         <v>19</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H157" s="4"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J157" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M157" s="2">
+        <v>100</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B158" s="4">
         <v>1</v>
@@ -6868,16 +9235,31 @@
         <v>19</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H158" s="4"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J158" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B159" s="4">
         <v>1</v>
@@ -6892,16 +9274,31 @@
         <v>19</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J159" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M159" s="2">
+        <v>200</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B160" s="4">
         <v>1</v>
@@ -6916,16 +9313,31 @@
         <v>22</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J160" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L160" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B161" s="4">
         <v>1</v>
@@ -6940,16 +9352,31 @@
         <v>8</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H161" s="4"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J161" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M161" s="2">
+        <v>100</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B162" s="4">
         <v>1</v>
@@ -6964,16 +9391,31 @@
         <v>8</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H162" s="4"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J162" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B163" s="4">
         <v>1</v>
@@ -6988,18 +9430,33 @@
         <v>8</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B164" s="4">
         <v>1</v>
@@ -7014,16 +9471,31 @@
         <v>8</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J164" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M164" s="2">
+        <v>100</v>
+      </c>
+      <c r="N164" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B165" s="4">
         <v>1</v>
@@ -7038,16 +9510,31 @@
         <v>8</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H165" s="4"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J165" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B166" s="4">
         <v>1</v>
@@ -7062,16 +9549,29 @@
         <v>8</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J166" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M166" s="2"/>
+      <c r="N166" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B167" s="4">
         <v>1</v>
@@ -7086,16 +9586,31 @@
         <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J167" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
@@ -7110,16 +9625,31 @@
         <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H168" s="4"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J168" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N168" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B169" s="4">
         <v>1</v>
@@ -7134,16 +9664,31 @@
         <v>8</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J169" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N169" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B170" s="4">
         <v>1</v>
@@ -7158,16 +9703,31 @@
         <v>19</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H170" s="4"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J170" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M170" s="2">
+        <v>200</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B171" s="4">
         <v>1</v>
@@ -7182,16 +9742,29 @@
         <v>19</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H171" s="4"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J171" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B172" s="4">
         <v>1</v>
@@ -7206,18 +9779,33 @@
         <v>8</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L172" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M172" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N172" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B173" s="4">
         <v>1</v>
@@ -7232,18 +9820,33 @@
         <v>8</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N173" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B174" s="4">
         <v>1</v>
@@ -7258,16 +9861,31 @@
         <v>19</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H174" s="4"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J174" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M174" s="2">
+        <v>100</v>
+      </c>
+      <c r="N174" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B175" s="4">
         <v>1</v>
@@ -7282,16 +9900,31 @@
         <v>8</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H175" s="4"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J175" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M175" s="2">
+        <v>100</v>
+      </c>
+      <c r="N175" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B176" s="4">
         <v>1</v>
@@ -7306,16 +9939,31 @@
         <v>8</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H176" s="4"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J176" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N176" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B177" s="4">
         <v>1</v>
@@ -7330,16 +9978,31 @@
         <v>19</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H177" s="4"/>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J177" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="K177" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M177" s="2">
+        <v>200</v>
+      </c>
+      <c r="N177" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B178" s="4">
         <v>1</v>
@@ -7354,16 +10017,29 @@
         <v>19</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H178" s="4"/>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J178" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M178" s="2"/>
+      <c r="N178" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B179" s="4">
         <v>1</v>
@@ -7378,16 +10054,31 @@
         <v>8</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J179" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N179" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B180" s="4">
         <v>1</v>
@@ -7402,7 +10093,7 @@
         <v>22</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>128</v>
@@ -7410,10 +10101,25 @@
       <c r="H180" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J180" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M180" s="2">
+        <v>200</v>
+      </c>
+      <c r="N180" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B181" s="4">
         <v>1</v>
@@ -7428,7 +10134,7 @@
         <v>22</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>128</v>
@@ -7436,10 +10142,25 @@
       <c r="H181" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J181" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L181" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M181" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N181" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B182" s="4">
         <v>1</v>
@@ -7454,16 +10175,31 @@
         <v>22</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H182" s="4"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J182" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N182" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B183" s="4">
         <v>1</v>
@@ -7478,16 +10214,31 @@
         <v>22</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H183" s="4"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J183" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L183" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M183" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N183" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B184" s="4">
         <v>1</v>
@@ -7502,16 +10253,31 @@
         <v>22</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H184" s="4"/>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J184" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="K184" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="L184" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="M184" s="2">
+        <v>1</v>
+      </c>
+      <c r="N184" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B185" s="4">
         <v>1</v>
@@ -7526,7 +10292,7 @@
         <v>8</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>128</v>
@@ -7534,10 +10300,25 @@
       <c r="H185" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J185" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N185" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B186" s="4">
         <v>1</v>
@@ -7552,7 +10333,7 @@
         <v>8</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>128</v>
@@ -7560,8 +10341,23 @@
       <c r="H186" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J186" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N186" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>185</v>
       </c>
@@ -7578,16 +10374,31 @@
         <v>8</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H187" s="4"/>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J187" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N187" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B188" s="4">
         <v>1</v>
@@ -7602,16 +10413,31 @@
         <v>19</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H188" s="4"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J188" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M188" s="2">
+        <v>100</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
@@ -7626,18 +10452,33 @@
         <v>22</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J189" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M189" s="2">
+        <v>2</v>
+      </c>
+      <c r="N189" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B190" s="4">
         <v>1</v>
@@ -7652,18 +10493,33 @@
         <v>8</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M190" s="2">
+        <v>100</v>
+      </c>
+      <c r="N190" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B191" s="4">
         <v>1</v>
@@ -7678,18 +10534,33 @@
         <v>8</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M191" s="2">
+        <v>100</v>
+      </c>
+      <c r="N191" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
@@ -7704,18 +10575,33 @@
         <v>8</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J192" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N192" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B193" s="4">
         <v>1</v>
@@ -7730,18 +10616,33 @@
         <v>19</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N193" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
@@ -7756,7 +10657,7 @@
         <v>8</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>128</v>
@@ -7764,10 +10665,25 @@
       <c r="H194" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J194" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N194" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B195" s="4">
         <v>1</v>
@@ -7782,7 +10698,7 @@
         <v>8</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>492</v>
+        <v>760</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>128</v>
@@ -7790,10 +10706,25 @@
       <c r="H195" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J195" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N195" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B196" s="4">
         <v>1</v>
@@ -7808,16 +10739,31 @@
         <v>22</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H196" s="4"/>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J196" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N196" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B197" s="4">
         <v>1</v>
@@ -7832,16 +10778,31 @@
         <v>22</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H197" s="4"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J197" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M197" s="2">
+        <v>2</v>
+      </c>
+      <c r="N197" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B198" s="4">
         <v>1</v>
@@ -7856,16 +10817,31 @@
         <v>22</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H198" s="4"/>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J198" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N198" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B199" s="4">
         <v>1</v>
@@ -7880,7 +10856,7 @@
         <v>8</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>128</v>
@@ -7888,10 +10864,25 @@
       <c r="H199" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J199" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="K199" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L199" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M199" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N199" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B200" s="4">
         <v>1</v>
@@ -7906,16 +10897,31 @@
         <v>8</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H200" s="4"/>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J200" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M200" s="2">
+        <v>100</v>
+      </c>
+      <c r="N200" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B201" s="4">
         <v>1</v>
@@ -7930,16 +10936,31 @@
         <v>22</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H201" s="4"/>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J201" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M201" s="2">
+        <v>750</v>
+      </c>
+      <c r="N201" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B202" s="4">
         <v>1</v>
@@ -7954,16 +10975,29 @@
         <v>19</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H202" s="4"/>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J202" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="K202" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="L202" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M202" s="2"/>
+      <c r="N202" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B203" s="4">
         <v>1</v>
@@ -7978,17 +11012,56 @@
         <v>8</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H203" s="4"/>
+      <c r="J203" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M203" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N203" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N203" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="C152:C203">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C204:C1048576 C2:C151">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D152:D203">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8000,7 +11073,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D204:D1048576 D2:D151">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8011,28 +11084,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C152:C203">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+  <conditionalFormatting sqref="J2:N203">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D152:D203">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>OR($L2="buff",$L2="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>OR($L2="dot",$L2="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>OR($L2="tank",$L2="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>OR($L2="heal",$L2="heal_all",$L2="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>OR($L2="extra_attack",$L2="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -8108,6 +11177,7 @@
     <hyperlink ref="F182" r:id="rId70" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
     <hyperlink ref="F184" r:id="rId71" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
     <hyperlink ref="F203" r:id="rId72" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
+    <hyperlink ref="F195" r:id="rId73" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125390B1-8892-4930-9832-C74F3423C2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C445FE-36AA-4558-9EC1-D9D646A44837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="762">
   <si>
     <t>Nombre</t>
   </si>
@@ -1960,18 +1960,12 @@
     <t>Doble destino</t>
   </si>
   <si>
-    <t>Venom desatado</t>
-  </si>
-  <si>
     <t>Lázaro inmortal</t>
   </si>
   <si>
     <t>Revive una carta del cementerio y la devuelve al mazo.</t>
   </si>
   <si>
-    <t>Control vegetal</t>
-  </si>
-  <si>
     <t>Furia bestial</t>
   </si>
   <si>
@@ -2306,6 +2300,15 @@
   </si>
   <si>
     <t>https://i.pinimg.com/1200x/84/98/f6/8498f6f9f4b218a61bb9773d50aa946b.jpg</t>
+  </si>
+  <si>
+    <t>Ofrenda al verde</t>
+  </si>
+  <si>
+    <t>Toxina de Bane</t>
+  </si>
+  <si>
+    <t>Envenena al objetivo causando @skill_power de daño durante varios turnos.</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2497,12 +2500,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -2542,62 +2551,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2906,7 +2859,7 @@
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="74.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" style="25" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2947,7 +2900,7 @@
       <c r="L1" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="9" t="s">
         <v>263</v>
       </c>
       <c r="N1" s="11" t="s">
@@ -3519,7 +3472,7 @@
         <v>501</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>289</v>
@@ -3599,7 +3552,7 @@
         <v>49</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>270</v>
@@ -3638,7 +3591,7 @@
       </c>
       <c r="H18" s="10"/>
       <c r="J18" s="12" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>298</v>
@@ -3685,7 +3638,7 @@
       <c r="L19" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M19" s="13" t="s">
         <v>274</v>
       </c>
       <c r="N19" s="20" t="s">
@@ -3724,7 +3677,7 @@
       <c r="L20" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="M20" s="21">
+      <c r="M20" s="15">
         <v>1000</v>
       </c>
       <c r="N20" s="21" t="s">
@@ -3763,7 +3716,7 @@
       <c r="L21" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="M21" s="21">
+      <c r="M21" s="15">
         <v>1000</v>
       </c>
       <c r="N21" s="21" t="s">
@@ -3841,7 +3794,7 @@
       <c r="L23" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="M23" s="20" t="s">
+      <c r="M23" s="13" t="s">
         <v>294</v>
       </c>
       <c r="N23" s="20" t="s">
@@ -3993,7 +3946,7 @@
         <v>29</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>270</v>
@@ -4116,7 +4069,7 @@
         <v>73</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="K30" s="22" t="s">
         <v>295</v>
@@ -4360,7 +4313,7 @@
         <v>49</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="K36" s="12" t="s">
         <v>298</v>
@@ -4442,7 +4395,7 @@
         <v>344</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="K38" s="22" t="s">
         <v>295</v>
@@ -4725,7 +4678,7 @@
         <v>102</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="K45" s="15" t="s">
         <v>299</v>
@@ -4926,7 +4879,7 @@
         <v>341</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K50" s="12" t="s">
         <v>297</v>
@@ -5008,7 +4961,7 @@
         <v>34</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="K52" s="14" t="s">
         <v>296</v>
@@ -5088,7 +5041,7 @@
       </c>
       <c r="H54" s="17"/>
       <c r="J54" s="12" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="K54" s="12" t="s">
         <v>297</v>
@@ -5773,7 +5726,7 @@
         <v>495</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="K71" s="12" t="s">
         <v>295</v>
@@ -6136,7 +6089,7 @@
       <c r="L80" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="M80" s="21">
+      <c r="M80" s="15">
         <v>1000</v>
       </c>
       <c r="N80" s="21" t="s">
@@ -6175,7 +6128,7 @@
       <c r="L81" s="19" t="s">
         <v>532</v>
       </c>
-      <c r="M81" s="19" t="s">
+      <c r="M81" s="12" t="s">
         <v>534</v>
       </c>
       <c r="N81" s="19" t="s">
@@ -6214,7 +6167,7 @@
       <c r="L82" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="M82" s="23">
+      <c r="M82" s="14">
         <v>100</v>
       </c>
       <c r="N82" s="23" t="s">
@@ -6255,7 +6208,7 @@
       <c r="L83" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="M83" s="21">
+      <c r="M83" s="15">
         <v>1000</v>
       </c>
       <c r="N83" s="21" t="s">
@@ -6294,7 +6247,7 @@
       <c r="L84" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="M84" s="20" t="s">
+      <c r="M84" s="13" t="s">
         <v>274</v>
       </c>
       <c r="N84" s="20" t="s">
@@ -6374,7 +6327,7 @@
       <c r="L86" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="M86" s="20" t="s">
+      <c r="M86" s="13" t="s">
         <v>294</v>
       </c>
       <c r="N86" s="20" t="s">
@@ -6415,7 +6368,7 @@
       <c r="L87" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="M87" s="23"/>
+      <c r="M87" s="14"/>
       <c r="N87" s="23" t="s">
         <v>271</v>
       </c>
@@ -6452,7 +6405,7 @@
       <c r="L88" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="M88" s="20" t="s">
+      <c r="M88" s="13" t="s">
         <v>274</v>
       </c>
       <c r="N88" s="20" t="s">
@@ -6522,7 +6475,7 @@
         <v>343</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K90" s="12" t="s">
         <v>297</v>
@@ -6563,7 +6516,7 @@
         <v>343</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="K91" s="12" t="s">
         <v>298</v>
@@ -6686,7 +6639,7 @@
         <v>110</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="K94" s="12" t="s">
         <v>295</v>
@@ -6733,7 +6686,7 @@
       <c r="L95" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="M95" s="23">
+      <c r="M95" s="14">
         <v>100</v>
       </c>
       <c r="N95" s="23" t="s">
@@ -6774,7 +6727,7 @@
       <c r="L96" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M96" s="2">
+      <c r="M96" s="24">
         <v>200</v>
       </c>
       <c r="N96" s="2" t="s">
@@ -6815,7 +6768,7 @@
       <c r="L97" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M97" s="2"/>
+      <c r="M97" s="24"/>
       <c r="N97" s="2" t="s">
         <v>271</v>
       </c>
@@ -6854,7 +6807,7 @@
       <c r="L98" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M98" s="2">
+      <c r="M98" s="24">
         <v>100</v>
       </c>
       <c r="N98" s="2" t="s">
@@ -6895,7 +6848,7 @@
       <c r="L99" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M99" s="2">
+      <c r="M99" s="24">
         <v>100</v>
       </c>
       <c r="N99" s="2" t="s">
@@ -6936,7 +6889,7 @@
       <c r="L100" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M100" s="2" t="s">
+      <c r="M100" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N100" s="2" t="s">
@@ -6975,7 +6928,7 @@
       <c r="L101" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M101" s="2">
+      <c r="M101" s="24">
         <v>100</v>
       </c>
       <c r="N101" s="2" t="s">
@@ -7014,7 +6967,7 @@
       <c r="L102" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M102" s="2" t="s">
+      <c r="M102" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N102" s="2" t="s">
@@ -7055,7 +7008,7 @@
       <c r="L103" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M103" s="2">
+      <c r="M103" s="24">
         <v>100</v>
       </c>
       <c r="N103" s="2" t="s">
@@ -7096,7 +7049,7 @@
       <c r="L104" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="M104" s="2">
+      <c r="M104" s="24">
         <v>50</v>
       </c>
       <c r="N104" s="2" t="s">
@@ -7137,7 +7090,7 @@
       <c r="L105" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="M105" s="2">
+      <c r="M105" s="24">
         <v>1000</v>
       </c>
       <c r="N105" s="2" t="s">
@@ -7176,7 +7129,7 @@
       <c r="L106" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="M106" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N106" s="2" t="s">
@@ -7217,7 +7170,7 @@
       <c r="L107" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M107" s="2" t="s">
+      <c r="M107" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N107" s="2" t="s">
@@ -7258,7 +7211,7 @@
       <c r="L108" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M108" s="2" t="s">
+      <c r="M108" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N108" s="2" t="s">
@@ -7297,7 +7250,7 @@
       <c r="L109" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M109" s="2" t="s">
+      <c r="M109" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N109" s="2" t="s">
@@ -7338,7 +7291,7 @@
       <c r="L110" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M110" s="2">
+      <c r="M110" s="24">
         <v>200</v>
       </c>
       <c r="N110" s="2" t="s">
@@ -7377,7 +7330,7 @@
       <c r="L111" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M111" s="2">
+      <c r="M111" s="24">
         <v>100</v>
       </c>
       <c r="N111" s="2" t="s">
@@ -7418,7 +7371,7 @@
       <c r="L112" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M112" s="2">
+      <c r="M112" s="24">
         <v>2</v>
       </c>
       <c r="N112" s="2" t="s">
@@ -7457,7 +7410,7 @@
       <c r="L113" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="M113" s="2">
+      <c r="M113" s="24">
         <v>50</v>
       </c>
       <c r="N113" s="2" t="s">
@@ -7498,7 +7451,7 @@
       <c r="L114" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M114" s="2" t="s">
+      <c r="M114" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N114" s="2" t="s">
@@ -7531,16 +7484,16 @@
         <v>167</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>645</v>
+        <v>760</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>578</v>
+        <v>761</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>282</v>
+        <v>529</v>
+      </c>
+      <c r="M115" s="24">
+        <v>200</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>272</v>
@@ -7572,15 +7525,15 @@
         <v>167</v>
       </c>
       <c r="J116" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="K116" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="M116" s="2">
+      <c r="M116" s="24">
         <v>1</v>
       </c>
       <c r="N116" s="2" t="s">
@@ -7613,7 +7566,7 @@
         <v>174</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>648</v>
+        <v>759</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>575</v>
@@ -7621,7 +7574,7 @@
       <c r="L117" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M117" s="2">
+      <c r="M117" s="24">
         <v>750</v>
       </c>
       <c r="N117" s="2" t="s">
@@ -7654,7 +7607,7 @@
         <v>149</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>628</v>
@@ -7662,7 +7615,7 @@
       <c r="L118" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M118" s="2" t="s">
+      <c r="M118" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N118" s="2" t="s">
@@ -7695,7 +7648,7 @@
         <v>179</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>628</v>
@@ -7703,7 +7656,7 @@
       <c r="L119" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M119" s="2" t="s">
+      <c r="M119" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N119" s="2" t="s">
@@ -7736,7 +7689,7 @@
         <v>179</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>618</v>
@@ -7744,7 +7697,7 @@
       <c r="L120" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M120" s="2" t="s">
+      <c r="M120" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N120" s="2" t="s">
@@ -7777,7 +7730,7 @@
         <v>182</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>628</v>
@@ -7785,7 +7738,7 @@
       <c r="L121" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M121" s="2" t="s">
+      <c r="M121" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N121" s="2" t="s">
@@ -7816,7 +7769,7 @@
       </c>
       <c r="H122" s="4"/>
       <c r="J122" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>578</v>
@@ -7824,7 +7777,7 @@
       <c r="L122" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M122" s="2" t="s">
+      <c r="M122" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N122" s="2" t="s">
@@ -7855,15 +7808,15 @@
       </c>
       <c r="H123" s="4"/>
       <c r="J123" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M123" s="2" t="s">
+      <c r="M123" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N123" s="2" t="s">
@@ -7894,7 +7847,7 @@
       </c>
       <c r="H124" s="4"/>
       <c r="J124" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>578</v>
@@ -7902,7 +7855,7 @@
       <c r="L124" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M124" s="2" t="s">
+      <c r="M124" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N124" s="2" t="s">
@@ -7935,7 +7888,7 @@
         <v>157</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>620</v>
@@ -7943,7 +7896,7 @@
       <c r="L125" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M125" s="2">
+      <c r="M125" s="24">
         <v>100</v>
       </c>
       <c r="N125" s="2" t="s">
@@ -7976,7 +7929,7 @@
         <v>135</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>580</v>
@@ -7984,7 +7937,7 @@
       <c r="L126" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M126" s="2">
+      <c r="M126" s="24">
         <v>2</v>
       </c>
       <c r="N126" s="2" t="s">
@@ -8015,15 +7968,15 @@
       </c>
       <c r="H127" s="4"/>
       <c r="J127" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L127" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M127" s="2">
+      <c r="M127" s="24">
         <v>200</v>
       </c>
       <c r="N127" s="2" t="s">
@@ -8054,15 +8007,15 @@
       </c>
       <c r="H128" s="4"/>
       <c r="J128" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="L128" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M128" s="2"/>
+      <c r="M128" s="24"/>
       <c r="N128" s="2" t="s">
         <v>271</v>
       </c>
@@ -8093,7 +8046,7 @@
         <v>199</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>628</v>
@@ -8101,7 +8054,7 @@
       <c r="L129" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M129" s="2" t="s">
+      <c r="M129" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N129" s="2" t="s">
@@ -8134,15 +8087,15 @@
         <v>202</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="L130" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="M130" s="2">
+      <c r="M130" s="24">
         <v>1000</v>
       </c>
       <c r="N130" s="2" t="s">
@@ -8175,7 +8128,7 @@
         <v>141</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>580</v>
@@ -8183,7 +8136,7 @@
       <c r="L131" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M131" s="2">
+      <c r="M131" s="24">
         <v>2</v>
       </c>
       <c r="N131" s="2" t="s">
@@ -8216,15 +8169,15 @@
         <v>182</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L132" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M132" s="2">
+      <c r="M132" s="24">
         <v>200</v>
       </c>
       <c r="N132" s="2" t="s">
@@ -8255,7 +8208,7 @@
       </c>
       <c r="H133" s="4"/>
       <c r="J133" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>628</v>
@@ -8263,7 +8216,7 @@
       <c r="L133" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M133" s="2" t="s">
+      <c r="M133" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N133" s="2" t="s">
@@ -8296,7 +8249,7 @@
         <v>149</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>628</v>
@@ -8304,7 +8257,7 @@
       <c r="L134" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M134" s="2" t="s">
+      <c r="M134" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N134" s="2" t="s">
@@ -8335,15 +8288,15 @@
       </c>
       <c r="H135" s="4"/>
       <c r="J135" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L135" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M135" s="2" t="s">
+      <c r="M135" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N135" s="2" t="s">
@@ -8376,15 +8329,15 @@
         <v>179</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M136" s="2">
+      <c r="M136" s="24">
         <v>100</v>
       </c>
       <c r="N136" s="2" t="s">
@@ -8417,15 +8370,15 @@
         <v>217</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M137" s="2">
+      <c r="M137" s="24">
         <v>100</v>
       </c>
       <c r="N137" s="2" t="s">
@@ -8456,7 +8409,7 @@
       </c>
       <c r="H138" s="4"/>
       <c r="J138" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>580</v>
@@ -8464,7 +8417,7 @@
       <c r="L138" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M138" s="2">
+      <c r="M138" s="24">
         <v>2</v>
       </c>
       <c r="N138" s="2" t="s">
@@ -8497,15 +8450,15 @@
         <v>141</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M139" s="2" t="s">
+      <c r="M139" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N139" s="2" t="s">
@@ -8536,15 +8489,15 @@
       </c>
       <c r="H140" s="4"/>
       <c r="J140" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L140" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M140" s="2">
+      <c r="M140" s="24">
         <v>200</v>
       </c>
       <c r="N140" s="2" t="s">
@@ -8575,15 +8528,15 @@
       </c>
       <c r="H141" s="4"/>
       <c r="J141" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L141" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M141" s="2" t="s">
+      <c r="M141" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N141" s="2" t="s">
@@ -8616,15 +8569,15 @@
         <v>149</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L142" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M142" s="2" t="s">
+      <c r="M142" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N142" s="2" t="s">
@@ -8655,15 +8608,15 @@
       </c>
       <c r="H143" s="4"/>
       <c r="J143" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M143" s="2">
+      <c r="M143" s="24">
         <v>200</v>
       </c>
       <c r="N143" s="2" t="s">
@@ -8694,15 +8647,15 @@
       </c>
       <c r="H144" s="4"/>
       <c r="J144" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M144" s="2"/>
+      <c r="M144" s="24"/>
       <c r="N144" s="2" t="s">
         <v>271</v>
       </c>
@@ -8731,15 +8684,15 @@
       </c>
       <c r="H145" s="4"/>
       <c r="J145" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M145" s="2" t="s">
+      <c r="M145" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N145" s="2" t="s">
@@ -8770,15 +8723,15 @@
       </c>
       <c r="H146" s="4"/>
       <c r="J146" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L146" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M146" s="2" t="s">
+      <c r="M146" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N146" s="2" t="s">
@@ -8809,15 +8762,15 @@
       </c>
       <c r="H147" s="4"/>
       <c r="J147" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L147" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M147" s="2" t="s">
+      <c r="M147" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N147" s="2" t="s">
@@ -8850,15 +8803,15 @@
         <v>182</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L148" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M148" s="2">
+      <c r="M148" s="24">
         <v>200</v>
       </c>
       <c r="N148" s="2" t="s">
@@ -8889,15 +8842,15 @@
       </c>
       <c r="H149" s="4"/>
       <c r="J149" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L149" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M149" s="2" t="s">
+      <c r="M149" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N149" s="2" t="s">
@@ -8930,15 +8883,15 @@
         <v>138</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L150" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M150" s="2">
+      <c r="M150" s="24">
         <v>100</v>
       </c>
       <c r="N150" s="2" t="s">
@@ -8969,15 +8922,15 @@
       </c>
       <c r="H151" s="4"/>
       <c r="J151" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M151" s="2">
+      <c r="M151" s="24">
         <v>2</v>
       </c>
       <c r="N151" s="2" t="s">
@@ -9008,15 +8961,15 @@
       </c>
       <c r="H152" s="4"/>
       <c r="J152" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L152" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M152" s="2" t="s">
+      <c r="M152" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N152" s="2" t="s">
@@ -9047,7 +9000,7 @@
       </c>
       <c r="H153" s="4"/>
       <c r="J153" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>565</v>
@@ -9055,7 +9008,7 @@
       <c r="L153" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M153" s="2">
+      <c r="M153" s="24">
         <v>100</v>
       </c>
       <c r="N153" s="2" t="s">
@@ -9086,7 +9039,7 @@
       </c>
       <c r="H154" s="4"/>
       <c r="J154" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>618</v>
@@ -9094,7 +9047,7 @@
       <c r="L154" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M154" s="2" t="s">
+      <c r="M154" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N154" s="2" t="s">
@@ -9133,7 +9086,7 @@
       <c r="L155" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="M155" s="2">
+      <c r="M155" s="24">
         <v>50</v>
       </c>
       <c r="N155" s="2" t="s">
@@ -9164,7 +9117,7 @@
       </c>
       <c r="H156" s="4"/>
       <c r="J156" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>628</v>
@@ -9172,7 +9125,7 @@
       <c r="L156" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M156" s="2" t="s">
+      <c r="M156" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N156" s="2" t="s">
@@ -9203,7 +9156,7 @@
       </c>
       <c r="H157" s="4"/>
       <c r="J157" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>626</v>
@@ -9211,7 +9164,7 @@
       <c r="L157" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M157" s="2">
+      <c r="M157" s="24">
         <v>100</v>
       </c>
       <c r="N157" s="2" t="s">
@@ -9242,7 +9195,7 @@
       </c>
       <c r="H158" s="4"/>
       <c r="J158" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>618</v>
@@ -9250,7 +9203,7 @@
       <c r="L158" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M158" s="2" t="s">
+      <c r="M158" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N158" s="2" t="s">
@@ -9281,15 +9234,15 @@
       </c>
       <c r="H159" s="4"/>
       <c r="J159" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M159" s="2">
+      <c r="M159" s="24">
         <v>200</v>
       </c>
       <c r="N159" s="2" t="s">
@@ -9320,7 +9273,7 @@
       </c>
       <c r="H160" s="4"/>
       <c r="J160" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>628</v>
@@ -9328,7 +9281,7 @@
       <c r="L160" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M160" s="2" t="s">
+      <c r="M160" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N160" s="2" t="s">
@@ -9359,7 +9312,7 @@
       </c>
       <c r="H161" s="4"/>
       <c r="J161" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>610</v>
@@ -9367,7 +9320,7 @@
       <c r="L161" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M161" s="2">
+      <c r="M161" s="24">
         <v>100</v>
       </c>
       <c r="N161" s="2" t="s">
@@ -9398,7 +9351,7 @@
       </c>
       <c r="H162" s="4"/>
       <c r="J162" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>628</v>
@@ -9406,7 +9359,7 @@
       <c r="L162" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M162" s="2" t="s">
+      <c r="M162" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N162" s="2" t="s">
@@ -9439,7 +9392,7 @@
         <v>462</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>578</v>
@@ -9447,7 +9400,7 @@
       <c r="L163" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M163" s="2" t="s">
+      <c r="M163" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N163" s="2" t="s">
@@ -9478,15 +9431,15 @@
       </c>
       <c r="H164" s="4"/>
       <c r="J164" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L164" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M164" s="2">
+      <c r="M164" s="24">
         <v>100</v>
       </c>
       <c r="N164" s="2" t="s">
@@ -9517,15 +9470,15 @@
       </c>
       <c r="H165" s="4"/>
       <c r="J165" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L165" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M165" s="2" t="s">
+      <c r="M165" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N165" s="2" t="s">
@@ -9556,7 +9509,7 @@
       </c>
       <c r="H166" s="4"/>
       <c r="J166" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K166" s="2" t="s">
         <v>600</v>
@@ -9564,7 +9517,7 @@
       <c r="L166" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M166" s="2"/>
+      <c r="M166" s="24"/>
       <c r="N166" s="2" t="s">
         <v>271</v>
       </c>
@@ -9593,7 +9546,7 @@
       </c>
       <c r="H167" s="4"/>
       <c r="J167" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="K167" s="2" t="s">
         <v>628</v>
@@ -9601,7 +9554,7 @@
       <c r="L167" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M167" s="2" t="s">
+      <c r="M167" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N167" s="2" t="s">
@@ -9632,7 +9585,7 @@
       </c>
       <c r="H168" s="4"/>
       <c r="J168" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K168" s="2" t="s">
         <v>618</v>
@@ -9640,7 +9593,7 @@
       <c r="L168" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M168" s="2" t="s">
+      <c r="M168" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N168" s="2" t="s">
@@ -9671,15 +9624,15 @@
       </c>
       <c r="H169" s="4"/>
       <c r="J169" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L169" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M169" s="2" t="s">
+      <c r="M169" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N169" s="2" t="s">
@@ -9710,15 +9663,15 @@
       </c>
       <c r="H170" s="4"/>
       <c r="J170" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M170" s="2">
+      <c r="M170" s="24">
         <v>200</v>
       </c>
       <c r="N170" s="2" t="s">
@@ -9749,15 +9702,15 @@
       </c>
       <c r="H171" s="4"/>
       <c r="J171" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M171" s="2"/>
+      <c r="M171" s="24"/>
       <c r="N171" s="2" t="s">
         <v>271</v>
       </c>
@@ -9796,7 +9749,7 @@
       <c r="L172" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M172" s="2" t="s">
+      <c r="M172" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N172" s="2" t="s">
@@ -9829,7 +9782,7 @@
         <v>462</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>618</v>
@@ -9837,7 +9790,7 @@
       <c r="L173" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M173" s="2" t="s">
+      <c r="M173" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N173" s="2" t="s">
@@ -9868,15 +9821,15 @@
       </c>
       <c r="H174" s="4"/>
       <c r="J174" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M174" s="2">
+      <c r="M174" s="24">
         <v>100</v>
       </c>
       <c r="N174" s="2" t="s">
@@ -9907,7 +9860,7 @@
       </c>
       <c r="H175" s="4"/>
       <c r="J175" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>589</v>
@@ -9915,7 +9868,7 @@
       <c r="L175" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M175" s="2">
+      <c r="M175" s="24">
         <v>100</v>
       </c>
       <c r="N175" s="2" t="s">
@@ -9946,15 +9899,15 @@
       </c>
       <c r="H176" s="4"/>
       <c r="J176" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L176" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M176" s="2" t="s">
+      <c r="M176" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N176" s="2" t="s">
@@ -9985,15 +9938,15 @@
       </c>
       <c r="H177" s="4"/>
       <c r="J177" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M177" s="2">
+      <c r="M177" s="24">
         <v>200</v>
       </c>
       <c r="N177" s="2" t="s">
@@ -10024,15 +9977,15 @@
       </c>
       <c r="H178" s="4"/>
       <c r="J178" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L178" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M178" s="2"/>
+      <c r="M178" s="24"/>
       <c r="N178" s="2" t="s">
         <v>271</v>
       </c>
@@ -10061,7 +10014,7 @@
       </c>
       <c r="H179" s="4"/>
       <c r="J179" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="K179" s="2" t="s">
         <v>628</v>
@@ -10069,7 +10022,7 @@
       <c r="L179" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M179" s="2" t="s">
+      <c r="M179" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N179" s="2" t="s">
@@ -10102,15 +10055,15 @@
         <v>182</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L180" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M180" s="2">
+      <c r="M180" s="24">
         <v>200</v>
       </c>
       <c r="N180" s="2" t="s">
@@ -10143,15 +10096,15 @@
         <v>182</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L181" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M181" s="2" t="s">
+      <c r="M181" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N181" s="2" t="s">
@@ -10182,7 +10135,7 @@
       </c>
       <c r="H182" s="4"/>
       <c r="J182" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>628</v>
@@ -10190,7 +10143,7 @@
       <c r="L182" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M182" s="2" t="s">
+      <c r="M182" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N182" s="2" t="s">
@@ -10221,7 +10174,7 @@
       </c>
       <c r="H183" s="4"/>
       <c r="J183" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="K183" s="2" t="s">
         <v>618</v>
@@ -10229,7 +10182,7 @@
       <c r="L183" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M183" s="2" t="s">
+      <c r="M183" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N183" s="2" t="s">
@@ -10260,15 +10213,15 @@
       </c>
       <c r="H184" s="4"/>
       <c r="J184" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="L184" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="M184" s="2">
+      <c r="M184" s="24">
         <v>1</v>
       </c>
       <c r="N184" s="2" t="s">
@@ -10301,7 +10254,7 @@
         <v>179</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K185" s="2" t="s">
         <v>628</v>
@@ -10309,7 +10262,7 @@
       <c r="L185" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M185" s="2" t="s">
+      <c r="M185" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N185" s="2" t="s">
@@ -10342,7 +10295,7 @@
         <v>179</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="K186" s="2" t="s">
         <v>628</v>
@@ -10350,7 +10303,7 @@
       <c r="L186" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M186" s="2" t="s">
+      <c r="M186" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N186" s="2" t="s">
@@ -10381,15 +10334,15 @@
       </c>
       <c r="H187" s="4"/>
       <c r="J187" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M187" s="2" t="s">
+      <c r="M187" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N187" s="2" t="s">
@@ -10420,15 +10373,15 @@
       </c>
       <c r="H188" s="4"/>
       <c r="J188" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L188" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M188" s="2">
+      <c r="M188" s="24">
         <v>100</v>
       </c>
       <c r="N188" s="2" t="s">
@@ -10461,7 +10414,7 @@
         <v>480</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="K189" s="2" t="s">
         <v>580</v>
@@ -10469,7 +10422,7 @@
       <c r="L189" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M189" s="2">
+      <c r="M189" s="24">
         <v>2</v>
       </c>
       <c r="N189" s="2" t="s">
@@ -10505,12 +10458,12 @@
         <v>619</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L190" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M190" s="2">
+      <c r="M190" s="24">
         <v>100</v>
       </c>
       <c r="N190" s="2" t="s">
@@ -10546,12 +10499,12 @@
         <v>566</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L191" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M191" s="2">
+      <c r="M191" s="24">
         <v>100</v>
       </c>
       <c r="N191" s="2" t="s">
@@ -10584,15 +10537,15 @@
         <v>480</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L192" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M192" s="2" t="s">
+      <c r="M192" s="24" t="s">
         <v>282</v>
       </c>
       <c r="N192" s="2" t="s">
@@ -10625,15 +10578,15 @@
         <v>480</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M193" s="2" t="s">
+      <c r="M193" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N193" s="2" t="s">
@@ -10666,7 +10619,7 @@
         <v>179</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="K194" s="2" t="s">
         <v>628</v>
@@ -10674,7 +10627,7 @@
       <c r="L194" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M194" s="2" t="s">
+      <c r="M194" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N194" s="2" t="s">
@@ -10698,7 +10651,7 @@
         <v>8</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>128</v>
@@ -10707,7 +10660,7 @@
         <v>179</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>628</v>
@@ -10715,7 +10668,7 @@
       <c r="L195" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M195" s="2" t="s">
+      <c r="M195" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N195" s="2" t="s">
@@ -10746,15 +10699,15 @@
       </c>
       <c r="H196" s="4"/>
       <c r="J196" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="L196" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="M196" s="2" t="s">
+      <c r="M196" s="24" t="s">
         <v>534</v>
       </c>
       <c r="N196" s="2" t="s">
@@ -10785,15 +10738,15 @@
       </c>
       <c r="H197" s="4"/>
       <c r="J197" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M197" s="2">
+      <c r="M197" s="24">
         <v>2</v>
       </c>
       <c r="N197" s="2" t="s">
@@ -10824,15 +10777,15 @@
       </c>
       <c r="H198" s="4"/>
       <c r="J198" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L198" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M198" s="2" t="s">
+      <c r="M198" s="24" t="s">
         <v>274</v>
       </c>
       <c r="N198" s="2" t="s">
@@ -10865,7 +10818,7 @@
         <v>179</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="K199" s="2" t="s">
         <v>628</v>
@@ -10873,7 +10826,7 @@
       <c r="L199" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M199" s="2" t="s">
+      <c r="M199" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N199" s="2" t="s">
@@ -10904,15 +10857,15 @@
       </c>
       <c r="H200" s="4"/>
       <c r="J200" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L200" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M200" s="2">
+      <c r="M200" s="24">
         <v>100</v>
       </c>
       <c r="N200" s="2" t="s">
@@ -10943,7 +10896,7 @@
       </c>
       <c r="H201" s="4"/>
       <c r="J201" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>575</v>
@@ -10951,7 +10904,7 @@
       <c r="L201" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M201" s="2">
+      <c r="M201" s="24">
         <v>750</v>
       </c>
       <c r="N201" s="2" t="s">
@@ -10982,15 +10935,15 @@
       </c>
       <c r="H202" s="4"/>
       <c r="J202" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="L202" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M202" s="2"/>
+      <c r="M202" s="24"/>
       <c r="N202" s="2" t="s">
         <v>271</v>
       </c>
@@ -11019,7 +10972,7 @@
       </c>
       <c r="H203" s="4"/>
       <c r="J203" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="K203" s="2" t="s">
         <v>628</v>
@@ -11027,7 +10980,7 @@
       <c r="L203" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M203" s="2" t="s">
+      <c r="M203" s="24" t="s">
         <v>294</v>
       </c>
       <c r="N203" s="2" t="s">

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C445FE-36AA-4558-9EC1-D9D646A44837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96293900-8D9A-4294-BBF8-1F68B884D5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96293900-8D9A-4294-BBF8-1F68B884D5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4E250D-0692-4A54-9091-57DCC9CA5CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2441,7 +2441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2506,6 +2506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2854,7 +2855,7 @@
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="86.140625" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="74.7109375" bestFit="1" customWidth="1"/>
@@ -5874,7 +5875,7 @@
       <c r="E75" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="26" t="s">
         <v>224</v>
       </c>
       <c r="G75" s="17" t="s">

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4E250D-0692-4A54-9091-57DCC9CA5CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058FE76B-B004-4E56-9E68-05D79CBD9034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3CA43F-8256-4B83-B99E-4687D9E3F237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CEEE0E-A733-4B10-A77A-548348CE4882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$253</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="945">
   <si>
     <t>Nombre</t>
   </si>
@@ -2852,6 +2852,12 @@
   </si>
   <si>
     <t>https://i.ibb.co/DHpVxkhc/artemis.jpg</t>
+  </si>
+  <si>
+    <t>Adam Strange</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/20HYnX6v/Adamstrange.webp</t>
   </si>
 </sst>
 </file>
@@ -3432,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N253"/>
+  <dimension ref="A1:N254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -8359,22 +8365,22 @@
     </row>
     <row r="121" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>888</v>
+        <v>943</v>
       </c>
       <c r="B121" s="17">
         <v>1</v>
       </c>
       <c r="C121" s="17">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D121" s="17">
         <v>2000</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>889</v>
+        <v>944</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>10</v>
@@ -8382,40 +8388,30 @@
       <c r="H121" s="10" t="s">
         <v>922</v>
       </c>
-      <c r="J121" s="13" t="s">
-        <v>890</v>
-      </c>
-      <c r="K121" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="L121" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="M121" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="N121" s="13" t="s">
-        <v>268</v>
-      </c>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+      <c r="M121" s="24"/>
+      <c r="N121" s="2"/>
     </row>
     <row r="122" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B122" s="17">
         <v>1</v>
       </c>
       <c r="C122" s="17">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D122" s="17">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>10</v>
@@ -8423,40 +8419,40 @@
       <c r="H122" s="10" t="s">
         <v>922</v>
       </c>
-      <c r="J122" s="15" t="s">
-        <v>887</v>
-      </c>
-      <c r="K122" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="L122" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="M122" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="N122" s="15" t="s">
+      <c r="J122" s="13" t="s">
+        <v>890</v>
+      </c>
+      <c r="K122" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="L122" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="M122" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="N122" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>315</v>
+        <v>885</v>
       </c>
       <c r="B123" s="17">
         <v>1</v>
       </c>
       <c r="C123" s="17">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D123" s="17">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>10</v>
@@ -8464,146 +8460,146 @@
       <c r="H123" s="10" t="s">
         <v>922</v>
       </c>
-      <c r="J123" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M123" s="24">
-        <v>100</v>
-      </c>
-      <c r="N123" s="2" t="s">
-        <v>267</v>
+      <c r="J123" s="15" t="s">
+        <v>887</v>
+      </c>
+      <c r="K123" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="L123" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="M123" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="N123" s="15" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>827</v>
+        <v>315</v>
       </c>
       <c r="B124" s="17">
         <v>1</v>
       </c>
       <c r="C124" s="17">
+        <v>5000</v>
+      </c>
+      <c r="D124" s="17">
         <v>3500</v>
-      </c>
-      <c r="D124" s="17">
-        <v>2000</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>828</v>
+        <v>894</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>829</v>
+        <v>922</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>836</v>
+        <v>895</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M124" s="24" t="s">
-        <v>270</v>
+        <v>260</v>
+      </c>
+      <c r="M124" s="24">
+        <v>100</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B125" s="3">
-        <v>1</v>
-      </c>
-      <c r="C125" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D125" s="3">
-        <v>2500</v>
+      <c r="A125" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="B125" s="17">
+        <v>1</v>
+      </c>
+      <c r="C125" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D125" s="17">
+        <v>2000</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>122</v>
+        <v>828</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H125" s="10"/>
-      <c r="J125" s="23" t="s">
+      <c r="H125" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M125" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B126" s="3">
+        <v>1</v>
+      </c>
+      <c r="C126" s="3">
+        <v>4500</v>
+      </c>
+      <c r="D126" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H126" s="10"/>
+      <c r="J126" s="23" t="s">
         <v>937</v>
       </c>
-      <c r="K125" s="23" t="s">
+      <c r="K126" s="23" t="s">
         <v>607</v>
       </c>
-      <c r="L125" s="23" t="s">
+      <c r="L126" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M125" s="14">
+      <c r="M126" s="14">
         <v>100</v>
       </c>
-      <c r="N125" s="23" t="s">
+      <c r="N126" s="23" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B126" s="4">
-        <v>1</v>
-      </c>
-      <c r="C126" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D126" s="4">
-        <v>2500</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M126" s="24">
-        <v>200</v>
-      </c>
-      <c r="N126" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B127" s="4">
         <v>1</v>
@@ -8618,102 +8614,102 @@
         <v>19</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>283</v>
+        <v>609</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M127" s="24"/>
+        <v>516</v>
+      </c>
+      <c r="M127" s="24">
+        <v>200</v>
+      </c>
       <c r="N127" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B128" s="4">
         <v>1</v>
       </c>
       <c r="C128" s="4">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D128" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>856</v>
+        <v>129</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>552</v>
+        <v>283</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M128" s="24">
-        <v>100</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M128" s="24"/>
       <c r="N128" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B129" s="4">
         <v>1</v>
       </c>
       <c r="C129" s="4">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="D129" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>135</v>
+        <v>856</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>613</v>
+        <v>552</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M129" s="24">
         <v>100</v>
@@ -8724,7 +8720,7 @@
     </row>
     <row r="130" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B130" s="4">
         <v>1</v>
@@ -8733,39 +8729,39 @@
         <v>5500</v>
       </c>
       <c r="D130" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M130" s="24" t="s">
-        <v>290</v>
+        <v>260</v>
+      </c>
+      <c r="M130" s="24">
+        <v>100</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="B131" s="4">
         <v>1</v>
@@ -8780,31 +8776,33 @@
         <v>22</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H131" s="4"/>
+      <c r="H131" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="J131" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>552</v>
+        <v>615</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M131" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M131" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B132" s="4">
         <v>1</v>
@@ -8813,111 +8811,109 @@
         <v>5500</v>
       </c>
       <c r="D132" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H132" s="4"/>
       <c r="J132" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>605</v>
+        <v>552</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M132" s="24" t="s">
-        <v>270</v>
+        <v>261</v>
+      </c>
+      <c r="M132" s="24">
+        <v>100</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="B133" s="4">
         <v>1</v>
       </c>
       <c r="C133" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D133" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H133" s="4" t="s">
-        <v>141</v>
-      </c>
+      <c r="H133" s="4"/>
       <c r="J133" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M133" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M133" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>246</v>
+        <v>139</v>
       </c>
       <c r="B134" s="4">
         <v>1</v>
       </c>
       <c r="C134" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D134" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>481</v>
+        <v>140</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>548</v>
+        <v>613</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="M134" s="24">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N134" s="2" t="s">
         <v>267</v>
@@ -8925,22 +8921,22 @@
     </row>
     <row r="135" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>891</v>
+        <v>246</v>
       </c>
       <c r="B135" s="4">
         <v>1</v>
       </c>
       <c r="C135" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D135" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>892</v>
+        <v>481</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>125</v>
@@ -8949,37 +8945,39 @@
         <v>213</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>893</v>
+        <v>619</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>283</v>
+        <v>548</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M135" s="24"/>
+        <v>275</v>
+      </c>
+      <c r="M135" s="24">
+        <v>50</v>
+      </c>
       <c r="N135" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>805</v>
+        <v>891</v>
       </c>
       <c r="B136" s="4">
         <v>1</v>
       </c>
       <c r="C136" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D136" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>806</v>
+        <v>892</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>125</v>
@@ -8987,40 +8985,38 @@
       <c r="H136" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J136" s="14" t="s">
-        <v>807</v>
-      </c>
-      <c r="K136" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L136" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M136" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N136" s="14" t="s">
+      <c r="J136" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M136" s="24"/>
+      <c r="N136" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="137" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>244</v>
+        <v>805</v>
       </c>
       <c r="B137" s="4">
         <v>1</v>
       </c>
       <c r="C137" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D137" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>245</v>
+        <v>806</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>125</v>
@@ -9028,56 +9024,58 @@
       <c r="H137" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J137" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="L137" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M137" s="24">
-        <v>1000</v>
-      </c>
-      <c r="N137" s="2" t="s">
-        <v>268</v>
+      <c r="J137" s="14" t="s">
+        <v>807</v>
+      </c>
+      <c r="K137" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L137" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M137" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N137" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="138" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="B138" s="4">
         <v>1</v>
       </c>
       <c r="C138" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D138" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H138" s="4"/>
+      <c r="H138" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="J138" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M138" s="24" t="s">
-        <v>290</v>
+        <v>264</v>
+      </c>
+      <c r="M138" s="24">
+        <v>1000</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>268</v>
@@ -9085,31 +9083,29 @@
     </row>
     <row r="139" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B139" s="4">
         <v>1</v>
       </c>
       <c r="C139" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D139" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H139" s="4" t="s">
-        <v>146</v>
-      </c>
+      <c r="H139" s="4"/>
       <c r="J139" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>615</v>
@@ -9126,40 +9122,40 @@
     </row>
     <row r="140" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B140" s="4">
         <v>1</v>
       </c>
       <c r="C140" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D140" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M140" s="24" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N140" s="2" t="s">
         <v>268</v>
@@ -9167,206 +9163,208 @@
     </row>
     <row r="141" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B141" s="4">
         <v>1</v>
       </c>
       <c r="C141" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D141" s="4">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H141" s="4"/>
+      <c r="H141" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="J141" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>520</v>
+        <v>605</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>519</v>
+        <v>269</v>
       </c>
       <c r="M141" s="24" t="s">
-        <v>521</v>
+        <v>270</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="142" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B142" s="4">
         <v>1</v>
       </c>
       <c r="C142" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D142" s="4">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H142" s="4" t="s">
-        <v>154</v>
-      </c>
+      <c r="H142" s="4"/>
       <c r="J142" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>627</v>
+        <v>520</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M142" s="24">
-        <v>200</v>
+        <v>519</v>
+      </c>
+      <c r="M142" s="24" t="s">
+        <v>521</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B143" s="4">
         <v>1</v>
       </c>
       <c r="C143" s="4">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="D143" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H143" s="4"/>
+      <c r="H143" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="J143" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>261</v>
+        <v>516</v>
       </c>
       <c r="M143" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="144" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B144" s="4">
         <v>1</v>
       </c>
       <c r="C144" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D144" s="4">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H144" s="4" t="s">
-        <v>159</v>
-      </c>
+      <c r="H144" s="4"/>
       <c r="J144" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M144" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B145" s="4">
         <v>1</v>
       </c>
       <c r="C145" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D145" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H145" s="4"/>
+      <c r="H145" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="J145" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="M145" s="24">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B146" s="4">
         <v>1</v>
@@ -9381,48 +9379,46 @@
         <v>19</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H146" s="4" t="s">
-        <v>164</v>
-      </c>
+      <c r="H146" s="4"/>
       <c r="J146" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>615</v>
+        <v>548</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M146" s="24" t="s">
-        <v>290</v>
+        <v>275</v>
+      </c>
+      <c r="M146" s="24">
+        <v>50</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B147" s="4">
         <v>1</v>
       </c>
       <c r="C147" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D147" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>166</v>
+        <v>19</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>125</v>
@@ -9431,16 +9427,16 @@
         <v>164</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>745</v>
+        <v>631</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>746</v>
+        <v>615</v>
       </c>
       <c r="L147" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M147" s="24">
-        <v>200</v>
+        <v>288</v>
+      </c>
+      <c r="M147" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N147" s="2" t="s">
         <v>268</v>
@@ -9448,53 +9444,63 @@
     </row>
     <row r="148" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>907</v>
+        <v>165</v>
       </c>
       <c r="B148" s="4">
         <v>1</v>
       </c>
       <c r="C148" s="4">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="D148" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>910</v>
+        <v>166</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="J148" s="2"/>
-      <c r="K148" s="2"/>
-      <c r="L148" s="2"/>
-      <c r="M148" s="24"/>
-      <c r="N148" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M148" s="24">
+        <v>200</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="149" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B149" s="4">
         <v>1</v>
       </c>
       <c r="C149" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D149" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>125</v>
@@ -9502,58 +9508,48 @@
       <c r="H149" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="J149" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="L149" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M149" s="24">
-        <v>200</v>
-      </c>
-      <c r="N149" s="2" t="s">
-        <v>268</v>
-      </c>
+      <c r="J149" s="2"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="2"/>
     </row>
     <row r="150" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>167</v>
+        <v>911</v>
       </c>
       <c r="B150" s="4">
         <v>1</v>
       </c>
       <c r="C150" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D150" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F150" s="4" t="s">
-        <v>168</v>
+      <c r="F150" s="8" t="s">
+        <v>912</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>164</v>
+        <v>909</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>632</v>
+        <v>913</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>633</v>
+        <v>914</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>263</v>
+        <v>516</v>
       </c>
       <c r="M150" s="24">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="N150" s="2" t="s">
         <v>268</v>
@@ -9561,7 +9557,7 @@
     </row>
     <row r="151" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B151" s="4">
         <v>1</v>
@@ -9576,25 +9572,25 @@
         <v>22</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>908</v>
+        <v>164</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>744</v>
+        <v>632</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>562</v>
+        <v>633</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M151" s="24">
-        <v>750</v>
+        <v>1</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>268</v>
@@ -9602,40 +9598,40 @@
     </row>
     <row r="152" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B152" s="4">
         <v>1</v>
       </c>
       <c r="C152" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D152" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>146</v>
+        <v>908</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>634</v>
+        <v>744</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>615</v>
+        <v>562</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M152" s="24" t="s">
-        <v>290</v>
+        <v>274</v>
+      </c>
+      <c r="M152" s="24">
+        <v>750</v>
       </c>
       <c r="N152" s="2" t="s">
         <v>268</v>
@@ -9643,31 +9639,31 @@
     </row>
     <row r="153" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B153" s="4">
         <v>1</v>
       </c>
       <c r="C153" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D153" s="4">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>615</v>
@@ -9684,7 +9680,7 @@
     </row>
     <row r="154" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>917</v>
+        <v>173</v>
       </c>
       <c r="B154" s="4">
         <v>1</v>
@@ -9693,13 +9689,13 @@
         <v>5500</v>
       </c>
       <c r="D154" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>918</v>
+        <v>174</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>125</v>
@@ -9708,37 +9704,39 @@
         <v>175</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>919</v>
+        <v>635</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>920</v>
+        <v>615</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M154" s="24"/>
+        <v>288</v>
+      </c>
+      <c r="M154" s="24" t="s">
+        <v>290</v>
+      </c>
       <c r="N154" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>249</v>
+        <v>917</v>
       </c>
       <c r="B155" s="4">
         <v>1</v>
       </c>
       <c r="C155" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D155" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>252</v>
+        <v>918</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>125</v>
@@ -9747,57 +9745,55 @@
         <v>175</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>636</v>
+        <v>919</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>605</v>
+        <v>920</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M155" s="24" t="s">
-        <v>270</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M155" s="24"/>
       <c r="N155" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>765</v>
+        <v>249</v>
       </c>
       <c r="B156" s="4">
         <v>1</v>
       </c>
       <c r="C156" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D156" s="4">
         <v>4000</v>
       </c>
-      <c r="D156" s="4">
-        <v>2000</v>
-      </c>
       <c r="E156" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>767</v>
+        <v>252</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>810</v>
+        <v>636</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>688</v>
+        <v>605</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M156" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M156" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N156" s="2" t="s">
         <v>268</v>
@@ -9805,22 +9801,22 @@
     </row>
     <row r="157" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B157" s="4">
         <v>1</v>
       </c>
       <c r="C157" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D157" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>818</v>
+        <v>767</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>125</v>
@@ -9829,39 +9825,39 @@
         <v>178</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>597</v>
+        <v>688</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>261</v>
+        <v>516</v>
       </c>
       <c r="M157" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>176</v>
+        <v>766</v>
       </c>
       <c r="B158" s="4">
         <v>1</v>
       </c>
       <c r="C158" s="4">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="D158" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>177</v>
+        <v>818</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>125</v>
@@ -9870,55 +9866,57 @@
         <v>178</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M158" s="24" t="s">
-        <v>290</v>
+        <v>261</v>
+      </c>
+      <c r="M158" s="24">
+        <v>100</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B159" s="4">
         <v>1</v>
       </c>
       <c r="C159" s="4">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="D159" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H159" s="4"/>
+      <c r="H159" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J159" s="2" t="s">
-        <v>637</v>
+        <v>808</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>565</v>
+        <v>615</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="M159" s="24" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N159" s="2" t="s">
         <v>268</v>
@@ -9926,167 +9924,165 @@
     </row>
     <row r="160" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B160" s="4">
         <v>1</v>
       </c>
       <c r="C160" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D160" s="4">
         <v>4000</v>
-      </c>
-      <c r="D160" s="4">
-        <v>2000</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H160" s="4"/>
       <c r="J160" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>639</v>
+        <v>565</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>519</v>
+        <v>277</v>
       </c>
       <c r="M160" s="24" t="s">
-        <v>521</v>
+        <v>278</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="161" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B161" s="4">
         <v>1</v>
       </c>
       <c r="C161" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D161" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H161" s="4"/>
       <c r="J161" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>565</v>
+        <v>639</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>277</v>
+        <v>519</v>
       </c>
       <c r="M161" s="24" t="s">
-        <v>278</v>
+        <v>521</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="162" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B162" s="4">
         <v>1</v>
       </c>
       <c r="C162" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D162" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F162" s="7" t="s">
-        <v>186</v>
+      <c r="F162" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H162" s="4" t="s">
-        <v>154</v>
-      </c>
+      <c r="H162" s="4"/>
       <c r="J162" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>607</v>
+        <v>565</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M162" s="24">
-        <v>100</v>
+        <v>277</v>
+      </c>
+      <c r="M162" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="163" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B163" s="4">
         <v>1</v>
       </c>
       <c r="C163" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D163" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>188</v>
+        <v>8</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M163" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="164" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B164" s="4">
         <v>1</v>
@@ -10101,23 +10097,25 @@
         <v>19</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H164" s="4"/>
+      <c r="H164" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="J164" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>644</v>
+        <v>567</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>516</v>
+        <v>297</v>
       </c>
       <c r="M164" s="24">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>268</v>
@@ -10125,7 +10123,7 @@
     </row>
     <row r="165" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B165" s="4">
         <v>1</v>
@@ -10140,94 +10138,92 @@
         <v>19</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H165" s="4"/>
       <c r="J165" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M165" s="24"/>
+        <v>516</v>
+      </c>
+      <c r="M165" s="24">
+        <v>200</v>
+      </c>
       <c r="N165" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="166" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B166" s="4">
         <v>1</v>
       </c>
       <c r="C166" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D166" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H166" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="H166" s="4"/>
       <c r="J166" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M166" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M166" s="24"/>
       <c r="N166" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="167" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>903</v>
+        <v>193</v>
       </c>
       <c r="B167" s="4">
         <v>1</v>
       </c>
       <c r="C167" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D167" s="4">
         <v>3000</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>904</v>
+        <v>194</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>905</v>
+        <v>647</v>
       </c>
       <c r="K167" s="2" t="s">
         <v>615</v>
@@ -10244,40 +10240,40 @@
     </row>
     <row r="168" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>196</v>
+        <v>903</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
       </c>
       <c r="C168" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D168" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>197</v>
+        <v>904</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>648</v>
+        <v>905</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M168" s="24">
-        <v>1000</v>
+        <v>288</v>
+      </c>
+      <c r="M168" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N168" s="2" t="s">
         <v>268</v>
@@ -10285,40 +10281,40 @@
     </row>
     <row r="169" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B169" s="4">
         <v>1</v>
       </c>
       <c r="C169" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D169" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>855</v>
+        <v>198</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>567</v>
+        <v>649</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="M169" s="24">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>268</v>
@@ -10326,13 +10322,13 @@
     </row>
     <row r="170" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>819</v>
+        <v>199</v>
       </c>
       <c r="B170" s="4">
         <v>1</v>
       </c>
       <c r="C170" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D170" s="4">
         <v>3000</v>
@@ -10341,28 +10337,25 @@
         <v>22</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>820</v>
+        <v>200</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I170" t="s">
-        <v>822</v>
+        <v>855</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>821</v>
+        <v>650</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>649</v>
+        <v>567</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="M170" s="24">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="N170" s="2" t="s">
         <v>268</v>
@@ -10370,22 +10363,22 @@
     </row>
     <row r="171" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>201</v>
+        <v>819</v>
       </c>
       <c r="B171" s="4">
         <v>1</v>
       </c>
       <c r="C171" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D171" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>202</v>
+        <v>820</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>125</v>
@@ -10393,17 +10386,20 @@
       <c r="H171" s="4" t="s">
         <v>178</v>
       </c>
+      <c r="I171" t="s">
+        <v>822</v>
+      </c>
       <c r="J171" s="2" t="s">
-        <v>651</v>
+        <v>821</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>516</v>
+        <v>264</v>
       </c>
       <c r="M171" s="24">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="N171" s="2" t="s">
         <v>268</v>
@@ -10411,7 +10407,7 @@
     </row>
     <row r="172" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B172" s="4">
         <v>1</v>
@@ -10423,26 +10419,28 @@
         <v>2500</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H172" s="4"/>
+      <c r="H172" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J172" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M172" s="24" t="s">
-        <v>290</v>
+        <v>516</v>
+      </c>
+      <c r="M172" s="24">
+        <v>200</v>
       </c>
       <c r="N172" s="2" t="s">
         <v>268</v>
@@ -10450,31 +10448,29 @@
     </row>
     <row r="173" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B173" s="4">
         <v>1</v>
       </c>
       <c r="C173" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D173" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H173" s="4" t="s">
-        <v>146</v>
-      </c>
+      <c r="H173" s="4"/>
       <c r="J173" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>615</v>
@@ -10491,38 +10487,40 @@
     </row>
     <row r="174" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B174" s="4">
         <v>1</v>
       </c>
       <c r="C174" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D174" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H174" s="4"/>
+      <c r="H174" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="J174" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="M174" s="24" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>268</v>
@@ -10530,7 +10528,7 @@
     </row>
     <row r="175" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B175" s="4">
         <v>1</v>
@@ -10542,58 +10540,58 @@
         <v>2500</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H175" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H175" s="4"/>
       <c r="J175" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M175" s="24">
-        <v>100</v>
+        <v>277</v>
+      </c>
+      <c r="M175" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="176" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B176" s="4">
         <v>1</v>
       </c>
       <c r="C176" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D176" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H176" s="4"/>
+      <c r="H176" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J176" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="K176" s="2" t="s">
         <v>657</v>
@@ -10610,79 +10608,77 @@
     </row>
     <row r="177" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B177" s="4">
         <v>1</v>
       </c>
       <c r="C177" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D177" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H177" s="4"/>
       <c r="J177" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>567</v>
+        <v>657</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M177" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="178" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B178" s="4">
         <v>1</v>
       </c>
       <c r="C178" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D178" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H178" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="H178" s="4"/>
       <c r="J178" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>661</v>
+        <v>567</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M178" s="24" t="s">
-        <v>290</v>
+        <v>297</v>
+      </c>
+      <c r="M178" s="24">
+        <v>2</v>
       </c>
       <c r="N178" s="2" t="s">
         <v>268</v>
@@ -10690,38 +10686,40 @@
     </row>
     <row r="179" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B179" s="4">
         <v>1</v>
       </c>
       <c r="C179" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D179" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H179" s="4"/>
+      <c r="H179" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="J179" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M179" s="24">
-        <v>200</v>
+        <v>288</v>
+      </c>
+      <c r="M179" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>268</v>
@@ -10729,118 +10727,118 @@
     </row>
     <row r="180" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B180" s="4">
         <v>1</v>
       </c>
       <c r="C180" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D180" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H180" s="4"/>
       <c r="J180" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M180" s="24" t="s">
-        <v>521</v>
+        <v>516</v>
+      </c>
+      <c r="M180" s="24">
+        <v>200</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="181" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B181" s="4">
         <v>1</v>
       </c>
       <c r="C181" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D181" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H181" s="4" t="s">
-        <v>146</v>
-      </c>
+      <c r="H181" s="4"/>
       <c r="J181" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>269</v>
+        <v>519</v>
       </c>
       <c r="M181" s="24" t="s">
-        <v>270</v>
+        <v>521</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="182" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B182" s="4">
         <v>1</v>
       </c>
       <c r="C182" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D182" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H182" s="4"/>
+      <c r="H182" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="J182" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M182" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M182" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>268</v>
@@ -10848,147 +10846,147 @@
     </row>
     <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B183" s="4">
         <v>1</v>
       </c>
       <c r="C183" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D183" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H183" s="4"/>
       <c r="J183" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M183" s="24"/>
+        <v>516</v>
+      </c>
+      <c r="M183" s="24">
+        <v>200</v>
+      </c>
       <c r="N183" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B184" s="4">
         <v>1</v>
       </c>
       <c r="C184" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D184" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H184" s="4"/>
       <c r="J184" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M184" s="24" t="s">
-        <v>521</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M184" s="24"/>
       <c r="N184" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B185" s="4">
         <v>1</v>
       </c>
       <c r="C185" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D185" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H185" s="4"/>
       <c r="J185" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>269</v>
+        <v>519</v>
       </c>
       <c r="M185" s="24" t="s">
-        <v>270</v>
+        <v>521</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B186" s="4">
         <v>1</v>
       </c>
       <c r="C186" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D186" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H186" s="4"/>
       <c r="J186" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="L186" s="2" t="s">
         <v>269</v>
@@ -11002,7 +11000,7 @@
     </row>
     <row r="187" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B187" s="4">
         <v>1</v>
@@ -11011,31 +11009,29 @@
         <v>5000</v>
       </c>
       <c r="D187" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H187" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H187" s="4"/>
       <c r="J187" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M187" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M187" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>268</v>
@@ -11043,38 +11039,40 @@
     </row>
     <row r="188" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B188" s="4">
         <v>1</v>
       </c>
       <c r="C188" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D188" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H188" s="4"/>
+      <c r="H188" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J188" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>673</v>
+        <v>644</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M188" s="24" t="s">
-        <v>270</v>
+        <v>516</v>
+      </c>
+      <c r="M188" s="24">
+        <v>200</v>
       </c>
       <c r="N188" s="2" t="s">
         <v>268</v>
@@ -11082,235 +11080,235 @@
     </row>
     <row r="189" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
       </c>
       <c r="C189" s="4">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="D189" s="4">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H189" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="H189" s="4"/>
       <c r="J189" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M189" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M189" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="190" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B190" s="4">
         <v>1</v>
       </c>
       <c r="C190" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D190" s="4">
         <v>3500</v>
-      </c>
-      <c r="D190" s="4">
-        <v>2000</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>242</v>
+      <c r="F190" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H190" s="4"/>
+      <c r="H190" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="J190" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>679</v>
+        <v>657</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M190" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="191" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>852</v>
+        <v>241</v>
       </c>
       <c r="B191" s="4">
         <v>1</v>
       </c>
       <c r="C191" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D191" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>853</v>
+        <v>242</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H191" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="J191" s="14" t="s">
-        <v>859</v>
-      </c>
-      <c r="K191" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L191" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M191" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N191" s="14" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H191" s="4"/>
+      <c r="J191" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="M191" s="24">
+        <v>2</v>
+      </c>
+      <c r="N191" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>378</v>
+        <v>852</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
       </c>
       <c r="C192" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D192" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>430</v>
+        <v>8</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>853</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H192" s="4"/>
-      <c r="J192" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="K192" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="L192" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M192" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="N192" s="2" t="s">
-        <v>268</v>
+      <c r="H192" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="J192" s="14" t="s">
+        <v>859</v>
+      </c>
+      <c r="K192" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L192" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M192" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N192" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>915</v>
+        <v>378</v>
       </c>
       <c r="B193" s="4">
         <v>1</v>
       </c>
       <c r="C193" s="4">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="D193" s="4">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>916</v>
+        <v>430</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H193" s="4"/>
-      <c r="J193" s="2"/>
-      <c r="K193" s="2"/>
-      <c r="L193" s="2"/>
-      <c r="M193" s="24"/>
-      <c r="N193" s="2"/>
+      <c r="J193" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M193" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="N193" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>379</v>
+        <v>915</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
       </c>
       <c r="C194" s="4">
-        <v>5500</v>
+        <v>2500</v>
       </c>
       <c r="D194" s="4">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>431</v>
+        <v>916</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H194" s="4"/>
-      <c r="J194" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="K194" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="L194" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M194" s="24">
-        <v>100</v>
-      </c>
-      <c r="N194" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
+      <c r="M194" s="24"/>
+      <c r="N194" s="2"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B195" s="4">
         <v>1</v>
@@ -11319,115 +11317,115 @@
         <v>5500</v>
       </c>
       <c r="D195" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H195" s="4"/>
       <c r="J195" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>605</v>
+        <v>552</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M195" s="24" t="s">
-        <v>270</v>
+        <v>261</v>
+      </c>
+      <c r="M195" s="24">
+        <v>100</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B196" s="4">
         <v>1</v>
       </c>
       <c r="C196" s="4">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="D196" s="4">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H196" s="4"/>
       <c r="J196" s="2" t="s">
-        <v>630</v>
+        <v>683</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>548</v>
+        <v>605</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M196" s="24">
-        <v>50</v>
+        <v>269</v>
+      </c>
+      <c r="M196" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B197" s="4">
         <v>1</v>
       </c>
       <c r="C197" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D197" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H197" s="4"/>
       <c r="J197" s="2" t="s">
-        <v>684</v>
+        <v>630</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>615</v>
+        <v>548</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M197" s="24" t="s">
-        <v>290</v>
+        <v>275</v>
+      </c>
+      <c r="M197" s="24">
+        <v>50</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B198" s="4">
         <v>1</v>
@@ -11436,76 +11434,76 @@
         <v>3000</v>
       </c>
       <c r="D198" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H198" s="4"/>
       <c r="J198" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M198" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M198" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B199" s="4">
         <v>1</v>
       </c>
       <c r="C199" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D199" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H199" s="4"/>
       <c r="J199" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M199" s="24" t="s">
-        <v>270</v>
+        <v>260</v>
+      </c>
+      <c r="M199" s="24">
+        <v>100</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B200" s="4">
         <v>1</v>
@@ -11520,23 +11518,23 @@
         <v>19</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H200" s="4"/>
       <c r="J200" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>688</v>
+        <v>605</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M200" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M200" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N200" s="2" t="s">
         <v>268</v>
@@ -11544,38 +11542,38 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B201" s="4">
         <v>1</v>
       </c>
       <c r="C201" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D201" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H201" s="4"/>
       <c r="J201" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>615</v>
+        <v>688</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M201" s="24" t="s">
-        <v>290</v>
+        <v>516</v>
+      </c>
+      <c r="M201" s="24">
+        <v>200</v>
       </c>
       <c r="N201" s="2" t="s">
         <v>268</v>
@@ -11583,165 +11581,163 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B202" s="4">
         <v>1</v>
       </c>
       <c r="C202" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D202" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H202" s="4"/>
       <c r="J202" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M202" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M202" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>797</v>
+        <v>387</v>
       </c>
       <c r="B203" s="4">
         <v>1</v>
       </c>
       <c r="C203" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D203" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>798</v>
+        <v>439</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H203" s="4"/>
-      <c r="J203" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="K203" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L203" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M203" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N203" s="14" t="s">
+      <c r="J203" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="M203" s="24">
+        <v>100</v>
+      </c>
+      <c r="N203" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>388</v>
+        <v>797</v>
       </c>
       <c r="B204" s="4">
         <v>1</v>
       </c>
       <c r="C204" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D204" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>440</v>
+        <v>798</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H204" s="4"/>
-      <c r="J204" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="K204" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="L204" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M204" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="N204" s="2" t="s">
-        <v>268</v>
+      <c r="J204" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="K204" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L204" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M204" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N204" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>878</v>
+        <v>388</v>
       </c>
       <c r="B205" s="4">
         <v>1</v>
       </c>
       <c r="C205" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D205" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>879</v>
+        <v>440</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H205" s="4" t="s">
-        <v>876</v>
-      </c>
+      <c r="H205" s="4"/>
       <c r="J205" s="2" t="s">
-        <v>880</v>
+        <v>691</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>548</v>
+        <v>615</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M205" s="24">
-        <v>50</v>
+        <v>288</v>
+      </c>
+      <c r="M205" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N205" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
@@ -11750,13 +11746,13 @@
         <v>4000</v>
       </c>
       <c r="D206" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>125</v>
@@ -11765,24 +11761,24 @@
         <v>876</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>666</v>
+        <v>548</v>
       </c>
       <c r="L206" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M206" s="24" t="s">
-        <v>270</v>
+        <v>275</v>
+      </c>
+      <c r="M206" s="24">
+        <v>50</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
@@ -11791,13 +11787,13 @@
         <v>4000</v>
       </c>
       <c r="D207" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>125</v>
@@ -11806,16 +11802,16 @@
         <v>876</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>615</v>
+        <v>666</v>
       </c>
       <c r="L207" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="M207" s="24" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="N207" s="2" t="s">
         <v>268</v>
@@ -11823,22 +11819,22 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
       </c>
       <c r="C208" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D208" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>125</v>
@@ -11846,40 +11842,40 @@
       <c r="H208" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="J208" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="K208" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L208" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M208" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N208" s="14" t="s">
-        <v>267</v>
+      <c r="J208" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M208" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="N208" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
       </c>
       <c r="C209" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D209" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>125</v>
@@ -11887,31 +11883,31 @@
       <c r="H209" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="J209" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="K209" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="L209" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M209" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="N209" s="2" t="s">
-        <v>268</v>
+      <c r="J209" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="K209" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L209" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M209" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N209" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
       </c>
       <c r="C210" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D210" s="4">
         <v>2000</v>
@@ -11920,7 +11916,7 @@
         <v>8</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>125</v>
@@ -11928,20 +11924,17 @@
       <c r="H210" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="I210" t="s">
-        <v>870</v>
-      </c>
       <c r="J210" s="2" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>688</v>
+        <v>655</v>
       </c>
       <c r="L210" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M210" s="24">
-        <v>200</v>
+        <v>277</v>
+      </c>
+      <c r="M210" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="N210" s="2" t="s">
         <v>268</v>
@@ -11949,22 +11942,22 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>389</v>
+        <v>866</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
       </c>
       <c r="C211" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D211" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>441</v>
+        <v>867</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>125</v>
@@ -11972,90 +11965,95 @@
       <c r="H211" s="4" t="s">
         <v>876</v>
       </c>
+      <c r="I211" t="s">
+        <v>870</v>
+      </c>
       <c r="J211" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>613</v>
+        <v>688</v>
       </c>
       <c r="L211" s="2" t="s">
-        <v>260</v>
+        <v>516</v>
       </c>
       <c r="M211" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N211" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>861</v>
+        <v>389</v>
       </c>
       <c r="B212" s="4">
         <v>1</v>
       </c>
       <c r="C212" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D212" s="4">
         <v>3000</v>
-      </c>
-      <c r="D212" s="4">
-        <v>1000</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>862</v>
+        <v>441</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>454</v>
+        <v>876</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="M212" s="24">
+        <v>100</v>
+      </c>
+      <c r="N212" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>390</v>
+        <v>861</v>
       </c>
       <c r="B213" s="4">
         <v>1</v>
       </c>
       <c r="C213" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D213" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>442</v>
+        <v>862</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H213" s="4"/>
-      <c r="J213" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="K213" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="L213" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M213" s="24">
-        <v>100</v>
-      </c>
-      <c r="N213" s="2" t="s">
-        <v>267</v>
+      <c r="H213" s="4" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B214" s="4">
         <v>1</v>
@@ -12070,23 +12068,23 @@
         <v>8</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H214" s="4"/>
       <c r="J214" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M214" s="24" t="s">
-        <v>521</v>
+        <v>261</v>
+      </c>
+      <c r="M214" s="24">
+        <v>100</v>
       </c>
       <c r="N214" s="2" t="s">
         <v>267</v>
@@ -12094,13 +12092,13 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B215" s="4">
         <v>1</v>
       </c>
       <c r="C215" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D215" s="4">
         <v>2500</v>
@@ -12109,99 +12107,99 @@
         <v>8</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H215" s="4"/>
       <c r="J215" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>587</v>
+        <v>639</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M215" s="24"/>
+        <v>519</v>
+      </c>
+      <c r="M215" s="24" t="s">
+        <v>521</v>
+      </c>
       <c r="N215" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="B216" s="4">
         <v>1</v>
       </c>
       <c r="C216" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D216" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H216" s="4"/>
       <c r="J216" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M216" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M216" s="24"/>
       <c r="N216" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B217" s="4">
         <v>1</v>
       </c>
       <c r="C217" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D217" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H217" s="4"/>
       <c r="J217" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M217" s="24" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N217" s="2" t="s">
         <v>268</v>
@@ -12209,38 +12207,38 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B218" s="4">
         <v>1</v>
       </c>
       <c r="C218" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D218" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H218" s="4"/>
       <c r="J218" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>698</v>
+        <v>605</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="M218" s="24" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="N218" s="2" t="s">
         <v>268</v>
@@ -12248,38 +12246,38 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B219" s="4">
         <v>1</v>
       </c>
       <c r="C219" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D219" s="4">
         <v>3500</v>
       </c>
-      <c r="D219" s="4">
-        <v>1500</v>
-      </c>
       <c r="E219" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H219" s="4"/>
       <c r="J219" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>644</v>
+        <v>698</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M219" s="24">
-        <v>200</v>
+        <v>288</v>
+      </c>
+      <c r="M219" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N219" s="2" t="s">
         <v>268</v>
@@ -12287,91 +12285,89 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B220" s="4">
         <v>1</v>
       </c>
       <c r="C220" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D220" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H220" s="4"/>
       <c r="J220" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M220" s="24"/>
+        <v>516</v>
+      </c>
+      <c r="M220" s="24">
+        <v>200</v>
+      </c>
       <c r="N220" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="B221" s="4">
         <v>1</v>
       </c>
       <c r="C221" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D221" s="4">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H221" s="4" t="s">
-        <v>454</v>
-      </c>
+      <c r="H221" s="4"/>
       <c r="J221" s="2" t="s">
-        <v>549</v>
+        <v>700</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M221" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M221" s="24"/>
       <c r="N221" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="B222" s="4">
         <v>1</v>
       </c>
       <c r="C222" s="4">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="D222" s="4">
         <v>3500</v>
@@ -12380,7 +12376,7 @@
         <v>8</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>125</v>
@@ -12389,16 +12385,16 @@
         <v>454</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>701</v>
+        <v>549</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M222" s="24" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N222" s="2" t="s">
         <v>268</v>
@@ -12406,74 +12402,76 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B223" s="4">
         <v>1</v>
       </c>
       <c r="C223" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D223" s="4">
         <v>3500</v>
       </c>
-      <c r="D223" s="4">
-        <v>1500</v>
-      </c>
       <c r="E223" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H223" s="4"/>
+      <c r="H223" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="J223" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>657</v>
+        <v>605</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M223" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M223" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B224" s="4">
         <v>1</v>
       </c>
       <c r="C224" s="4">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="D224" s="4">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H224" s="4"/>
       <c r="J224" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>576</v>
+        <v>657</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M224" s="24">
         <v>100</v>
@@ -12484,38 +12482,38 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B225" s="4">
         <v>1</v>
       </c>
       <c r="C225" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D225" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H225" s="4"/>
       <c r="J225" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K225" s="2" t="s">
-        <v>639</v>
+        <v>576</v>
       </c>
       <c r="L225" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M225" s="24" t="s">
-        <v>521</v>
+        <v>260</v>
+      </c>
+      <c r="M225" s="24">
+        <v>100</v>
       </c>
       <c r="N225" s="2" t="s">
         <v>267</v>
@@ -12523,46 +12521,46 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B226" s="4">
         <v>1</v>
       </c>
       <c r="C226" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D226" s="4">
         <v>3000</v>
       </c>
-      <c r="D226" s="4">
-        <v>1000</v>
-      </c>
       <c r="E226" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H226" s="4"/>
       <c r="J226" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M226" s="24">
-        <v>200</v>
+        <v>519</v>
+      </c>
+      <c r="M226" s="24" t="s">
+        <v>521</v>
       </c>
       <c r="N226" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B227" s="4">
         <v>1</v>
@@ -12577,29 +12575,31 @@
         <v>19</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H227" s="4"/>
       <c r="J227" s="2" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M227" s="24"/>
+        <v>516</v>
+      </c>
+      <c r="M227" s="24">
+        <v>200</v>
+      </c>
       <c r="N227" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B228" s="4">
         <v>1</v>
@@ -12611,90 +12611,86 @@
         <v>1000</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H228" s="4"/>
       <c r="J228" s="2" t="s">
-        <v>706</v>
+        <v>668</v>
       </c>
       <c r="K228" s="2" t="s">
-        <v>615</v>
+        <v>669</v>
       </c>
       <c r="L228" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M228" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M228" s="24"/>
       <c r="N228" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B229" s="4">
         <v>1</v>
       </c>
       <c r="C229" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D229" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H229" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H229" s="4"/>
       <c r="J229" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>644</v>
+        <v>615</v>
       </c>
       <c r="L229" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M229" s="24">
-        <v>200</v>
+        <v>288</v>
+      </c>
+      <c r="M229" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N229" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B230" s="4">
         <v>1</v>
       </c>
       <c r="C230" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D230" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>125</v>
@@ -12703,24 +12699,24 @@
         <v>178</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M230" s="24" t="s">
-        <v>278</v>
+        <v>516</v>
+      </c>
+      <c r="M230" s="24">
+        <v>200</v>
       </c>
       <c r="N230" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B231" s="4">
         <v>1</v>
@@ -12735,23 +12731,25 @@
         <v>22</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>748</v>
+        <v>462</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H231" s="4"/>
+      <c r="H231" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J231" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>615</v>
+        <v>655</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M231" s="24" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="N231" s="2" t="s">
         <v>268</v>
@@ -12759,41 +12757,38 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B232" s="4">
         <v>1</v>
       </c>
       <c r="C232" s="4">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D232" s="4">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>901</v>
+        <v>748</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H232" s="4"/>
-      <c r="I232" t="s">
-        <v>902</v>
-      </c>
       <c r="J232" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M232" s="24" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N232" s="2" t="s">
         <v>268</v>
@@ -12801,38 +12796,41 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B233" s="4">
         <v>1</v>
       </c>
       <c r="C233" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D233" s="4">
         <v>5000</v>
-      </c>
-      <c r="D233" s="4">
-        <v>3000</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>463</v>
+        <v>901</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H233" s="4"/>
+      <c r="I233" t="s">
+        <v>902</v>
+      </c>
       <c r="J233" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>712</v>
+        <v>605</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="M233" s="24">
-        <v>1</v>
+        <v>269</v>
+      </c>
+      <c r="M233" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N233" s="2" t="s">
         <v>268</v>
@@ -12840,7 +12838,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B234" s="4">
         <v>1</v>
@@ -12852,28 +12850,26 @@
         <v>3000</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H234" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H234" s="4"/>
       <c r="J234" s="2" t="s">
-        <v>635</v>
+        <v>711</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>615</v>
+        <v>712</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M234" s="24" t="s">
-        <v>290</v>
+        <v>263</v>
+      </c>
+      <c r="M234" s="24">
+        <v>1</v>
       </c>
       <c r="N234" s="2" t="s">
         <v>268</v>
@@ -12881,7 +12877,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B235" s="4">
         <v>1</v>
@@ -12896,7 +12892,7 @@
         <v>8</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>125</v>
@@ -12905,7 +12901,7 @@
         <v>175</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>713</v>
+        <v>635</v>
       </c>
       <c r="K235" s="2" t="s">
         <v>615</v>
@@ -12922,77 +12918,79 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>181</v>
+        <v>410</v>
       </c>
       <c r="B236" s="4">
         <v>1</v>
       </c>
       <c r="C236" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D236" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H236" s="4"/>
+      <c r="H236" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J236" s="2" t="s">
-        <v>638</v>
+        <v>713</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>664</v>
+        <v>615</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>519</v>
+        <v>288</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>521</v>
+        <v>290</v>
       </c>
       <c r="N236" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>412</v>
+        <v>181</v>
       </c>
       <c r="B237" s="4">
         <v>1</v>
       </c>
       <c r="C237" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D237" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>747</v>
+        <v>466</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H237" s="4"/>
       <c r="J237" s="2" t="s">
-        <v>714</v>
+        <v>638</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M237" s="24">
-        <v>100</v>
+        <v>519</v>
+      </c>
+      <c r="M237" s="24" t="s">
+        <v>521</v>
       </c>
       <c r="N237" s="2" t="s">
         <v>267</v>
@@ -13000,7 +12998,7 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B238" s="4">
         <v>1</v>
@@ -13012,51 +13010,49 @@
         <v>2500</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>467</v>
+        <v>747</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H238" s="4" t="s">
-        <v>468</v>
-      </c>
+      <c r="H238" s="4"/>
       <c r="J238" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>567</v>
+        <v>657</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M238" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="239" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B239" s="4">
         <v>1</v>
       </c>
       <c r="C239" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D239" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>125</v>
@@ -13065,39 +13061,39 @@
         <v>468</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>606</v>
+        <v>715</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>657</v>
+        <v>567</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="M239" s="24">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B240" s="4">
         <v>1</v>
       </c>
       <c r="C240" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D240" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E240" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>125</v>
@@ -13106,7 +13102,7 @@
         <v>468</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>553</v>
+        <v>606</v>
       </c>
       <c r="K240" s="2" t="s">
         <v>657</v>
@@ -13121,9 +13117,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B241" s="4">
         <v>1</v>
@@ -13138,7 +13134,7 @@
         <v>8</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>125</v>
@@ -13147,39 +13143,39 @@
         <v>468</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>716</v>
+        <v>553</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L241" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M241" s="24" t="s">
-        <v>278</v>
+        <v>261</v>
+      </c>
+      <c r="M241" s="24">
+        <v>100</v>
       </c>
       <c r="N241" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B242" s="4">
         <v>1</v>
       </c>
       <c r="C242" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D242" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>125</v>
@@ -13188,16 +13184,16 @@
         <v>468</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>718</v>
+        <v>655</v>
       </c>
       <c r="L242" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M242" s="24" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="N242" s="2" t="s">
         <v>268</v>
@@ -13205,40 +13201,40 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B243" s="4">
         <v>1</v>
       </c>
       <c r="C243" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D243" s="4">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>175</v>
+        <v>468</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>615</v>
+        <v>718</v>
       </c>
       <c r="L243" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="M243" s="24" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="N243" s="2" t="s">
         <v>268</v>
@@ -13246,13 +13242,13 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B244" s="4">
         <v>1</v>
       </c>
       <c r="C244" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D244" s="4">
         <v>3500</v>
@@ -13261,7 +13257,7 @@
         <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>743</v>
+        <v>473</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>125</v>
@@ -13270,7 +13266,7 @@
         <v>175</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="K244" s="2" t="s">
         <v>615</v>
@@ -13285,48 +13281,50 @@
         <v>268</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B245" s="4">
         <v>1</v>
       </c>
       <c r="C245" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D245" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>474</v>
+        <v>743</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H245" s="4"/>
+      <c r="H245" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J245" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="L245" s="2" t="s">
-        <v>519</v>
+        <v>288</v>
       </c>
       <c r="M245" s="24" t="s">
-        <v>521</v>
+        <v>290</v>
       </c>
       <c r="N245" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B246" s="4">
         <v>1</v>
@@ -13335,68 +13333,68 @@
         <v>4000</v>
       </c>
       <c r="D246" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E246" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H246" s="4"/>
       <c r="J246" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>723</v>
+        <v>671</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M246" s="24">
-        <v>2</v>
+        <v>519</v>
+      </c>
+      <c r="M246" s="24" t="s">
+        <v>521</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>921</v>
+        <v>421</v>
       </c>
       <c r="B247" s="4">
         <v>1</v>
       </c>
       <c r="C247" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D247" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H247" s="4"/>
       <c r="J247" s="2" t="s">
-        <v>665</v>
+        <v>722</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M247" s="24" t="s">
-        <v>270</v>
+        <v>297</v>
+      </c>
+      <c r="M247" s="24">
+        <v>2</v>
       </c>
       <c r="N247" s="2" t="s">
         <v>268</v>
@@ -13404,40 +13402,38 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>422</v>
+        <v>921</v>
       </c>
       <c r="B248" s="4">
         <v>1</v>
       </c>
       <c r="C248" s="4">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="D248" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H248" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H248" s="4"/>
       <c r="J248" s="2" t="s">
-        <v>724</v>
+        <v>665</v>
       </c>
       <c r="K248" s="2" t="s">
-        <v>615</v>
+        <v>718</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="M248" s="24" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="N248" s="2" t="s">
         <v>268</v>
@@ -13445,46 +13441,48 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B249" s="4">
         <v>1</v>
       </c>
       <c r="C249" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D249" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H249" s="4"/>
+      <c r="H249" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J249" s="2" t="s">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>657</v>
+        <v>615</v>
       </c>
       <c r="L249" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M249" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M249" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N249" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B250" s="4">
         <v>1</v>
@@ -13496,34 +13494,34 @@
         <v>2500</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H250" s="4"/>
       <c r="J250" s="2" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>562</v>
+        <v>657</v>
       </c>
       <c r="L250" s="2" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="M250" s="24">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="N250" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B251" s="4">
         <v>1</v>
@@ -13535,32 +13533,34 @@
         <v>2500</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H251" s="4"/>
       <c r="J251" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="L251" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M251" s="24"/>
+        <v>274</v>
+      </c>
+      <c r="M251" s="24">
+        <v>750</v>
+      </c>
       <c r="N251" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B252" s="4">
         <v>1</v>
@@ -13569,76 +13569,113 @@
         <v>4500</v>
       </c>
       <c r="D252" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H252" s="4"/>
       <c r="J252" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="K252" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M252" s="24"/>
+      <c r="N252" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B253" s="4">
+        <v>1</v>
+      </c>
+      <c r="C253" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D253" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H253" s="4"/>
+      <c r="J253" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="K252" s="2" t="s">
+      <c r="K253" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="L252" s="2" t="s">
+      <c r="L253" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M252" s="24" t="s">
+      <c r="M253" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="N252" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" s="26" t="s">
+      <c r="N253" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A254" s="26" t="s">
         <v>762</v>
       </c>
-      <c r="B253" s="26">
-        <v>1</v>
-      </c>
-      <c r="C253" s="26">
+      <c r="B254" s="26">
+        <v>1</v>
+      </c>
+      <c r="C254" s="26">
         <v>5000</v>
       </c>
-      <c r="D253" s="26">
+      <c r="D254" s="26">
         <v>3000</v>
       </c>
-      <c r="E253" s="26" t="s">
+      <c r="E254" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F253" s="4" t="s">
+      <c r="F254" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="G253" s="26" t="s">
+      <c r="G254" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="H253" s="4"/>
-      <c r="J253" s="14" t="s">
+      <c r="H254" s="4"/>
+      <c r="J254" s="14" t="s">
         <v>764</v>
       </c>
-      <c r="K253" s="14" t="s">
+      <c r="K254" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L253" s="14" t="s">
+      <c r="L254" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="M253" s="14" t="s">
+      <c r="M254" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="N253" s="14" t="s">
+      <c r="N254" s="14" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N252" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="C192:C252">
+  <autoFilter ref="A1:N253" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="C193:C253">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -13650,7 +13687,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C253:C1048576 C2:C191">
+  <conditionalFormatting sqref="C254:C1048576 C2:C192">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -13662,7 +13699,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D192:D252">
+  <conditionalFormatting sqref="D193:D253">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -13674,7 +13711,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D253:D1048576 D2:D191">
+  <conditionalFormatting sqref="D254:D1048576 D2:D192">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
@@ -13686,7 +13723,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:N211">
+  <conditionalFormatting sqref="J2:N212">
     <cfRule type="expression" dxfId="11" priority="7">
       <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
     </cfRule>
@@ -13706,24 +13743,24 @@
       <formula>OR($L2="extra_attack",$L2="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J213:N253">
+  <conditionalFormatting sqref="J214:N254">
     <cfRule type="expression" dxfId="5" priority="37">
-      <formula>OR($L213="debuff",$L213="bonus_debuff",$L213="revive")</formula>
+      <formula>OR($L214="debuff",$L214="bonus_debuff",$L214="revive")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="38">
-      <formula>OR($L213="buff",$L213="bonus_buff")</formula>
+      <formula>OR($L214="buff",$L214="bonus_buff")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="39">
-      <formula>OR($L213="dot",$L213="stun")</formula>
+      <formula>OR($L214="dot",$L214="stun")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="40">
-      <formula>OR($L213="tank",$L213="shield")</formula>
+      <formula>OR($L214="tank",$L214="shield")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="41">
-      <formula>OR($L213="heal",$L213="heal_all",$L213="life_steal")</formula>
+      <formula>OR($L214="heal",$L214="heal_all",$L214="life_steal")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="42">
-      <formula>OR($L213="extra_attack",$L213="aoe")</formula>
+      <formula>OR($L214="extra_attack",$L214="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -13740,12 +13777,12 @@
     <hyperlink ref="F38" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="F45" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="F53" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F158" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F162" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F137" r:id="rId16" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
-    <hyperlink ref="F132" r:id="rId17" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
-    <hyperlink ref="F155" r:id="rId18" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
-    <hyperlink ref="F131" r:id="rId19" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
+    <hyperlink ref="F159" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F163" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F138" r:id="rId16" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
+    <hyperlink ref="F133" r:id="rId17" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
+    <hyperlink ref="F156" r:id="rId18" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
+    <hyperlink ref="F132" r:id="rId19" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
     <hyperlink ref="F30" r:id="rId20" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
     <hyperlink ref="F78" r:id="rId21" xr:uid="{8B8635A9-7759-45CB-8B60-1697B5FF9938}"/>
     <hyperlink ref="F54" r:id="rId22" xr:uid="{FAF75EE9-F39E-499A-ACD1-703CCBD91506}"/>
@@ -13785,22 +13822,22 @@
     <hyperlink ref="F111" r:id="rId56" xr:uid="{0BE12A25-88E9-40D7-B6CF-F734F050661F}"/>
     <hyperlink ref="F20" r:id="rId57" xr:uid="{BABB0F5C-56BD-4A07-93B3-021E469232CD}"/>
     <hyperlink ref="F32" r:id="rId58" xr:uid="{61098037-76F4-4673-81EC-2C0BEA11F28D}"/>
-    <hyperlink ref="F192" r:id="rId59" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
-    <hyperlink ref="F194" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
-    <hyperlink ref="F195" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
-    <hyperlink ref="F196" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
-    <hyperlink ref="F199" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
-    <hyperlink ref="F200" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
-    <hyperlink ref="F201" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
-    <hyperlink ref="F231" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
-    <hyperlink ref="F233" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
-    <hyperlink ref="F252" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
-    <hyperlink ref="F244" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
-    <hyperlink ref="F237" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
+    <hyperlink ref="F193" r:id="rId59" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
+    <hyperlink ref="F195" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
+    <hyperlink ref="F196" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
+    <hyperlink ref="F197" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
+    <hyperlink ref="F200" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
+    <hyperlink ref="F201" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
+    <hyperlink ref="F202" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
+    <hyperlink ref="F232" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
+    <hyperlink ref="F234" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
+    <hyperlink ref="F253" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
+    <hyperlink ref="F245" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
+    <hyperlink ref="F238" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
     <hyperlink ref="F116" r:id="rId71" xr:uid="{163A63BB-52A6-4D6C-B00A-1A7F1F28061D}"/>
     <hyperlink ref="F15" r:id="rId72" xr:uid="{C439613B-BEC0-48C5-814E-36E868E99B31}"/>
     <hyperlink ref="F93" r:id="rId73" xr:uid="{7E273EDB-40F6-4371-AC08-0F1FA586E40C}"/>
-    <hyperlink ref="F208" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
+    <hyperlink ref="F209" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
     <hyperlink ref="I94" r:id="rId75" xr:uid="{FE3AAB39-C871-4F64-AA22-E89C4CD15539}"/>
     <hyperlink ref="F89" r:id="rId76" xr:uid="{3D7B2B26-3280-40AF-A4C5-1389477FB9D2}"/>
   </hyperlinks>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CEEE0E-A733-4B10-A77A-548348CE4882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F2E8A1-5903-43E3-8852-8767327BA05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="946">
   <si>
     <t>Nombre</t>
   </si>
@@ -2858,6 +2858,9 @@
   </si>
   <si>
     <t>https://i.ibb.co/20HYnX6v/Adamstrange.webp</t>
+  </si>
+  <si>
+    <t>Estimulante neuronal</t>
   </si>
 </sst>
 </file>
@@ -7734,7 +7737,7 @@
         <v>262</v>
       </c>
       <c r="M105" s="12">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="N105" s="12" t="s">
         <v>268</v>
@@ -8388,11 +8391,21 @@
       <c r="H121" s="10" t="s">
         <v>922</v>
       </c>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
-      <c r="L121" s="2"/>
-      <c r="M121" s="24"/>
-      <c r="N121" s="2"/>
+      <c r="J121" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="K121" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="L121" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="M121" s="12">
+        <v>1000</v>
+      </c>
+      <c r="N121" s="12" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="122" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F2E8A1-5903-43E3-8852-8767327BA05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93707D17-9865-484A-A6FE-18A075A3740B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93707D17-9865-484A-A6FE-18A075A3740B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C31A7-60AD-4B70-BE8D-C0BCE71668AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C31A7-60AD-4B70-BE8D-C0BCE71668AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC11D6DC-86C6-411F-83DF-BE079354D21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1345,9 +1345,6 @@
     <t>https://i.pinimg.com/736x/b8/ff/6d/b8ff6d771307cdfa3526bf5a55e8d407.jpg</t>
   </si>
   <si>
-    <t>https://i.pinimg.com/736x/07/7b/04/077b0409d32d20546af2b67a666d7a0d.jpg</t>
-  </si>
-  <si>
     <t>https://i.pinimg.com/736x/65/d2/21/65d221b257b9f7c1cfff9f3cedf471d2.jpg</t>
   </si>
   <si>
@@ -2861,6 +2858,9 @@
   </si>
   <si>
     <t>Estimulante neuronal</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/gMyfKdh3/Giganta-035.webp</t>
   </si>
 </sst>
 </file>
@@ -3531,10 +3531,10 @@
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>288</v>
@@ -3573,10 +3573,10 @@
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="22" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L3" s="22" t="s">
         <v>275</v>
@@ -3615,10 +3615,10 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>269</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>283</v>
@@ -3697,10 +3697,10 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L6" s="15" t="s">
         <v>264</v>
@@ -3739,10 +3739,10 @@
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>500</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>501</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>288</v>
@@ -3781,10 +3781,10 @@
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="K8" s="12" t="s">
         <v>504</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>505</v>
       </c>
       <c r="L8" s="12" t="s">
         <v>260</v>
@@ -3823,10 +3823,10 @@
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="K9" s="14" t="s">
         <v>502</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>503</v>
       </c>
       <c r="L9" s="14" t="s">
         <v>261</v>
@@ -3855,20 +3855,20 @@
         <v>8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>288</v>
@@ -3907,10 +3907,10 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>523</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>524</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>288</v>
@@ -3949,10 +3949,10 @@
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>525</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>526</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>269</v>
@@ -4027,13 +4027,13 @@
         <v>10</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>289</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>288</v>
@@ -4062,19 +4062,19 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>285</v>
@@ -4115,7 +4115,7 @@
         <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>282</v>
@@ -4157,7 +4157,7 @@
         <v>47</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>266</v>
@@ -4198,7 +4198,7 @@
         <v>47</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>294</v>
@@ -4237,10 +4237,10 @@
       </c>
       <c r="H19" s="10"/>
       <c r="J19" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="K19" s="20" t="s">
         <v>527</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>528</v>
       </c>
       <c r="L19" s="20" t="s">
         <v>269</v>
@@ -4276,10 +4276,10 @@
       </c>
       <c r="H20" s="10"/>
       <c r="J20" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="K20" s="21" t="s">
         <v>529</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>530</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>264</v>
@@ -4315,10 +4315,10 @@
       </c>
       <c r="H21" s="10"/>
       <c r="J21" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>531</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>532</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>264</v>
@@ -4354,13 +4354,13 @@
       </c>
       <c r="H22" s="10"/>
       <c r="J22" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="K22" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="K22" s="18" t="s">
-        <v>518</v>
-      </c>
       <c r="L22" s="18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M22" s="18">
         <v>200</v>
@@ -4393,10 +4393,10 @@
       </c>
       <c r="H23" s="10"/>
       <c r="J23" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="K23" s="20" t="s">
         <v>533</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>534</v>
       </c>
       <c r="L23" s="20" t="s">
         <v>288</v>
@@ -4432,16 +4432,16 @@
       </c>
       <c r="H24" s="10"/>
       <c r="J24" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="K24" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="K24" s="12" t="s">
-        <v>536</v>
-      </c>
       <c r="L24" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N24" s="12" t="s">
         <v>267</v>
@@ -4471,10 +4471,10 @@
       </c>
       <c r="H25" s="10"/>
       <c r="J25" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="K25" s="15" t="s">
         <v>537</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>538</v>
       </c>
       <c r="L25" s="15" t="s">
         <v>264</v>
@@ -4515,7 +4515,7 @@
         <v>289</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L26" s="13" t="s">
         <v>288</v>
@@ -4553,7 +4553,7 @@
         <v>29</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>266</v>
@@ -4635,7 +4635,7 @@
         <v>255</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>272</v>
@@ -4676,7 +4676,7 @@
         <v>71</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K30" s="22" t="s">
         <v>291</v>
@@ -4717,10 +4717,10 @@
         <v>71</v>
       </c>
       <c r="J31" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>510</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>511</v>
       </c>
       <c r="L31" s="14" t="s">
         <v>261</v>
@@ -4761,7 +4761,7 @@
         <v>289</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L32" s="13" t="s">
         <v>288</v>
@@ -4838,13 +4838,13 @@
       </c>
       <c r="H34" s="10"/>
       <c r="J34" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="K34" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="K34" s="18" t="s">
-        <v>540</v>
-      </c>
       <c r="L34" s="18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M34" s="18">
         <v>200</v>
@@ -4879,10 +4879,10 @@
         <v>44</v>
       </c>
       <c r="J35" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>541</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>542</v>
       </c>
       <c r="L35" s="14" t="s">
         <v>288</v>
@@ -4920,7 +4920,7 @@
         <v>47</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K36" s="12" t="s">
         <v>294</v>
@@ -5002,7 +5002,7 @@
         <v>338</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K38" s="22" t="s">
         <v>291</v>
@@ -5041,13 +5041,13 @@
       </c>
       <c r="H39" s="10"/>
       <c r="J39" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="K39" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="K39" s="18" t="s">
-        <v>518</v>
-      </c>
       <c r="L39" s="18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M39" s="18">
         <v>200</v>
@@ -5080,10 +5080,10 @@
       </c>
       <c r="H40" s="10"/>
       <c r="J40" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="K40" s="13" t="s">
         <v>543</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>544</v>
       </c>
       <c r="L40" s="13" t="s">
         <v>269</v>
@@ -5121,10 +5121,10 @@
         <v>71</v>
       </c>
       <c r="J41" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>545</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>546</v>
       </c>
       <c r="L41" s="13" t="s">
         <v>288</v>
@@ -5162,10 +5162,10 @@
         <v>38</v>
       </c>
       <c r="J42" s="22" t="s">
+        <v>546</v>
+      </c>
+      <c r="K42" s="22" t="s">
         <v>547</v>
-      </c>
-      <c r="K42" s="22" t="s">
-        <v>548</v>
       </c>
       <c r="L42" s="22" t="s">
         <v>275</v>
@@ -5206,7 +5206,7 @@
         <v>289</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L43" s="13" t="s">
         <v>288</v>
@@ -5244,10 +5244,10 @@
         <v>103</v>
       </c>
       <c r="J44" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="K44" s="13" t="s">
         <v>549</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>550</v>
       </c>
       <c r="L44" s="13" t="s">
         <v>288</v>
@@ -5285,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K45" s="15" t="s">
         <v>295</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="46" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
@@ -5317,7 +5317,7 @@
         <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>10</v>
@@ -5326,16 +5326,16 @@
         <v>108</v>
       </c>
       <c r="J46" s="19" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K46" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="M46" s="12" t="s">
         <v>520</v>
-      </c>
-      <c r="L46" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="M46" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="N46" s="19" t="s">
         <v>267</v>
@@ -5367,10 +5367,10 @@
         <v>108</v>
       </c>
       <c r="J47" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="K47" s="14" t="s">
         <v>551</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>552</v>
       </c>
       <c r="L47" s="14" t="s">
         <v>261</v>
@@ -5405,13 +5405,13 @@
         <v>10</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J48" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="K48" s="14" t="s">
         <v>553</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>554</v>
       </c>
       <c r="L48" s="14" t="s">
         <v>261</v>
@@ -5446,7 +5446,7 @@
         <v>10</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J49" s="15" t="s">
         <v>280</v>
@@ -5488,10 +5488,10 @@
       </c>
       <c r="H50" s="10"/>
       <c r="J50" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="K50" s="13" t="s">
         <v>555</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>556</v>
       </c>
       <c r="L50" s="13" t="s">
         <v>288</v>
@@ -5520,7 +5520,7 @@
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>10</v>
@@ -5529,10 +5529,10 @@
         <v>335</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K51" s="12" t="s">
         <v>293</v>
@@ -5614,7 +5614,7 @@
         <v>33</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K53" s="14" t="s">
         <v>292</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>280</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H55" s="17"/>
       <c r="J55" s="12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="K55" s="12" t="s">
         <v>293</v>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="56" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B56" s="17">
         <v>1</v>
@@ -5726,7 +5726,7 @@
         <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>10</v>
@@ -5735,10 +5735,10 @@
         <v>332</v>
       </c>
       <c r="J56" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="K56" s="13" t="s">
         <v>557</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>558</v>
       </c>
       <c r="L56" s="13" t="s">
         <v>288</v>
@@ -5776,10 +5776,10 @@
         <v>332</v>
       </c>
       <c r="J57" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="K57" s="13" t="s">
         <v>559</v>
-      </c>
-      <c r="K57" s="13" t="s">
-        <v>560</v>
       </c>
       <c r="L57" s="13" t="s">
         <v>269</v>
@@ -5817,10 +5817,10 @@
         <v>335</v>
       </c>
       <c r="J58" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="K58" s="12" t="s">
         <v>561</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>562</v>
       </c>
       <c r="L58" s="12" t="s">
         <v>274</v>
@@ -5858,10 +5858,10 @@
         <v>71</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L59" s="14" t="s">
         <v>261</v>
@@ -5937,16 +5937,16 @@
         <v>10</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I61" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J61" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="K61" s="15" t="s">
         <v>564</v>
-      </c>
-      <c r="K61" s="15" t="s">
-        <v>565</v>
       </c>
       <c r="L61" s="15" t="s">
         <v>277</v>
@@ -5982,10 +5982,10 @@
       </c>
       <c r="H62" s="17"/>
       <c r="J62" s="18" t="s">
+        <v>565</v>
+      </c>
+      <c r="K62" s="18" t="s">
         <v>566</v>
-      </c>
-      <c r="K62" s="18" t="s">
-        <v>567</v>
       </c>
       <c r="L62" s="18" t="s">
         <v>297</v>
@@ -6021,10 +6021,10 @@
       </c>
       <c r="H63" s="17"/>
       <c r="J63" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="K63" s="13" t="s">
         <v>568</v>
-      </c>
-      <c r="K63" s="13" t="s">
-        <v>569</v>
       </c>
       <c r="L63" s="13" t="s">
         <v>269</v>
@@ -6062,13 +6062,13 @@
         <v>71</v>
       </c>
       <c r="J64" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="K64" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="K64" s="18" t="s">
-        <v>571</v>
-      </c>
       <c r="L64" s="18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M64" s="18">
         <v>200</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="65" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B65" s="17">
         <v>1</v>
@@ -6094,7 +6094,7 @@
         <v>22</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>10</v>
@@ -6103,10 +6103,10 @@
         <v>47</v>
       </c>
       <c r="J65" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="K65" s="13" t="s">
         <v>572</v>
-      </c>
-      <c r="K65" s="13" t="s">
-        <v>573</v>
       </c>
       <c r="L65" s="13" t="s">
         <v>288</v>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="66" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B66" s="17">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>22</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>10</v>
@@ -6185,10 +6185,10 @@
         <v>47</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K67" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L67" s="18" t="s">
         <v>297</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="68" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B68" s="17">
         <v>1</v>
@@ -6217,7 +6217,7 @@
         <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>10</v>
@@ -6226,10 +6226,10 @@
         <v>338</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L68" s="12" t="s">
         <v>274</v>
@@ -6267,10 +6267,10 @@
         <v>338</v>
       </c>
       <c r="J69" s="22" t="s">
+        <v>574</v>
+      </c>
+      <c r="K69" s="22" t="s">
         <v>575</v>
-      </c>
-      <c r="K69" s="22" t="s">
-        <v>576</v>
       </c>
       <c r="L69" s="22" t="s">
         <v>260</v>
@@ -6306,10 +6306,10 @@
       </c>
       <c r="H70" s="17"/>
       <c r="J70" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L70" s="12" t="s">
         <v>274</v>
@@ -6344,13 +6344,13 @@
         <v>10</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J71" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="K71" s="13" t="s">
         <v>578</v>
-      </c>
-      <c r="K71" s="13" t="s">
-        <v>579</v>
       </c>
       <c r="L71" s="13" t="s">
         <v>288</v>
@@ -6364,7 +6364,7 @@
     </row>
     <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B72" s="17">
         <v>1</v>
@@ -6379,7 +6379,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>10</v>
@@ -6388,10 +6388,10 @@
         <v>335</v>
       </c>
       <c r="J72" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="K72" s="12" t="s">
         <v>580</v>
-      </c>
-      <c r="K72" s="12" t="s">
-        <v>581</v>
       </c>
       <c r="L72" s="12" t="s">
         <v>262</v>
@@ -6426,10 +6426,10 @@
         <v>10</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="K73" s="12" t="s">
         <v>291</v>
@@ -6446,7 +6446,7 @@
     </row>
     <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B74" s="17">
         <v>1</v>
@@ -6461,7 +6461,7 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>10</v>
@@ -6470,10 +6470,10 @@
         <v>338</v>
       </c>
       <c r="J74" s="18" t="s">
+        <v>812</v>
+      </c>
+      <c r="K74" s="18" t="s">
         <v>813</v>
-      </c>
-      <c r="K74" s="18" t="s">
-        <v>814</v>
       </c>
       <c r="L74" s="18" t="s">
         <v>297</v>
@@ -6511,10 +6511,10 @@
         <v>338</v>
       </c>
       <c r="J75" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="K75" s="15" t="s">
         <v>582</v>
-      </c>
-      <c r="K75" s="15" t="s">
-        <v>583</v>
       </c>
       <c r="L75" s="15" t="s">
         <v>264</v>
@@ -6550,10 +6550,10 @@
       </c>
       <c r="H76" s="17"/>
       <c r="J76" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="K76" s="13" t="s">
         <v>584</v>
-      </c>
-      <c r="K76" s="13" t="s">
-        <v>585</v>
       </c>
       <c r="L76" s="13" t="s">
         <v>288</v>
@@ -6589,10 +6589,10 @@
       </c>
       <c r="H77" s="17"/>
       <c r="J77" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="K77" s="14" t="s">
         <v>586</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>587</v>
       </c>
       <c r="L77" s="14" t="s">
         <v>276</v>
@@ -6628,13 +6628,13 @@
         <v>337</v>
       </c>
       <c r="I78" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L78" s="12" t="s">
         <v>274</v>
@@ -6670,10 +6670,10 @@
       </c>
       <c r="H79" s="10"/>
       <c r="J79" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="K79" s="18" t="s">
         <v>514</v>
-      </c>
-      <c r="K79" s="18" t="s">
-        <v>515</v>
       </c>
       <c r="L79" s="18" t="s">
         <v>297</v>
@@ -6711,16 +6711,16 @@
         <v>33</v>
       </c>
       <c r="J80" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="K80" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="K80" s="12" t="s">
-        <v>590</v>
-      </c>
       <c r="L80" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M80" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>267</v>
@@ -6750,10 +6750,10 @@
       </c>
       <c r="H81" s="17"/>
       <c r="J81" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="K81" s="14" t="s">
         <v>591</v>
-      </c>
-      <c r="K81" s="14" t="s">
-        <v>592</v>
       </c>
       <c r="L81" s="14" t="s">
         <v>261</v>
@@ -6789,10 +6789,10 @@
       </c>
       <c r="H82" s="17"/>
       <c r="J82" s="22" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L82" s="22" t="s">
         <v>260</v>
@@ -6827,13 +6827,13 @@
         <v>10</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J83" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="K83" s="21" t="s">
         <v>594</v>
-      </c>
-      <c r="K83" s="21" t="s">
-        <v>595</v>
       </c>
       <c r="L83" s="21" t="s">
         <v>264</v>
@@ -6869,16 +6869,16 @@
       </c>
       <c r="H84" s="17"/>
       <c r="J84" s="19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K84" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="L84" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="M84" s="12" t="s">
         <v>520</v>
-      </c>
-      <c r="L84" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="M84" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="N84" s="19" t="s">
         <v>267</v>
@@ -6908,10 +6908,10 @@
       </c>
       <c r="H85" s="17"/>
       <c r="J85" s="23" t="s">
+        <v>595</v>
+      </c>
+      <c r="K85" s="23" t="s">
         <v>596</v>
-      </c>
-      <c r="K85" s="23" t="s">
-        <v>597</v>
       </c>
       <c r="L85" s="23" t="s">
         <v>261</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="86" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B86" s="17">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>10</v>
@@ -6949,13 +6949,13 @@
         <v>338</v>
       </c>
       <c r="I86" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J86" s="13" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L86" s="13" t="s">
         <v>288</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="87" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B87" s="17">
         <v>1</v>
@@ -6984,7 +6984,7 @@
         <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>10</v>
@@ -6993,13 +6993,13 @@
         <v>338</v>
       </c>
       <c r="I87" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J87" s="18" t="s">
+        <v>848</v>
+      </c>
+      <c r="K87" s="18" t="s">
         <v>849</v>
-      </c>
-      <c r="K87" s="18" t="s">
-        <v>850</v>
       </c>
       <c r="L87" s="18" t="s">
         <v>297</v>
@@ -7037,10 +7037,10 @@
         <v>338</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K88" s="21" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L88" s="21" t="s">
         <v>264</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="89" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B89" s="17">
         <v>1</v>
@@ -7069,19 +7069,19 @@
         <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="K89" s="20" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L89" s="20" t="s">
         <v>288</v>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="90" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B90" s="17">
         <v>1</v>
@@ -7110,19 +7110,19 @@
         <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J90" s="18" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="K90" s="18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L90" s="18" t="s">
         <v>297</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="91" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B91" s="17">
         <v>1</v>
@@ -7151,17 +7151,17 @@
         <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="10"/>
       <c r="J91" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="K91" s="18" t="s">
         <v>932</v>
-      </c>
-      <c r="K91" s="18" t="s">
-        <v>933</v>
       </c>
       <c r="L91" s="18" t="s">
         <v>297</v>
@@ -7196,13 +7196,13 @@
         <v>10</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J92" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="K92" s="20" t="s">
         <v>599</v>
-      </c>
-      <c r="K92" s="20" t="s">
-        <v>600</v>
       </c>
       <c r="L92" s="20" t="s">
         <v>269</v>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="93" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B93" s="17">
         <v>1</v>
@@ -7231,7 +7231,7 @@
         <v>19</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>10</v>
@@ -7240,10 +7240,10 @@
         <v>71</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K93" s="21" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L93" s="21" t="s">
         <v>264</v>
@@ -7272,7 +7272,7 @@
         <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>10</v>
@@ -7284,10 +7284,10 @@
         <v>375</v>
       </c>
       <c r="J94" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="K94" s="18" t="s">
         <v>512</v>
-      </c>
-      <c r="K94" s="18" t="s">
-        <v>513</v>
       </c>
       <c r="L94" s="18" t="s">
         <v>297</v>
@@ -7323,10 +7323,10 @@
       </c>
       <c r="H95" s="17"/>
       <c r="J95" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="K95" s="20" t="s">
         <v>601</v>
-      </c>
-      <c r="K95" s="20" t="s">
-        <v>602</v>
       </c>
       <c r="L95" s="20" t="s">
         <v>288</v>
@@ -7364,10 +7364,10 @@
         <v>71</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L96" s="23" t="s">
         <v>276</v>
@@ -7401,10 +7401,10 @@
       </c>
       <c r="H97" s="17"/>
       <c r="J97" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="K97" s="20" t="s">
         <v>604</v>
-      </c>
-      <c r="K97" s="20" t="s">
-        <v>605</v>
       </c>
       <c r="L97" s="20" t="s">
         <v>269</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="99" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B99" s="17">
         <v>1</v>
@@ -7470,25 +7470,25 @@
         <v>22</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J99" s="19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K99" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="L99" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="M99" s="12" t="s">
         <v>520</v>
-      </c>
-      <c r="L99" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="M99" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="N99" s="19" t="s">
         <v>267</v>
@@ -7496,7 +7496,7 @@
     </row>
     <row r="100" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B100" s="17">
         <v>1</v>
@@ -7511,16 +7511,16 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>285</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="101" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B101" s="17">
         <v>1</v>
@@ -7552,19 +7552,19 @@
         <v>22</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H101" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J101" s="18" t="s">
+        <v>777</v>
+      </c>
+      <c r="K101" s="18" t="s">
         <v>778</v>
-      </c>
-      <c r="K101" s="18" t="s">
-        <v>779</v>
       </c>
       <c r="L101" s="18" t="s">
         <v>297</v>
@@ -7578,7 +7578,7 @@
     </row>
     <row r="102" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B102" s="17">
         <v>1</v>
@@ -7593,16 +7593,16 @@
         <v>22</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J102" s="15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="K102" s="15" t="s">
         <v>279</v>
@@ -7619,7 +7619,7 @@
     </row>
     <row r="103" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B103" s="17">
         <v>1</v>
@@ -7634,16 +7634,16 @@
         <v>22</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K103" s="12" t="s">
         <v>294</v>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="104" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B104" s="17">
         <v>1</v>
@@ -7675,19 +7675,19 @@
         <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G104" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I104" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K104" s="13" t="s">
         <v>272</v>
@@ -7725,10 +7725,10 @@
         <v>10</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K105" s="12" t="s">
         <v>293</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="106" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B106" s="17">
         <v>1</v>
@@ -7760,19 +7760,19 @@
         <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G106" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J106" s="23" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K106" s="23" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L106" s="23" t="s">
         <v>261</v>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="107" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B107" s="17">
         <v>1</v>
@@ -7801,22 +7801,22 @@
         <v>22</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G107" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M107" s="24">
         <v>200</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="108" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B108" s="17">
         <v>1</v>
@@ -7842,7 +7842,7 @@
         <v>22</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G108" s="10" t="s">
         <v>10</v>
@@ -7851,7 +7851,7 @@
         <v>337</v>
       </c>
       <c r="J108" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="K108" s="15" t="s">
         <v>279</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="109" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B109" s="17">
         <v>1</v>
@@ -7883,7 +7883,7 @@
         <v>22</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>10</v>
@@ -7892,10 +7892,10 @@
         <v>337</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>260</v>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="110" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B110" s="17">
         <v>1</v>
@@ -7930,13 +7930,13 @@
         <v>10</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="I110" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="K110" s="12" t="s">
         <v>294</v>
@@ -7977,7 +7977,7 @@
         <v>108</v>
       </c>
       <c r="I111" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>280</v>
@@ -8012,7 +8012,7 @@
         <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G112" s="10" t="s">
         <v>10</v>
@@ -8038,7 +8038,7 @@
     </row>
     <row r="113" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B113" s="17">
         <v>1</v>
@@ -8053,7 +8053,7 @@
         <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>10</v>
@@ -8062,10 +8062,10 @@
         <v>108</v>
       </c>
       <c r="J113" s="20" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="K113" s="20" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L113" s="20" t="s">
         <v>288</v>
@@ -8079,7 +8079,7 @@
     </row>
     <row r="114" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B114" s="17">
         <v>1</v>
@@ -8094,20 +8094,20 @@
         <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G114" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H114" s="10"/>
       <c r="J114" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K114" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="K114" s="2" t="s">
-        <v>941</v>
-      </c>
       <c r="L114" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M114" s="24">
         <v>200</v>
@@ -8142,7 +8142,7 @@
         <v>108</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K115" s="12" t="s">
         <v>291</v>
@@ -8159,7 +8159,7 @@
     </row>
     <row r="116" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B116" s="17">
         <v>1</v>
@@ -8174,22 +8174,22 @@
         <v>22</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G116" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="I116" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="J116" s="21" t="s">
+        <v>750</v>
+      </c>
+      <c r="K116" s="21" t="s">
         <v>751</v>
-      </c>
-      <c r="K116" s="21" t="s">
-        <v>752</v>
       </c>
       <c r="L116" s="21" t="s">
         <v>264</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="117" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B117" s="17">
         <v>1</v>
@@ -8218,19 +8218,19 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="I117" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K117" s="13" t="s">
         <v>272</v>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="118" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B118" s="17">
         <v>1</v>
@@ -8262,25 +8262,25 @@
         <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G118" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="K118" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="M118" s="24" t="s">
         <v>520</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M118" s="24" t="s">
-        <v>521</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>267</v>
@@ -8288,7 +8288,7 @@
     </row>
     <row r="119" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B119" s="17">
         <v>1</v>
@@ -8303,19 +8303,19 @@
         <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J119" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="K119" s="23" t="s">
         <v>606</v>
-      </c>
-      <c r="K119" s="23" t="s">
-        <v>607</v>
       </c>
       <c r="L119" s="23" t="s">
         <v>261</v>
@@ -8329,7 +8329,7 @@
     </row>
     <row r="120" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B120" s="17">
         <v>1</v>
@@ -8344,16 +8344,16 @@
         <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G120" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>283</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="121" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B121" s="17">
         <v>1</v>
@@ -8383,16 +8383,16 @@
         <v>19</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="K121" s="12" t="s">
         <v>293</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="122" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B122" s="17">
         <v>1</v>
@@ -8424,16 +8424,16 @@
         <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K122" s="13" t="s">
         <v>272</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="123" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B123" s="17">
         <v>1</v>
@@ -8465,16 +8465,16 @@
         <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J123" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K123" s="15" t="s">
         <v>279</v>
@@ -8506,19 +8506,19 @@
         <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>260</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="125" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B125" s="17">
         <v>1</v>
@@ -8547,19 +8547,19 @@
         <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>269</v>
@@ -8595,10 +8595,10 @@
       </c>
       <c r="H126" s="10"/>
       <c r="J126" s="23" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L126" s="23" t="s">
         <v>261</v>
@@ -8636,13 +8636,13 @@
         <v>126</v>
       </c>
       <c r="J127" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="K127" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="K127" s="2" t="s">
-        <v>609</v>
-      </c>
       <c r="L127" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M127" s="24">
         <v>200</v>
@@ -8677,7 +8677,7 @@
         <v>129</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>283</v>
@@ -8713,13 +8713,13 @@
         <v>125</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>261</v>
@@ -8757,10 +8757,10 @@
         <v>135</v>
       </c>
       <c r="J130" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="K130" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="L130" s="2" t="s">
         <v>260</v>
@@ -8798,10 +8798,10 @@
         <v>138</v>
       </c>
       <c r="J131" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="K131" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="L131" s="2" t="s">
         <v>288</v>
@@ -8837,10 +8837,10 @@
       </c>
       <c r="H132" s="4"/>
       <c r="J132" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L132" s="2" t="s">
         <v>261</v>
@@ -8876,10 +8876,10 @@
       </c>
       <c r="H133" s="4"/>
       <c r="J133" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L133" s="2" t="s">
         <v>269</v>
@@ -8917,10 +8917,10 @@
         <v>141</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L134" s="2" t="s">
         <v>260</v>
@@ -8949,7 +8949,7 @@
         <v>22</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>125</v>
@@ -8958,10 +8958,10 @@
         <v>213</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L135" s="2" t="s">
         <v>275</v>
@@ -8975,7 +8975,7 @@
     </row>
     <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B136" s="4">
         <v>1</v>
@@ -8990,7 +8990,7 @@
         <v>22</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>125</v>
@@ -8999,7 +8999,7 @@
         <v>213</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>283</v>
@@ -9014,7 +9014,7 @@
     </row>
     <row r="137" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B137" s="4">
         <v>1</v>
@@ -9029,7 +9029,7 @@
         <v>22</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>125</v>
@@ -9038,7 +9038,7 @@
         <v>213</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K137" s="14" t="s">
         <v>285</v>
@@ -9079,10 +9079,10 @@
         <v>213</v>
       </c>
       <c r="J138" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="K138" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>264</v>
@@ -9118,10 +9118,10 @@
       </c>
       <c r="H139" s="4"/>
       <c r="J139" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>288</v>
@@ -9159,10 +9159,10 @@
         <v>146</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L140" s="2" t="s">
         <v>288</v>
@@ -9200,10 +9200,10 @@
         <v>149</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L141" s="2" t="s">
         <v>269</v>
@@ -9239,16 +9239,16 @@
       </c>
       <c r="H142" s="4"/>
       <c r="J142" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K142" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="M142" s="24" t="s">
         <v>520</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M142" s="24" t="s">
-        <v>521</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>267</v>
@@ -9280,13 +9280,13 @@
         <v>154</v>
       </c>
       <c r="J143" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="K143" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="K143" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="L143" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M143" s="24">
         <v>200</v>
@@ -9319,10 +9319,10 @@
       </c>
       <c r="H144" s="4"/>
       <c r="J144" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>261</v>
@@ -9360,10 +9360,10 @@
         <v>159</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>297</v>
@@ -9399,10 +9399,10 @@
       </c>
       <c r="H146" s="4"/>
       <c r="J146" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L146" s="2" t="s">
         <v>275</v>
@@ -9440,10 +9440,10 @@
         <v>164</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L147" s="2" t="s">
         <v>288</v>
@@ -9481,13 +9481,13 @@
         <v>164</v>
       </c>
       <c r="J148" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="K148" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="K148" s="2" t="s">
-        <v>746</v>
-      </c>
       <c r="L148" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M148" s="24">
         <v>200</v>
@@ -9498,7 +9498,7 @@
     </row>
     <row r="149" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B149" s="4">
         <v>1</v>
@@ -9513,13 +9513,13 @@
         <v>22</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
@@ -9529,7 +9529,7 @@
     </row>
     <row r="150" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B150" s="4">
         <v>1</v>
@@ -9544,22 +9544,22 @@
         <v>22</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J150" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="K150" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="K150" s="2" t="s">
-        <v>914</v>
-      </c>
       <c r="L150" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M150" s="24">
         <v>200</v>
@@ -9594,10 +9594,10 @@
         <v>164</v>
       </c>
       <c r="J151" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="K151" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>263</v>
@@ -9632,13 +9632,13 @@
         <v>125</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L152" s="2" t="s">
         <v>274</v>
@@ -9676,10 +9676,10 @@
         <v>146</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L153" s="2" t="s">
         <v>288</v>
@@ -9717,10 +9717,10 @@
         <v>175</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L154" s="2" t="s">
         <v>288</v>
@@ -9734,7 +9734,7 @@
     </row>
     <row r="155" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B155" s="4">
         <v>1</v>
@@ -9749,7 +9749,7 @@
         <v>8</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>125</v>
@@ -9758,10 +9758,10 @@
         <v>175</v>
       </c>
       <c r="J155" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K155" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>920</v>
       </c>
       <c r="L155" s="2" t="s">
         <v>276</v>
@@ -9797,10 +9797,10 @@
         <v>175</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L156" s="2" t="s">
         <v>269</v>
@@ -9814,7 +9814,7 @@
     </row>
     <row r="157" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B157" s="4">
         <v>1</v>
@@ -9829,7 +9829,7 @@
         <v>22</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>125</v>
@@ -9838,13 +9838,13 @@
         <v>178</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M157" s="24">
         <v>200</v>
@@ -9855,7 +9855,7 @@
     </row>
     <row r="158" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B158" s="4">
         <v>1</v>
@@ -9870,7 +9870,7 @@
         <v>22</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>125</v>
@@ -9879,10 +9879,10 @@
         <v>178</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L158" s="2" t="s">
         <v>261</v>
@@ -9920,10 +9920,10 @@
         <v>178</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>288</v>
@@ -9959,10 +9959,10 @@
       </c>
       <c r="H160" s="4"/>
       <c r="J160" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L160" s="2" t="s">
         <v>277</v>
@@ -9998,16 +9998,16 @@
       </c>
       <c r="H161" s="4"/>
       <c r="J161" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="K161" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="K161" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="L161" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M161" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N161" s="2" t="s">
         <v>267</v>
@@ -10037,10 +10037,10 @@
       </c>
       <c r="H162" s="4"/>
       <c r="J162" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L162" s="2" t="s">
         <v>277</v>
@@ -10078,10 +10078,10 @@
         <v>154</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L163" s="2" t="s">
         <v>261</v>
@@ -10119,10 +10119,10 @@
         <v>132</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L164" s="2" t="s">
         <v>297</v>
@@ -10158,13 +10158,13 @@
       </c>
       <c r="H165" s="4"/>
       <c r="J165" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="K165" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="K165" s="2" t="s">
-        <v>644</v>
-      </c>
       <c r="L165" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M165" s="24">
         <v>200</v>
@@ -10197,10 +10197,10 @@
       </c>
       <c r="H166" s="4"/>
       <c r="J166" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="K166" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="L166" s="2" t="s">
         <v>276</v>
@@ -10236,10 +10236,10 @@
         <v>195</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>288</v>
@@ -10253,7 +10253,7 @@
     </row>
     <row r="168" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
@@ -10268,7 +10268,7 @@
         <v>19</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>125</v>
@@ -10277,10 +10277,10 @@
         <v>175</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L168" s="2" t="s">
         <v>288</v>
@@ -10318,10 +10318,10 @@
         <v>198</v>
       </c>
       <c r="J169" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="K169" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="K169" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="L169" s="2" t="s">
         <v>264</v>
@@ -10356,13 +10356,13 @@
         <v>125</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>297</v>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="171" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B171" s="4">
         <v>1</v>
@@ -10391,7 +10391,7 @@
         <v>22</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>125</v>
@@ -10400,13 +10400,13 @@
         <v>178</v>
       </c>
       <c r="I171" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>264</v>
@@ -10444,13 +10444,13 @@
         <v>178</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M172" s="24">
         <v>200</v>
@@ -10483,10 +10483,10 @@
       </c>
       <c r="H173" s="4"/>
       <c r="J173" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>288</v>
@@ -10524,10 +10524,10 @@
         <v>146</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>288</v>
@@ -10563,10 +10563,10 @@
       </c>
       <c r="H175" s="4"/>
       <c r="J175" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="K175" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="K175" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>277</v>
@@ -10604,10 +10604,10 @@
         <v>175</v>
       </c>
       <c r="J176" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="K176" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="K176" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="L176" s="2" t="s">
         <v>261</v>
@@ -10643,10 +10643,10 @@
       </c>
       <c r="H177" s="4"/>
       <c r="J177" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>261</v>
@@ -10682,10 +10682,10 @@
       </c>
       <c r="H178" s="4"/>
       <c r="J178" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L178" s="2" t="s">
         <v>297</v>
@@ -10723,10 +10723,10 @@
         <v>138</v>
       </c>
       <c r="J179" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="K179" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>288</v>
@@ -10762,13 +10762,13 @@
       </c>
       <c r="H180" s="4"/>
       <c r="J180" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M180" s="24">
         <v>200</v>
@@ -10801,16 +10801,16 @@
       </c>
       <c r="H181" s="4"/>
       <c r="J181" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="K181" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="K181" s="2" t="s">
-        <v>664</v>
-      </c>
       <c r="L181" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M181" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>267</v>
@@ -10842,10 +10842,10 @@
         <v>146</v>
       </c>
       <c r="J182" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="K182" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="K182" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="L182" s="2" t="s">
         <v>269</v>
@@ -10881,13 +10881,13 @@
       </c>
       <c r="H183" s="4"/>
       <c r="J183" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M183" s="24">
         <v>200</v>
@@ -10920,10 +10920,10 @@
       </c>
       <c r="H184" s="4"/>
       <c r="J184" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="K184" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="K184" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="L184" s="2" t="s">
         <v>276</v>
@@ -10957,16 +10957,16 @@
       </c>
       <c r="H185" s="4"/>
       <c r="J185" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="K185" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="K185" s="2" t="s">
-        <v>671</v>
-      </c>
       <c r="L185" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M185" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>267</v>
@@ -10996,10 +10996,10 @@
       </c>
       <c r="H186" s="4"/>
       <c r="J186" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="K186" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="K186" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="L186" s="2" t="s">
         <v>269</v>
@@ -11035,10 +11035,10 @@
       </c>
       <c r="H187" s="4"/>
       <c r="J187" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>269</v>
@@ -11076,13 +11076,13 @@
         <v>178</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M188" s="24">
         <v>200</v>
@@ -11115,10 +11115,10 @@
       </c>
       <c r="H189" s="4"/>
       <c r="J189" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L189" s="2" t="s">
         <v>269</v>
@@ -11156,10 +11156,10 @@
         <v>135</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L190" s="2" t="s">
         <v>261</v>
@@ -11195,10 +11195,10 @@
       </c>
       <c r="H191" s="4"/>
       <c r="J191" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="K191" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="L191" s="2" t="s">
         <v>297</v>
@@ -11212,7 +11212,7 @@
     </row>
     <row r="192" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
@@ -11227,16 +11227,16 @@
         <v>8</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J192" s="14" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K192" s="14" t="s">
         <v>285</v>
@@ -11275,10 +11275,10 @@
       </c>
       <c r="H193" s="4"/>
       <c r="J193" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="K193" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="K193" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>288</v>
@@ -11292,7 +11292,7 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         <v>22</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>125</v>
@@ -11343,10 +11343,10 @@
       </c>
       <c r="H195" s="4"/>
       <c r="J195" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L195" s="2" t="s">
         <v>261</v>
@@ -11382,10 +11382,10 @@
       </c>
       <c r="H196" s="4"/>
       <c r="J196" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L196" s="2" t="s">
         <v>269</v>
@@ -11421,10 +11421,10 @@
       </c>
       <c r="H197" s="4"/>
       <c r="J197" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>275</v>
@@ -11460,10 +11460,10 @@
       </c>
       <c r="H198" s="4"/>
       <c r="J198" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L198" s="2" t="s">
         <v>288</v>
@@ -11499,10 +11499,10 @@
       </c>
       <c r="H199" s="4"/>
       <c r="J199" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L199" s="2" t="s">
         <v>260</v>
@@ -11538,10 +11538,10 @@
       </c>
       <c r="H200" s="4"/>
       <c r="J200" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L200" s="2" t="s">
         <v>269</v>
@@ -11577,13 +11577,13 @@
       </c>
       <c r="H201" s="4"/>
       <c r="J201" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="K201" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="K201" s="2" t="s">
-        <v>688</v>
-      </c>
       <c r="L201" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M201" s="24">
         <v>200</v>
@@ -11616,10 +11616,10 @@
       </c>
       <c r="H202" s="4"/>
       <c r="J202" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L202" s="2" t="s">
         <v>288</v>
@@ -11655,10 +11655,10 @@
       </c>
       <c r="H203" s="4"/>
       <c r="J203" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L203" s="2" t="s">
         <v>261</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B204" s="4">
         <v>1</v>
@@ -11687,14 +11687,14 @@
         <v>8</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H204" s="4"/>
       <c r="J204" s="14" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K204" s="14" t="s">
         <v>285</v>
@@ -11726,17 +11726,17 @@
         <v>8</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>440</v>
+        <v>945</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H205" s="4"/>
       <c r="J205" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L205" s="2" t="s">
         <v>288</v>
@@ -11750,7 +11750,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
@@ -11765,19 +11765,19 @@
         <v>8</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L206" s="2" t="s">
         <v>275</v>
@@ -11791,7 +11791,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
@@ -11806,19 +11806,19 @@
         <v>8</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L207" s="2" t="s">
         <v>269</v>
@@ -11832,7 +11832,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
@@ -11847,19 +11847,19 @@
         <v>8</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H208" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="J208" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="J208" s="2" t="s">
-        <v>877</v>
-      </c>
       <c r="K208" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L208" s="2" t="s">
         <v>288</v>
@@ -11873,7 +11873,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
@@ -11888,16 +11888,16 @@
         <v>8</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K209" s="14" t="s">
         <v>285</v>
@@ -11914,7 +11914,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
@@ -11929,19 +11929,19 @@
         <v>8</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L210" s="2" t="s">
         <v>277</v>
@@ -11955,7 +11955,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
@@ -11970,25 +11970,25 @@
         <v>8</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I211" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L211" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M211" s="24">
         <v>200</v>
@@ -12014,19 +12014,19 @@
         <v>8</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J212" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L212" s="2" t="s">
         <v>260</v>
@@ -12040,7 +12040,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B213" s="4">
         <v>1</v>
@@ -12055,13 +12055,13 @@
         <v>8</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
@@ -12081,17 +12081,17 @@
         <v>8</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H214" s="4"/>
       <c r="J214" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L214" s="2" t="s">
         <v>261</v>
@@ -12120,23 +12120,23 @@
         <v>8</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H215" s="4"/>
       <c r="J215" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M215" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N215" s="2" t="s">
         <v>267</v>
@@ -12159,17 +12159,17 @@
         <v>8</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H216" s="4"/>
       <c r="J216" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L216" s="2" t="s">
         <v>276</v>
@@ -12196,17 +12196,17 @@
         <v>8</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H217" s="4"/>
       <c r="J217" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L217" s="2" t="s">
         <v>288</v>
@@ -12235,17 +12235,17 @@
         <v>8</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H218" s="4"/>
       <c r="J218" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L218" s="2" t="s">
         <v>269</v>
@@ -12274,17 +12274,17 @@
         <v>8</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H219" s="4"/>
       <c r="J219" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="K219" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="K219" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="L219" s="2" t="s">
         <v>288</v>
@@ -12313,20 +12313,20 @@
         <v>19</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H220" s="4"/>
       <c r="J220" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M220" s="24">
         <v>200</v>
@@ -12352,17 +12352,17 @@
         <v>19</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H221" s="4"/>
       <c r="J221" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L221" s="2" t="s">
         <v>276</v>
@@ -12374,7 +12374,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B222" s="4">
         <v>1</v>
@@ -12389,19 +12389,19 @@
         <v>8</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L222" s="2" t="s">
         <v>288</v>
@@ -12430,19 +12430,19 @@
         <v>8</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J223" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L223" s="2" t="s">
         <v>269</v>
@@ -12471,17 +12471,17 @@
         <v>19</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H224" s="4"/>
       <c r="J224" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L224" s="2" t="s">
         <v>261</v>
@@ -12510,17 +12510,17 @@
         <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H225" s="4"/>
       <c r="J225" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="K225" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L225" s="2" t="s">
         <v>260</v>
@@ -12549,23 +12549,23 @@
         <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H226" s="4"/>
       <c r="J226" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M226" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N226" s="2" t="s">
         <v>267</v>
@@ -12588,20 +12588,20 @@
         <v>19</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H227" s="4"/>
       <c r="J227" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M227" s="24">
         <v>200</v>
@@ -12627,17 +12627,17 @@
         <v>19</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H228" s="4"/>
       <c r="J228" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="K228" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="K228" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="L228" s="2" t="s">
         <v>276</v>
@@ -12664,17 +12664,17 @@
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H229" s="4"/>
       <c r="J229" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L229" s="2" t="s">
         <v>288</v>
@@ -12703,7 +12703,7 @@
         <v>22</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>125</v>
@@ -12712,13 +12712,13 @@
         <v>178</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M230" s="24">
         <v>200</v>
@@ -12744,7 +12744,7 @@
         <v>22</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>125</v>
@@ -12753,10 +12753,10 @@
         <v>178</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L231" s="2" t="s">
         <v>277</v>
@@ -12785,17 +12785,17 @@
         <v>22</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H232" s="4"/>
       <c r="J232" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L232" s="2" t="s">
         <v>288</v>
@@ -12824,20 +12824,20 @@
         <v>22</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H233" s="4"/>
       <c r="I233" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J233" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L233" s="2" t="s">
         <v>269</v>
@@ -12866,17 +12866,17 @@
         <v>22</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H234" s="4"/>
       <c r="J234" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="K234" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="K234" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="L234" s="2" t="s">
         <v>263</v>
@@ -12905,7 +12905,7 @@
         <v>8</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>125</v>
@@ -12914,10 +12914,10 @@
         <v>175</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L235" s="2" t="s">
         <v>288</v>
@@ -12946,7 +12946,7 @@
         <v>8</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>125</v>
@@ -12955,10 +12955,10 @@
         <v>175</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L236" s="2" t="s">
         <v>288</v>
@@ -12987,23 +12987,23 @@
         <v>8</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H237" s="4"/>
       <c r="J237" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M237" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N237" s="2" t="s">
         <v>267</v>
@@ -13026,17 +13026,17 @@
         <v>19</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H238" s="4"/>
       <c r="J238" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L238" s="2" t="s">
         <v>261</v>
@@ -13065,19 +13065,19 @@
         <v>22</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L239" s="2" t="s">
         <v>297</v>
@@ -13106,19 +13106,19 @@
         <v>8</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L240" s="2" t="s">
         <v>261</v>
@@ -13147,19 +13147,19 @@
         <v>8</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L241" s="2" t="s">
         <v>261</v>
@@ -13188,19 +13188,19 @@
         <v>8</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L242" s="2" t="s">
         <v>277</v>
@@ -13229,19 +13229,19 @@
         <v>19</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J243" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="K243" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="K243" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="L243" s="2" t="s">
         <v>269</v>
@@ -13270,7 +13270,7 @@
         <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>125</v>
@@ -13279,10 +13279,10 @@
         <v>175</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L244" s="2" t="s">
         <v>288</v>
@@ -13311,7 +13311,7 @@
         <v>8</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>125</v>
@@ -13320,10 +13320,10 @@
         <v>175</v>
       </c>
       <c r="J245" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L245" s="2" t="s">
         <v>288</v>
@@ -13352,23 +13352,23 @@
         <v>22</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H246" s="4"/>
       <c r="J246" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M246" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N246" s="2" t="s">
         <v>267</v>
@@ -13391,17 +13391,17 @@
         <v>22</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H247" s="4"/>
       <c r="J247" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="K247" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="K247" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="L247" s="2" t="s">
         <v>297</v>
@@ -13415,7 +13415,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B248" s="4">
         <v>1</v>
@@ -13430,17 +13430,17 @@
         <v>22</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H248" s="4"/>
       <c r="J248" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K248" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L248" s="2" t="s">
         <v>269</v>
@@ -13469,7 +13469,7 @@
         <v>8</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>125</v>
@@ -13478,10 +13478,10 @@
         <v>175</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L249" s="2" t="s">
         <v>288</v>
@@ -13510,17 +13510,17 @@
         <v>8</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H250" s="4"/>
       <c r="J250" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L250" s="2" t="s">
         <v>261</v>
@@ -13549,17 +13549,17 @@
         <v>22</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H251" s="4"/>
       <c r="J251" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L251" s="2" t="s">
         <v>274</v>
@@ -13588,17 +13588,17 @@
         <v>19</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H252" s="4"/>
       <c r="J252" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L252" s="2" t="s">
         <v>276</v>
@@ -13625,17 +13625,17 @@
         <v>8</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H253" s="4"/>
       <c r="J253" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K253" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L253" s="2" t="s">
         <v>288</v>
@@ -13649,7 +13649,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="26" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B254" s="26">
         <v>1</v>
@@ -13664,14 +13664,14 @@
         <v>22</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G254" s="26" t="s">
         <v>125</v>
       </c>
       <c r="H254" s="4"/>
       <c r="J254" s="14" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="K254" s="14" t="s">
         <v>285</v>
@@ -13853,6 +13853,7 @@
     <hyperlink ref="F209" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
     <hyperlink ref="I94" r:id="rId75" xr:uid="{FE3AAB39-C871-4F64-AA22-E89C4CD15539}"/>
     <hyperlink ref="F89" r:id="rId76" xr:uid="{3D7B2B26-3280-40AF-A4C5-1389477FB9D2}"/>
+    <hyperlink ref="F205" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9040C916-1E31-4BEC-9C81-2B24749B8741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ED96AA-82C8-4370-8FD3-CE366C75A492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$272</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="1005">
   <si>
     <t>Nombre</t>
   </si>
@@ -2969,6 +2969,75 @@
   </si>
   <si>
     <t>Avalancha</t>
+  </si>
+  <si>
+    <t>Grim Knight</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/3tM4V9k/batman-who-laughs-the-grim-knight-textless-variant-cover-by-v0-rgxncsng34h21.webp</t>
+  </si>
+  <si>
+    <t>Multiverso oscuro</t>
+  </si>
+  <si>
+    <t>Pistolas duales</t>
+  </si>
+  <si>
+    <t>The Drowned</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/rR8N8Y8z/drowned.jpg</t>
+  </si>
+  <si>
+    <t>Lamentos ahogados</t>
+  </si>
+  <si>
+    <t>The Devastator</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/4Z0zW9RP/Batman-The-Devastator-Vol-1-1-Textless.webp</t>
+  </si>
+  <si>
+    <t>Devastación</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/1fYh5DHs/The-Murder-Machine.jpg</t>
+  </si>
+  <si>
+    <t>The Murder Machine</t>
+  </si>
+  <si>
+    <t>Ataque sorpresa</t>
+  </si>
+  <si>
+    <t>The Dawnbreaker</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/DfG6DH5R/Dawnbreaker.jpg</t>
+  </si>
+  <si>
+    <t>Escudo de luz</t>
+  </si>
+  <si>
+    <t>The Merciless</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/60txDWyh/Merciless.jpg</t>
+  </si>
+  <si>
+    <t>Sin piedad</t>
+  </si>
+  <si>
+    <t>The Red Death</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/qF1HGBz8/red-death-by-mariano1990-de2weby-fullview.jpg</t>
+  </si>
+  <si>
+    <t>Acechador veloz</t>
+  </si>
+  <si>
+    <t>Oscuridad caótica</t>
   </si>
 </sst>
 </file>
@@ -3549,7 +3618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N266"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -11880,58 +11949,72 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>913</v>
+        <v>1001</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
       </c>
       <c r="C206" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="D206" s="4">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>914</v>
+        <v>1002</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H206" s="4"/>
-      <c r="J206" s="2"/>
-      <c r="K206" s="2"/>
-      <c r="L206" s="2"/>
-      <c r="M206" s="24"/>
-      <c r="N206" s="2"/>
+      <c r="H206" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M206" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="N206" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>379</v>
+        <v>998</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
       </c>
       <c r="C207" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D207" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>431</v>
+        <v>999</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H207" s="4"/>
+      <c r="H207" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J207" s="2" t="s">
-        <v>681</v>
+        <v>1000</v>
       </c>
       <c r="K207" s="2" t="s">
         <v>551</v>
@@ -11948,38 +12031,40 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>380</v>
+        <v>995</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
       </c>
       <c r="C208" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D208" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>432</v>
+        <v>996</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H208" s="4"/>
+      <c r="H208" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J208" s="2" t="s">
-        <v>682</v>
+        <v>997</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M208" s="24" t="s">
-        <v>270</v>
+        <v>264</v>
+      </c>
+      <c r="M208" s="24">
+        <v>1000</v>
       </c>
       <c r="N208" s="2" t="s">
         <v>268</v>
@@ -11987,7 +12072,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>381</v>
+        <v>993</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
@@ -11996,62 +12081,64 @@
         <v>3500</v>
       </c>
       <c r="D209" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>433</v>
+        <v>992</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H209" s="4"/>
+      <c r="H209" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J209" s="2" t="s">
-        <v>629</v>
+        <v>994</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>547</v>
+        <v>668</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M209" s="24">
-        <v>50</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M209" s="24"/>
       <c r="N209" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>382</v>
+        <v>989</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
       </c>
       <c r="C210" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="D210" s="4">
         <v>2000</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>434</v>
+        <v>990</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H210" s="4"/>
+      <c r="H210" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J210" s="2" t="s">
-        <v>683</v>
+        <v>991</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>614</v>
+        <v>680</v>
       </c>
       <c r="L210" s="2" t="s">
         <v>288</v>
@@ -12065,29 +12152,31 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>383</v>
+        <v>913</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
       </c>
       <c r="C211" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="D211" s="4">
         <v>1000</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>435</v>
+        <v>914</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H211" s="4"/>
+      <c r="H211" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J211" s="2" t="s">
-        <v>684</v>
+        <v>1004</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>612</v>
@@ -12104,77 +12193,81 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>384</v>
+        <v>986</v>
       </c>
       <c r="B212" s="4">
         <v>1</v>
       </c>
       <c r="C212" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="D212" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>436</v>
+        <v>987</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H212" s="4"/>
-      <c r="J212" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="L212" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M212" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="N212" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H212" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="J212" s="14" t="s">
+        <v>988</v>
+      </c>
+      <c r="K212" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L212" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M212" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N212" s="14" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>385</v>
+        <v>982</v>
       </c>
       <c r="B213" s="4">
         <v>1</v>
       </c>
       <c r="C213" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D213" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>437</v>
+        <v>983</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H213" s="4"/>
+      <c r="H213" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J213" s="2" t="s">
-        <v>686</v>
+        <v>985</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M213" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M213" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N213" s="2" t="s">
         <v>268</v>
@@ -12182,85 +12275,89 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B214" s="4">
         <v>1</v>
       </c>
       <c r="C214" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D214" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H214" s="4"/>
+      <c r="H214" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J214" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>614</v>
+        <v>551</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M214" s="24" t="s">
-        <v>290</v>
+        <v>261</v>
+      </c>
+      <c r="M214" s="24">
+        <v>100</v>
       </c>
       <c r="N214" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B215" s="4">
         <v>1</v>
       </c>
       <c r="C215" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D215" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H215" s="4"/>
+      <c r="H215" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="J215" s="2" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M215" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M215" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N215" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>795</v>
+        <v>381</v>
       </c>
       <c r="B216" s="4">
         <v>1</v>
@@ -12269,59 +12366,59 @@
         <v>3500</v>
       </c>
       <c r="D216" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>796</v>
+        <v>433</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H216" s="4"/>
-      <c r="J216" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="K216" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L216" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M216" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N216" s="14" t="s">
+      <c r="J216" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M216" s="24">
+        <v>50</v>
+      </c>
+      <c r="N216" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B217" s="4">
         <v>1</v>
       </c>
       <c r="C217" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D217" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>944</v>
+        <v>434</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H217" s="4"/>
       <c r="J217" s="2" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="K217" s="2" t="s">
         <v>614</v>
@@ -12338,40 +12435,38 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>876</v>
+        <v>383</v>
       </c>
       <c r="B218" s="4">
         <v>1</v>
       </c>
       <c r="C218" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D218" s="4">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>877</v>
+        <v>435</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H218" s="4" t="s">
-        <v>874</v>
-      </c>
+      <c r="H218" s="4"/>
       <c r="J218" s="2" t="s">
-        <v>878</v>
+        <v>684</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="M218" s="24">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N218" s="2" t="s">
         <v>267</v>
@@ -12379,7 +12474,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>861</v>
+        <v>384</v>
       </c>
       <c r="B219" s="4">
         <v>1</v>
@@ -12388,25 +12483,23 @@
         <v>4000</v>
       </c>
       <c r="D219" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>862</v>
+        <v>436</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H219" s="4" t="s">
-        <v>874</v>
-      </c>
+      <c r="H219" s="4"/>
       <c r="J219" s="2" t="s">
-        <v>863</v>
+        <v>685</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>665</v>
+        <v>604</v>
       </c>
       <c r="L219" s="2" t="s">
         <v>269</v>
@@ -12420,7 +12513,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>872</v>
+        <v>385</v>
       </c>
       <c r="B220" s="4">
         <v>1</v>
@@ -12432,28 +12525,26 @@
         <v>2000</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>873</v>
+        <v>437</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H220" s="4" t="s">
-        <v>874</v>
-      </c>
+      <c r="H220" s="4"/>
       <c r="J220" s="2" t="s">
-        <v>875</v>
+        <v>686</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>614</v>
+        <v>687</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M220" s="24" t="s">
-        <v>290</v>
+        <v>515</v>
+      </c>
+      <c r="M220" s="24">
+        <v>200</v>
       </c>
       <c r="N220" s="2" t="s">
         <v>268</v>
@@ -12461,48 +12552,46 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>855</v>
+        <v>386</v>
       </c>
       <c r="B221" s="4">
         <v>1</v>
       </c>
       <c r="C221" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D221" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>856</v>
+        <v>438</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H221" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="J221" s="14" t="s">
-        <v>858</v>
-      </c>
-      <c r="K221" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L221" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M221" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="N221" s="14" t="s">
-        <v>267</v>
+      <c r="H221" s="4"/>
+      <c r="J221" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M221" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="N221" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>869</v>
+        <v>387</v>
       </c>
       <c r="B222" s="4">
         <v>1</v>
@@ -12511,39 +12600,37 @@
         <v>4500</v>
       </c>
       <c r="D222" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>870</v>
+        <v>439</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H222" s="4" t="s">
-        <v>874</v>
-      </c>
+      <c r="H222" s="4"/>
       <c r="J222" s="2" t="s">
-        <v>871</v>
+        <v>689</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>654</v>
+        <v>596</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M222" s="24" t="s">
-        <v>278</v>
+        <v>261</v>
+      </c>
+      <c r="M222" s="24">
+        <v>100</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>864</v>
+        <v>795</v>
       </c>
       <c r="B223" s="4">
         <v>1</v>
@@ -12558,109 +12645,117 @@
         <v>8</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>865</v>
+        <v>796</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H223" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="I223" t="s">
-        <v>868</v>
-      </c>
-      <c r="J223" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="K223" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="L223" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M223" s="24">
-        <v>200</v>
-      </c>
-      <c r="N223" s="2" t="s">
-        <v>268</v>
+      <c r="H223" s="4"/>
+      <c r="J223" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="K223" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L223" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M223" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N223" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B224" s="4">
         <v>1</v>
       </c>
       <c r="C224" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D224" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E224" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>440</v>
+        <v>944</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H224" s="4" t="s">
-        <v>874</v>
-      </c>
+      <c r="H224" s="4"/>
       <c r="J224" s="2" t="s">
-        <v>866</v>
+        <v>690</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M224" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M224" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N224" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="B225" s="4">
         <v>1</v>
       </c>
       <c r="C225" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D225" s="4">
         <v>3000</v>
-      </c>
-      <c r="D225" s="4">
-        <v>1000</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>453</v>
+        <v>874</v>
+      </c>
+      <c r="J225" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M225" s="24">
+        <v>50</v>
+      </c>
+      <c r="N225" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>390</v>
+        <v>861</v>
       </c>
       <c r="B226" s="4">
         <v>1</v>
       </c>
       <c r="C226" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D226" s="4">
         <v>2500</v>
@@ -12669,70 +12764,74 @@
         <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>441</v>
+        <v>862</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H226" s="4"/>
+      <c r="H226" s="4" t="s">
+        <v>874</v>
+      </c>
       <c r="J226" s="2" t="s">
-        <v>691</v>
+        <v>863</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M226" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M226" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N226" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>391</v>
+        <v>872</v>
       </c>
       <c r="B227" s="4">
         <v>1</v>
       </c>
       <c r="C227" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D227" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>442</v>
+        <v>873</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H227" s="4"/>
+      <c r="H227" s="4" t="s">
+        <v>874</v>
+      </c>
       <c r="J227" s="2" t="s">
-        <v>692</v>
+        <v>875</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>638</v>
+        <v>614</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>518</v>
+        <v>288</v>
       </c>
       <c r="M227" s="24" t="s">
-        <v>520</v>
+        <v>290</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>392</v>
+        <v>855</v>
       </c>
       <c r="B228" s="4">
         <v>1</v>
@@ -12747,60 +12846,66 @@
         <v>8</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>443</v>
+        <v>856</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H228" s="4"/>
-      <c r="J228" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="K228" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="L228" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M228" s="24"/>
-      <c r="N228" s="2" t="s">
+      <c r="H228" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="J228" s="14" t="s">
+        <v>858</v>
+      </c>
+      <c r="K228" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L228" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M228" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="N228" s="14" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>411</v>
+        <v>869</v>
       </c>
       <c r="B229" s="4">
         <v>1</v>
       </c>
       <c r="C229" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D229" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>444</v>
+        <v>870</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H229" s="4"/>
+      <c r="H229" s="4" t="s">
+        <v>874</v>
+      </c>
       <c r="J229" s="2" t="s">
-        <v>694</v>
+        <v>871</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>614</v>
+        <v>654</v>
       </c>
       <c r="L229" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M229" s="24" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="N229" s="2" t="s">
         <v>268</v>
@@ -12808,38 +12913,43 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>393</v>
+        <v>864</v>
       </c>
       <c r="B230" s="4">
         <v>1</v>
       </c>
       <c r="C230" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D230" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>445</v>
+        <v>865</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H230" s="4"/>
+      <c r="H230" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="I230" t="s">
+        <v>868</v>
+      </c>
       <c r="J230" s="2" t="s">
-        <v>695</v>
+        <v>867</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>604</v>
+        <v>687</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M230" s="24" t="s">
-        <v>270</v>
+        <v>515</v>
+      </c>
+      <c r="M230" s="24">
+        <v>200</v>
       </c>
       <c r="N230" s="2" t="s">
         <v>268</v>
@@ -12847,343 +12957,328 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B231" s="4">
         <v>1</v>
       </c>
       <c r="C231" s="4">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="D231" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H231" s="4"/>
+      <c r="H231" s="4" t="s">
+        <v>874</v>
+      </c>
       <c r="J231" s="2" t="s">
-        <v>696</v>
+        <v>866</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>697</v>
+        <v>612</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M231" s="24" t="s">
-        <v>290</v>
+        <v>260</v>
+      </c>
+      <c r="M231" s="24">
+        <v>100</v>
       </c>
       <c r="N231" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>395</v>
+        <v>859</v>
       </c>
       <c r="B232" s="4">
         <v>1</v>
       </c>
       <c r="C232" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D232" s="4">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>448</v>
+        <v>860</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H232" s="4"/>
-      <c r="J232" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="K232" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="L232" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M232" s="24">
-        <v>200</v>
-      </c>
-      <c r="N232" s="2" t="s">
-        <v>268</v>
+      <c r="H232" s="4" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B233" s="4">
         <v>1</v>
       </c>
       <c r="C233" s="4">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="D233" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H233" s="4"/>
       <c r="J233" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M233" s="24"/>
+        <v>261</v>
+      </c>
+      <c r="M233" s="24">
+        <v>100</v>
+      </c>
       <c r="N233" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="B234" s="4">
         <v>1</v>
       </c>
       <c r="C234" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D234" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H234" s="4" t="s">
-        <v>453</v>
-      </c>
+      <c r="H234" s="4"/>
       <c r="J234" s="2" t="s">
-        <v>548</v>
+        <v>692</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>288</v>
+        <v>518</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>290</v>
+        <v>520</v>
       </c>
       <c r="N234" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B235" s="4">
         <v>1</v>
       </c>
       <c r="C235" s="4">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="D235" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H235" s="4" t="s">
-        <v>453</v>
-      </c>
+      <c r="H235" s="4"/>
       <c r="J235" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M235" s="24" t="s">
-        <v>270</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M235" s="24"/>
       <c r="N235" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B236" s="4">
         <v>1</v>
       </c>
       <c r="C236" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D236" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H236" s="4"/>
       <c r="J236" s="2" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>656</v>
+        <v>614</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M236" s="24">
-        <v>100</v>
+        <v>288</v>
+      </c>
+      <c r="M236" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N236" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B237" s="4">
         <v>1</v>
       </c>
       <c r="C237" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D237" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H237" s="4"/>
       <c r="J237" s="2" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M237" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M237" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N237" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B238" s="4">
         <v>1</v>
       </c>
       <c r="C238" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D238" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H238" s="4"/>
       <c r="J238" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>638</v>
+        <v>697</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>518</v>
+        <v>288</v>
       </c>
       <c r="M238" s="24" t="s">
-        <v>520</v>
+        <v>290</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B239" s="4">
         <v>1</v>
       </c>
       <c r="C239" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D239" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H239" s="4"/>
       <c r="J239" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="K239" s="2" t="s">
         <v>643</v>
@@ -13200,7 +13295,7 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B240" s="4">
         <v>1</v>
@@ -13215,17 +13310,17 @@
         <v>19</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H240" s="4"/>
       <c r="J240" s="2" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>668</v>
+        <v>645</v>
       </c>
       <c r="L240" s="2" t="s">
         <v>276</v>
@@ -13237,29 +13332,31 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="B241" s="4">
         <v>1</v>
       </c>
       <c r="C241" s="4">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="D241" s="4">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H241" s="4"/>
+      <c r="H241" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="J241" s="2" t="s">
-        <v>705</v>
+        <v>548</v>
       </c>
       <c r="K241" s="2" t="s">
         <v>614</v>
@@ -13276,201 +13373,196 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B242" s="4">
         <v>1</v>
       </c>
       <c r="C242" s="4">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="D242" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>178</v>
+        <v>453</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="L242" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M242" s="24">
-        <v>200</v>
+        <v>269</v>
+      </c>
+      <c r="M242" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N242" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B243" s="4">
         <v>1</v>
       </c>
       <c r="C243" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D243" s="4">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H243" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H243" s="4"/>
       <c r="J243" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L243" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M243" s="24" t="s">
-        <v>278</v>
+        <v>261</v>
+      </c>
+      <c r="M243" s="24">
+        <v>100</v>
       </c>
       <c r="N243" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B244" s="4">
         <v>1</v>
       </c>
       <c r="C244" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D244" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>747</v>
+        <v>455</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H244" s="4"/>
       <c r="J244" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="L244" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M244" s="24" t="s">
-        <v>290</v>
+        <v>260</v>
+      </c>
+      <c r="M244" s="24">
+        <v>100</v>
       </c>
       <c r="N244" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B245" s="4">
         <v>1</v>
       </c>
       <c r="C245" s="4">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D245" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>899</v>
+        <v>456</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H245" s="4"/>
-      <c r="I245" t="s">
-        <v>900</v>
-      </c>
       <c r="J245" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>604</v>
+        <v>638</v>
       </c>
       <c r="L245" s="2" t="s">
-        <v>269</v>
+        <v>518</v>
       </c>
       <c r="M245" s="24" t="s">
-        <v>270</v>
+        <v>520</v>
       </c>
       <c r="N245" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B246" s="4">
         <v>1</v>
       </c>
       <c r="C246" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D246" s="4">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H246" s="4"/>
       <c r="J246" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>711</v>
+        <v>643</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>263</v>
+        <v>515</v>
       </c>
       <c r="M246" s="24">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="N246" s="2" t="s">
         <v>268</v>
@@ -13478,72 +13570,66 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B247" s="4">
         <v>1</v>
       </c>
       <c r="C247" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D247" s="4">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E247" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H247" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H247" s="4"/>
       <c r="J247" s="2" t="s">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>614</v>
+        <v>668</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M247" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="M247" s="24"/>
       <c r="N247" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B248" s="4">
         <v>1</v>
       </c>
       <c r="C248" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D248" s="4">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H248" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H248" s="4"/>
       <c r="J248" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="K248" s="2" t="s">
         <v>614</v>
@@ -13560,7 +13646,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="B249" s="4">
         <v>1</v>
@@ -13572,34 +13658,36 @@
         <v>2000</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H249" s="4"/>
+      <c r="H249" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J249" s="2" t="s">
-        <v>637</v>
+        <v>706</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="L249" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="M249" s="24" t="s">
-        <v>520</v>
+        <v>515</v>
+      </c>
+      <c r="M249" s="24">
+        <v>200</v>
       </c>
       <c r="N249" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B250" s="4">
         <v>1</v>
@@ -13611,34 +13699,36 @@
         <v>2500</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>746</v>
+        <v>461</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H250" s="4"/>
+      <c r="H250" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J250" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="L250" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M250" s="24">
-        <v>100</v>
+        <v>277</v>
+      </c>
+      <c r="M250" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="N250" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B251" s="4">
         <v>1</v>
@@ -13653,148 +13743,145 @@
         <v>22</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>466</v>
+        <v>747</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H251" s="4" t="s">
-        <v>467</v>
-      </c>
+      <c r="H251" s="4"/>
       <c r="J251" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="L251" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M251" s="24">
-        <v>2</v>
+        <v>288</v>
+      </c>
+      <c r="M251" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N251" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B252" s="4">
         <v>1</v>
       </c>
       <c r="C252" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D252" s="4">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>468</v>
+        <v>899</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H252" s="4" t="s">
-        <v>467</v>
+      <c r="H252" s="4"/>
+      <c r="I252" t="s">
+        <v>900</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>605</v>
+        <v>709</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>656</v>
+        <v>604</v>
       </c>
       <c r="L252" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M252" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M252" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N252" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B253" s="4">
         <v>1</v>
       </c>
       <c r="C253" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D253" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H253" s="4" t="s">
-        <v>467</v>
-      </c>
+      <c r="H253" s="4"/>
       <c r="J253" s="2" t="s">
-        <v>552</v>
+        <v>710</v>
       </c>
       <c r="K253" s="2" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="L253" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M253" s="24">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="N253" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B254" s="4">
         <v>1</v>
       </c>
       <c r="C254" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D254" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E254" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>467</v>
+        <v>175</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>715</v>
+        <v>634</v>
       </c>
       <c r="K254" s="2" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="L254" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="M254" s="24" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N254" s="2" t="s">
         <v>268</v>
@@ -13802,40 +13889,40 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B255" s="4">
         <v>1</v>
       </c>
       <c r="C255" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D255" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>467</v>
+        <v>175</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="K255" s="2" t="s">
-        <v>717</v>
+        <v>614</v>
       </c>
       <c r="L255" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M255" s="24" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N255" s="2" t="s">
         <v>268</v>
@@ -13843,48 +13930,46 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>418</v>
+        <v>181</v>
       </c>
       <c r="B256" s="4">
         <v>1</v>
       </c>
       <c r="C256" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D256" s="4">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H256" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H256" s="4"/>
       <c r="J256" s="2" t="s">
-        <v>718</v>
+        <v>637</v>
       </c>
       <c r="K256" s="2" t="s">
-        <v>614</v>
+        <v>663</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>288</v>
+        <v>518</v>
       </c>
       <c r="M256" s="24" t="s">
-        <v>290</v>
+        <v>520</v>
       </c>
       <c r="N256" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B257" s="4">
         <v>1</v>
@@ -13893,78 +13978,78 @@
         <v>4500</v>
       </c>
       <c r="D257" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H257" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H257" s="4"/>
       <c r="J257" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>614</v>
+        <v>656</v>
       </c>
       <c r="L257" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M257" s="24" t="s">
-        <v>290</v>
+        <v>261</v>
+      </c>
+      <c r="M257" s="24">
+        <v>100</v>
       </c>
       <c r="N257" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B258" s="4">
         <v>1</v>
       </c>
       <c r="C258" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D258" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E258" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H258" s="4"/>
+      <c r="H258" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="J258" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="K258" s="2" t="s">
-        <v>670</v>
+        <v>566</v>
       </c>
       <c r="L258" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="M258" s="24" t="s">
-        <v>520</v>
+        <v>297</v>
+      </c>
+      <c r="M258" s="24">
+        <v>2</v>
       </c>
       <c r="N258" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B259" s="4">
         <v>1</v>
@@ -13973,109 +14058,113 @@
         <v>4000</v>
       </c>
       <c r="D259" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H259" s="4"/>
+      <c r="H259" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="J259" s="2" t="s">
-        <v>721</v>
+        <v>605</v>
       </c>
       <c r="K259" s="2" t="s">
-        <v>722</v>
+        <v>656</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="M259" s="24">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>919</v>
+        <v>415</v>
       </c>
       <c r="B260" s="4">
         <v>1</v>
       </c>
       <c r="C260" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D260" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H260" s="4"/>
+      <c r="H260" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="J260" s="2" t="s">
-        <v>664</v>
+        <v>552</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>717</v>
+        <v>656</v>
       </c>
       <c r="L260" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M260" s="24" t="s">
-        <v>270</v>
+        <v>261</v>
+      </c>
+      <c r="M260" s="24">
+        <v>100</v>
       </c>
       <c r="N260" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B261" s="4">
         <v>1</v>
       </c>
       <c r="C261" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D261" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>175</v>
+        <v>467</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="K261" s="2" t="s">
-        <v>614</v>
+        <v>654</v>
       </c>
       <c r="L261" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M261" s="24" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="N261" s="2" t="s">
         <v>268</v>
@@ -14083,77 +14172,81 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B262" s="4">
         <v>1</v>
       </c>
       <c r="C262" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D262" s="4">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H262" s="4"/>
+      <c r="H262" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="J262" s="2" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="K262" s="2" t="s">
-        <v>656</v>
+        <v>717</v>
       </c>
       <c r="L262" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M262" s="24">
-        <v>100</v>
+        <v>269</v>
+      </c>
+      <c r="M262" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N262" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
       </c>
       <c r="C263" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D263" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H263" s="4"/>
+      <c r="H263" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J263" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="K263" s="2" t="s">
-        <v>561</v>
+        <v>614</v>
       </c>
       <c r="L263" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M263" s="24">
-        <v>750</v>
+        <v>288</v>
+      </c>
+      <c r="M263" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="N263" s="2" t="s">
         <v>268</v>
@@ -14161,7 +14254,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B264" s="4">
         <v>1</v>
@@ -14170,113 +14263,390 @@
         <v>4500</v>
       </c>
       <c r="D264" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>478</v>
+        <v>742</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H264" s="4"/>
+      <c r="H264" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J264" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="K264" s="2" t="s">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M264" s="24"/>
+        <v>288</v>
+      </c>
+      <c r="M264" s="24" t="s">
+        <v>290</v>
+      </c>
       <c r="N264" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B265" s="4">
         <v>1</v>
       </c>
       <c r="C265" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D265" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H265" s="4"/>
       <c r="J265" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="K265" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="L265" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="M265" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="N265" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B266" s="4">
+        <v>1</v>
+      </c>
+      <c r="C266" s="4">
+        <v>4000</v>
+      </c>
+      <c r="D266" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H266" s="4"/>
+      <c r="J266" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="L266" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="M266" s="24">
+        <v>2</v>
+      </c>
+      <c r="N266" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="B267" s="4">
+        <v>1</v>
+      </c>
+      <c r="C267" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D267" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H267" s="4"/>
+      <c r="J267" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="K267" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="L267" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M267" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="N267" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B268" s="4">
+        <v>1</v>
+      </c>
+      <c r="C268" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D268" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H268" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J268" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K268" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="L268" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M268" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="N268" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B269" s="4">
+        <v>1</v>
+      </c>
+      <c r="C269" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D269" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E269" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H269" s="4"/>
+      <c r="J269" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="K269" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="L269" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="M269" s="24">
+        <v>100</v>
+      </c>
+      <c r="N269" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B270" s="4">
+        <v>1</v>
+      </c>
+      <c r="C270" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D270" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H270" s="4"/>
+      <c r="J270" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="K270" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="L270" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M270" s="24">
+        <v>750</v>
+      </c>
+      <c r="N270" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B271" s="4">
+        <v>1</v>
+      </c>
+      <c r="C271" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D271" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E271" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G271" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H271" s="4"/>
+      <c r="J271" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="K271" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="L271" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M271" s="24"/>
+      <c r="N271" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B272" s="4">
+        <v>1</v>
+      </c>
+      <c r="C272" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D272" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H272" s="4"/>
+      <c r="J272" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="K265" s="2" t="s">
+      <c r="K272" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="L265" s="2" t="s">
+      <c r="L272" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="M265" s="24" t="s">
+      <c r="M272" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="N265" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="26" t="s">
+      <c r="N272" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
         <v>761</v>
       </c>
-      <c r="B266" s="26">
-        <v>1</v>
-      </c>
-      <c r="C266" s="26">
+      <c r="B273" s="26">
+        <v>1</v>
+      </c>
+      <c r="C273" s="26">
         <v>5000</v>
       </c>
-      <c r="D266" s="26">
+      <c r="D273" s="26">
         <v>3000</v>
       </c>
-      <c r="E266" s="26" t="s">
+      <c r="E273" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F266" s="4" t="s">
+      <c r="F273" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="G266" s="26" t="s">
+      <c r="G273" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="H266" s="4"/>
-      <c r="J266" s="14" t="s">
+      <c r="H273" s="4"/>
+      <c r="J273" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="K266" s="14" t="s">
+      <c r="K273" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L266" s="14" t="s">
+      <c r="L273" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="M266" s="14" t="s">
+      <c r="M273" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="N266" s="14" t="s">
+      <c r="N273" s="14" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N265" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="C205:C265">
+  <autoFilter ref="A1:N272" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="C205:C272">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -14288,7 +14658,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C266:C1048576 C2:C204">
+  <conditionalFormatting sqref="C273:C1048576 C2:C204">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -14300,7 +14670,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D205:D265">
+  <conditionalFormatting sqref="D205:D272">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -14312,7 +14682,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D266:D1048576 D2:D204">
+  <conditionalFormatting sqref="D273:D1048576 D2:D204">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
@@ -14324,7 +14694,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:N224">
+  <conditionalFormatting sqref="J2:N231">
     <cfRule type="expression" dxfId="11" priority="7">
       <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
     </cfRule>
@@ -14344,24 +14714,24 @@
       <formula>OR($L2="extra_attack",$L2="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J226:N266">
+  <conditionalFormatting sqref="J233:N273">
     <cfRule type="expression" dxfId="5" priority="37">
-      <formula>OR($L226="debuff",$L226="bonus_debuff",$L226="revive")</formula>
+      <formula>OR($L233="debuff",$L233="bonus_debuff",$L233="revive")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="38">
-      <formula>OR($L226="buff",$L226="bonus_buff")</formula>
+      <formula>OR($L233="buff",$L233="bonus_buff")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="39">
-      <formula>OR($L226="dot",$L226="stun")</formula>
+      <formula>OR($L233="dot",$L233="stun")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="40">
-      <formula>OR($L226="tank",$L226="shield")</formula>
+      <formula>OR($L233="tank",$L233="shield")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="41">
-      <formula>OR($L226="heal",$L226="heal_all",$L226="life_steal")</formula>
+      <formula>OR($L233="heal",$L233="heal_all",$L233="life_steal")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="42">
-      <formula>OR($L226="extra_attack",$L226="aoe")</formula>
+      <formula>OR($L233="extra_attack",$L233="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -14424,24 +14794,24 @@
     <hyperlink ref="F20" r:id="rId57" xr:uid="{BABB0F5C-56BD-4A07-93B3-021E469232CD}"/>
     <hyperlink ref="F32" r:id="rId58" xr:uid="{61098037-76F4-4673-81EC-2C0BEA11F28D}"/>
     <hyperlink ref="F205" r:id="rId59" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
-    <hyperlink ref="F207" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
-    <hyperlink ref="F208" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
-    <hyperlink ref="F209" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
-    <hyperlink ref="F212" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
-    <hyperlink ref="F213" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
-    <hyperlink ref="F214" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
-    <hyperlink ref="F244" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
-    <hyperlink ref="F246" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
-    <hyperlink ref="F265" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
-    <hyperlink ref="F257" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
-    <hyperlink ref="F250" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
+    <hyperlink ref="F214" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
+    <hyperlink ref="F215" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
+    <hyperlink ref="F216" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
+    <hyperlink ref="F219" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
+    <hyperlink ref="F220" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
+    <hyperlink ref="F221" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
+    <hyperlink ref="F251" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
+    <hyperlink ref="F253" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
+    <hyperlink ref="F272" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
+    <hyperlink ref="F264" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
+    <hyperlink ref="F257" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
     <hyperlink ref="F124" r:id="rId71" xr:uid="{163A63BB-52A6-4D6C-B00A-1A7F1F28061D}"/>
     <hyperlink ref="F15" r:id="rId72" xr:uid="{C439613B-BEC0-48C5-814E-36E868E99B31}"/>
     <hyperlink ref="F98" r:id="rId73" xr:uid="{7E273EDB-40F6-4371-AC08-0F1FA586E40C}"/>
-    <hyperlink ref="F221" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
+    <hyperlink ref="F228" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
     <hyperlink ref="I99" r:id="rId75" xr:uid="{FE3AAB39-C871-4F64-AA22-E89C4CD15539}"/>
     <hyperlink ref="F94" r:id="rId76" xr:uid="{3D7B2B26-3280-40AF-A4C5-1389477FB9D2}"/>
-    <hyperlink ref="F217" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
+    <hyperlink ref="F224" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
     <hyperlink ref="F126" r:id="rId78" xr:uid="{F3D65CAC-0B07-443F-8FF4-96BA556BCF65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ED96AA-82C8-4370-8FD3-CE366C75A492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FEDB1D-787A-4261-8006-9369590D24F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$272</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$273</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="1007">
   <si>
     <t>Nombre</t>
   </si>
@@ -841,9 +841,6 @@
     <t>Ataque múltiple</t>
   </si>
   <si>
-    <t>Ataca a todas las cartas enemigas enemigos de forma simultanea.</t>
-  </si>
-  <si>
     <t>Salud</t>
   </si>
   <si>
@@ -2020,9 +2017,6 @@
     <t>Magia caótica</t>
   </si>
   <si>
-    <t>Ataca a todos los enemigos con @skill_power.</t>
-  </si>
-  <si>
     <t>Violencia desatada</t>
   </si>
   <si>
@@ -2041,9 +2035,6 @@
     <t>Grito sónico</t>
   </si>
   <si>
-    <t>Ataca a todos los enemigos.</t>
-  </si>
-  <si>
     <t>Poder demoníaco</t>
   </si>
   <si>
@@ -2176,9 +2167,6 @@
     <t>Inventos letales</t>
   </si>
   <si>
-    <t>Ataca a todos los enemigos causando @skill_power.</t>
-  </si>
-  <si>
     <t>Cazadora kryptoniana</t>
   </si>
   <si>
@@ -3038,6 +3026,24 @@
   </si>
   <si>
     <t>Oscuridad caótica</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/2pJyncH/latest.webp</t>
+  </si>
+  <si>
+    <t>(poder/3) * 4</t>
+  </si>
+  <si>
+    <t>(poder/3) * 2.5</t>
+  </si>
+  <si>
+    <t>poder * 0.1</t>
+  </si>
+  <si>
+    <t>poder / 10</t>
+  </si>
+  <si>
+    <t>(poder/4) * 5</t>
   </si>
 </sst>
 </file>
@@ -3170,7 +3176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3238,12 +3244,322 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="54">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF82D8B1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9F57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD253"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3645,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3708,16 +4024,16 @@
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N2" s="13" t="s">
         <v>268</v>
@@ -3750,16 +4066,16 @@
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="22" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="M3" s="22">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N3" s="22" t="s">
         <v>267</v>
@@ -3792,10 +4108,10 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>269</v>
@@ -3834,13 +4150,13 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M5" s="14"/>
       <c r="N5" s="14" t="s">
@@ -3849,7 +4165,7 @@
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -3870,20 +4186,20 @@
         <v>10</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L6" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="M6" s="15">
-        <v>1000</v>
+      <c r="M6" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N6" s="15" t="s">
         <v>268</v>
@@ -3912,20 +4228,20 @@
         <v>10</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="K7" s="13" t="s">
-        <v>500</v>
-      </c>
       <c r="L7" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>268</v>
@@ -3954,20 +4270,20 @@
         <v>10</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="K8" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>504</v>
       </c>
       <c r="L8" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="M8" s="12">
-        <v>100</v>
+      <c r="M8" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>267</v>
@@ -4000,16 +4316,16 @@
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="K9" s="14" t="s">
         <v>501</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>502</v>
       </c>
       <c r="L9" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M9" s="14">
-        <v>100</v>
+      <c r="M9" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N9" s="14" t="s">
         <v>267</v>
@@ -4032,26 +4348,26 @@
         <v>8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>268</v>
@@ -4084,16 +4400,16 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="K11" s="13" t="s">
-        <v>523</v>
-      </c>
       <c r="L11" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>268</v>
@@ -4126,10 +4442,10 @@
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>524</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>525</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>269</v>
@@ -4168,8 +4484,8 @@
       <c r="J13" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>272</v>
+      <c r="K13" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>269</v>
@@ -4204,19 +4520,19 @@
         <v>10</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="J14" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>289</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>290</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>268</v>
@@ -4239,28 +4555,28 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I15" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N15" s="14" t="s">
         <v>267</v>
@@ -4292,16 +4608,16 @@
         <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="J16" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="K16" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>283</v>
-      </c>
       <c r="L16" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M16" s="14"/>
       <c r="N16" s="14" t="s">
@@ -4334,7 +4650,7 @@
         <v>47</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>266</v>
@@ -4375,16 +4691,16 @@
         <v>47</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M18" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M18" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N18" s="12" t="s">
         <v>268</v>
@@ -4414,10 +4730,10 @@
       </c>
       <c r="H19" s="10"/>
       <c r="J19" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="K19" s="20" t="s">
         <v>526</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>527</v>
       </c>
       <c r="L19" s="20" t="s">
         <v>269</v>
@@ -4446,23 +4762,23 @@
         <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="10"/>
       <c r="J20" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="K20" s="21" t="s">
         <v>528</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>529</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M20" s="15">
-        <v>1000</v>
+      <c r="M20" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N20" s="21" t="s">
         <v>268</v>
@@ -4492,16 +4808,16 @@
       </c>
       <c r="H21" s="10"/>
       <c r="J21" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>530</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>531</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M21" s="15">
-        <v>1000</v>
+      <c r="M21" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N21" s="21" t="s">
         <v>268</v>
@@ -4531,16 +4847,16 @@
       </c>
       <c r="H22" s="10"/>
       <c r="J22" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="K22" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="K22" s="18" t="s">
-        <v>517</v>
-      </c>
       <c r="L22" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="M22" s="18">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M22" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N22" s="18" t="s">
         <v>268</v>
@@ -4570,16 +4886,16 @@
       </c>
       <c r="H23" s="10"/>
       <c r="J23" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="K23" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="K23" s="20" t="s">
-        <v>533</v>
-      </c>
       <c r="L23" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N23" s="20" t="s">
         <v>268</v>
@@ -4609,16 +4925,16 @@
       </c>
       <c r="H24" s="10"/>
       <c r="J24" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="K24" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="K24" s="12" t="s">
-        <v>535</v>
-      </c>
       <c r="L24" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N24" s="12" t="s">
         <v>267</v>
@@ -4648,16 +4964,16 @@
       </c>
       <c r="H25" s="10"/>
       <c r="J25" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="K25" s="15" t="s">
         <v>536</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>537</v>
       </c>
       <c r="L25" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="M25" s="15">
-        <v>1000</v>
+      <c r="M25" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N25" s="15" t="s">
         <v>268</v>
@@ -4689,16 +5005,16 @@
         <v>29</v>
       </c>
       <c r="J26" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="M26" s="13" t="s">
         <v>289</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>290</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>268</v>
@@ -4730,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>266</v>
@@ -4771,16 +5087,16 @@
         <v>71</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="M28" s="22">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M28" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N28" s="22" t="s">
         <v>267</v>
@@ -4812,10 +5128,10 @@
         <v>255</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>272</v>
+        <v>491</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>269</v>
@@ -4853,16 +5169,16 @@
         <v>71</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="K30" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L30" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="M30" s="22">
-        <v>100</v>
+      <c r="M30" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N30" s="22" t="s">
         <v>267</v>
@@ -4894,16 +5210,16 @@
         <v>71</v>
       </c>
       <c r="J31" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>509</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>510</v>
       </c>
       <c r="L31" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M31" s="14">
-        <v>100</v>
+      <c r="M31" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N31" s="14" t="s">
         <v>267</v>
@@ -4926,7 +5242,7 @@
         <v>19</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>10</v>
@@ -4935,16 +5251,16 @@
         <v>77</v>
       </c>
       <c r="J32" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="M32" s="13" t="s">
         <v>289</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L32" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="M32" s="13" t="s">
-        <v>290</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>268</v>
@@ -4976,16 +5292,16 @@
         <v>33</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L33" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M33" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N33" s="15" t="s">
         <v>268</v>
@@ -5015,16 +5331,16 @@
       </c>
       <c r="H34" s="10"/>
       <c r="J34" s="18" t="s">
+        <v>537</v>
+      </c>
+      <c r="K34" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="K34" s="18" t="s">
-        <v>539</v>
-      </c>
       <c r="L34" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="M34" s="18">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M34" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N34" s="18" t="s">
         <v>268</v>
@@ -5056,16 +5372,16 @@
         <v>44</v>
       </c>
       <c r="J35" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="K35" s="14" t="s">
-        <v>541</v>
-      </c>
       <c r="L35" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M35" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N35" s="14" t="s">
         <v>268</v>
@@ -5097,16 +5413,16 @@
         <v>47</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M36" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M36" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N36" s="12" t="s">
         <v>268</v>
@@ -5135,19 +5451,19 @@
         <v>10</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="M37" s="16">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M37" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N37" s="16" t="s">
         <v>267</v>
@@ -5176,19 +5492,19 @@
         <v>10</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="K38" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L38" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="M38" s="22">
-        <v>100</v>
+      <c r="M38" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N38" s="22" t="s">
         <v>267</v>
@@ -5218,16 +5534,16 @@
       </c>
       <c r="H39" s="10"/>
       <c r="J39" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="K39" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="K39" s="18" t="s">
-        <v>517</v>
-      </c>
       <c r="L39" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="M39" s="18">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M39" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N39" s="18" t="s">
         <v>268</v>
@@ -5257,10 +5573,10 @@
       </c>
       <c r="H40" s="10"/>
       <c r="J40" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="K40" s="13" t="s">
         <v>542</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>543</v>
       </c>
       <c r="L40" s="13" t="s">
         <v>269</v>
@@ -5298,16 +5614,16 @@
         <v>71</v>
       </c>
       <c r="J41" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="K41" s="13" t="s">
-        <v>545</v>
-      </c>
       <c r="L41" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N41" s="13" t="s">
         <v>268</v>
@@ -5339,16 +5655,16 @@
         <v>38</v>
       </c>
       <c r="J42" s="22" t="s">
+        <v>545</v>
+      </c>
+      <c r="K42" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="K42" s="22" t="s">
-        <v>547</v>
-      </c>
       <c r="L42" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="M42" s="22">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M42" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N42" s="22" t="s">
         <v>267</v>
@@ -5380,16 +5696,16 @@
         <v>100</v>
       </c>
       <c r="J43" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="M43" s="13" t="s">
         <v>289</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L43" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="M43" s="13" t="s">
-        <v>290</v>
       </c>
       <c r="N43" s="13" t="s">
         <v>268</v>
@@ -5421,16 +5737,16 @@
         <v>103</v>
       </c>
       <c r="J44" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="K44" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="K44" s="13" t="s">
-        <v>549</v>
-      </c>
       <c r="L44" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N44" s="13" t="s">
         <v>268</v>
@@ -5462,16 +5778,16 @@
         <v>100</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L45" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="M45" s="15">
-        <v>1000</v>
+      <c r="M45" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N45" s="15" t="s">
         <v>268</v>
@@ -5479,7 +5795,7 @@
     </row>
     <row r="46" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
@@ -5494,7 +5810,7 @@
         <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>10</v>
@@ -5503,16 +5819,16 @@
         <v>108</v>
       </c>
       <c r="J46" s="19" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="K46" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="M46" s="12" t="s">
         <v>519</v>
-      </c>
-      <c r="L46" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="M46" s="12" t="s">
-        <v>520</v>
       </c>
       <c r="N46" s="19" t="s">
         <v>267</v>
@@ -5544,16 +5860,16 @@
         <v>108</v>
       </c>
       <c r="J47" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="K47" s="14" t="s">
         <v>550</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>551</v>
       </c>
       <c r="L47" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M47" s="14">
-        <v>100</v>
+      <c r="M47" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N47" s="14" t="s">
         <v>267</v>
@@ -5582,19 +5898,19 @@
         <v>10</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J48" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="K48" s="14" t="s">
         <v>552</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>553</v>
       </c>
       <c r="L48" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M48" s="14">
-        <v>100</v>
+      <c r="M48" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N48" s="14" t="s">
         <v>267</v>
@@ -5623,19 +5939,19 @@
         <v>10</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L49" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M49" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M49" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N49" s="15" t="s">
         <v>268</v>
@@ -5665,16 +5981,16 @@
       </c>
       <c r="H50" s="10"/>
       <c r="J50" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="K50" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="K50" s="13" t="s">
-        <v>555</v>
-      </c>
       <c r="L50" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N50" s="13" t="s">
         <v>268</v>
@@ -5697,28 +6013,28 @@
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L51" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M51" s="12">
-        <v>1000</v>
+      <c r="M51" s="29" t="s">
+        <v>1002</v>
       </c>
       <c r="N51" s="12" t="s">
         <v>268</v>
@@ -5752,8 +6068,8 @@
       <c r="J52" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="K52" s="13" t="s">
-        <v>272</v>
+      <c r="K52" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L52" s="13" t="s">
         <v>269</v>
@@ -5791,16 +6107,16 @@
         <v>33</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L53" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M53" s="14">
-        <v>100</v>
+      <c r="M53" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N53" s="14" t="s">
         <v>267</v>
@@ -5808,7 +6124,7 @@
     </row>
     <row r="54" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B54" s="17">
         <v>1</v>
@@ -5823,25 +6139,25 @@
         <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L54" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M54" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M54" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N54" s="15" t="s">
         <v>268</v>
@@ -5849,7 +6165,7 @@
     </row>
     <row r="55" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B55" s="17">
         <v>1</v>
@@ -5858,29 +6174,29 @@
         <v>4500</v>
       </c>
       <c r="D55" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H55" s="17"/>
       <c r="J55" s="12" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L55" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M55" s="12">
-        <v>1000</v>
+      <c r="M55" s="29" t="s">
+        <v>1002</v>
       </c>
       <c r="N55" s="12" t="s">
         <v>268</v>
@@ -5888,7 +6204,7 @@
     </row>
     <row r="56" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B56" s="17">
         <v>1</v>
@@ -5903,25 +6219,25 @@
         <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J56" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="K56" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="K56" s="13" t="s">
-        <v>557</v>
-      </c>
       <c r="L56" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N56" s="13" t="s">
         <v>268</v>
@@ -5929,7 +6245,7 @@
     </row>
     <row r="57" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B57" s="17">
         <v>1</v>
@@ -5944,19 +6260,19 @@
         <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J57" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="K57" s="13" t="s">
         <v>558</v>
-      </c>
-      <c r="K57" s="13" t="s">
-        <v>559</v>
       </c>
       <c r="L57" s="13" t="s">
         <v>269</v>
@@ -5970,7 +6286,7 @@
     </row>
     <row r="58" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B58" s="17">
         <v>1</v>
@@ -5979,31 +6295,31 @@
         <v>4000</v>
       </c>
       <c r="D58" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J58" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="K58" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="K58" s="12" t="s">
-        <v>561</v>
-      </c>
       <c r="L58" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M58" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M58" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N58" s="12" t="s">
         <v>268</v>
@@ -6011,7 +6327,7 @@
     </row>
     <row r="59" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B59" s="17">
         <v>1</v>
@@ -6026,7 +6342,7 @@
         <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>10</v>
@@ -6035,16 +6351,16 @@
         <v>71</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L59" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M59" s="14">
-        <v>100</v>
+      <c r="M59" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N59" s="14" t="s">
         <v>267</v>
@@ -6052,7 +6368,7 @@
     </row>
     <row r="60" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B60" s="17">
         <v>1</v>
@@ -6067,7 +6383,7 @@
         <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>10</v>
@@ -6076,16 +6392,16 @@
         <v>29</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L60" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M60" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M60" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N60" s="15" t="s">
         <v>268</v>
@@ -6093,7 +6409,7 @@
     </row>
     <row r="61" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B61" s="17">
         <v>1</v>
@@ -6108,28 +6424,28 @@
         <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="I61" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="J61" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="K61" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="K61" s="15" t="s">
-        <v>564</v>
-      </c>
       <c r="L61" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M61" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M61" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N61" s="15" t="s">
         <v>268</v>
@@ -6137,7 +6453,7 @@
     </row>
     <row r="62" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B62" s="17">
         <v>1</v>
@@ -6152,20 +6468,20 @@
         <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H62" s="17"/>
       <c r="J62" s="18" t="s">
+        <v>564</v>
+      </c>
+      <c r="K62" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="K62" s="18" t="s">
-        <v>566</v>
-      </c>
       <c r="L62" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M62" s="18">
         <v>2</v>
@@ -6176,7 +6492,7 @@
     </row>
     <row r="63" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B63" s="17">
         <v>1</v>
@@ -6191,17 +6507,22 @@
         <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H63" s="17"/>
+      <c r="H63" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="27" t="s">
+        <v>1001</v>
+      </c>
       <c r="J63" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="K63" s="13" t="s">
         <v>567</v>
-      </c>
-      <c r="K63" s="13" t="s">
-        <v>568</v>
       </c>
       <c r="L63" s="13" t="s">
         <v>269</v>
@@ -6215,7 +6536,7 @@
     </row>
     <row r="64" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B64" s="17">
         <v>1</v>
@@ -6230,7 +6551,7 @@
         <v>19</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>10</v>
@@ -6239,16 +6560,16 @@
         <v>71</v>
       </c>
       <c r="J64" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="K64" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="K64" s="18" t="s">
-        <v>570</v>
-      </c>
       <c r="L64" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="M64" s="18">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M64" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N64" s="18" t="s">
         <v>268</v>
@@ -6256,7 +6577,7 @@
     </row>
     <row r="65" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B65" s="17">
         <v>1</v>
@@ -6271,7 +6592,7 @@
         <v>22</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>10</v>
@@ -6280,16 +6601,16 @@
         <v>47</v>
       </c>
       <c r="J65" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="K65" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="K65" s="13" t="s">
-        <v>572</v>
-      </c>
       <c r="L65" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N65" s="13" t="s">
         <v>268</v>
@@ -6297,7 +6618,7 @@
     </row>
     <row r="66" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B66" s="17">
         <v>1</v>
@@ -6312,7 +6633,7 @@
         <v>22</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>10</v>
@@ -6321,16 +6642,16 @@
         <v>47</v>
       </c>
       <c r="J66" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L66" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M66" s="14" t="s">
         <v>286</v>
-      </c>
-      <c r="K66" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L66" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="M66" s="14" t="s">
-        <v>287</v>
       </c>
       <c r="N66" s="14" t="s">
         <v>267</v>
@@ -6338,7 +6659,7 @@
     </row>
     <row r="67" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B67" s="17">
         <v>1</v>
@@ -6353,7 +6674,7 @@
         <v>22</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>10</v>
@@ -6362,13 +6683,13 @@
         <v>47</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K67" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L67" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M67" s="18">
         <v>2</v>
@@ -6379,7 +6700,7 @@
     </row>
     <row r="68" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B68" s="17">
         <v>1</v>
@@ -6394,25 +6715,25 @@
         <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L68" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M68" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M68" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N68" s="12" t="s">
         <v>268</v>
@@ -6420,7 +6741,7 @@
     </row>
     <row r="69" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B69" s="17">
         <v>1</v>
@@ -6435,25 +6756,25 @@
         <v>19</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J69" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="K69" s="22" t="s">
         <v>574</v>
-      </c>
-      <c r="K69" s="22" t="s">
-        <v>575</v>
       </c>
       <c r="L69" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="M69" s="22">
-        <v>100</v>
+      <c r="M69" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N69" s="22" t="s">
         <v>267</v>
@@ -6461,7 +6782,7 @@
     </row>
     <row r="70" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B70" s="17">
         <v>1</v>
@@ -6470,29 +6791,29 @@
         <v>4000</v>
       </c>
       <c r="D70" s="17">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H70" s="17"/>
       <c r="J70" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L70" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M70" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M70" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N70" s="12" t="s">
         <v>268</v>
@@ -6500,7 +6821,7 @@
     </row>
     <row r="71" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B71" s="17">
         <v>1</v>
@@ -6515,25 +6836,25 @@
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="J71" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="K71" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="K71" s="13" t="s">
-        <v>578</v>
-      </c>
       <c r="L71" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M71" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N71" s="13" t="s">
         <v>268</v>
@@ -6541,7 +6862,7 @@
     </row>
     <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B72" s="17">
         <v>1</v>
@@ -6556,25 +6877,25 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L72" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="M72" s="22">
-        <v>100</v>
+      <c r="M72" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N72" s="22" t="s">
         <v>267</v>
@@ -6582,7 +6903,7 @@
     </row>
     <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B73" s="17">
         <v>1</v>
@@ -6597,22 +6918,22 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="K73" s="18" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M73" s="18">
         <v>2</v>
@@ -6623,7 +6944,7 @@
     </row>
     <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B74" s="17">
         <v>1</v>
@@ -6638,28 +6959,28 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I74" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M74" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N74" s="13" t="s">
         <v>268</v>
@@ -6667,7 +6988,7 @@
     </row>
     <row r="75" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B75" s="17">
         <v>1</v>
@@ -6682,25 +7003,25 @@
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L75" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M75" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M75" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N75" s="12" t="s">
         <v>268</v>
@@ -6708,7 +7029,7 @@
     </row>
     <row r="76" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B76" s="17">
         <v>1</v>
@@ -6723,25 +7044,25 @@
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="K76" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L76" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M76" s="15">
-        <v>1000</v>
+      <c r="M76" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N76" s="21" t="s">
         <v>268</v>
@@ -6749,7 +7070,7 @@
     </row>
     <row r="77" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B77" s="17">
         <v>1</v>
@@ -6758,31 +7079,31 @@
         <v>3500</v>
       </c>
       <c r="D77" s="17">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J77" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="K77" s="12" t="s">
         <v>579</v>
-      </c>
-      <c r="K77" s="12" t="s">
-        <v>580</v>
       </c>
       <c r="L77" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M77" s="12">
-        <v>1000</v>
+      <c r="M77" s="29" t="s">
+        <v>1002</v>
       </c>
       <c r="N77" s="12" t="s">
         <v>268</v>
@@ -6790,7 +7111,7 @@
     </row>
     <row r="78" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B78" s="17">
         <v>1</v>
@@ -6805,25 +7126,25 @@
         <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L78" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="M78" s="12">
-        <v>100</v>
+      <c r="M78" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N78" s="12" t="s">
         <v>267</v>
@@ -6831,7 +7152,7 @@
     </row>
     <row r="79" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B79" s="17">
         <v>1</v>
@@ -6846,22 +7167,22 @@
         <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="K79" s="18" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M79" s="18">
         <v>2</v>
@@ -6872,7 +7193,7 @@
     </row>
     <row r="80" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B80" s="17">
         <v>1</v>
@@ -6887,25 +7208,25 @@
         <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J80" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="K80" s="15" t="s">
         <v>581</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>582</v>
       </c>
       <c r="L80" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="M80" s="15">
-        <v>1000</v>
+      <c r="M80" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N80" s="15" t="s">
         <v>268</v>
@@ -6913,7 +7234,7 @@
     </row>
     <row r="81" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B81" s="17">
         <v>1</v>
@@ -6928,23 +7249,23 @@
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H81" s="17"/>
       <c r="J81" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="K81" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="K81" s="13" t="s">
-        <v>584</v>
-      </c>
       <c r="L81" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M81" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N81" s="13" t="s">
         <v>268</v>
@@ -6952,7 +7273,7 @@
     </row>
     <row r="82" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B82" s="17">
         <v>1</v>
@@ -6967,20 +7288,20 @@
         <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="17"/>
       <c r="J82" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="K82" s="14" t="s">
         <v>585</v>
       </c>
-      <c r="K82" s="14" t="s">
-        <v>586</v>
-      </c>
       <c r="L82" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M82" s="14"/>
       <c r="N82" s="14" t="s">
@@ -6989,7 +7310,7 @@
     </row>
     <row r="83" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B83" s="17">
         <v>1</v>
@@ -7010,22 +7331,22 @@
         <v>10</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I83" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L83" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M83" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M83" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N83" s="12" t="s">
         <v>268</v>
@@ -7033,7 +7354,7 @@
     </row>
     <row r="84" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B84" s="17">
         <v>1</v>
@@ -7048,20 +7369,20 @@
         <v>22</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H84" s="10"/>
       <c r="J84" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="K84" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="K84" s="18" t="s">
-        <v>514</v>
-      </c>
       <c r="L84" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M84" s="18">
         <v>2</v>
@@ -7072,7 +7393,7 @@
     </row>
     <row r="85" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B85" s="17">
         <v>1</v>
@@ -7087,7 +7408,7 @@
         <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>10</v>
@@ -7096,16 +7417,16 @@
         <v>33</v>
       </c>
       <c r="J85" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="K85" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="K85" s="12" t="s">
-        <v>589</v>
-      </c>
       <c r="L85" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M85" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N85" s="12" t="s">
         <v>267</v>
@@ -7113,7 +7434,7 @@
     </row>
     <row r="86" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B86" s="17">
         <v>1</v>
@@ -7128,23 +7449,23 @@
         <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H86" s="17"/>
       <c r="J86" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="K86" s="14" t="s">
         <v>590</v>
-      </c>
-      <c r="K86" s="14" t="s">
-        <v>591</v>
       </c>
       <c r="L86" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="M86" s="14">
-        <v>100</v>
+      <c r="M86" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N86" s="14" t="s">
         <v>267</v>
@@ -7152,7 +7473,7 @@
     </row>
     <row r="87" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B87" s="17">
         <v>1</v>
@@ -7167,23 +7488,23 @@
         <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H87" s="17"/>
       <c r="J87" s="22" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K87" s="22" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L87" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="M87" s="22">
-        <v>100</v>
+      <c r="M87" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N87" s="22" t="s">
         <v>267</v>
@@ -7191,7 +7512,7 @@
     </row>
     <row r="88" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B88" s="17">
         <v>1</v>
@@ -7206,25 +7527,25 @@
         <v>19</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J88" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="K88" s="21" t="s">
         <v>593</v>
-      </c>
-      <c r="K88" s="21" t="s">
-        <v>594</v>
       </c>
       <c r="L88" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M88" s="15">
-        <v>1000</v>
+      <c r="M88" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N88" s="21" t="s">
         <v>268</v>
@@ -7232,7 +7553,7 @@
     </row>
     <row r="89" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B89" s="17">
         <v>1</v>
@@ -7247,23 +7568,23 @@
         <v>22</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="17"/>
       <c r="J89" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K89" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="L89" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="M89" s="12" t="s">
         <v>519</v>
-      </c>
-      <c r="L89" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="M89" s="12" t="s">
-        <v>520</v>
       </c>
       <c r="N89" s="19" t="s">
         <v>267</v>
@@ -7271,7 +7592,7 @@
     </row>
     <row r="90" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B90" s="17">
         <v>1</v>
@@ -7286,23 +7607,23 @@
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="17"/>
       <c r="J90" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="K90" s="23" t="s">
         <v>595</v>
-      </c>
-      <c r="K90" s="23" t="s">
-        <v>596</v>
       </c>
       <c r="L90" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M90" s="14">
-        <v>100</v>
+      <c r="M90" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N90" s="23" t="s">
         <v>267</v>
@@ -7310,7 +7631,7 @@
     </row>
     <row r="91" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B91" s="17">
         <v>1</v>
@@ -7325,28 +7646,28 @@
         <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I91" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L91" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M91" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N91" s="13" t="s">
         <v>268</v>
@@ -7354,7 +7675,7 @@
     </row>
     <row r="92" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B92" s="17">
         <v>1</v>
@@ -7369,25 +7690,25 @@
         <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I92" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="J92" s="18" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="L92" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M92" s="18">
         <v>2</v>
@@ -7398,7 +7719,7 @@
     </row>
     <row r="93" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B93" s="17">
         <v>1</v>
@@ -7413,25 +7734,25 @@
         <v>19</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K93" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L93" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M93" s="15">
-        <v>1000</v>
+      <c r="M93" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N93" s="21" t="s">
         <v>268</v>
@@ -7439,7 +7760,7 @@
     </row>
     <row r="94" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B94" s="17">
         <v>1</v>
@@ -7454,25 +7775,25 @@
         <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="J94" s="20" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="K94" s="20" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L94" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M94" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N94" s="20" t="s">
         <v>268</v>
@@ -7480,7 +7801,7 @@
     </row>
     <row r="95" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B95" s="17">
         <v>1</v>
@@ -7495,22 +7816,22 @@
         <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="J95" s="18" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="K95" s="18" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M95" s="18">
         <v>2</v>
@@ -7521,7 +7842,7 @@
     </row>
     <row r="96" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B96" s="17">
         <v>1</v>
@@ -7536,20 +7857,20 @@
         <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="G96" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H96" s="10"/>
       <c r="J96" s="18" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="K96" s="18" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M96" s="18">
         <v>2</v>
@@ -7560,7 +7881,7 @@
     </row>
     <row r="97" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B97" s="17">
         <v>1</v>
@@ -7575,19 +7896,19 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G97" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="J97" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="K97" s="20" t="s">
         <v>598</v>
-      </c>
-      <c r="K97" s="20" t="s">
-        <v>599</v>
       </c>
       <c r="L97" s="20" t="s">
         <v>269</v>
@@ -7601,7 +7922,7 @@
     </row>
     <row r="98" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B98" s="17">
         <v>1</v>
@@ -7616,7 +7937,7 @@
         <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>10</v>
@@ -7625,16 +7946,16 @@
         <v>71</v>
       </c>
       <c r="J98" s="21" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="K98" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L98" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M98" s="15">
-        <v>1000</v>
+      <c r="M98" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N98" s="21" t="s">
         <v>268</v>
@@ -7642,7 +7963,7 @@
     </row>
     <row r="99" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B99" s="17">
         <v>1</v>
@@ -7657,7 +7978,7 @@
         <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>10</v>
@@ -7666,16 +7987,16 @@
         <v>71</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J99" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="K99" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="K99" s="18" t="s">
-        <v>512</v>
-      </c>
       <c r="L99" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M99" s="18">
         <v>2</v>
@@ -7686,7 +8007,7 @@
     </row>
     <row r="100" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="17">
         <v>1</v>
@@ -7701,23 +8022,23 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H100" s="17"/>
       <c r="J100" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="K100" s="20" t="s">
         <v>600</v>
       </c>
-      <c r="K100" s="20" t="s">
-        <v>601</v>
-      </c>
       <c r="L100" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M100" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N100" s="20" t="s">
         <v>268</v>
@@ -7725,7 +8046,7 @@
     </row>
     <row r="101" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B101" s="17">
         <v>1</v>
@@ -7740,7 +8061,7 @@
         <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>10</v>
@@ -7749,13 +8070,13 @@
         <v>71</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M101" s="14"/>
       <c r="N101" s="23" t="s">
@@ -7764,7 +8085,7 @@
     </row>
     <row r="102" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B102" s="17">
         <v>1</v>
@@ -7779,17 +8100,17 @@
         <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H102" s="17"/>
       <c r="J102" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="K102" s="20" t="s">
         <v>603</v>
-      </c>
-      <c r="K102" s="20" t="s">
-        <v>604</v>
       </c>
       <c r="L102" s="20" t="s">
         <v>269</v>
@@ -7803,7 +8124,7 @@
     </row>
     <row r="103" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B103" s="17">
         <v>1</v>
@@ -7818,20 +8139,20 @@
         <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H103" s="17"/>
       <c r="J103" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="K103" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="K103" s="14" t="s">
-        <v>283</v>
-      </c>
       <c r="L103" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M103" s="14"/>
       <c r="N103" s="14" t="s">
@@ -7840,7 +8161,7 @@
     </row>
     <row r="104" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B104" s="17">
         <v>1</v>
@@ -7855,25 +8176,25 @@
         <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="G104" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J104" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K104" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="L104" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="M104" s="12" t="s">
         <v>519</v>
-      </c>
-      <c r="L104" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="M104" s="12" t="s">
-        <v>520</v>
       </c>
       <c r="N104" s="19" t="s">
         <v>267</v>
@@ -7881,7 +8202,7 @@
     </row>
     <row r="105" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B105" s="17">
         <v>1</v>
@@ -7896,25 +8217,25 @@
         <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="K105" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L105" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M105" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N105" s="14" t="s">
         <v>267</v>
@@ -7922,7 +8243,7 @@
     </row>
     <row r="106" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B106" s="17">
         <v>1</v>
@@ -7937,22 +8258,22 @@
         <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="G106" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J106" s="18" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="K106" s="18" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="L106" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M106" s="18">
         <v>2</v>
@@ -7963,7 +8284,7 @@
     </row>
     <row r="107" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B107" s="17">
         <v>1</v>
@@ -7978,25 +8299,25 @@
         <v>22</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="G107" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J107" s="15" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="K107" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L107" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M107" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M107" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N107" s="15" t="s">
         <v>268</v>
@@ -8004,7 +8325,7 @@
     </row>
     <row r="108" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B108" s="17">
         <v>1</v>
@@ -8019,25 +8340,25 @@
         <v>22</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="G108" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L108" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M108" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M108" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N108" s="12" t="s">
         <v>268</v>
@@ -8045,7 +8366,7 @@
     </row>
     <row r="109" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B109" s="17">
         <v>1</v>
@@ -8060,22 +8381,22 @@
         <v>22</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="I109" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>774</v>
-      </c>
-      <c r="K109" s="13" t="s">
-        <v>272</v>
+        <v>770</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L109" s="13" t="s">
         <v>269</v>
@@ -8089,7 +8410,7 @@
     </row>
     <row r="110" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B110" s="17">
         <v>1</v>
@@ -8098,31 +8419,31 @@
         <v>5000</v>
       </c>
       <c r="D110" s="17">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L110" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M110" s="12">
-        <v>1000</v>
+      <c r="M110" s="29" t="s">
+        <v>1002</v>
       </c>
       <c r="N110" s="12" t="s">
         <v>268</v>
@@ -8130,7 +8451,7 @@
     </row>
     <row r="111" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B111" s="17">
         <v>1</v>
@@ -8145,25 +8466,25 @@
         <v>22</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="G111" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="J111" s="23" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="K111" s="23" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L111" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M111" s="14">
-        <v>100</v>
+      <c r="M111" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N111" s="23" t="s">
         <v>267</v>
@@ -8171,7 +8492,7 @@
     </row>
     <row r="112" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B112" s="17">
         <v>1</v>
@@ -8186,25 +8507,25 @@
         <v>22</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="G112" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H112" s="17" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M112" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M112" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>268</v>
@@ -8212,7 +8533,7 @@
     </row>
     <row r="113" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B113" s="17">
         <v>1</v>
@@ -8227,25 +8548,25 @@
         <v>22</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H113" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J113" s="15" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="K113" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L113" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M113" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M113" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N113" s="15" t="s">
         <v>268</v>
@@ -8253,7 +8574,7 @@
     </row>
     <row r="114" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B114" s="17">
         <v>1</v>
@@ -8268,25 +8589,25 @@
         <v>22</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="G114" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H114" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M114" s="24">
-        <v>100</v>
+      <c r="M114" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>267</v>
@@ -8294,7 +8615,7 @@
     </row>
     <row r="115" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B115" s="17">
         <v>1</v>
@@ -8309,28 +8630,28 @@
         <v>22</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H115" s="17" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="I115" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L115" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M115" s="12">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M115" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N115" s="12" t="s">
         <v>268</v>
@@ -8338,7 +8659,7 @@
     </row>
     <row r="116" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B116" s="17">
         <v>1</v>
@@ -8353,7 +8674,7 @@
         <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G116" s="10" t="s">
         <v>10</v>
@@ -8362,19 +8683,19 @@
         <v>108</v>
       </c>
       <c r="I116" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="J116" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K116" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L116" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M116" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M116" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N116" s="15" t="s">
         <v>268</v>
@@ -8382,7 +8703,7 @@
     </row>
     <row r="117" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B117" s="17">
         <v>1</v>
@@ -8397,7 +8718,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>10</v>
@@ -8408,8 +8729,8 @@
       <c r="J117" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="K117" s="13" t="s">
-        <v>272</v>
+      <c r="K117" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L117" s="13" t="s">
         <v>269</v>
@@ -8423,7 +8744,7 @@
     </row>
     <row r="118" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B118" s="17">
         <v>1</v>
@@ -8438,7 +8759,7 @@
         <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="G118" s="10" t="s">
         <v>10</v>
@@ -8447,16 +8768,16 @@
         <v>108</v>
       </c>
       <c r="J118" s="20" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="K118" s="20" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L118" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M118" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N118" s="20" t="s">
         <v>268</v>
@@ -8464,7 +8785,7 @@
     </row>
     <row r="119" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B119" s="17">
         <v>1</v>
@@ -8479,7 +8800,7 @@
         <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>10</v>
@@ -8488,13 +8809,13 @@
         <v>108</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M119" s="24"/>
       <c r="N119" s="2" t="s">
@@ -8503,7 +8824,7 @@
     </row>
     <row r="120" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B120" s="17">
         <v>1</v>
@@ -8518,7 +8839,7 @@
         <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G120" s="10" t="s">
         <v>10</v>
@@ -8527,16 +8848,16 @@
         <v>108</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="K120" s="23" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L120" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M120" s="14">
-        <v>100</v>
+      <c r="M120" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N120" s="23" t="s">
         <v>267</v>
@@ -8544,7 +8865,7 @@
     </row>
     <row r="121" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B121" s="17">
         <v>1</v>
@@ -8559,7 +8880,7 @@
         <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>10</v>
@@ -8568,16 +8889,16 @@
         <v>108</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="K121" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L121" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="M121" s="12">
-        <v>100</v>
+      <c r="M121" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N121" s="12" t="s">
         <v>267</v>
@@ -8585,7 +8906,7 @@
     </row>
     <row r="122" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B122" s="17">
         <v>1</v>
@@ -8600,23 +8921,23 @@
         <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H122" s="10"/>
       <c r="J122" s="2" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M122" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M122" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>268</v>
@@ -8624,7 +8945,7 @@
     </row>
     <row r="123" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B123" s="17">
         <v>1</v>
@@ -8639,7 +8960,7 @@
         <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>10</v>
@@ -8648,16 +8969,16 @@
         <v>108</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L123" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="M123" s="12">
-        <v>100</v>
+      <c r="M123" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N123" s="12" t="s">
         <v>267</v>
@@ -8665,7 +8986,7 @@
     </row>
     <row r="124" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B124" s="17">
         <v>1</v>
@@ -8680,28 +9001,28 @@
         <v>22</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="I124" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="J124" s="21" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="K124" s="21" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="L124" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="M124" s="15">
-        <v>1000</v>
+      <c r="M124" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N124" s="21" t="s">
         <v>268</v>
@@ -8709,7 +9030,7 @@
     </row>
     <row r="125" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B125" s="17">
         <v>1</v>
@@ -8724,22 +9045,22 @@
         <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="I125" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>981</v>
-      </c>
-      <c r="K125" s="13" t="s">
-        <v>272</v>
+        <v>977</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L125" s="13" t="s">
         <v>269</v>
@@ -8753,7 +9074,7 @@
     </row>
     <row r="126" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B126" s="17">
         <v>1</v>
@@ -8768,14 +9089,14 @@
         <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G126" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H126" s="10"/>
       <c r="I126" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="J126" s="13"/>
       <c r="K126" s="13"/>
@@ -8785,7 +9106,7 @@
     </row>
     <row r="127" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B127" s="17">
         <v>1</v>
@@ -8800,25 +9121,25 @@
         <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G127" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="K127" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="M127" s="24" t="s">
         <v>519</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="M127" s="24" t="s">
-        <v>520</v>
       </c>
       <c r="N127" s="2" t="s">
         <v>267</v>
@@ -8826,7 +9147,7 @@
     </row>
     <row r="128" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B128" s="17">
         <v>1</v>
@@ -8841,25 +9162,25 @@
         <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J128" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="K128" s="23" t="s">
         <v>605</v>
-      </c>
-      <c r="K128" s="23" t="s">
-        <v>606</v>
       </c>
       <c r="L128" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M128" s="14">
-        <v>100</v>
+      <c r="M128" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N128" s="23" t="s">
         <v>267</v>
@@ -8867,7 +9188,7 @@
     </row>
     <row r="129" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B129" s="17">
         <v>1</v>
@@ -8882,22 +9203,22 @@
         <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M129" s="24"/>
       <c r="N129" s="2" t="s">
@@ -8906,7 +9227,7 @@
     </row>
     <row r="130" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B130" s="17">
         <v>1</v>
@@ -8921,25 +9242,25 @@
         <v>19</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="K130" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L130" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M130" s="12">
-        <v>1000</v>
+      <c r="M130" s="29" t="s">
+        <v>1002</v>
       </c>
       <c r="N130" s="12" t="s">
         <v>268</v>
@@ -8947,7 +9268,7 @@
     </row>
     <row r="131" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B131" s="17">
         <v>1</v>
@@ -8962,19 +9283,19 @@
         <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="G131" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="K131" s="13" t="s">
-        <v>272</v>
+        <v>884</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="L131" s="13" t="s">
         <v>269</v>
@@ -8988,7 +9309,7 @@
     </row>
     <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B132" s="17">
         <v>1</v>
@@ -9003,25 +9324,25 @@
         <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G132" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J132" s="15" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="K132" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L132" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M132" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="M132" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="N132" s="15" t="s">
         <v>268</v>
@@ -9029,7 +9350,7 @@
     </row>
     <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B133" s="17">
         <v>1</v>
@@ -9044,25 +9365,25 @@
         <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G133" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L133" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M133" s="24">
-        <v>100</v>
+      <c r="M133" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N133" s="2" t="s">
         <v>267</v>
@@ -9070,7 +9391,7 @@
     </row>
     <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B134" s="17">
         <v>1</v>
@@ -9085,19 +9406,19 @@
         <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L134" s="2" t="s">
         <v>269</v>
@@ -9133,16 +9454,16 @@
       </c>
       <c r="H135" s="10"/>
       <c r="J135" s="23" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="K135" s="23" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L135" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M135" s="14">
-        <v>100</v>
+      <c r="M135" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N135" s="23" t="s">
         <v>267</v>
@@ -9174,16 +9495,16 @@
         <v>126</v>
       </c>
       <c r="J136" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="K136" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="K136" s="2" t="s">
-        <v>608</v>
-      </c>
       <c r="L136" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M136" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M136" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N136" s="2" t="s">
         <v>268</v>
@@ -9215,13 +9536,13 @@
         <v>129</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M137" s="24"/>
       <c r="N137" s="2" t="s">
@@ -9251,19 +9572,19 @@
         <v>125</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M138" s="24">
-        <v>100</v>
+      <c r="M138" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>267</v>
@@ -9295,16 +9616,16 @@
         <v>135</v>
       </c>
       <c r="J139" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="K139" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="K139" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M139" s="24">
-        <v>100</v>
+      <c r="M139" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N139" s="2" t="s">
         <v>267</v>
@@ -9312,7 +9633,7 @@
     </row>
     <row r="140" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B140" s="4">
         <v>1</v>
@@ -9327,23 +9648,23 @@
         <v>8</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H140" s="4"/>
       <c r="J140" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M140" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N140" s="2" t="s">
         <v>268</v>
@@ -9375,16 +9696,16 @@
         <v>138</v>
       </c>
       <c r="J141" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="K141" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K141" s="2" t="s">
-        <v>614</v>
-      </c>
       <c r="L141" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M141" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N141" s="2" t="s">
         <v>268</v>
@@ -9414,16 +9735,16 @@
       </c>
       <c r="H142" s="4"/>
       <c r="J142" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L142" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M142" s="24">
-        <v>100</v>
+      <c r="M142" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>267</v>
@@ -9453,10 +9774,10 @@
       </c>
       <c r="H143" s="4"/>
       <c r="J143" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>269</v>
@@ -9494,16 +9815,16 @@
         <v>141</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M144" s="24">
-        <v>100</v>
+      <c r="M144" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N144" s="2" t="s">
         <v>267</v>
@@ -9526,7 +9847,7 @@
         <v>22</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>125</v>
@@ -9535,16 +9856,16 @@
         <v>213</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M145" s="24">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M145" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N145" s="2" t="s">
         <v>267</v>
@@ -9552,7 +9873,7 @@
     </row>
     <row r="146" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B146" s="4">
         <v>1</v>
@@ -9567,7 +9888,7 @@
         <v>22</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>125</v>
@@ -9576,13 +9897,13 @@
         <v>213</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M146" s="24"/>
       <c r="N146" s="2" t="s">
@@ -9591,7 +9912,7 @@
     </row>
     <row r="147" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B147" s="4">
         <v>1</v>
@@ -9606,7 +9927,7 @@
         <v>22</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>125</v>
@@ -9615,16 +9936,16 @@
         <v>213</v>
       </c>
       <c r="J147" s="14" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="K147" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L147" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M147" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N147" s="14" t="s">
         <v>267</v>
@@ -9656,16 +9977,16 @@
         <v>213</v>
       </c>
       <c r="J148" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="K148" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="L148" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M148" s="24">
-        <v>1000</v>
+      <c r="M148" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N148" s="2" t="s">
         <v>268</v>
@@ -9695,16 +10016,16 @@
       </c>
       <c r="H149" s="4"/>
       <c r="J149" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M149" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>268</v>
@@ -9736,16 +10057,16 @@
         <v>146</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M150" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N150" s="2" t="s">
         <v>268</v>
@@ -9777,10 +10098,10 @@
         <v>149</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>269</v>
@@ -9816,16 +10137,16 @@
       </c>
       <c r="H152" s="4"/>
       <c r="J152" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K152" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="M152" s="24" t="s">
         <v>519</v>
-      </c>
-      <c r="L152" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="M152" s="24" t="s">
-        <v>520</v>
       </c>
       <c r="N152" s="2" t="s">
         <v>267</v>
@@ -9857,16 +10178,16 @@
         <v>154</v>
       </c>
       <c r="J153" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="K153" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="K153" s="2" t="s">
-        <v>626</v>
-      </c>
       <c r="L153" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M153" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M153" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>268</v>
@@ -9896,16 +10217,16 @@
       </c>
       <c r="H154" s="4"/>
       <c r="J154" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L154" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M154" s="24">
-        <v>100</v>
+      <c r="M154" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>267</v>
@@ -9937,13 +10258,13 @@
         <v>159</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M155" s="24">
         <v>2</v>
@@ -9976,16 +10297,16 @@
       </c>
       <c r="H156" s="4"/>
       <c r="J156" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M156" s="24">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M156" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N156" s="2" t="s">
         <v>267</v>
@@ -10017,16 +10338,16 @@
         <v>164</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M157" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>268</v>
@@ -10058,16 +10379,16 @@
         <v>164</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M158" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M158" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>268</v>
@@ -10075,7 +10396,7 @@
     </row>
     <row r="159" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B159" s="4">
         <v>1</v>
@@ -10090,13 +10411,13 @@
         <v>22</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
@@ -10106,7 +10427,7 @@
     </row>
     <row r="160" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B160" s="4">
         <v>1</v>
@@ -10121,25 +10442,25 @@
         <v>22</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H160" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="J160" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="J160" s="2" t="s">
-        <v>911</v>
-      </c>
       <c r="K160" s="2" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M160" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M160" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N160" s="2" t="s">
         <v>268</v>
@@ -10171,10 +10492,10 @@
         <v>164</v>
       </c>
       <c r="J161" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="K161" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="L161" s="2" t="s">
         <v>263</v>
@@ -10209,19 +10530,19 @@
         <v>125</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M162" s="24">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M162" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>268</v>
@@ -10253,16 +10574,16 @@
         <v>146</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M163" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N163" s="2" t="s">
         <v>268</v>
@@ -10294,16 +10615,16 @@
         <v>175</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M164" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>268</v>
@@ -10311,7 +10632,7 @@
     </row>
     <row r="165" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B165" s="4">
         <v>1</v>
@@ -10326,7 +10647,7 @@
         <v>8</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>125</v>
@@ -10335,13 +10656,13 @@
         <v>175</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M165" s="24"/>
       <c r="N165" s="2" t="s">
@@ -10374,10 +10695,10 @@
         <v>175</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L166" s="2" t="s">
         <v>269</v>
@@ -10391,7 +10712,7 @@
     </row>
     <row r="167" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B167" s="4">
         <v>1</v>
@@ -10406,7 +10727,7 @@
         <v>22</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>125</v>
@@ -10415,16 +10736,16 @@
         <v>178</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M167" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M167" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N167" s="2" t="s">
         <v>268</v>
@@ -10432,7 +10753,7 @@
     </row>
     <row r="168" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
@@ -10447,7 +10768,7 @@
         <v>22</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>125</v>
@@ -10456,16 +10777,16 @@
         <v>178</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L168" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M168" s="24">
-        <v>100</v>
+      <c r="M168" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N168" s="2" t="s">
         <v>267</v>
@@ -10497,16 +10818,16 @@
         <v>178</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M169" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>268</v>
@@ -10536,16 +10857,16 @@
       </c>
       <c r="H170" s="4"/>
       <c r="J170" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L170" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M170" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M170" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N170" s="2" t="s">
         <v>268</v>
@@ -10575,16 +10896,16 @@
       </c>
       <c r="H171" s="4"/>
       <c r="J171" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="K171" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="K171" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="L171" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M171" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N171" s="2" t="s">
         <v>267</v>
@@ -10614,16 +10935,16 @@
       </c>
       <c r="H172" s="4"/>
       <c r="J172" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L172" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M172" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M172" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N172" s="2" t="s">
         <v>268</v>
@@ -10655,16 +10976,16 @@
         <v>154</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M173" s="24">
-        <v>100</v>
+      <c r="M173" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N173" s="2" t="s">
         <v>267</v>
@@ -10696,13 +11017,13 @@
         <v>132</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M174" s="24">
         <v>2</v>
@@ -10735,16 +11056,16 @@
       </c>
       <c r="H175" s="4"/>
       <c r="J175" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="K175" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="K175" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="L175" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M175" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M175" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N175" s="2" t="s">
         <v>268</v>
@@ -10774,13 +11095,13 @@
       </c>
       <c r="H176" s="4"/>
       <c r="J176" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="K176" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="K176" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="L176" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M176" s="24"/>
       <c r="N176" s="2" t="s">
@@ -10813,16 +11134,16 @@
         <v>195</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M177" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N177" s="2" t="s">
         <v>268</v>
@@ -10830,7 +11151,7 @@
     </row>
     <row r="178" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B178" s="4">
         <v>1</v>
@@ -10845,7 +11166,7 @@
         <v>19</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>125</v>
@@ -10854,16 +11175,16 @@
         <v>175</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M178" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N178" s="2" t="s">
         <v>268</v>
@@ -10895,16 +11216,16 @@
         <v>198</v>
       </c>
       <c r="J179" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="K179" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M179" s="24">
-        <v>1000</v>
+      <c r="M179" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>268</v>
@@ -10933,16 +11254,16 @@
         <v>125</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M180" s="24">
         <v>2</v>
@@ -10953,7 +11274,7 @@
     </row>
     <row r="181" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B181" s="4">
         <v>1</v>
@@ -10968,7 +11289,7 @@
         <v>22</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>125</v>
@@ -10977,19 +11298,19 @@
         <v>178</v>
       </c>
       <c r="I181" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L181" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M181" s="24">
-        <v>1000</v>
+      <c r="M181" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>268</v>
@@ -11021,16 +11342,16 @@
         <v>178</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M182" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M182" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>268</v>
@@ -11060,16 +11381,16 @@
       </c>
       <c r="H183" s="4"/>
       <c r="J183" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M183" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N183" s="2" t="s">
         <v>268</v>
@@ -11101,16 +11422,16 @@
         <v>146</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M184" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N184" s="2" t="s">
         <v>268</v>
@@ -11140,16 +11461,16 @@
       </c>
       <c r="H185" s="4"/>
       <c r="J185" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="K185" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="K185" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="L185" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M185" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M185" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>268</v>
@@ -11181,16 +11502,16 @@
         <v>175</v>
       </c>
       <c r="J186" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="K186" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="K186" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="L186" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M186" s="24">
-        <v>100</v>
+      <c r="M186" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N186" s="2" t="s">
         <v>267</v>
@@ -11220,16 +11541,16 @@
       </c>
       <c r="H187" s="4"/>
       <c r="J187" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M187" s="24">
-        <v>100</v>
+      <c r="M187" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>267</v>
@@ -11259,13 +11580,13 @@
       </c>
       <c r="H188" s="4"/>
       <c r="J188" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M188" s="24">
         <v>2</v>
@@ -11276,7 +11597,7 @@
     </row>
     <row r="189" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
@@ -11291,23 +11612,23 @@
         <v>22</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H189" s="4"/>
       <c r="J189" s="14" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="K189" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L189" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M189" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N189" s="14" t="s">
         <v>267</v>
@@ -11339,16 +11660,16 @@
         <v>138</v>
       </c>
       <c r="J190" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="K190" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="K190" s="2" t="s">
-        <v>660</v>
-      </c>
       <c r="L190" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M190" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N190" s="2" t="s">
         <v>268</v>
@@ -11378,16 +11699,16 @@
       </c>
       <c r="H191" s="4"/>
       <c r="J191" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M191" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M191" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N191" s="2" t="s">
         <v>268</v>
@@ -11417,16 +11738,16 @@
       </c>
       <c r="H192" s="4"/>
       <c r="J192" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="K192" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="K192" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="L192" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M192" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N192" s="2" t="s">
         <v>267</v>
@@ -11458,10 +11779,10 @@
         <v>146</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>269</v>
@@ -11497,16 +11818,16 @@
       </c>
       <c r="H194" s="4"/>
       <c r="J194" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M194" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M194" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N194" s="2" t="s">
         <v>268</v>
@@ -11536,13 +11857,13 @@
       </c>
       <c r="H195" s="4"/>
       <c r="J195" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M195" s="24"/>
       <c r="N195" s="2" t="s">
@@ -11573,16 +11894,16 @@
       </c>
       <c r="H196" s="4"/>
       <c r="J196" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M196" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N196" s="2" t="s">
         <v>267</v>
@@ -11612,10 +11933,10 @@
       </c>
       <c r="H197" s="4"/>
       <c r="J197" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>269</v>
@@ -11651,10 +11972,10 @@
       </c>
       <c r="H198" s="4"/>
       <c r="J198" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="L198" s="2" t="s">
         <v>269</v>
@@ -11692,16 +12013,16 @@
         <v>178</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M199" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M199" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N199" s="2" t="s">
         <v>268</v>
@@ -11731,10 +12052,10 @@
       </c>
       <c r="H200" s="4"/>
       <c r="J200" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="L200" s="2" t="s">
         <v>269</v>
@@ -11772,16 +12093,16 @@
         <v>135</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L201" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M201" s="24">
-        <v>100</v>
+      <c r="M201" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N201" s="2" t="s">
         <v>267</v>
@@ -11811,13 +12132,13 @@
       </c>
       <c r="H202" s="4"/>
       <c r="J202" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M202" s="24">
         <v>2</v>
@@ -11828,7 +12149,7 @@
     </row>
     <row r="203" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B203" s="4">
         <v>1</v>
@@ -11843,25 +12164,25 @@
         <v>8</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M203" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N203" s="2" t="s">
         <v>268</v>
@@ -11869,7 +12190,7 @@
     </row>
     <row r="204" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B204" s="4">
         <v>1</v>
@@ -11884,25 +12205,25 @@
         <v>8</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="K204" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L204" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M204" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N204" s="14" t="s">
         <v>267</v>
@@ -11910,7 +12231,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B205" s="4">
         <v>1</v>
@@ -11925,23 +12246,23 @@
         <v>19</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H205" s="4"/>
       <c r="J205" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M205" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N205" s="2" t="s">
         <v>268</v>
@@ -11949,7 +12270,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
@@ -11964,19 +12285,19 @@
         <v>22</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="L206" s="2" t="s">
         <v>269</v>
@@ -11990,7 +12311,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
@@ -12005,25 +12326,25 @@
         <v>22</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L207" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M207" s="24">
-        <v>100</v>
+      <c r="M207" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N207" s="2" t="s">
         <v>267</v>
@@ -12031,7 +12352,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
@@ -12046,25 +12367,25 @@
         <v>22</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L208" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M208" s="24">
-        <v>1000</v>
+      <c r="M208" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N208" s="2" t="s">
         <v>268</v>
@@ -12072,7 +12393,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
@@ -12087,22 +12408,22 @@
         <v>22</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M209" s="24"/>
       <c r="N209" s="2" t="s">
@@ -12111,7 +12432,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
@@ -12126,25 +12447,25 @@
         <v>22</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="L210" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M210" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N210" s="2" t="s">
         <v>268</v>
@@ -12152,7 +12473,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
@@ -12167,25 +12488,25 @@
         <v>22</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L211" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M211" s="24">
-        <v>100</v>
+      <c r="M211" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N211" s="2" t="s">
         <v>267</v>
@@ -12193,7 +12514,7 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B212" s="4">
         <v>1</v>
@@ -12208,25 +12529,25 @@
         <v>22</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H212" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J212" s="14" t="s">
         <v>984</v>
       </c>
-      <c r="J212" s="14" t="s">
-        <v>988</v>
-      </c>
       <c r="K212" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L212" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M212" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N212" s="14" t="s">
         <v>267</v>
@@ -12234,7 +12555,7 @@
     </row>
     <row r="213" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B213" s="4">
         <v>1</v>
@@ -12249,19 +12570,19 @@
         <v>22</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="L213" s="2" t="s">
         <v>269</v>
@@ -12275,7 +12596,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B214" s="4">
         <v>1</v>
@@ -12290,25 +12611,25 @@
         <v>22</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L214" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M214" s="24">
-        <v>100</v>
+      <c r="M214" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N214" s="2" t="s">
         <v>267</v>
@@ -12316,7 +12637,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B215" s="4">
         <v>1</v>
@@ -12331,19 +12652,19 @@
         <v>22</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J215" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L215" s="2" t="s">
         <v>269</v>
@@ -12357,7 +12678,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B216" s="4">
         <v>1</v>
@@ -12372,23 +12693,23 @@
         <v>19</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H216" s="4"/>
       <c r="J216" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M216" s="24">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M216" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N216" s="2" t="s">
         <v>267</v>
@@ -12396,7 +12717,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B217" s="4">
         <v>1</v>
@@ -12411,23 +12732,23 @@
         <v>19</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H217" s="4"/>
       <c r="J217" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M217" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N217" s="2" t="s">
         <v>268</v>
@@ -12435,7 +12756,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B218" s="4">
         <v>1</v>
@@ -12450,23 +12771,23 @@
         <v>19</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H218" s="4"/>
       <c r="J218" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L218" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M218" s="24">
-        <v>100</v>
+      <c r="M218" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N218" s="2" t="s">
         <v>267</v>
@@ -12474,7 +12795,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B219" s="4">
         <v>1</v>
@@ -12489,17 +12810,17 @@
         <v>19</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H219" s="4"/>
       <c r="J219" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L219" s="2" t="s">
         <v>269</v>
@@ -12513,7 +12834,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B220" s="4">
         <v>1</v>
@@ -12528,23 +12849,23 @@
         <v>19</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H220" s="4"/>
       <c r="J220" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M220" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M220" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N220" s="2" t="s">
         <v>268</v>
@@ -12552,7 +12873,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B221" s="4">
         <v>1</v>
@@ -12567,23 +12888,23 @@
         <v>22</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H221" s="4"/>
       <c r="J221" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M221" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N221" s="2" t="s">
         <v>268</v>
@@ -12591,7 +12912,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B222" s="4">
         <v>1</v>
@@ -12606,23 +12927,23 @@
         <v>8</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H222" s="4"/>
       <c r="J222" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L222" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M222" s="24">
-        <v>100</v>
+      <c r="M222" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N222" s="2" t="s">
         <v>267</v>
@@ -12630,7 +12951,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B223" s="4">
         <v>1</v>
@@ -12645,23 +12966,23 @@
         <v>8</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H223" s="4"/>
       <c r="J223" s="14" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="K223" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L223" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M223" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N223" s="14" t="s">
         <v>267</v>
@@ -12669,7 +12990,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B224" s="4">
         <v>1</v>
@@ -12684,23 +13005,23 @@
         <v>8</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H224" s="4"/>
       <c r="J224" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M224" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N224" s="2" t="s">
         <v>268</v>
@@ -12708,7 +13029,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B225" s="4">
         <v>1</v>
@@ -12723,25 +13044,25 @@
         <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H225" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="J225" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="J225" s="2" t="s">
-        <v>878</v>
-      </c>
       <c r="K225" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L225" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M225" s="24">
-        <v>50</v>
+        <v>274</v>
+      </c>
+      <c r="M225" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N225" s="2" t="s">
         <v>267</v>
@@ -12749,7 +13070,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B226" s="4">
         <v>1</v>
@@ -12764,19 +13085,19 @@
         <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J226" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="L226" s="2" t="s">
         <v>269</v>
@@ -12790,7 +13111,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B227" s="4">
         <v>1</v>
@@ -12805,25 +13126,25 @@
         <v>8</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J227" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M227" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N227" s="2" t="s">
         <v>268</v>
@@ -12831,7 +13152,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B228" s="4">
         <v>1</v>
@@ -12846,25 +13167,25 @@
         <v>8</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J228" s="14" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="K228" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L228" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M228" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N228" s="14" t="s">
         <v>267</v>
@@ -12872,7 +13193,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B229" s="4">
         <v>1</v>
@@ -12887,25 +13208,25 @@
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J229" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L229" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M229" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M229" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N229" s="2" t="s">
         <v>268</v>
@@ -12913,7 +13234,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B230" s="4">
         <v>1</v>
@@ -12928,28 +13249,28 @@
         <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="I230" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M230" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M230" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N230" s="2" t="s">
         <v>268</v>
@@ -12957,7 +13278,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B231" s="4">
         <v>1</v>
@@ -12972,25 +13293,25 @@
         <v>8</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L231" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M231" s="24">
-        <v>100</v>
+      <c r="M231" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N231" s="2" t="s">
         <v>267</v>
@@ -12998,7 +13319,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B232" s="4">
         <v>1</v>
@@ -13013,18 +13334,18 @@
         <v>8</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B233" s="4">
         <v>1</v>
@@ -13039,23 +13360,23 @@
         <v>8</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H233" s="4"/>
       <c r="J233" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L233" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M233" s="24">
-        <v>100</v>
+      <c r="M233" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N233" s="2" t="s">
         <v>267</v>
@@ -13063,7 +13384,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B234" s="4">
         <v>1</v>
@@ -13078,23 +13399,23 @@
         <v>8</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H234" s="4"/>
       <c r="J234" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N234" s="2" t="s">
         <v>267</v>
@@ -13102,7 +13423,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B235" s="4">
         <v>1</v>
@@ -13117,20 +13438,20 @@
         <v>8</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H235" s="4"/>
       <c r="J235" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M235" s="24"/>
       <c r="N235" s="2" t="s">
@@ -13139,7 +13460,7 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B236" s="4">
         <v>1</v>
@@ -13154,23 +13475,23 @@
         <v>8</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H236" s="4"/>
       <c r="J236" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N236" s="2" t="s">
         <v>268</v>
@@ -13178,7 +13499,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B237" s="4">
         <v>1</v>
@@ -13193,17 +13514,17 @@
         <v>8</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H237" s="4"/>
       <c r="J237" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L237" s="2" t="s">
         <v>269</v>
@@ -13217,7 +13538,7 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B238" s="4">
         <v>1</v>
@@ -13232,23 +13553,23 @@
         <v>8</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H238" s="4"/>
       <c r="J238" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M238" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N238" s="2" t="s">
         <v>268</v>
@@ -13256,7 +13577,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B239" s="4">
         <v>1</v>
@@ -13271,23 +13592,23 @@
         <v>19</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H239" s="4"/>
       <c r="J239" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M239" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M239" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N239" s="2" t="s">
         <v>268</v>
@@ -13295,7 +13616,7 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B240" s="4">
         <v>1</v>
@@ -13310,20 +13631,20 @@
         <v>19</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H240" s="4"/>
       <c r="J240" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M240" s="24"/>
       <c r="N240" s="2" t="s">
@@ -13332,7 +13653,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B241" s="4">
         <v>1</v>
@@ -13347,25 +13668,25 @@
         <v>8</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L241" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M241" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N241" s="2" t="s">
         <v>268</v>
@@ -13373,7 +13694,7 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B242" s="4">
         <v>1</v>
@@ -13388,19 +13709,19 @@
         <v>8</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L242" s="2" t="s">
         <v>269</v>
@@ -13414,7 +13735,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B243" s="4">
         <v>1</v>
@@ -13429,23 +13750,23 @@
         <v>19</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H243" s="4"/>
       <c r="J243" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L243" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M243" s="24">
-        <v>100</v>
+      <c r="M243" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N243" s="2" t="s">
         <v>267</v>
@@ -13453,7 +13774,7 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B244" s="4">
         <v>1</v>
@@ -13468,23 +13789,23 @@
         <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H244" s="4"/>
       <c r="J244" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L244" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M244" s="24">
-        <v>100</v>
+      <c r="M244" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N244" s="2" t="s">
         <v>267</v>
@@ -13492,7 +13813,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B245" s="4">
         <v>1</v>
@@ -13507,23 +13828,23 @@
         <v>8</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H245" s="4"/>
       <c r="J245" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L245" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M245" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N245" s="2" t="s">
         <v>267</v>
@@ -13531,7 +13852,7 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B246" s="4">
         <v>1</v>
@@ -13546,23 +13867,23 @@
         <v>19</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H246" s="4"/>
       <c r="J246" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M246" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M246" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N246" s="2" t="s">
         <v>268</v>
@@ -13570,7 +13891,7 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B247" s="4">
         <v>1</v>
@@ -13585,20 +13906,20 @@
         <v>19</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H247" s="4"/>
       <c r="J247" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M247" s="24"/>
       <c r="N247" s="2" t="s">
@@ -13607,7 +13928,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B248" s="4">
         <v>1</v>
@@ -13622,23 +13943,23 @@
         <v>8</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H248" s="4"/>
       <c r="J248" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="K248" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M248" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N248" s="2" t="s">
         <v>268</v>
@@ -13646,7 +13967,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B249" s="4">
         <v>1</v>
@@ -13661,7 +13982,7 @@
         <v>22</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>125</v>
@@ -13670,16 +13991,16 @@
         <v>178</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L249" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M249" s="24">
-        <v>200</v>
+        <v>514</v>
+      </c>
+      <c r="M249" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N249" s="2" t="s">
         <v>268</v>
@@ -13687,7 +14008,7 @@
     </row>
     <row r="250" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B250" s="4">
         <v>1</v>
@@ -13702,7 +14023,7 @@
         <v>22</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>125</v>
@@ -13711,16 +14032,16 @@
         <v>178</v>
       </c>
       <c r="J250" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L250" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M250" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M250" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N250" s="2" t="s">
         <v>268</v>
@@ -13728,7 +14049,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B251" s="4">
         <v>1</v>
@@ -13743,23 +14064,23 @@
         <v>22</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H251" s="4"/>
       <c r="J251" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L251" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M251" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N251" s="2" t="s">
         <v>268</v>
@@ -13767,7 +14088,7 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B252" s="4">
         <v>1</v>
@@ -13782,20 +14103,20 @@
         <v>22</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L252" s="2" t="s">
         <v>269</v>
@@ -13809,7 +14130,7 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B253" s="4">
         <v>1</v>
@@ -13824,17 +14145,17 @@
         <v>22</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H253" s="4"/>
       <c r="J253" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="K253" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="L253" s="2" t="s">
         <v>263</v>
@@ -13848,7 +14169,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B254" s="4">
         <v>1</v>
@@ -13863,7 +14184,7 @@
         <v>8</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>125</v>
@@ -13872,16 +14193,16 @@
         <v>175</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K254" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L254" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M254" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N254" s="2" t="s">
         <v>268</v>
@@ -13889,7 +14210,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B255" s="4">
         <v>1</v>
@@ -13904,7 +14225,7 @@
         <v>8</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>125</v>
@@ -13913,16 +14234,16 @@
         <v>175</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="K255" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L255" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M255" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N255" s="2" t="s">
         <v>268</v>
@@ -13945,23 +14266,23 @@
         <v>8</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H256" s="4"/>
       <c r="J256" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K256" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M256" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N256" s="2" t="s">
         <v>267</v>
@@ -13969,7 +14290,7 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B257" s="4">
         <v>1</v>
@@ -13984,23 +14305,23 @@
         <v>19</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H257" s="4"/>
       <c r="J257" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L257" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M257" s="24">
-        <v>100</v>
+      <c r="M257" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N257" s="2" t="s">
         <v>267</v>
@@ -14008,7 +14329,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B258" s="4">
         <v>1</v>
@@ -14023,22 +14344,22 @@
         <v>22</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J258" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="K258" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L258" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M258" s="24">
         <v>2</v>
@@ -14049,7 +14370,7 @@
     </row>
     <row r="259" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B259" s="4">
         <v>1</v>
@@ -14064,25 +14385,25 @@
         <v>8</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K259" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L259" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M259" s="24">
-        <v>100</v>
+      <c r="M259" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N259" s="2" t="s">
         <v>267</v>
@@ -14090,7 +14411,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B260" s="4">
         <v>1</v>
@@ -14105,25 +14426,25 @@
         <v>8</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L260" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M260" s="24">
-        <v>100</v>
+      <c r="M260" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N260" s="2" t="s">
         <v>267</v>
@@ -14131,7 +14452,7 @@
     </row>
     <row r="261" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B261" s="4">
         <v>1</v>
@@ -14146,25 +14467,25 @@
         <v>8</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="K261" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L261" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M261" s="24" t="s">
         <v>277</v>
-      </c>
-      <c r="M261" s="24" t="s">
-        <v>278</v>
       </c>
       <c r="N261" s="2" t="s">
         <v>268</v>
@@ -14172,7 +14493,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B262" s="4">
         <v>1</v>
@@ -14187,19 +14508,19 @@
         <v>19</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="K262" s="2" t="s">
-        <v>717</v>
+        <v>603</v>
       </c>
       <c r="L262" s="2" t="s">
         <v>269</v>
@@ -14213,7 +14534,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
@@ -14228,7 +14549,7 @@
         <v>8</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>125</v>
@@ -14237,16 +14558,16 @@
         <v>175</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="K263" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L263" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M263" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N263" s="2" t="s">
         <v>268</v>
@@ -14254,7 +14575,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B264" s="4">
         <v>1</v>
@@ -14269,7 +14590,7 @@
         <v>8</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>125</v>
@@ -14278,16 +14599,16 @@
         <v>175</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="K264" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M264" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N264" s="2" t="s">
         <v>268</v>
@@ -14295,7 +14616,7 @@
     </row>
     <row r="265" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B265" s="4">
         <v>1</v>
@@ -14310,23 +14631,23 @@
         <v>22</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H265" s="4"/>
       <c r="J265" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="K265" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="L265" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M265" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N265" s="2" t="s">
         <v>267</v>
@@ -14334,7 +14655,7 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B266" s="4">
         <v>1</v>
@@ -14349,20 +14670,20 @@
         <v>22</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H266" s="4"/>
       <c r="J266" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="K266" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="L266" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M266" s="24">
         <v>2</v>
@@ -14373,7 +14694,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B267" s="4">
         <v>1</v>
@@ -14388,17 +14709,17 @@
         <v>22</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H267" s="4"/>
       <c r="J267" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K267" s="2" t="s">
-        <v>717</v>
+        <v>603</v>
       </c>
       <c r="L267" s="2" t="s">
         <v>269</v>
@@ -14412,7 +14733,7 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B268" s="4">
         <v>1</v>
@@ -14427,7 +14748,7 @@
         <v>8</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>125</v>
@@ -14436,16 +14757,16 @@
         <v>175</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="K268" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M268" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N268" s="2" t="s">
         <v>268</v>
@@ -14453,7 +14774,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B269" s="4">
         <v>1</v>
@@ -14468,23 +14789,23 @@
         <v>8</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H269" s="4"/>
       <c r="J269" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K269" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L269" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M269" s="24">
-        <v>100</v>
+      <c r="M269" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N269" s="2" t="s">
         <v>267</v>
@@ -14492,7 +14813,7 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B270" s="4">
         <v>1</v>
@@ -14507,23 +14828,23 @@
         <v>22</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H270" s="4"/>
       <c r="J270" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="K270" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L270" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M270" s="24">
-        <v>750</v>
+        <v>273</v>
+      </c>
+      <c r="M270" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N270" s="2" t="s">
         <v>268</v>
@@ -14531,7 +14852,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B271" s="4">
         <v>1</v>
@@ -14546,20 +14867,20 @@
         <v>19</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H271" s="4"/>
       <c r="J271" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="K271" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L271" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M271" s="24"/>
       <c r="N271" s="2" t="s">
@@ -14568,7 +14889,7 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B272" s="4">
         <v>1</v>
@@ -14583,23 +14904,23 @@
         <v>8</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H272" s="4"/>
       <c r="J272" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="K272" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L272" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M272" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N272" s="2" t="s">
         <v>268</v>
@@ -14607,7 +14928,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="26" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B273" s="26">
         <v>1</v>
@@ -14622,32 +14943,31 @@
         <v>22</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G273" s="26" t="s">
         <v>125</v>
       </c>
       <c r="H273" s="4"/>
       <c r="J273" s="14" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="K273" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L273" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M273" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N273" s="14" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N272" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C205:C272">
-    <cfRule type="colorScale" priority="89">
+    <cfRule type="colorScale" priority="131">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14659,7 +14979,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C273:C1048576 C2:C204">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14671,7 +14991,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D205:D272">
-    <cfRule type="colorScale" priority="91">
+    <cfRule type="colorScale" priority="133">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14683,7 +15003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D273:D1048576 D2:D204">
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14695,43 +15015,143 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:N231">
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="11" priority="49">
       <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="10" priority="50">
       <formula>OR($L2="buff",$L2="bonus_buff")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="9" priority="51">
       <formula>OR($L2="dot",$L2="stun")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="8" priority="52">
       <formula>OR($L2="tank",$L2="shield")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="7" priority="53">
       <formula>OR($L2="heal",$L2="heal_all",$L2="life_steal")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="6" priority="54">
       <formula>OR($L2="extra_attack",$L2="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J233:N273">
-    <cfRule type="expression" dxfId="5" priority="37">
+  <conditionalFormatting sqref="J234:N236 J271:N273 J245:N245 J233:L233 N233 J243:L244 N243:N244 J258:N258 J257:L257 N257 J261:N261 J259:L260 N259:N260 J269:L270 N269:N270 J240:N241 J239:L239 N239 J247:N248 J246:L246 N246 J250:N251 J249:L249 N249 J238:N238 J237 L237:N237 J242 L242:N242 J253:N256 J252 L252:N252 J263:N266 J262 L262:N262 J268:N268 J267 L267:N267">
+    <cfRule type="expression" dxfId="53" priority="79">
       <formula>OR($L233="debuff",$L233="bonus_debuff",$L233="revive")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="38">
+    <cfRule type="expression" dxfId="52" priority="80">
       <formula>OR($L233="buff",$L233="bonus_buff")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="39">
+    <cfRule type="expression" dxfId="51" priority="81">
       <formula>OR($L233="dot",$L233="stun")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="40">
+    <cfRule type="expression" dxfId="50" priority="82">
       <formula>OR($L233="tank",$L233="shield")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="41">
+    <cfRule type="expression" dxfId="49" priority="83">
       <formula>OR($L233="heal",$L233="heal_all",$L233="life_steal")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="48" priority="84">
       <formula>OR($L233="extra_attack",$L233="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M270">
+    <cfRule type="expression" dxfId="41" priority="31">
+      <formula>OR($L270="debuff",$L270="bonus_debuff",$L270="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="32">
+      <formula>OR($L270="buff",$L270="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="33">
+      <formula>OR($L270="dot",$L270="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="34">
+      <formula>OR($L270="tank",$L270="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="35">
+      <formula>OR($L270="heal",$L270="heal_all",$L270="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="36">
+      <formula>OR($L270="extra_attack",$L270="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M244">
+    <cfRule type="expression" dxfId="29" priority="19">
+      <formula>OR($L244="debuff",$L244="bonus_debuff",$L244="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="20">
+      <formula>OR($L244="buff",$L244="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="21">
+      <formula>OR($L244="dot",$L244="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="22">
+      <formula>OR($L244="tank",$L244="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>OR($L244="heal",$L244="heal_all",$L244="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="24">
+      <formula>OR($L244="extra_attack",$L244="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M269 M259:M260 M257 M243 M233">
+    <cfRule type="expression" dxfId="23" priority="13">
+      <formula>OR($L233="debuff",$L233="bonus_debuff",$L233="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="14">
+      <formula>OR($L233="buff",$L233="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="15">
+      <formula>OR($L233="dot",$L233="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="16">
+      <formula>OR($L233="tank",$L233="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>OR($L233="heal",$L233="heal_all",$L233="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>OR($L233="extra_attack",$L233="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M249 M246 M239">
+    <cfRule type="expression" dxfId="17" priority="7">
+      <formula>OR($L239="debuff",$L239="bonus_debuff",$L239="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="8">
+      <formula>OR($L239="buff",$L239="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>OR($L239="dot",$L239="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="10">
+      <formula>OR($L239="tank",$L239="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>OR($L239="heal",$L239="heal_all",$L239="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>OR($L239="extra_attack",$L239="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K267 K262 K252 K242 K237">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>OR($L237="debuff",$L237="bonus_debuff",$L237="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>OR($L237="buff",$L237="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>OR($L237="dot",$L237="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>OR($L237="tank",$L237="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>OR($L237="heal",$L237="heal_all",$L237="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>OR($L237="extra_attack",$L237="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -14813,6 +15233,7 @@
     <hyperlink ref="F94" r:id="rId76" xr:uid="{3D7B2B26-3280-40AF-A4C5-1389477FB9D2}"/>
     <hyperlink ref="F224" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
     <hyperlink ref="F126" r:id="rId78" xr:uid="{F3D65CAC-0B07-443F-8FF4-96BA556BCF65}"/>
+    <hyperlink ref="I63" r:id="rId79" xr:uid="{881A0CE1-DA76-4C1F-9249-7E2DF77D0A79}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FEDB1D-787A-4261-8006-9369590D24F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380BCC0B-03B5-4B65-85E8-FC4FA3FF7480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$275</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2627" uniqueCount="1014">
   <si>
     <t>Nombre</t>
   </si>
@@ -3044,6 +3044,27 @@
   </si>
   <si>
     <t>(poder/4) * 5</t>
+  </si>
+  <si>
+    <t>Element Woman</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/5gYNHPph/Element-Woman.jpg</t>
+  </si>
+  <si>
+    <t>Flashpoint</t>
+  </si>
+  <si>
+    <t>Barrera elemental</t>
+  </si>
+  <si>
+    <t>Ignición esmeralda</t>
+  </si>
+  <si>
+    <t>Paradox Demon</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/fYFGGbbd/Paradox-Demon.jpg</t>
   </si>
 </sst>
 </file>
@@ -3265,301 +3286,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="54">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -3934,7 +3661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N273"/>
+  <dimension ref="A1:N275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -9056,19 +8783,19 @@
       <c r="I125" t="s">
         <v>751</v>
       </c>
-      <c r="J125" s="13" t="s">
-        <v>977</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="L125" s="13" t="s">
-        <v>269</v>
+      <c r="J125" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K125" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="L125" s="20" t="s">
+        <v>287</v>
       </c>
       <c r="M125" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="N125" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="N125" s="20" t="s">
         <v>268</v>
       </c>
     </row>
@@ -9098,71 +8825,81 @@
       <c r="I126" t="s">
         <v>975</v>
       </c>
-      <c r="J126" s="13"/>
-      <c r="K126" s="13"/>
-      <c r="L126" s="13"/>
-      <c r="M126" s="13"/>
-      <c r="N126" s="13"/>
+      <c r="J126" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="L126" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="M126" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="N126" s="13" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="127" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>827</v>
+        <v>1007</v>
       </c>
       <c r="B127" s="17">
         <v>1</v>
       </c>
       <c r="C127" s="17">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D127" s="17">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>828</v>
+        <v>1008</v>
       </c>
       <c r="G127" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>823</v>
+        <v>1009</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>829</v>
+        <v>1010</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>518</v>
+        <v>619</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="M127" s="24" t="s">
-        <v>519</v>
+        <v>264</v>
+      </c>
+      <c r="M127" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>929</v>
+        <v>827</v>
       </c>
       <c r="B128" s="17">
         <v>1</v>
       </c>
       <c r="C128" s="17">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="D128" s="17">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>930</v>
+        <v>828</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>10</v>
@@ -9170,40 +8907,40 @@
       <c r="H128" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="J128" s="23" t="s">
-        <v>604</v>
-      </c>
-      <c r="K128" s="23" t="s">
-        <v>605</v>
-      </c>
-      <c r="L128" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="M128" s="14" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N128" s="23" t="s">
+      <c r="J128" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="M128" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="N128" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>831</v>
+        <v>929</v>
       </c>
       <c r="B129" s="17">
         <v>1</v>
       </c>
       <c r="C129" s="17">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D129" s="17">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>832</v>
+        <v>930</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>10</v>
@@ -9211,79 +8948,79 @@
       <c r="H129" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="J129" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L129" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M129" s="24"/>
-      <c r="N129" s="2" t="s">
+      <c r="J129" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="K129" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="L129" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="M129" s="14" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N129" s="23" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>937</v>
+        <v>831</v>
       </c>
       <c r="B130" s="17">
         <v>1</v>
       </c>
       <c r="C130" s="17">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D130" s="17">
         <v>2000</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>938</v>
+        <v>832</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>916</v>
-      </c>
-      <c r="J130" s="12" t="s">
-        <v>939</v>
-      </c>
-      <c r="K130" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="L130" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="M130" s="29" t="s">
-        <v>1002</v>
-      </c>
-      <c r="N130" s="12" t="s">
-        <v>268</v>
+        <v>823</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M130" s="24"/>
+      <c r="N130" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>882</v>
+        <v>937</v>
       </c>
       <c r="B131" s="17">
         <v>1</v>
       </c>
       <c r="C131" s="17">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D131" s="17">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>883</v>
+        <v>938</v>
       </c>
       <c r="G131" s="10" t="s">
         <v>10</v>
@@ -9291,40 +9028,40 @@
       <c r="H131" s="10" t="s">
         <v>916</v>
       </c>
-      <c r="J131" s="13" t="s">
-        <v>884</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="L131" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="M131" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="N131" s="13" t="s">
+      <c r="J131" s="12" t="s">
+        <v>939</v>
+      </c>
+      <c r="K131" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="L131" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="M131" s="29" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N131" s="12" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B132" s="17">
         <v>1</v>
       </c>
       <c r="C132" s="17">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D132" s="17">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="G132" s="10" t="s">
         <v>10</v>
@@ -9332,40 +9069,40 @@
       <c r="H132" s="10" t="s">
         <v>916</v>
       </c>
-      <c r="J132" s="15" t="s">
-        <v>881</v>
-      </c>
-      <c r="K132" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="L132" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="M132" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="N132" s="15" t="s">
+      <c r="J132" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="L132" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="M132" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="N132" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>314</v>
+        <v>879</v>
       </c>
       <c r="B133" s="17">
         <v>1</v>
       </c>
       <c r="C133" s="17">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D133" s="17">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="G133" s="10" t="s">
         <v>10</v>
@@ -9373,146 +9110,146 @@
       <c r="H133" s="10" t="s">
         <v>916</v>
       </c>
-      <c r="J133" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M133" s="28" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N133" s="2" t="s">
-        <v>267</v>
+      <c r="J133" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="K133" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="L133" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M133" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="N133" s="15" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>821</v>
+        <v>314</v>
       </c>
       <c r="B134" s="17">
         <v>1</v>
       </c>
       <c r="C134" s="17">
+        <v>5000</v>
+      </c>
+      <c r="D134" s="17">
         <v>3500</v>
-      </c>
-      <c r="D134" s="17">
-        <v>2000</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>822</v>
+        <v>888</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>823</v>
+        <v>916</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>830</v>
+        <v>889</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M134" s="24" t="s">
-        <v>270</v>
+        <v>260</v>
+      </c>
+      <c r="M134" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="135" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B135" s="3">
-        <v>1</v>
-      </c>
-      <c r="C135" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D135" s="3">
-        <v>2500</v>
+      <c r="A135" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="B135" s="17">
+        <v>1</v>
+      </c>
+      <c r="C135" s="17">
+        <v>3500</v>
+      </c>
+      <c r="D135" s="17">
+        <v>2000</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>122</v>
+        <v>822</v>
       </c>
       <c r="G135" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H135" s="10"/>
-      <c r="J135" s="23" t="s">
+      <c r="H135" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M135" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B136" s="3">
+        <v>1</v>
+      </c>
+      <c r="C136" s="3">
+        <v>4500</v>
+      </c>
+      <c r="D136" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H136" s="10"/>
+      <c r="J136" s="23" t="s">
         <v>931</v>
       </c>
-      <c r="K135" s="23" t="s">
+      <c r="K136" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="L135" s="23" t="s">
+      <c r="L136" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="M135" s="14" t="s">
+      <c r="M136" s="14" t="s">
         <v>1004</v>
       </c>
-      <c r="N135" s="23" t="s">
+      <c r="N136" s="23" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B136" s="4">
-        <v>1</v>
-      </c>
-      <c r="C136" s="4">
-        <v>4500</v>
-      </c>
-      <c r="D136" s="4">
-        <v>2500</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M136" s="31" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="137" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B137" s="4">
         <v>1</v>
@@ -9527,104 +9264,104 @@
         <v>19</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>282</v>
+        <v>607</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M137" s="24"/>
+        <v>514</v>
+      </c>
+      <c r="M137" s="31" t="s">
+        <v>1005</v>
+      </c>
       <c r="N137" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="138" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B138" s="4">
         <v>1</v>
       </c>
       <c r="C138" s="4">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D138" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>850</v>
+        <v>129</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>550</v>
+        <v>282</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M138" s="14" t="s">
-        <v>1004</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M138" s="24"/>
       <c r="N138" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="139" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B139" s="4">
         <v>1</v>
       </c>
       <c r="C139" s="4">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="D139" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>135</v>
+        <v>850</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>611</v>
+        <v>550</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M139" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="M139" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="N139" s="2" t="s">
@@ -9633,70 +9370,70 @@
     </row>
     <row r="140" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>956</v>
+        <v>133</v>
       </c>
       <c r="B140" s="4">
         <v>1</v>
       </c>
       <c r="C140" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D140" s="4">
         <v>4000</v>
       </c>
-      <c r="D140" s="4">
-        <v>2500</v>
-      </c>
       <c r="E140" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>957</v>
+        <v>134</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H140" s="4"/>
+      <c r="H140" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="J140" s="2" t="s">
-        <v>958</v>
+        <v>610</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M140" s="24" t="s">
-        <v>289</v>
+        <v>260</v>
+      </c>
+      <c r="M140" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="141" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>136</v>
+        <v>956</v>
       </c>
       <c r="B141" s="4">
         <v>1</v>
       </c>
       <c r="C141" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D141" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>137</v>
+        <v>957</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H141" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="H141" s="4"/>
       <c r="J141" s="2" t="s">
-        <v>612</v>
+        <v>958</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>613</v>
@@ -9713,7 +9450,7 @@
     </row>
     <row r="142" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="B142" s="4">
         <v>1</v>
@@ -9728,31 +9465,33 @@
         <v>22</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H142" s="4"/>
+      <c r="H142" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="J142" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>550</v>
+        <v>613</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M142" s="14" t="s">
-        <v>1004</v>
+        <v>287</v>
+      </c>
+      <c r="M142" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="143" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B143" s="4">
         <v>1</v>
@@ -9761,110 +9500,108 @@
         <v>5500</v>
       </c>
       <c r="D143" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H143" s="4"/>
       <c r="J143" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>603</v>
+        <v>550</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M143" s="24" t="s">
-        <v>270</v>
+        <v>261</v>
+      </c>
+      <c r="M143" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="144" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="B144" s="4">
         <v>1</v>
       </c>
       <c r="C144" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D144" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H144" s="4" t="s">
-        <v>141</v>
-      </c>
+      <c r="H144" s="4"/>
       <c r="J144" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M144" s="28" t="s">
-        <v>1004</v>
+        <v>269</v>
+      </c>
+      <c r="M144" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="145" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>246</v>
+        <v>139</v>
       </c>
       <c r="B145" s="4">
         <v>1</v>
       </c>
       <c r="C145" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D145" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>479</v>
+        <v>140</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>546</v>
+        <v>611</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M145" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="M145" s="28" t="s">
         <v>1004</v>
       </c>
       <c r="N145" s="2" t="s">
@@ -9873,22 +9610,22 @@
     </row>
     <row r="146" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>885</v>
+        <v>246</v>
       </c>
       <c r="B146" s="4">
         <v>1</v>
       </c>
       <c r="C146" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D146" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>886</v>
+        <v>479</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>125</v>
@@ -9897,37 +9634,39 @@
         <v>213</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>887</v>
+        <v>617</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>282</v>
+        <v>546</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M146" s="24"/>
+        <v>274</v>
+      </c>
+      <c r="M146" s="30" t="s">
+        <v>1004</v>
+      </c>
       <c r="N146" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>799</v>
+        <v>885</v>
       </c>
       <c r="B147" s="4">
         <v>1</v>
       </c>
       <c r="C147" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D147" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>800</v>
+        <v>886</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>125</v>
@@ -9935,40 +9674,38 @@
       <c r="H147" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J147" s="14" t="s">
-        <v>801</v>
-      </c>
-      <c r="K147" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L147" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="M147" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N147" s="14" t="s">
+      <c r="J147" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M147" s="24"/>
+      <c r="N147" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="148" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>244</v>
+        <v>799</v>
       </c>
       <c r="B148" s="4">
         <v>1</v>
       </c>
       <c r="C148" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D148" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>245</v>
+        <v>800</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>125</v>
@@ -9976,56 +9713,58 @@
       <c r="H148" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J148" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="L148" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M148" s="32" t="s">
-        <v>1006</v>
-      </c>
-      <c r="N148" s="2" t="s">
-        <v>268</v>
+      <c r="J148" s="14" t="s">
+        <v>801</v>
+      </c>
+      <c r="K148" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L148" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M148" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="N148" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="B149" s="4">
         <v>1</v>
       </c>
       <c r="C149" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D149" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H149" s="4"/>
+      <c r="H149" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="J149" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M149" s="24" t="s">
-        <v>289</v>
+        <v>264</v>
+      </c>
+      <c r="M149" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>268</v>
@@ -10033,81 +9772,67 @@
     </row>
     <row r="150" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>144</v>
+        <v>1012</v>
       </c>
       <c r="B150" s="4">
         <v>1</v>
       </c>
       <c r="C150" s="4">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="D150" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>145</v>
+        <v>1013</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H150" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="J150" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M150" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="N150" s="2" t="s">
-        <v>268</v>
-      </c>
+      <c r="H150" s="4"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+      <c r="M150" s="32"/>
+      <c r="N150" s="2"/>
     </row>
     <row r="151" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B151" s="4">
         <v>1</v>
       </c>
       <c r="C151" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D151" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H151" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="H151" s="4"/>
       <c r="J151" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="M151" s="24" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>268</v>
@@ -10115,79 +9840,81 @@
     </row>
     <row r="152" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B152" s="4">
         <v>1</v>
       </c>
       <c r="C152" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D152" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H152" s="4"/>
+      <c r="H152" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="J152" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>518</v>
+        <v>613</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>517</v>
+        <v>287</v>
       </c>
       <c r="M152" s="24" t="s">
-        <v>519</v>
+        <v>289</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="153" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B153" s="4">
         <v>1</v>
       </c>
       <c r="C153" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D153" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M153" s="31" t="s">
-        <v>1005</v>
+        <v>269</v>
+      </c>
+      <c r="M153" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>268</v>
@@ -10195,38 +9922,38 @@
     </row>
     <row r="154" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B154" s="4">
         <v>1</v>
       </c>
       <c r="C154" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D154" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H154" s="4"/>
       <c r="J154" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>595</v>
+        <v>518</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M154" s="14" t="s">
-        <v>1004</v>
+        <v>517</v>
+      </c>
+      <c r="M154" s="24" t="s">
+        <v>519</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>267</v>
@@ -10234,40 +9961,40 @@
     </row>
     <row r="155" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B155" s="4">
         <v>1</v>
       </c>
       <c r="C155" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D155" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>565</v>
+        <v>625</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M155" s="24">
-        <v>2</v>
+        <v>514</v>
+      </c>
+      <c r="M155" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>268</v>
@@ -10275,7 +10002,7 @@
     </row>
     <row r="156" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B156" s="4">
         <v>1</v>
@@ -10290,22 +10017,22 @@
         <v>19</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H156" s="4"/>
       <c r="J156" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>546</v>
+        <v>595</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M156" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="M156" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="N156" s="2" t="s">
@@ -10314,40 +10041,40 @@
     </row>
     <row r="157" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B157" s="4">
         <v>1</v>
       </c>
       <c r="C157" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D157" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>613</v>
+        <v>565</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M157" s="24" t="s">
-        <v>289</v>
+        <v>296</v>
+      </c>
+      <c r="M157" s="24">
+        <v>2</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>268</v>
@@ -10355,48 +10082,46 @@
     </row>
     <row r="158" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B158" s="4">
         <v>1</v>
       </c>
       <c r="C158" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D158" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>166</v>
+        <v>19</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H158" s="4" t="s">
-        <v>164</v>
-      </c>
+      <c r="H158" s="4"/>
       <c r="J158" s="2" t="s">
-        <v>740</v>
+        <v>628</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>741</v>
+        <v>546</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M158" s="31" t="s">
-        <v>1005</v>
+        <v>274</v>
+      </c>
+      <c r="M158" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>901</v>
+        <v>162</v>
       </c>
       <c r="B159" s="4">
         <v>1</v>
@@ -10408,53 +10133,63 @@
         <v>1000</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>904</v>
+        <v>19</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="J159" s="2"/>
-      <c r="K159" s="2"/>
-      <c r="L159" s="2"/>
-      <c r="M159" s="24"/>
-      <c r="N159" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M159" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="160" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>905</v>
+        <v>165</v>
       </c>
       <c r="B160" s="4">
         <v>1</v>
       </c>
       <c r="C160" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D160" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>906</v>
+        <v>166</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>903</v>
+        <v>164</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>907</v>
+        <v>740</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>908</v>
+        <v>741</v>
       </c>
       <c r="L160" s="2" t="s">
         <v>514</v>
@@ -10468,81 +10203,71 @@
     </row>
     <row r="161" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>167</v>
+        <v>901</v>
       </c>
       <c r="B161" s="4">
         <v>1</v>
       </c>
       <c r="C161" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D161" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="4" t="s">
-        <v>168</v>
+      <c r="F161" s="8" t="s">
+        <v>904</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="L161" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="M161" s="24">
-        <v>1</v>
-      </c>
-      <c r="N161" s="2" t="s">
-        <v>268</v>
-      </c>
+        <v>903</v>
+      </c>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+      <c r="M161" s="24"/>
+      <c r="N161" s="2"/>
     </row>
     <row r="162" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>169</v>
+        <v>905</v>
       </c>
       <c r="B162" s="4">
         <v>1</v>
       </c>
       <c r="C162" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D162" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F162" s="4" t="s">
-        <v>170</v>
+      <c r="F162" s="8" t="s">
+        <v>906</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>739</v>
+        <v>907</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>560</v>
+        <v>908</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M162" s="29" t="s">
-        <v>1003</v>
+        <v>514</v>
+      </c>
+      <c r="M162" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>268</v>
@@ -10550,40 +10275,40 @@
     </row>
     <row r="163" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B163" s="4">
         <v>1</v>
       </c>
       <c r="C163" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D163" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M163" s="24" t="s">
-        <v>289</v>
+        <v>263</v>
+      </c>
+      <c r="M163" s="24">
+        <v>1</v>
       </c>
       <c r="N163" s="2" t="s">
         <v>268</v>
@@ -10591,40 +10316,40 @@
     </row>
     <row r="164" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B164" s="4">
         <v>1</v>
       </c>
       <c r="C164" s="4">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="D164" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>175</v>
+        <v>902</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>633</v>
+        <v>739</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>613</v>
+        <v>560</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M164" s="24" t="s">
-        <v>289</v>
+        <v>273</v>
+      </c>
+      <c r="M164" s="29" t="s">
+        <v>1003</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>268</v>
@@ -10632,61 +10357,63 @@
     </row>
     <row r="165" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>911</v>
+        <v>171</v>
       </c>
       <c r="B165" s="4">
         <v>1</v>
       </c>
       <c r="C165" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D165" s="4">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>912</v>
+        <v>172</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>913</v>
+        <v>632</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>914</v>
+        <v>613</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M165" s="24"/>
+        <v>287</v>
+      </c>
+      <c r="M165" s="24" t="s">
+        <v>289</v>
+      </c>
       <c r="N165" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="166" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="B166" s="4">
         <v>1</v>
       </c>
       <c r="C166" s="4">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D166" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>252</v>
+        <v>174</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>125</v>
@@ -10695,16 +10422,16 @@
         <v>175</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="M166" s="24" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N166" s="2" t="s">
         <v>268</v>
@@ -10712,104 +10439,102 @@
     </row>
     <row r="167" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>760</v>
+        <v>911</v>
       </c>
       <c r="B167" s="4">
         <v>1</v>
       </c>
       <c r="C167" s="4">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="D167" s="4">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>762</v>
+        <v>912</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>804</v>
+        <v>913</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>684</v>
+        <v>914</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M167" s="31" t="s">
-        <v>1005</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M167" s="24"/>
       <c r="N167" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="168" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>761</v>
+        <v>249</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
       </c>
       <c r="C168" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D168" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>812</v>
+        <v>252</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>803</v>
+        <v>634</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M168" s="14" t="s">
-        <v>1004</v>
+        <v>269</v>
+      </c>
+      <c r="M168" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="169" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>176</v>
+        <v>760</v>
       </c>
       <c r="B169" s="4">
         <v>1</v>
       </c>
       <c r="C169" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D169" s="4">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>177</v>
+        <v>762</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>125</v>
@@ -10818,16 +10543,16 @@
         <v>178</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>613</v>
+        <v>684</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M169" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M169" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>268</v>
@@ -10835,107 +10560,111 @@
     </row>
     <row r="170" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>179</v>
+        <v>761</v>
       </c>
       <c r="B170" s="4">
         <v>1</v>
       </c>
       <c r="C170" s="4">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="D170" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>180</v>
+        <v>812</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H170" s="4"/>
+      <c r="H170" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J170" s="2" t="s">
-        <v>635</v>
+        <v>803</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M170" s="24" t="s">
-        <v>277</v>
+        <v>261</v>
+      </c>
+      <c r="M170" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="171" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B171" s="4">
         <v>1</v>
       </c>
       <c r="C171" s="4">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="D171" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H171" s="4"/>
+      <c r="H171" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J171" s="2" t="s">
-        <v>636</v>
+        <v>802</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>637</v>
+        <v>613</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>517</v>
+        <v>287</v>
       </c>
       <c r="M171" s="24" t="s">
-        <v>519</v>
+        <v>289</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="172" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B172" s="4">
         <v>1</v>
       </c>
       <c r="C172" s="4">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="D172" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H172" s="4"/>
       <c r="J172" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="K172" s="2" t="s">
         <v>563</v>
@@ -10952,40 +10681,38 @@
     </row>
     <row r="173" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B173" s="4">
         <v>1</v>
       </c>
       <c r="C173" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D173" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F173" s="7" t="s">
-        <v>186</v>
+      <c r="F173" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H173" s="4" t="s">
-        <v>154</v>
-      </c>
+      <c r="H173" s="4"/>
       <c r="J173" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M173" s="14" t="s">
-        <v>1004</v>
+        <v>517</v>
+      </c>
+      <c r="M173" s="24" t="s">
+        <v>519</v>
       </c>
       <c r="N173" s="2" t="s">
         <v>267</v>
@@ -10993,40 +10720,38 @@
     </row>
     <row r="174" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B174" s="4">
         <v>1</v>
       </c>
       <c r="C174" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D174" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H174" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="H174" s="4"/>
       <c r="J174" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M174" s="24">
-        <v>2</v>
+        <v>276</v>
+      </c>
+      <c r="M174" s="24" t="s">
+        <v>277</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>268</v>
@@ -11034,46 +10759,48 @@
     </row>
     <row r="175" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B175" s="4">
         <v>1</v>
       </c>
       <c r="C175" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D175" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H175" s="4"/>
+      <c r="H175" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="J175" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>642</v>
+        <v>605</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M175" s="31" t="s">
-        <v>1005</v>
+        <v>261</v>
+      </c>
+      <c r="M175" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="176" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B176" s="4">
         <v>1</v>
@@ -11088,62 +10815,64 @@
         <v>19</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H176" s="4"/>
+      <c r="H176" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="J176" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>644</v>
+        <v>565</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M176" s="24"/>
+        <v>296</v>
+      </c>
+      <c r="M176" s="24">
+        <v>2</v>
+      </c>
       <c r="N176" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="177" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B177" s="4">
         <v>1</v>
       </c>
       <c r="C177" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D177" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H177" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="H177" s="4"/>
       <c r="J177" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M177" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M177" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N177" s="2" t="s">
         <v>268</v>
@@ -11151,7 +10880,7 @@
     </row>
     <row r="178" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>897</v>
+        <v>191</v>
       </c>
       <c r="B178" s="4">
         <v>1</v>
@@ -11160,72 +10889,68 @@
         <v>4000</v>
       </c>
       <c r="D178" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>898</v>
+        <v>192</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H178" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H178" s="4"/>
       <c r="J178" s="2" t="s">
-        <v>899</v>
+        <v>643</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M178" s="24" t="s">
-        <v>289</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M178" s="24"/>
       <c r="N178" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="179" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B179" s="4">
         <v>1</v>
       </c>
       <c r="C179" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D179" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>647</v>
+        <v>613</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M179" s="32" t="s">
-        <v>1006</v>
+        <v>287</v>
+      </c>
+      <c r="M179" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>268</v>
@@ -11233,40 +10958,40 @@
     </row>
     <row r="180" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>199</v>
+        <v>897</v>
       </c>
       <c r="B180" s="4">
         <v>1</v>
       </c>
       <c r="C180" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D180" s="4">
         <v>3000</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>200</v>
+        <v>898</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>849</v>
+        <v>175</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>648</v>
+        <v>899</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>565</v>
+        <v>613</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M180" s="24">
-        <v>2</v>
+        <v>287</v>
+      </c>
+      <c r="M180" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N180" s="2" t="s">
         <v>268</v>
@@ -11274,34 +10999,31 @@
     </row>
     <row r="181" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>813</v>
+        <v>196</v>
       </c>
       <c r="B181" s="4">
         <v>1</v>
       </c>
       <c r="C181" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D181" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>814</v>
+        <v>197</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I181" t="s">
-        <v>816</v>
+        <v>198</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>815</v>
+        <v>646</v>
       </c>
       <c r="K181" s="2" t="s">
         <v>647</v>
@@ -11318,40 +11040,40 @@
     </row>
     <row r="182" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B182" s="4">
         <v>1</v>
       </c>
       <c r="C182" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D182" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>178</v>
+        <v>849</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>642</v>
+        <v>565</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M182" s="31" t="s">
-        <v>1005</v>
+        <v>296</v>
+      </c>
+      <c r="M182" s="24">
+        <v>2</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>268</v>
@@ -11359,38 +11081,43 @@
     </row>
     <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>203</v>
+        <v>813</v>
       </c>
       <c r="B183" s="4">
         <v>1</v>
       </c>
       <c r="C183" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D183" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>204</v>
+        <v>814</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H183" s="4"/>
+      <c r="H183" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I183" t="s">
+        <v>816</v>
+      </c>
       <c r="J183" s="2" t="s">
-        <v>650</v>
+        <v>815</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>613</v>
+        <v>647</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M183" s="24" t="s">
-        <v>289</v>
+        <v>264</v>
+      </c>
+      <c r="M183" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N183" s="2" t="s">
         <v>268</v>
@@ -11398,40 +11125,40 @@
     </row>
     <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B184" s="4">
         <v>1</v>
       </c>
       <c r="C184" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D184" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M184" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M184" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N184" s="2" t="s">
         <v>268</v>
@@ -11439,7 +11166,7 @@
     </row>
     <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B185" s="4">
         <v>1</v>
@@ -11451,26 +11178,26 @@
         <v>2500</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H185" s="4"/>
       <c r="J185" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M185" s="24" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>268</v>
@@ -11478,198 +11205,198 @@
     </row>
     <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B186" s="4">
         <v>1</v>
       </c>
       <c r="C186" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D186" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M186" s="14" t="s">
-        <v>1004</v>
+        <v>287</v>
+      </c>
+      <c r="M186" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="187" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B187" s="4">
         <v>1</v>
       </c>
       <c r="C187" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D187" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H187" s="4"/>
       <c r="J187" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M187" s="14" t="s">
-        <v>1004</v>
+        <v>276</v>
+      </c>
+      <c r="M187" s="24" t="s">
+        <v>277</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="188" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B188" s="4">
         <v>1</v>
       </c>
       <c r="C188" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D188" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H188" s="4"/>
+      <c r="H188" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J188" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>565</v>
+        <v>655</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M188" s="24">
-        <v>2</v>
+        <v>261</v>
+      </c>
+      <c r="M188" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="189" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>947</v>
+        <v>211</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
       </c>
       <c r="C189" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D189" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>948</v>
+        <v>212</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H189" s="4"/>
-      <c r="J189" s="14" t="s">
-        <v>949</v>
-      </c>
-      <c r="K189" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L189" s="14" t="s">
-        <v>283</v>
+      <c r="J189" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="M189" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N189" s="14" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N189" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="190" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B190" s="4">
         <v>1</v>
       </c>
       <c r="C190" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D190" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H190" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="H190" s="4"/>
       <c r="J190" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>659</v>
+        <v>565</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M190" s="24" t="s">
-        <v>289</v>
+        <v>296</v>
+      </c>
+      <c r="M190" s="24">
+        <v>2</v>
       </c>
       <c r="N190" s="2" t="s">
         <v>268</v>
@@ -11677,46 +11404,46 @@
     </row>
     <row r="191" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>218</v>
+        <v>947</v>
       </c>
       <c r="B191" s="4">
         <v>1</v>
       </c>
       <c r="C191" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D191" s="4">
         <v>2000</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>219</v>
+        <v>948</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H191" s="4"/>
-      <c r="J191" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="L191" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M191" s="31" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N191" s="2" t="s">
-        <v>268</v>
+      <c r="J191" s="14" t="s">
+        <v>949</v>
+      </c>
+      <c r="K191" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L191" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M191" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="N191" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="192" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
@@ -11728,67 +11455,67 @@
         <v>2500</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H192" s="4"/>
+      <c r="H192" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="J192" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>517</v>
+        <v>287</v>
       </c>
       <c r="M192" s="24" t="s">
-        <v>519</v>
+        <v>289</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="193" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B193" s="4">
         <v>1</v>
       </c>
       <c r="C193" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D193" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H193" s="4" t="s">
-        <v>146</v>
-      </c>
+      <c r="H193" s="4"/>
       <c r="J193" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M193" s="24" t="s">
-        <v>270</v>
+        <v>514</v>
+      </c>
+      <c r="M193" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N193" s="2" t="s">
         <v>268</v>
@@ -11796,161 +11523,163 @@
     </row>
     <row r="194" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
       </c>
       <c r="C194" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D194" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H194" s="4"/>
       <c r="J194" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M194" s="31" t="s">
-        <v>1005</v>
+        <v>517</v>
+      </c>
+      <c r="M194" s="24" t="s">
+        <v>519</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="195" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B195" s="4">
         <v>1</v>
       </c>
       <c r="C195" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D195" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H195" s="4"/>
+      <c r="H195" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="J195" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>666</v>
+        <v>603</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M195" s="24"/>
+        <v>269</v>
+      </c>
+      <c r="M195" s="24" t="s">
+        <v>270</v>
+      </c>
       <c r="N195" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="196" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B196" s="4">
         <v>1</v>
       </c>
       <c r="C196" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D196" s="4">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H196" s="4"/>
       <c r="J196" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>668</v>
+        <v>642</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="M196" s="24" t="s">
-        <v>519</v>
+        <v>514</v>
+      </c>
+      <c r="M196" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="197" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B197" s="4">
         <v>1</v>
       </c>
       <c r="C197" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D197" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H197" s="4"/>
       <c r="J197" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>603</v>
+        <v>666</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M197" s="24" t="s">
-        <v>270</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M197" s="24"/>
       <c r="N197" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="198" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B198" s="4">
         <v>1</v>
@@ -11959,70 +11688,68 @@
         <v>5000</v>
       </c>
       <c r="D198" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H198" s="4"/>
       <c r="J198" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>603</v>
+        <v>668</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>269</v>
+        <v>517</v>
       </c>
       <c r="M198" s="24" t="s">
-        <v>270</v>
+        <v>519</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="199" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B199" s="4">
         <v>1</v>
       </c>
       <c r="C199" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D199" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H199" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H199" s="4"/>
       <c r="J199" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>642</v>
+        <v>603</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M199" s="31" t="s">
-        <v>1005</v>
+        <v>269</v>
+      </c>
+      <c r="M199" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N199" s="2" t="s">
         <v>268</v>
@@ -12030,29 +11757,29 @@
     </row>
     <row r="200" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B200" s="4">
         <v>1</v>
       </c>
       <c r="C200" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D200" s="4">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H200" s="4"/>
       <c r="J200" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>603</v>
@@ -12069,48 +11796,48 @@
     </row>
     <row r="201" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B201" s="4">
         <v>1</v>
       </c>
       <c r="C201" s="4">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="D201" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M201" s="14" t="s">
-        <v>1004</v>
+        <v>514</v>
+      </c>
+      <c r="M201" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N201" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="202" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B202" s="4">
         <v>1</v>
@@ -12119,29 +11846,29 @@
         <v>3500</v>
       </c>
       <c r="D202" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F202" s="5" t="s">
-        <v>242</v>
+      <c r="F202" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H202" s="4"/>
       <c r="J202" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>675</v>
+        <v>603</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M202" s="24">
-        <v>2</v>
+        <v>269</v>
+      </c>
+      <c r="M202" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N202" s="2" t="s">
         <v>268</v>
@@ -12149,111 +11876,111 @@
     </row>
     <row r="203" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>968</v>
+        <v>239</v>
       </c>
       <c r="B203" s="4">
         <v>1</v>
       </c>
       <c r="C203" s="4">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="D203" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F203" s="5" t="s">
-        <v>969</v>
+      <c r="F203" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>848</v>
+        <v>135</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>970</v>
+        <v>673</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>677</v>
+        <v>655</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M203" s="24" t="s">
-        <v>289</v>
+        <v>261</v>
+      </c>
+      <c r="M203" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N203" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>846</v>
+        <v>241</v>
       </c>
       <c r="B204" s="4">
         <v>1</v>
       </c>
       <c r="C204" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D204" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>847</v>
+        <v>242</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H204" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="J204" s="14" t="s">
-        <v>853</v>
-      </c>
-      <c r="K204" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L204" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="M204" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N204" s="14" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H204" s="4"/>
+      <c r="J204" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="M204" s="24">
+        <v>2</v>
+      </c>
+      <c r="N204" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>377</v>
+        <v>968</v>
       </c>
       <c r="B205" s="4">
         <v>1</v>
       </c>
       <c r="C205" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D205" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>429</v>
+        <v>8</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>969</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H205" s="4"/>
+      <c r="H205" s="4" t="s">
+        <v>848</v>
+      </c>
       <c r="J205" s="2" t="s">
-        <v>676</v>
+        <v>970</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>677</v>
@@ -12268,91 +11995,89 @@
         <v>268</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>997</v>
+        <v>846</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
       </c>
       <c r="C206" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D206" s="4">
         <v>3000</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>998</v>
+        <v>8</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>847</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>980</v>
-      </c>
-      <c r="J206" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="K206" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="L206" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M206" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="N206" s="2" t="s">
-        <v>268</v>
+        <v>848</v>
+      </c>
+      <c r="J206" s="14" t="s">
+        <v>853</v>
+      </c>
+      <c r="K206" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L206" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M206" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="N206" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>994</v>
+        <v>377</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
       </c>
       <c r="C207" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D207" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>995</v>
+        <v>429</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H207" s="4" t="s">
-        <v>980</v>
-      </c>
+      <c r="H207" s="4"/>
       <c r="J207" s="2" t="s">
-        <v>996</v>
+        <v>676</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>550</v>
+        <v>677</v>
       </c>
       <c r="L207" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M207" s="14" t="s">
-        <v>1004</v>
+        <v>287</v>
+      </c>
+      <c r="M207" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N207" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
@@ -12361,13 +12086,13 @@
         <v>4000</v>
       </c>
       <c r="D208" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>125</v>
@@ -12376,16 +12101,16 @@
         <v>980</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M208" s="32" t="s">
-        <v>1006</v>
+        <v>269</v>
+      </c>
+      <c r="M208" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N208" s="2" t="s">
         <v>268</v>
@@ -12393,13 +12118,13 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
       </c>
       <c r="C209" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D209" s="4">
         <v>2500</v>
@@ -12408,7 +12133,7 @@
         <v>22</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>125</v>
@@ -12417,22 +12142,24 @@
         <v>980</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>666</v>
+        <v>550</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M209" s="24"/>
+        <v>261</v>
+      </c>
+      <c r="M209" s="14" t="s">
+        <v>1004</v>
+      </c>
       <c r="N209" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
@@ -12441,13 +12168,13 @@
         <v>4000</v>
       </c>
       <c r="D210" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>125</v>
@@ -12456,16 +12183,16 @@
         <v>980</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>677</v>
+        <v>619</v>
       </c>
       <c r="L210" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M210" s="24" t="s">
-        <v>289</v>
+        <v>264</v>
+      </c>
+      <c r="M210" s="32" t="s">
+        <v>1006</v>
       </c>
       <c r="N210" s="2" t="s">
         <v>268</v>
@@ -12473,22 +12200,22 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>909</v>
+        <v>989</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
       </c>
       <c r="C211" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D211" s="4">
         <v>2500</v>
-      </c>
-      <c r="D211" s="4">
-        <v>1000</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>910</v>
+        <v>988</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>125</v>
@@ -12497,39 +12224,37 @@
         <v>980</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>611</v>
+        <v>666</v>
       </c>
       <c r="L211" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M211" s="28" t="s">
-        <v>1004</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M211" s="24"/>
       <c r="N211" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B212" s="4">
         <v>1</v>
       </c>
       <c r="C212" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="D212" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>125</v>
@@ -12537,40 +12262,40 @@
       <c r="H212" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="J212" s="14" t="s">
-        <v>984</v>
-      </c>
-      <c r="K212" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L212" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="M212" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N212" s="14" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="J212" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M212" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="N212" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>978</v>
+        <v>909</v>
       </c>
       <c r="B213" s="4">
         <v>1</v>
       </c>
       <c r="C213" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="D213" s="4">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>979</v>
+        <v>910</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>125</v>
@@ -12579,39 +12304,39 @@
         <v>980</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>981</v>
+        <v>1000</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M213" s="24" t="s">
-        <v>270</v>
+        <v>260</v>
+      </c>
+      <c r="M213" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N213" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>378</v>
+        <v>982</v>
       </c>
       <c r="B214" s="4">
         <v>1</v>
       </c>
       <c r="C214" s="4">
-        <v>5500</v>
+        <v>2500</v>
       </c>
       <c r="D214" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>430</v>
+        <v>983</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>125</v>
@@ -12619,40 +12344,40 @@
       <c r="H214" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="J214" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="K214" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="L214" s="2" t="s">
-        <v>261</v>
+      <c r="J214" s="14" t="s">
+        <v>984</v>
+      </c>
+      <c r="K214" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L214" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N214" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N214" s="14" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>379</v>
+        <v>978</v>
       </c>
       <c r="B215" s="4">
         <v>1</v>
       </c>
       <c r="C215" s="4">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="D215" s="4">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>431</v>
+        <v>979</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>125</v>
@@ -12661,7 +12386,7 @@
         <v>980</v>
       </c>
       <c r="J215" s="2" t="s">
-        <v>679</v>
+        <v>981</v>
       </c>
       <c r="K215" s="2" t="s">
         <v>603</v>
@@ -12678,37 +12403,39 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B216" s="4">
         <v>1</v>
       </c>
       <c r="C216" s="4">
+        <v>5500</v>
+      </c>
+      <c r="D216" s="4">
         <v>3500</v>
       </c>
-      <c r="D216" s="4">
-        <v>1500</v>
-      </c>
       <c r="E216" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H216" s="4"/>
+      <c r="H216" s="4" t="s">
+        <v>980</v>
+      </c>
       <c r="J216" s="2" t="s">
-        <v>628</v>
+        <v>678</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M216" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="M216" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="N216" s="2" t="s">
@@ -12717,38 +12444,40 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B217" s="4">
         <v>1</v>
       </c>
       <c r="C217" s="4">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="D217" s="4">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H217" s="4"/>
+      <c r="H217" s="4" t="s">
+        <v>980</v>
+      </c>
       <c r="J217" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M217" s="24" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N217" s="2" t="s">
         <v>268</v>
@@ -12756,37 +12485,37 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B218" s="4">
         <v>1</v>
       </c>
       <c r="C218" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D218" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H218" s="4"/>
       <c r="J218" s="2" t="s">
-        <v>681</v>
+        <v>628</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>611</v>
+        <v>546</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M218" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="M218" s="30" t="s">
         <v>1004</v>
       </c>
       <c r="N218" s="2" t="s">
@@ -12795,13 +12524,13 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B219" s="4">
         <v>1</v>
       </c>
       <c r="C219" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D219" s="4">
         <v>2000</v>
@@ -12810,23 +12539,23 @@
         <v>19</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H219" s="4"/>
       <c r="J219" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="M219" s="24" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N219" s="2" t="s">
         <v>268</v>
@@ -12834,77 +12563,77 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B220" s="4">
         <v>1</v>
       </c>
       <c r="C220" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D220" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H220" s="4"/>
       <c r="J220" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>684</v>
+        <v>611</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M220" s="31" t="s">
-        <v>1005</v>
+        <v>260</v>
+      </c>
+      <c r="M220" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B221" s="4">
         <v>1</v>
       </c>
       <c r="C221" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D221" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H221" s="4"/>
       <c r="J221" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M221" s="24" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N221" s="2" t="s">
         <v>268</v>
@@ -12912,85 +12641,85 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B222" s="4">
         <v>1</v>
       </c>
       <c r="C222" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D222" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H222" s="4"/>
       <c r="J222" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>595</v>
+        <v>684</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M222" s="14" t="s">
-        <v>1004</v>
+        <v>514</v>
+      </c>
+      <c r="M222" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>791</v>
+        <v>385</v>
       </c>
       <c r="B223" s="4">
         <v>1</v>
       </c>
       <c r="C223" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D223" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>792</v>
+        <v>437</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H223" s="4"/>
-      <c r="J223" s="14" t="s">
-        <v>793</v>
-      </c>
-      <c r="K223" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L223" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="M223" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N223" s="14" t="s">
-        <v>267</v>
+      <c r="J223" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="L223" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M223" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="N223" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B224" s="4">
         <v>1</v>
@@ -13005,78 +12734,76 @@
         <v>8</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>940</v>
+        <v>438</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H224" s="4"/>
       <c r="J224" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M224" s="24" t="s">
-        <v>289</v>
+        <v>261</v>
+      </c>
+      <c r="M224" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N224" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>872</v>
+        <v>791</v>
       </c>
       <c r="B225" s="4">
         <v>1</v>
       </c>
       <c r="C225" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D225" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>873</v>
+        <v>792</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H225" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="J225" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="K225" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="L225" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M225" s="30" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N225" s="2" t="s">
+      <c r="H225" s="4"/>
+      <c r="J225" s="14" t="s">
+        <v>793</v>
+      </c>
+      <c r="K225" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L225" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M225" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="N225" s="14" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>857</v>
+        <v>387</v>
       </c>
       <c r="B226" s="4">
         <v>1</v>
       </c>
       <c r="C226" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D226" s="4">
         <v>2500</v>
@@ -13085,25 +12812,23 @@
         <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>858</v>
+        <v>940</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H226" s="4" t="s">
-        <v>870</v>
-      </c>
+      <c r="H226" s="4"/>
       <c r="J226" s="2" t="s">
-        <v>859</v>
+        <v>687</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="M226" s="24" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N226" s="2" t="s">
         <v>268</v>
@@ -13111,7 +12836,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B227" s="4">
         <v>1</v>
@@ -13120,13 +12845,13 @@
         <v>4000</v>
       </c>
       <c r="D227" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>125</v>
@@ -13135,30 +12860,30 @@
         <v>870</v>
       </c>
       <c r="J227" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>613</v>
+        <v>546</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M227" s="24" t="s">
-        <v>289</v>
+        <v>274</v>
+      </c>
+      <c r="M227" s="30" t="s">
+        <v>1004</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B228" s="4">
         <v>1</v>
       </c>
       <c r="C228" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D228" s="4">
         <v>2500</v>
@@ -13167,7 +12892,7 @@
         <v>8</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>125</v>
@@ -13175,31 +12900,31 @@
       <c r="H228" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="J228" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="K228" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="L228" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="M228" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="N228" s="14" t="s">
-        <v>267</v>
+      <c r="J228" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="L228" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M228" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="N228" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B229" s="4">
         <v>1</v>
       </c>
       <c r="C229" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D229" s="4">
         <v>2000</v>
@@ -13208,7 +12933,7 @@
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>125</v>
@@ -13217,16 +12942,16 @@
         <v>870</v>
       </c>
       <c r="J229" s="2" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="L229" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M229" s="24" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="N229" s="2" t="s">
         <v>268</v>
@@ -13234,7 +12959,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B230" s="4">
         <v>1</v>
@@ -13243,13 +12968,13 @@
         <v>3500</v>
       </c>
       <c r="D230" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>125</v>
@@ -13257,43 +12982,40 @@
       <c r="H230" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="I230" t="s">
-        <v>864</v>
-      </c>
-      <c r="J230" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="K230" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="L230" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M230" s="31" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N230" s="2" t="s">
-        <v>268</v>
+      <c r="J230" s="14" t="s">
+        <v>854</v>
+      </c>
+      <c r="K230" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L230" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="M230" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="N230" s="14" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>388</v>
+        <v>865</v>
       </c>
       <c r="B231" s="4">
         <v>1</v>
       </c>
       <c r="C231" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D231" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>439</v>
+        <v>866</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>125</v>
@@ -13302,80 +13024,100 @@
         <v>870</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>611</v>
+        <v>653</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M231" s="28" t="s">
-        <v>1004</v>
+        <v>276</v>
+      </c>
+      <c r="M231" s="24" t="s">
+        <v>277</v>
       </c>
       <c r="N231" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B232" s="4">
         <v>1</v>
       </c>
       <c r="C232" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D232" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>452</v>
+        <v>870</v>
+      </c>
+      <c r="I232" t="s">
+        <v>864</v>
+      </c>
+      <c r="J232" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="M232" s="31" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N232" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B233" s="4">
         <v>1</v>
       </c>
       <c r="C233" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D233" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H233" s="4"/>
+      <c r="H233" s="4" t="s">
+        <v>870</v>
+      </c>
       <c r="J233" s="2" t="s">
-        <v>688</v>
+        <v>862</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>655</v>
+        <v>611</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M233" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="M233" s="28" t="s">
         <v>1004</v>
       </c>
       <c r="N233" s="2" t="s">
@@ -13384,52 +13126,39 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>390</v>
+        <v>855</v>
       </c>
       <c r="B234" s="4">
         <v>1</v>
       </c>
       <c r="C234" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D234" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>441</v>
+        <v>856</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H234" s="4"/>
-      <c r="J234" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="K234" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="L234" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="M234" s="24" t="s">
-        <v>519</v>
-      </c>
-      <c r="N234" s="2" t="s">
-        <v>267</v>
+      <c r="H234" s="4" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B235" s="4">
         <v>1</v>
       </c>
       <c r="C235" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D235" s="4">
         <v>2500</v>
@@ -13438,74 +13167,76 @@
         <v>8</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H235" s="4"/>
       <c r="J235" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>585</v>
+        <v>655</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M235" s="24"/>
+        <v>261</v>
+      </c>
+      <c r="M235" s="14" t="s">
+        <v>1004</v>
+      </c>
       <c r="N235" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B236" s="4">
         <v>1</v>
       </c>
       <c r="C236" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D236" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H236" s="4"/>
       <c r="J236" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>287</v>
+        <v>517</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>289</v>
+        <v>519</v>
       </c>
       <c r="N236" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B237" s="4">
         <v>1</v>
       </c>
       <c r="C237" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D237" s="4">
         <v>2500</v>
@@ -13514,56 +13245,54 @@
         <v>8</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H237" s="4"/>
       <c r="J237" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M237" s="24" t="s">
-        <v>270</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M237" s="24"/>
       <c r="N237" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="B238" s="4">
         <v>1</v>
       </c>
       <c r="C238" s="4">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="D238" s="4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H238" s="4"/>
       <c r="J238" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>694</v>
+        <v>613</v>
       </c>
       <c r="L238" s="2" t="s">
         <v>287</v>
@@ -13577,38 +13306,38 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B239" s="4">
         <v>1</v>
       </c>
       <c r="C239" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D239" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H239" s="4"/>
       <c r="J239" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>642</v>
+        <v>603</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M239" s="31" t="s">
-        <v>1005</v>
+        <v>269</v>
+      </c>
+      <c r="M239" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N239" s="2" t="s">
         <v>268</v>
@@ -13616,77 +13345,77 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B240" s="4">
         <v>1</v>
       </c>
       <c r="C240" s="4">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="D240" s="4">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H240" s="4"/>
       <c r="J240" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>644</v>
+        <v>694</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M240" s="24"/>
+        <v>287</v>
+      </c>
+      <c r="M240" s="24" t="s">
+        <v>289</v>
+      </c>
       <c r="N240" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>450</v>
+        <v>394</v>
       </c>
       <c r="B241" s="4">
         <v>1</v>
       </c>
       <c r="C241" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D241" s="4">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H241" s="4" t="s">
-        <v>452</v>
-      </c>
+      <c r="H241" s="4"/>
       <c r="J241" s="2" t="s">
-        <v>547</v>
+        <v>695</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="L241" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M241" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M241" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N241" s="2" t="s">
         <v>268</v>
@@ -13694,87 +13423,85 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B242" s="4">
         <v>1</v>
       </c>
       <c r="C242" s="4">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="D242" s="4">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H242" s="4" t="s">
-        <v>452</v>
-      </c>
+      <c r="H242" s="4"/>
       <c r="J242" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>603</v>
+        <v>644</v>
       </c>
       <c r="L242" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M242" s="24" t="s">
-        <v>270</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M242" s="24"/>
       <c r="N242" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>397</v>
+        <v>450</v>
       </c>
       <c r="B243" s="4">
         <v>1</v>
       </c>
       <c r="C243" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D243" s="4">
         <v>3500</v>
       </c>
-      <c r="D243" s="4">
-        <v>1500</v>
-      </c>
       <c r="E243" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H243" s="4"/>
+      <c r="H243" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="J243" s="2" t="s">
-        <v>698</v>
+        <v>547</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="L243" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M243" s="14" t="s">
-        <v>1004</v>
+        <v>287</v>
+      </c>
+      <c r="M243" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N243" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B244" s="4">
         <v>1</v>
@@ -13789,62 +13516,64 @@
         <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H244" s="4"/>
+      <c r="H244" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="J244" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="L244" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M244" s="28" t="s">
-        <v>1004</v>
+        <v>269</v>
+      </c>
+      <c r="M244" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N244" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B245" s="4">
         <v>1</v>
       </c>
       <c r="C245" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D245" s="4">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H245" s="4"/>
       <c r="J245" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="L245" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="M245" s="24" t="s">
-        <v>519</v>
+        <v>261</v>
+      </c>
+      <c r="M245" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N245" s="2" t="s">
         <v>267</v>
@@ -13852,83 +13581,85 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B246" s="4">
         <v>1</v>
       </c>
       <c r="C246" s="4">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="D246" s="4">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H246" s="4"/>
       <c r="J246" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>642</v>
+        <v>574</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M246" s="31" t="s">
-        <v>1005</v>
+        <v>260</v>
+      </c>
+      <c r="M246" s="28" t="s">
+        <v>1004</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B247" s="4">
         <v>1</v>
       </c>
       <c r="C247" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D247" s="4">
         <v>3000</v>
       </c>
-      <c r="D247" s="4">
-        <v>1000</v>
-      </c>
       <c r="E247" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H247" s="4"/>
       <c r="J247" s="2" t="s">
-        <v>665</v>
+        <v>700</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>666</v>
+        <v>637</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M247" s="24"/>
+        <v>517</v>
+      </c>
+      <c r="M247" s="24" t="s">
+        <v>519</v>
+      </c>
       <c r="N247" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B248" s="4">
         <v>1</v>
@@ -13940,26 +13671,26 @@
         <v>1000</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H248" s="4"/>
       <c r="J248" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K248" s="2" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M248" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M248" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N248" s="2" t="s">
         <v>268</v>
@@ -13967,81 +13698,75 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B249" s="4">
         <v>1</v>
       </c>
       <c r="C249" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D249" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H249" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H249" s="4"/>
       <c r="J249" s="2" t="s">
-        <v>703</v>
+        <v>665</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="L249" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M249" s="31" t="s">
-        <v>1005</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="M249" s="24"/>
       <c r="N249" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B250" s="4">
         <v>1</v>
       </c>
       <c r="C250" s="4">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D250" s="4">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H250" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H250" s="4"/>
       <c r="J250" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="L250" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M250" s="24" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="N250" s="2" t="s">
         <v>268</v>
@@ -14049,80 +13774,81 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B251" s="4">
         <v>1</v>
       </c>
       <c r="C251" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D251" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>743</v>
+        <v>459</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H251" s="4"/>
+      <c r="H251" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="J251" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="L251" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M251" s="24" t="s">
-        <v>289</v>
+        <v>514</v>
+      </c>
+      <c r="M251" s="31" t="s">
+        <v>1005</v>
       </c>
       <c r="N251" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B252" s="4">
         <v>1</v>
       </c>
       <c r="C252" s="4">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D252" s="4">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E252" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>895</v>
+        <v>460</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H252" s="4"/>
-      <c r="I252" t="s">
-        <v>896</v>
+      <c r="H252" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>603</v>
+        <v>653</v>
       </c>
       <c r="L252" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M252" s="24" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="N252" s="2" t="s">
         <v>268</v>
@@ -14130,38 +13856,38 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B253" s="4">
         <v>1</v>
       </c>
       <c r="C253" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D253" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E253" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>461</v>
+        <v>743</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H253" s="4"/>
       <c r="J253" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K253" s="2" t="s">
-        <v>708</v>
+        <v>613</v>
       </c>
       <c r="L253" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="M253" s="24">
-        <v>1</v>
+        <v>287</v>
+      </c>
+      <c r="M253" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N253" s="2" t="s">
         <v>268</v>
@@ -14169,40 +13895,41 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B254" s="4">
         <v>1</v>
       </c>
       <c r="C254" s="4">
+        <v>6000</v>
+      </c>
+      <c r="D254" s="4">
         <v>5000</v>
       </c>
-      <c r="D254" s="4">
-        <v>3000</v>
-      </c>
       <c r="E254" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>462</v>
+        <v>895</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H254" s="4" t="s">
-        <v>175</v>
+      <c r="H254" s="4"/>
+      <c r="I254" t="s">
+        <v>896</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>633</v>
+        <v>706</v>
       </c>
       <c r="K254" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="L254" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M254" s="24" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N254" s="2" t="s">
         <v>268</v>
@@ -14210,7 +13937,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B255" s="4">
         <v>1</v>
@@ -14222,28 +13949,26 @@
         <v>3000</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H255" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H255" s="4"/>
       <c r="J255" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K255" s="2" t="s">
-        <v>613</v>
+        <v>708</v>
       </c>
       <c r="L255" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M255" s="24" t="s">
-        <v>289</v>
+        <v>263</v>
+      </c>
+      <c r="M255" s="24">
+        <v>1</v>
       </c>
       <c r="N255" s="2" t="s">
         <v>268</v>
@@ -14251,150 +13976,150 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>181</v>
+        <v>408</v>
       </c>
       <c r="B256" s="4">
         <v>1</v>
       </c>
       <c r="C256" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D256" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H256" s="4"/>
+      <c r="H256" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J256" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="K256" s="2" t="s">
-        <v>662</v>
+        <v>613</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>517</v>
+        <v>287</v>
       </c>
       <c r="M256" s="24" t="s">
-        <v>519</v>
+        <v>289</v>
       </c>
       <c r="N256" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B257" s="4">
         <v>1</v>
       </c>
       <c r="C257" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D257" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>742</v>
+        <v>463</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H257" s="4"/>
+      <c r="H257" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J257" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="L257" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M257" s="14" t="s">
-        <v>1004</v>
+        <v>287</v>
+      </c>
+      <c r="M257" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N257" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>412</v>
+        <v>181</v>
       </c>
       <c r="B258" s="4">
         <v>1</v>
       </c>
       <c r="C258" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D258" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H258" s="4" t="s">
-        <v>466</v>
-      </c>
+      <c r="H258" s="4"/>
       <c r="J258" s="2" t="s">
-        <v>711</v>
+        <v>636</v>
       </c>
       <c r="K258" s="2" t="s">
-        <v>565</v>
+        <v>662</v>
       </c>
       <c r="L258" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M258" s="24">
-        <v>2</v>
+        <v>517</v>
+      </c>
+      <c r="M258" s="24" t="s">
+        <v>519</v>
       </c>
       <c r="N258" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B259" s="4">
         <v>1</v>
       </c>
       <c r="C259" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D259" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>467</v>
+        <v>742</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H259" s="4" t="s">
-        <v>466</v>
-      </c>
+      <c r="H259" s="4"/>
       <c r="J259" s="2" t="s">
-        <v>604</v>
+        <v>710</v>
       </c>
       <c r="K259" s="2" t="s">
         <v>655</v>
@@ -14411,7 +14136,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B260" s="4">
         <v>1</v>
@@ -14423,10 +14148,10 @@
         <v>2500</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>125</v>
@@ -14435,39 +14160,39 @@
         <v>466</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>551</v>
+        <v>711</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>655</v>
+        <v>565</v>
       </c>
       <c r="L260" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M260" s="14" t="s">
-        <v>1004</v>
+        <v>296</v>
+      </c>
+      <c r="M260" s="24">
+        <v>2</v>
       </c>
       <c r="N260" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="261" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B261" s="4">
         <v>1</v>
       </c>
       <c r="C261" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D261" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>125</v>
@@ -14476,39 +14201,39 @@
         <v>466</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>712</v>
+        <v>604</v>
       </c>
       <c r="K261" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L261" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M261" s="24" t="s">
-        <v>277</v>
+        <v>261</v>
+      </c>
+      <c r="M261" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N261" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B262" s="4">
         <v>1</v>
       </c>
       <c r="C262" s="4">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D262" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>125</v>
@@ -14517,57 +14242,57 @@
         <v>466</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>713</v>
+        <v>551</v>
       </c>
       <c r="K262" s="2" t="s">
-        <v>603</v>
+        <v>655</v>
       </c>
       <c r="L262" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M262" s="24" t="s">
-        <v>270</v>
+        <v>261</v>
+      </c>
+      <c r="M262" s="14" t="s">
+        <v>1004</v>
       </c>
       <c r="N262" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
       </c>
       <c r="C263" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D263" s="4">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>175</v>
+        <v>466</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K263" s="2" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
       <c r="L263" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="M263" s="24" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="N263" s="2" t="s">
         <v>268</v>
@@ -14575,198 +14300,200 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B264" s="4">
         <v>1</v>
       </c>
       <c r="C264" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D264" s="4">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>738</v>
+        <v>470</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>175</v>
+        <v>466</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="K264" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M264" s="24" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N264" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B265" s="4">
         <v>1</v>
       </c>
       <c r="C265" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D265" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H265" s="4"/>
+      <c r="H265" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J265" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="K265" s="2" t="s">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="L265" s="2" t="s">
-        <v>517</v>
+        <v>287</v>
       </c>
       <c r="M265" s="24" t="s">
-        <v>519</v>
+        <v>289</v>
       </c>
       <c r="N265" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B266" s="4">
         <v>1</v>
       </c>
       <c r="C266" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D266" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>446</v>
+        <v>738</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H266" s="4"/>
+      <c r="H266" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J266" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="K266" s="2" t="s">
-        <v>718</v>
+        <v>613</v>
       </c>
       <c r="L266" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M266" s="24">
-        <v>2</v>
+        <v>287</v>
+      </c>
+      <c r="M266" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N266" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>915</v>
+        <v>419</v>
       </c>
       <c r="B267" s="4">
         <v>1</v>
       </c>
       <c r="C267" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D267" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H267" s="4"/>
       <c r="J267" s="2" t="s">
-        <v>663</v>
+        <v>716</v>
       </c>
       <c r="K267" s="2" t="s">
-        <v>603</v>
+        <v>668</v>
       </c>
       <c r="L267" s="2" t="s">
-        <v>269</v>
+        <v>517</v>
       </c>
       <c r="M267" s="24" t="s">
-        <v>270</v>
+        <v>519</v>
       </c>
       <c r="N267" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B268" s="4">
         <v>1</v>
       </c>
       <c r="C268" s="4">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="D268" s="4">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>474</v>
+        <v>446</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H268" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="H268" s="4"/>
       <c r="J268" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="K268" s="2" t="s">
-        <v>613</v>
+        <v>718</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M268" s="24" t="s">
-        <v>289</v>
+        <v>296</v>
+      </c>
+      <c r="M268" s="24">
+        <v>2</v>
       </c>
       <c r="N268" s="2" t="s">
         <v>268</v>
@@ -14774,77 +14501,79 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>422</v>
+        <v>915</v>
       </c>
       <c r="B269" s="4">
         <v>1</v>
       </c>
       <c r="C269" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D269" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H269" s="4"/>
       <c r="J269" s="2" t="s">
-        <v>688</v>
+        <v>663</v>
       </c>
       <c r="K269" s="2" t="s">
-        <v>655</v>
+        <v>603</v>
       </c>
       <c r="L269" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M269" s="14" t="s">
-        <v>1004</v>
+        <v>269</v>
+      </c>
+      <c r="M269" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="N269" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B270" s="4">
         <v>1</v>
       </c>
       <c r="C270" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D270" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E270" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H270" s="4"/>
+      <c r="H270" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J270" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="K270" s="2" t="s">
-        <v>560</v>
+        <v>613</v>
       </c>
       <c r="L270" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M270" s="29" t="s">
-        <v>1003</v>
+        <v>287</v>
+      </c>
+      <c r="M270" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="N270" s="2" t="s">
         <v>268</v>
@@ -14852,7 +14581,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B271" s="4">
         <v>1</v>
@@ -14864,32 +14593,34 @@
         <v>2500</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H271" s="4"/>
       <c r="J271" s="2" t="s">
-        <v>721</v>
+        <v>688</v>
       </c>
       <c r="K271" s="2" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="L271" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M271" s="24"/>
+        <v>261</v>
+      </c>
+      <c r="M271" s="14" t="s">
+        <v>1004</v>
+      </c>
       <c r="N271" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B272" s="4">
         <v>1</v>
@@ -14898,75 +14629,151 @@
         <v>4500</v>
       </c>
       <c r="D272" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H272" s="4"/>
       <c r="J272" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="K272" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="L272" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M272" s="29" t="s">
+        <v>1003</v>
+      </c>
+      <c r="N272" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B273" s="4">
+        <v>1</v>
+      </c>
+      <c r="C273" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D273" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E273" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G273" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H273" s="4"/>
+      <c r="J273" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="L273" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M273" s="24"/>
+      <c r="N273" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B274" s="4">
+        <v>1</v>
+      </c>
+      <c r="C274" s="4">
+        <v>4500</v>
+      </c>
+      <c r="D274" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E274" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H274" s="4"/>
+      <c r="J274" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="K272" s="2" t="s">
+      <c r="K274" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L272" s="2" t="s">
+      <c r="L274" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="M272" s="24" t="s">
+      <c r="M274" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="N272" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="N274" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A275" s="26" t="s">
         <v>757</v>
       </c>
-      <c r="B273" s="26">
-        <v>1</v>
-      </c>
-      <c r="C273" s="26">
+      <c r="B275" s="26">
+        <v>1</v>
+      </c>
+      <c r="C275" s="26">
         <v>5000</v>
       </c>
-      <c r="D273" s="26">
+      <c r="D275" s="26">
         <v>3000</v>
       </c>
-      <c r="E273" s="26" t="s">
+      <c r="E275" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F273" s="4" t="s">
+      <c r="F275" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="G273" s="26" t="s">
+      <c r="G275" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="H273" s="4"/>
-      <c r="J273" s="14" t="s">
+      <c r="H275" s="4"/>
+      <c r="J275" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="K273" s="14" t="s">
+      <c r="K275" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="L273" s="14" t="s">
+      <c r="L275" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="M273" s="14" t="s">
+      <c r="M275" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="N273" s="14" t="s">
+      <c r="N275" s="14" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C205:C272">
+  <conditionalFormatting sqref="C207:C274">
     <cfRule type="colorScale" priority="131">
       <colorScale>
         <cfvo type="min"/>
@@ -14978,7 +14785,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C273:C1048576 C2:C204">
+  <conditionalFormatting sqref="C275:C1048576 C2:C206">
     <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
@@ -14990,7 +14797,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D205:D272">
+  <conditionalFormatting sqref="D207:D274">
     <cfRule type="colorScale" priority="133">
       <colorScale>
         <cfvo type="min"/>
@@ -15002,7 +14809,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D273:D1048576 D2:D204">
+  <conditionalFormatting sqref="D275:D1048576 D2:D206">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -15014,7 +14821,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:N231">
+  <conditionalFormatting sqref="J2:N233">
     <cfRule type="expression" dxfId="11" priority="49">
       <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
     </cfRule>
@@ -15034,124 +14841,24 @@
       <formula>OR($L2="extra_attack",$L2="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J234:N236 J271:N273 J245:N245 J233:L233 N233 J243:L244 N243:N244 J258:N258 J257:L257 N257 J261:N261 J259:L260 N259:N260 J269:L270 N269:N270 J240:N241 J239:L239 N239 J247:N248 J246:L246 N246 J250:N251 J249:L249 N249 J238:N238 J237 L237:N237 J242 L242:N242 J253:N256 J252 L252:N252 J263:N266 J262 L262:N262 J268:N268 J267 L267:N267">
-    <cfRule type="expression" dxfId="53" priority="79">
-      <formula>OR($L233="debuff",$L233="bonus_debuff",$L233="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="80">
-      <formula>OR($L233="buff",$L233="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="81">
-      <formula>OR($L233="dot",$L233="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="82">
-      <formula>OR($L233="tank",$L233="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="83">
-      <formula>OR($L233="heal",$L233="heal_all",$L233="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="84">
-      <formula>OR($L233="extra_attack",$L233="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M270">
-    <cfRule type="expression" dxfId="41" priority="31">
-      <formula>OR($L270="debuff",$L270="bonus_debuff",$L270="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="32">
-      <formula>OR($L270="buff",$L270="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="33">
-      <formula>OR($L270="dot",$L270="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="34">
-      <formula>OR($L270="tank",$L270="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="35">
-      <formula>OR($L270="heal",$L270="heal_all",$L270="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="36">
-      <formula>OR($L270="extra_attack",$L270="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M244">
-    <cfRule type="expression" dxfId="29" priority="19">
-      <formula>OR($L244="debuff",$L244="bonus_debuff",$L244="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="20">
-      <formula>OR($L244="buff",$L244="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="21">
-      <formula>OR($L244="dot",$L244="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22">
-      <formula>OR($L244="tank",$L244="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="23">
-      <formula>OR($L244="heal",$L244="heal_all",$L244="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
-      <formula>OR($L244="extra_attack",$L244="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M269 M259:M260 M257 M243 M233">
-    <cfRule type="expression" dxfId="23" priority="13">
-      <formula>OR($L233="debuff",$L233="bonus_debuff",$L233="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="14">
-      <formula>OR($L233="buff",$L233="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="15">
-      <formula>OR($L233="dot",$L233="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="16">
-      <formula>OR($L233="tank",$L233="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="17">
-      <formula>OR($L233="heal",$L233="heal_all",$L233="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>OR($L233="extra_attack",$L233="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M249 M246 M239">
-    <cfRule type="expression" dxfId="17" priority="7">
-      <formula>OR($L239="debuff",$L239="bonus_debuff",$L239="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="8">
-      <formula>OR($L239="buff",$L239="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>OR($L239="dot",$L239="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10">
-      <formula>OR($L239="tank",$L239="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11">
-      <formula>OR($L239="heal",$L239="heal_all",$L239="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>OR($L239="extra_attack",$L239="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K267 K262 K252 K242 K237">
+  <conditionalFormatting sqref="J235:N275">
     <cfRule type="expression" dxfId="5" priority="1">
-      <formula>OR($L237="debuff",$L237="bonus_debuff",$L237="revive")</formula>
+      <formula>OR($L235="debuff",$L235="bonus_debuff",$L235="revive")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="2">
-      <formula>OR($L237="buff",$L237="bonus_buff")</formula>
+      <formula>OR($L235="buff",$L235="bonus_buff")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="3">
-      <formula>OR($L237="dot",$L237="stun")</formula>
+      <formula>OR($L235="dot",$L235="stun")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="4">
-      <formula>OR($L237="tank",$L237="shield")</formula>
+      <formula>OR($L235="tank",$L235="shield")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>OR($L237="heal",$L237="heal_all",$L237="life_steal")</formula>
+      <formula>OR($L235="heal",$L235="heal_all",$L235="life_steal")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>OR($L237="extra_attack",$L237="aoe")</formula>
+      <formula>OR($L235="extra_attack",$L235="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -15168,12 +14875,12 @@
     <hyperlink ref="F38" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="F45" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="F53" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F169" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F173" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F148" r:id="rId16" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
-    <hyperlink ref="F143" r:id="rId17" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
-    <hyperlink ref="F166" r:id="rId18" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
-    <hyperlink ref="F142" r:id="rId19" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
+    <hyperlink ref="F171" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F175" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F149" r:id="rId16" xr:uid="{B18A4056-2B5D-414C-A9F6-273D95C7ED18}"/>
+    <hyperlink ref="F144" r:id="rId17" xr:uid="{EA7715C1-7791-4747-91D3-03A4B27F1C4F}"/>
+    <hyperlink ref="F168" r:id="rId18" xr:uid="{94830BFD-52CC-4963-9874-F1F984E1589C}"/>
+    <hyperlink ref="F143" r:id="rId19" xr:uid="{92F7858F-B769-4909-A899-8246468D0096}"/>
     <hyperlink ref="F30" r:id="rId20" xr:uid="{66D24E2B-EF6D-4417-A0A4-812E5961FB81}"/>
     <hyperlink ref="F83" r:id="rId21" xr:uid="{8B8635A9-7759-45CB-8B60-1697B5FF9938}"/>
     <hyperlink ref="F54" r:id="rId22" xr:uid="{FAF75EE9-F39E-499A-ACD1-703CCBD91506}"/>
@@ -15213,25 +14920,25 @@
     <hyperlink ref="F116" r:id="rId56" xr:uid="{0BE12A25-88E9-40D7-B6CF-F734F050661F}"/>
     <hyperlink ref="F20" r:id="rId57" xr:uid="{BABB0F5C-56BD-4A07-93B3-021E469232CD}"/>
     <hyperlink ref="F32" r:id="rId58" xr:uid="{61098037-76F4-4673-81EC-2C0BEA11F28D}"/>
-    <hyperlink ref="F205" r:id="rId59" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
-    <hyperlink ref="F214" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
-    <hyperlink ref="F215" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
-    <hyperlink ref="F216" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
-    <hyperlink ref="F219" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
-    <hyperlink ref="F220" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
-    <hyperlink ref="F221" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
-    <hyperlink ref="F251" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
-    <hyperlink ref="F253" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
-    <hyperlink ref="F272" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
-    <hyperlink ref="F264" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
-    <hyperlink ref="F257" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
+    <hyperlink ref="F207" r:id="rId59" xr:uid="{CDB9697E-B5DD-4B05-A87F-9948E71EB15D}"/>
+    <hyperlink ref="F216" r:id="rId60" xr:uid="{1C16544A-4F4A-4C08-89CC-4F37E0986D91}"/>
+    <hyperlink ref="F217" r:id="rId61" xr:uid="{06E0FEDA-F7DA-458D-8F09-76B80DE09AB2}"/>
+    <hyperlink ref="F218" r:id="rId62" xr:uid="{08075219-10D9-404E-8E18-C232DE173646}"/>
+    <hyperlink ref="F221" r:id="rId63" xr:uid="{8346A542-3C7A-4501-8018-E883F1C014BD}"/>
+    <hyperlink ref="F222" r:id="rId64" xr:uid="{086976A0-E476-44F3-A1A7-A52FDD5C6A16}"/>
+    <hyperlink ref="F223" r:id="rId65" xr:uid="{7779F7F1-7C83-4CBB-AB2B-7D87ED427D90}"/>
+    <hyperlink ref="F253" r:id="rId66" xr:uid="{0E7F5509-4BC7-4B9D-A1EB-D898649A078B}"/>
+    <hyperlink ref="F255" r:id="rId67" xr:uid="{44F6718A-2854-42BF-B97F-E837DDE75498}"/>
+    <hyperlink ref="F274" r:id="rId68" xr:uid="{3BC7514F-0333-437E-B491-EC00925189BB}"/>
+    <hyperlink ref="F266" r:id="rId69" xr:uid="{13B89169-25A4-4FB6-A6AE-2EF0BD97D55D}"/>
+    <hyperlink ref="F259" r:id="rId70" xr:uid="{84363341-8DC7-4D5A-A434-7D3C17151FB3}"/>
     <hyperlink ref="F124" r:id="rId71" xr:uid="{163A63BB-52A6-4D6C-B00A-1A7F1F28061D}"/>
     <hyperlink ref="F15" r:id="rId72" xr:uid="{C439613B-BEC0-48C5-814E-36E868E99B31}"/>
     <hyperlink ref="F98" r:id="rId73" xr:uid="{7E273EDB-40F6-4371-AC08-0F1FA586E40C}"/>
-    <hyperlink ref="F228" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
+    <hyperlink ref="F230" r:id="rId74" xr:uid="{4ADCEE38-28CD-43D8-9123-B30FA02F7AB5}"/>
     <hyperlink ref="I99" r:id="rId75" xr:uid="{FE3AAB39-C871-4F64-AA22-E89C4CD15539}"/>
     <hyperlink ref="F94" r:id="rId76" xr:uid="{3D7B2B26-3280-40AF-A4C5-1389477FB9D2}"/>
-    <hyperlink ref="F224" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
+    <hyperlink ref="F226" r:id="rId77" xr:uid="{E1BA550E-4266-46F1-900F-62B4237C6D85}"/>
     <hyperlink ref="F126" r:id="rId78" xr:uid="{F3D65CAC-0B07-443F-8FF4-96BA556BCF65}"/>
     <hyperlink ref="I63" r:id="rId79" xr:uid="{881A0CE1-DA76-4C1F-9249-7E2DF77D0A79}"/>
   </hyperlinks>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EF4F08-5BA1-4B0D-B0D3-537C12CA5649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CD7097-9228-45A0-AB69-8B9C4ABBB1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="1230">
   <si>
     <t>Nombre</t>
   </si>
@@ -2359,9 +2359,6 @@
     <t>Corrupción</t>
   </si>
   <si>
-    <t>https://i.ibb.co/m54tkQfV/130cbd6b162e208d79e46d7a03d1160a.webp</t>
-  </si>
-  <si>
     <t>Golpe en las costillas</t>
   </si>
   <si>
@@ -3710,6 +3707,12 @@
   </si>
   <si>
     <t>Pringue radiactivo</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/gMpGnyTW/indigo-master.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Wv6p8Xqc/supergirl-master.jpg</t>
   </si>
 </sst>
 </file>
@@ -4275,7 +4278,7 @@
     <col min="6" max="6" width="86.140625" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="74.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -4405,7 +4408,7 @@
         <v>270</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N3" s="22" t="s">
         <v>263</v>
@@ -4529,7 +4532,7 @@
         <v>260</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N6" s="15" t="s">
         <v>264</v>
@@ -4558,7 +4561,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="13" t="s">
@@ -4600,7 +4603,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="12" t="s">
@@ -4613,7 +4616,7 @@
         <v>256</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>263</v>
@@ -4655,7 +4658,7 @@
         <v>257</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N9" s="14" t="s">
         <v>263</v>
@@ -4663,7 +4666,7 @@
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -4678,17 +4681,17 @@
         <v>8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="14" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>280</v>
@@ -4720,15 +4723,17 @@
         <v>8</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>808</v>
-      </c>
-      <c r="I11" s="2"/>
+        <v>807</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>1229</v>
+      </c>
       <c r="J11" s="13" t="s">
         <v>479</v>
       </c>
@@ -4892,7 +4897,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>284</v>
@@ -4998,7 +5003,7 @@
     </row>
     <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -5013,14 +5018,14 @@
         <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="10"/>
       <c r="J18" s="14" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>496</v>
@@ -5029,7 +5034,7 @@
         <v>257</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N18" s="14" t="s">
         <v>263</v>
@@ -5111,7 +5116,7 @@
         <v>269</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N20" s="12" t="s">
         <v>264</v>
@@ -5119,7 +5124,7 @@
     </row>
     <row r="21" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -5134,7 +5139,7 @@
         <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>10</v>
@@ -5143,7 +5148,7 @@
         <v>47</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="K21" s="14" t="s">
         <v>496</v>
@@ -5152,7 +5157,7 @@
         <v>257</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N21" s="14" t="s">
         <v>263</v>
@@ -5181,7 +5186,7 @@
         <v>10</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="J22" s="20" t="s">
         <v>512</v>
@@ -5222,7 +5227,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>514</v>
@@ -5234,7 +5239,7 @@
         <v>260</v>
       </c>
       <c r="M23" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N23" s="21" t="s">
         <v>264</v>
@@ -5263,7 +5268,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>516</v>
@@ -5275,7 +5280,7 @@
         <v>260</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N24" s="21" t="s">
         <v>264</v>
@@ -5304,7 +5309,7 @@
         <v>10</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J25" s="18" t="s">
         <v>502</v>
@@ -5316,7 +5321,7 @@
         <v>501</v>
       </c>
       <c r="M25" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N25" s="18" t="s">
         <v>264</v>
@@ -5433,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="M28" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N28" s="15" t="s">
         <v>264</v>
@@ -5544,7 +5549,7 @@
         <v>10</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="J31" s="22" t="s">
         <v>276</v>
@@ -5556,7 +5561,7 @@
         <v>270</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N31" s="22" t="s">
         <v>263</v>
@@ -5638,7 +5643,7 @@
         <v>256</v>
       </c>
       <c r="M33" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N33" s="22" t="s">
         <v>263</v>
@@ -5679,7 +5684,7 @@
         <v>257</v>
       </c>
       <c r="M34" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N34" s="14" t="s">
         <v>263</v>
@@ -5702,13 +5707,13 @@
         <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>284</v>
@@ -5800,7 +5805,7 @@
         <v>501</v>
       </c>
       <c r="M37" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N37" s="18" t="s">
         <v>264</v>
@@ -5849,7 +5854,7 @@
     </row>
     <row r="39" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
@@ -5864,16 +5869,16 @@
         <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="K39" s="12" t="s">
         <v>288</v>
@@ -5882,7 +5887,7 @@
         <v>258</v>
       </c>
       <c r="M39" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N39" s="12" t="s">
         <v>264</v>
@@ -5890,7 +5895,7 @@
     </row>
     <row r="40" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -5905,25 +5910,25 @@
         <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H40" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J40" s="15" t="s">
         <v>1088</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>1089</v>
       </c>
       <c r="K40" s="15" t="s">
         <v>523</v>
       </c>
       <c r="L40" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M40" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M40" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N40" s="15" t="s">
         <v>264</v>
@@ -5952,7 +5957,7 @@
         <v>10</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>713</v>
@@ -5964,7 +5969,7 @@
         <v>269</v>
       </c>
       <c r="M41" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N41" s="12" t="s">
         <v>264</v>
@@ -6005,7 +6010,7 @@
         <v>270</v>
       </c>
       <c r="M42" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N42" s="16" t="s">
         <v>263</v>
@@ -6046,7 +6051,7 @@
         <v>256</v>
       </c>
       <c r="M43" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N43" s="22" t="s">
         <v>263</v>
@@ -6085,7 +6090,7 @@
         <v>501</v>
       </c>
       <c r="M44" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N44" s="18" t="s">
         <v>264</v>
@@ -6114,7 +6119,7 @@
         <v>10</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J45" s="13" t="s">
         <v>528</v>
@@ -6208,7 +6213,7 @@
         <v>270</v>
       </c>
       <c r="M47" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N47" s="22" t="s">
         <v>263</v>
@@ -6298,7 +6303,7 @@
     </row>
     <row r="50" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
@@ -6319,7 +6324,7 @@
         <v>10</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="J50" s="15" t="s">
         <v>715</v>
@@ -6331,7 +6336,7 @@
         <v>260</v>
       </c>
       <c r="M50" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N50" s="15" t="s">
         <v>264</v>
@@ -6339,7 +6344,7 @@
     </row>
     <row r="51" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
@@ -6354,7 +6359,7 @@
         <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>10</v>
@@ -6363,7 +6368,7 @@
         <v>106</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K51" s="19" t="s">
         <v>505</v>
@@ -6401,7 +6406,7 @@
         <v>10</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="J52" s="14" t="s">
         <v>536</v>
@@ -6413,7 +6418,7 @@
         <v>257</v>
       </c>
       <c r="M52" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N52" s="14" t="s">
         <v>263</v>
@@ -6442,7 +6447,7 @@
         <v>10</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J53" s="14" t="s">
         <v>538</v>
@@ -6454,7 +6459,7 @@
         <v>257</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N53" s="14" t="s">
         <v>263</v>
@@ -6563,7 +6568,7 @@
         <v>10</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>740</v>
@@ -6578,7 +6583,7 @@
         <v>258</v>
       </c>
       <c r="M56" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N56" s="12" t="s">
         <v>264</v>
@@ -6648,7 +6653,7 @@
         <v>10</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="J58" s="14" t="s">
         <v>717</v>
@@ -6660,7 +6665,7 @@
         <v>257</v>
       </c>
       <c r="M58" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N58" s="14" t="s">
         <v>263</v>
@@ -6668,7 +6673,7 @@
     </row>
     <row r="59" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
@@ -6683,7 +6688,7 @@
         <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>10</v>
@@ -6692,7 +6697,7 @@
         <v>329</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K59" s="13" t="s">
         <v>541</v>
@@ -6771,7 +6776,7 @@
         <v>10</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="J61" s="12" t="s">
         <v>718</v>
@@ -6783,7 +6788,7 @@
         <v>258</v>
       </c>
       <c r="M61" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N61" s="12" t="s">
         <v>264</v>
@@ -6791,7 +6796,7 @@
     </row>
     <row r="62" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B62" s="17">
         <v>1</v>
@@ -6806,13 +6811,13 @@
         <v>19</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="J62" s="13" t="s">
         <v>542</v>
@@ -6853,7 +6858,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="J63" s="13" t="s">
         <v>544</v>
@@ -6906,7 +6911,7 @@
         <v>269</v>
       </c>
       <c r="M64" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N64" s="12" t="s">
         <v>264</v>
@@ -6947,7 +6952,7 @@
         <v>257</v>
       </c>
       <c r="M65" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N65" s="14" t="s">
         <v>263</v>
@@ -6976,7 +6981,7 @@
         <v>10</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>275</v>
@@ -7017,10 +7022,10 @@
         <v>10</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I67" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J67" s="15" t="s">
         <v>549</v>
@@ -7100,10 +7105,10 @@
         <v>10</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="J69" s="13" t="s">
         <v>553</v>
@@ -7246,7 +7251,7 @@
     </row>
     <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B73" s="17">
         <v>1</v>
@@ -7261,7 +7266,7 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>10</v>
@@ -7270,7 +7275,7 @@
         <v>329</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="K73" s="12" t="s">
         <v>547</v>
@@ -7279,7 +7284,7 @@
         <v>269</v>
       </c>
       <c r="M73" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N73" s="12" t="s">
         <v>264</v>
@@ -7320,7 +7325,7 @@
         <v>256</v>
       </c>
       <c r="M74" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N74" s="22" t="s">
         <v>263</v>
@@ -7359,7 +7364,7 @@
         <v>269</v>
       </c>
       <c r="M75" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N75" s="12" t="s">
         <v>264</v>
@@ -7388,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J76" s="13" t="s">
         <v>561</v>
@@ -7408,7 +7413,7 @@
     </row>
     <row r="77" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B77" s="17">
         <v>1</v>
@@ -7423,13 +7428,13 @@
         <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="J77" s="22" t="s">
         <v>576</v>
@@ -7441,7 +7446,7 @@
         <v>256</v>
       </c>
       <c r="M77" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N77" s="22" t="s">
         <v>263</v>
@@ -7449,7 +7454,7 @@
     </row>
     <row r="78" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B78" s="17">
         <v>1</v>
@@ -7464,7 +7469,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>10</v>
@@ -7473,10 +7478,10 @@
         <v>327</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="K78" s="18" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L78" s="18" t="s">
         <v>292</v>
@@ -7490,7 +7495,7 @@
     </row>
     <row r="79" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B79" s="17">
         <v>1</v>
@@ -7505,7 +7510,7 @@
         <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>10</v>
@@ -7514,10 +7519,10 @@
         <v>327</v>
       </c>
       <c r="I79" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="K79" s="13" t="s">
         <v>562</v>
@@ -7534,7 +7539,7 @@
     </row>
     <row r="80" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B80" s="17">
         <v>1</v>
@@ -7549,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>10</v>
@@ -7558,7 +7563,7 @@
         <v>327</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="K80" s="12" t="s">
         <v>547</v>
@@ -7567,7 +7572,7 @@
         <v>269</v>
       </c>
       <c r="M80" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>264</v>
@@ -7575,7 +7580,7 @@
     </row>
     <row r="81" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B81" s="17">
         <v>1</v>
@@ -7590,16 +7595,16 @@
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="K81" s="21" t="s">
         <v>566</v>
@@ -7608,7 +7613,7 @@
         <v>260</v>
       </c>
       <c r="M81" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N81" s="21" t="s">
         <v>264</v>
@@ -7616,7 +7621,7 @@
     </row>
     <row r="82" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B82" s="17">
         <v>1</v>
@@ -7631,13 +7636,13 @@
         <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J82" s="12" t="s">
         <v>563</v>
@@ -7649,7 +7654,7 @@
         <v>258</v>
       </c>
       <c r="M82" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N82" s="12" t="s">
         <v>264</v>
@@ -7657,7 +7662,7 @@
     </row>
     <row r="83" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B83" s="17">
         <v>1</v>
@@ -7672,7 +7677,7 @@
         <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>10</v>
@@ -7681,16 +7686,16 @@
         <v>99</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="K83" s="21" t="s">
         <v>566</v>
       </c>
       <c r="L83" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M83" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M83" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N83" s="21" t="s">
         <v>264</v>
@@ -7698,7 +7703,7 @@
     </row>
     <row r="84" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B84" s="17">
         <v>1</v>
@@ -7713,7 +7718,7 @@
         <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>10</v>
@@ -7722,7 +7727,7 @@
         <v>99</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>280</v>
@@ -7739,7 +7744,7 @@
     </row>
     <row r="85" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B85" s="17">
         <v>1</v>
@@ -7754,7 +7759,7 @@
         <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>10</v>
@@ -7763,7 +7768,7 @@
         <v>99</v>
       </c>
       <c r="J85" s="23" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="K85" s="23" t="s">
         <v>580</v>
@@ -7772,7 +7777,7 @@
         <v>257</v>
       </c>
       <c r="M85" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N85" s="23" t="s">
         <v>263</v>
@@ -7780,7 +7785,7 @@
     </row>
     <row r="86" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B86" s="17">
         <v>1</v>
@@ -7795,16 +7800,16 @@
         <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="K86" s="20" t="s">
         <v>583</v>
@@ -7821,7 +7826,7 @@
     </row>
     <row r="87" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B87" s="17">
         <v>1</v>
@@ -7836,7 +7841,7 @@
         <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>10</v>
@@ -7845,7 +7850,7 @@
         <v>99</v>
       </c>
       <c r="J87" s="23" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="K87" s="23" t="s">
         <v>580</v>
@@ -7854,7 +7859,7 @@
         <v>257</v>
       </c>
       <c r="M87" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N87" s="23" t="s">
         <v>263</v>
@@ -7862,7 +7867,7 @@
     </row>
     <row r="88" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B88" s="17">
         <v>1</v>
@@ -7877,7 +7882,7 @@
         <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>10</v>
@@ -7886,7 +7891,7 @@
         <v>99</v>
       </c>
       <c r="J88" s="23" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="K88" s="20" t="s">
         <v>583</v>
@@ -7901,7 +7906,7 @@
     </row>
     <row r="89" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B89" s="17">
         <v>1</v>
@@ -7916,7 +7921,7 @@
         <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>10</v>
@@ -7925,7 +7930,7 @@
         <v>99</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="K89" s="13" t="s">
         <v>562</v>
@@ -7942,7 +7947,7 @@
     </row>
     <row r="90" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B90" s="17">
         <v>1</v>
@@ -7957,16 +7962,16 @@
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J90" s="22" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="K90" s="22" t="s">
         <v>559</v>
@@ -7975,7 +7980,7 @@
         <v>256</v>
       </c>
       <c r="M90" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N90" s="22" t="s">
         <v>263</v>
@@ -7983,7 +7988,7 @@
     </row>
     <row r="91" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B91" s="17">
         <v>1</v>
@@ -7998,16 +8003,16 @@
         <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J91" s="21" t="s">
         <v>1052</v>
-      </c>
-      <c r="J91" s="21" t="s">
-        <v>1053</v>
       </c>
       <c r="K91" s="21" t="s">
         <v>566</v>
@@ -8016,7 +8021,7 @@
         <v>260</v>
       </c>
       <c r="M91" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N91" s="21" t="s">
         <v>264</v>
@@ -8057,7 +8062,7 @@
         <v>256</v>
       </c>
       <c r="M92" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N92" s="12" t="s">
         <v>263</v>
@@ -8065,7 +8070,7 @@
     </row>
     <row r="93" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B93" s="17">
         <v>1</v>
@@ -8080,7 +8085,7 @@
         <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>10</v>
@@ -8089,10 +8094,10 @@
         <v>329</v>
       </c>
       <c r="J93" s="18" t="s">
+        <v>790</v>
+      </c>
+      <c r="K93" s="18" t="s">
         <v>791</v>
-      </c>
-      <c r="K93" s="18" t="s">
-        <v>792</v>
       </c>
       <c r="L93" s="18" t="s">
         <v>292</v>
@@ -8139,7 +8144,7 @@
         <v>260</v>
       </c>
       <c r="M94" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N94" s="15" t="s">
         <v>264</v>
@@ -8208,7 +8213,7 @@
         <v>328</v>
       </c>
       <c r="I96" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="J96" s="12" t="s">
         <v>571</v>
@@ -8220,7 +8225,7 @@
         <v>269</v>
       </c>
       <c r="M96" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N96" s="12" t="s">
         <v>264</v>
@@ -8339,7 +8344,7 @@
         <v>257</v>
       </c>
       <c r="M99" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N99" s="14" t="s">
         <v>263</v>
@@ -8378,7 +8383,7 @@
         <v>256</v>
       </c>
       <c r="M100" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N100" s="22" t="s">
         <v>263</v>
@@ -8407,7 +8412,7 @@
         <v>10</v>
       </c>
       <c r="H101" s="17" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J101" s="21" t="s">
         <v>577</v>
@@ -8419,7 +8424,7 @@
         <v>260</v>
       </c>
       <c r="M101" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N101" s="21" t="s">
         <v>264</v>
@@ -8497,7 +8502,7 @@
         <v>257</v>
       </c>
       <c r="M103" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N103" s="23" t="s">
         <v>263</v>
@@ -8505,7 +8510,7 @@
     </row>
     <row r="104" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B104" s="17">
         <v>1</v>
@@ -8520,7 +8525,7 @@
         <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G104" s="10" t="s">
         <v>10</v>
@@ -8529,10 +8534,10 @@
         <v>329</v>
       </c>
       <c r="I104" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="K104" s="13" t="s">
         <v>562</v>
@@ -8549,7 +8554,7 @@
     </row>
     <row r="105" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B105" s="17">
         <v>1</v>
@@ -8564,7 +8569,7 @@
         <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>10</v>
@@ -8573,13 +8578,13 @@
         <v>329</v>
       </c>
       <c r="I105" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J105" s="18" t="s">
+        <v>826</v>
+      </c>
+      <c r="K105" s="18" t="s">
         <v>827</v>
-      </c>
-      <c r="K105" s="18" t="s">
-        <v>828</v>
       </c>
       <c r="L105" s="18" t="s">
         <v>292</v>
@@ -8626,7 +8631,7 @@
         <v>260</v>
       </c>
       <c r="M106" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N106" s="21" t="s">
         <v>264</v>
@@ -8634,7 +8639,7 @@
     </row>
     <row r="107" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B107" s="17">
         <v>1</v>
@@ -8649,16 +8654,16 @@
         <v>19</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G107" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J107" s="20" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K107" s="20" t="s">
         <v>585</v>
@@ -8675,7 +8680,7 @@
     </row>
     <row r="108" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B108" s="17">
         <v>1</v>
@@ -8690,16 +8695,16 @@
         <v>19</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G108" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J108" s="18" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="K108" s="18" t="s">
         <v>498</v>
@@ -8716,7 +8721,7 @@
     </row>
     <row r="109" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B109" s="17">
         <v>1</v>
@@ -8731,17 +8736,17 @@
         <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H109" s="10"/>
       <c r="J109" s="18" t="s">
+        <v>908</v>
+      </c>
+      <c r="K109" s="18" t="s">
         <v>909</v>
-      </c>
-      <c r="K109" s="18" t="s">
-        <v>910</v>
       </c>
       <c r="L109" s="18" t="s">
         <v>292</v>
@@ -8776,7 +8781,7 @@
         <v>10</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J110" s="20" t="s">
         <v>582</v>
@@ -8796,7 +8801,7 @@
     </row>
     <row r="111" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B111" s="17">
         <v>1</v>
@@ -8811,7 +8816,7 @@
         <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G111" s="10" t="s">
         <v>10</v>
@@ -8820,7 +8825,7 @@
         <v>71</v>
       </c>
       <c r="J111" s="21" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K111" s="21" t="s">
         <v>566</v>
@@ -8829,7 +8834,7 @@
         <v>260</v>
       </c>
       <c r="M111" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N111" s="21" t="s">
         <v>264</v>
@@ -8852,13 +8857,13 @@
         <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G112" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>364</v>
@@ -8896,7 +8901,7 @@
         <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>10</v>
@@ -8941,7 +8946,7 @@
         <v>10</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="J114" s="23" t="s">
         <v>586</v>
@@ -9201,7 +9206,7 @@
     </row>
     <row r="121" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B121" s="17">
         <v>1</v>
@@ -9216,7 +9221,7 @@
         <v>22</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>10</v>
@@ -9225,7 +9230,7 @@
         <v>765</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K121" s="12" t="s">
         <v>289</v>
@@ -9234,7 +9239,7 @@
         <v>269</v>
       </c>
       <c r="M121" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N121" s="12" t="s">
         <v>264</v>
@@ -9319,7 +9324,7 @@
         <v>258</v>
       </c>
       <c r="M123" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N123" s="12" t="s">
         <v>264</v>
@@ -9360,7 +9365,7 @@
         <v>257</v>
       </c>
       <c r="M124" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N124" s="23" t="s">
         <v>263</v>
@@ -9392,7 +9397,7 @@
         <v>765</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>592</v>
@@ -9401,7 +9406,7 @@
         <v>501</v>
       </c>
       <c r="M125" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>264</v>
@@ -9409,7 +9414,7 @@
     </row>
     <row r="126" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B126" s="17">
         <v>1</v>
@@ -9424,7 +9429,7 @@
         <v>22</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G126" s="10" t="s">
         <v>10</v>
@@ -9433,7 +9438,7 @@
         <v>328</v>
       </c>
       <c r="J126" s="15" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K126" s="15" t="s">
         <v>274</v>
@@ -9483,7 +9488,7 @@
         <v>256</v>
       </c>
       <c r="M127" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N127" s="2" t="s">
         <v>263</v>
@@ -9514,8 +9519,8 @@
       <c r="H128" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="I128" t="s">
-        <v>778</v>
+      <c r="I128" s="26" t="s">
+        <v>1228</v>
       </c>
       <c r="J128" s="12" t="s">
         <v>721</v>
@@ -9527,7 +9532,7 @@
         <v>269</v>
       </c>
       <c r="M128" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N128" s="12" t="s">
         <v>264</v>
@@ -9559,7 +9564,7 @@
         <v>106</v>
       </c>
       <c r="I129" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="J129" s="15" t="s">
         <v>275</v>
@@ -9594,7 +9599,7 @@
         <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>10</v>
@@ -9620,7 +9625,7 @@
     </row>
     <row r="131" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B131" s="17">
         <v>1</v>
@@ -9635,7 +9640,7 @@
         <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G131" s="10" t="s">
         <v>10</v>
@@ -9644,7 +9649,7 @@
         <v>106</v>
       </c>
       <c r="J131" s="20" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K131" s="20" t="s">
         <v>585</v>
@@ -9661,7 +9666,7 @@
     </row>
     <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B132" s="17">
         <v>1</v>
@@ -9676,7 +9681,7 @@
         <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G132" s="10" t="s">
         <v>10</v>
@@ -9685,7 +9690,7 @@
         <v>106</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>278</v>
@@ -9700,7 +9705,7 @@
     </row>
     <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B133" s="17">
         <v>1</v>
@@ -9715,7 +9720,7 @@
         <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G133" s="10" t="s">
         <v>10</v>
@@ -9724,7 +9729,7 @@
         <v>106</v>
       </c>
       <c r="J133" s="23" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="K133" s="23" t="s">
         <v>590</v>
@@ -9733,7 +9738,7 @@
         <v>257</v>
       </c>
       <c r="M133" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N133" s="23" t="s">
         <v>263</v>
@@ -9741,7 +9746,7 @@
     </row>
     <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B134" s="17">
         <v>1</v>
@@ -9756,7 +9761,7 @@
         <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G134" s="10" t="s">
         <v>10</v>
@@ -9765,7 +9770,7 @@
         <v>106</v>
       </c>
       <c r="J134" s="15" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="K134" s="15" t="s">
         <v>274</v>
@@ -9782,7 +9787,7 @@
     </row>
     <row r="135" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B135" s="17">
         <v>1</v>
@@ -9797,7 +9802,7 @@
         <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G135" s="10" t="s">
         <v>10</v>
@@ -9806,7 +9811,7 @@
         <v>106</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K135" s="12" t="s">
         <v>286</v>
@@ -9815,7 +9820,7 @@
         <v>256</v>
       </c>
       <c r="M135" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N135" s="12" t="s">
         <v>263</v>
@@ -9823,7 +9828,7 @@
     </row>
     <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B136" s="17">
         <v>1</v>
@@ -9838,25 +9843,25 @@
         <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G136" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="J136" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="K136" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>918</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>501</v>
       </c>
       <c r="M136" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N136" s="2" t="s">
         <v>264</v>
@@ -9897,7 +9902,7 @@
         <v>256</v>
       </c>
       <c r="M137" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N137" s="12" t="s">
         <v>263</v>
@@ -9935,13 +9940,13 @@
         <v>731</v>
       </c>
       <c r="K138" s="21" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L138" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M138" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M138" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N138" s="21" t="s">
         <v>264</v>
@@ -9976,7 +9981,7 @@
         <v>735</v>
       </c>
       <c r="J139" s="20" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="K139" s="20" t="s">
         <v>585</v>
@@ -9993,7 +9998,7 @@
     </row>
     <row r="140" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B140" s="17">
         <v>1</v>
@@ -10008,19 +10013,19 @@
         <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G140" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H140" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I140" t="s">
+        <v>957</v>
+      </c>
+      <c r="J140" s="13" t="s">
         <v>1125</v>
-      </c>
-      <c r="I140" t="s">
-        <v>958</v>
-      </c>
-      <c r="J140" s="13" t="s">
-        <v>1126</v>
       </c>
       <c r="K140" s="20" t="s">
         <v>585</v>
@@ -10037,7 +10042,7 @@
     </row>
     <row r="141" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B141" s="17">
         <v>1</v>
@@ -10052,19 +10057,19 @@
         <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G141" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="I141" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>588</v>
@@ -10081,7 +10086,7 @@
     </row>
     <row r="142" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="17" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B142" s="17">
         <v>1</v>
@@ -10096,16 +10101,16 @@
         <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G142" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H142" s="10" t="s">
+        <v>991</v>
+      </c>
+      <c r="J142" s="2" t="s">
         <v>992</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>993</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>604</v>
@@ -10114,7 +10119,7 @@
         <v>260</v>
       </c>
       <c r="M142" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>264</v>
@@ -10122,7 +10127,7 @@
     </row>
     <row r="143" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B143" s="17">
         <v>1</v>
@@ -10137,16 +10142,16 @@
         <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G143" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>505</v>
@@ -10163,7 +10168,7 @@
     </row>
     <row r="144" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B144" s="17">
         <v>1</v>
@@ -10178,13 +10183,13 @@
         <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G144" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H144" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J144" s="23" t="s">
         <v>589</v>
@@ -10196,7 +10201,7 @@
         <v>257</v>
       </c>
       <c r="M144" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N144" s="23" t="s">
         <v>263</v>
@@ -10204,7 +10209,7 @@
     </row>
     <row r="145" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B145" s="17">
         <v>1</v>
@@ -10219,16 +10224,16 @@
         <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G145" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>278</v>
@@ -10243,7 +10248,7 @@
     </row>
     <row r="146" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B146" s="17">
         <v>1</v>
@@ -10258,16 +10263,16 @@
         <v>19</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G146" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H146" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J146" s="12" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K146" s="12" t="s">
         <v>288</v>
@@ -10276,7 +10281,7 @@
         <v>258</v>
       </c>
       <c r="M146" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N146" s="12" t="s">
         <v>264</v>
@@ -10284,7 +10289,7 @@
     </row>
     <row r="147" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B147" s="17">
         <v>1</v>
@@ -10299,16 +10304,16 @@
         <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G147" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J147" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>588</v>
@@ -10325,7 +10330,7 @@
     </row>
     <row r="148" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B148" s="17">
         <v>1</v>
@@ -10340,16 +10345,16 @@
         <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G148" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J148" s="15" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K148" s="15" t="s">
         <v>274</v>
@@ -10381,16 +10386,16 @@
         <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G149" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>596</v>
@@ -10399,7 +10404,7 @@
         <v>256</v>
       </c>
       <c r="M149" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>263</v>
@@ -10407,7 +10412,7 @@
     </row>
     <row r="150" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B150" s="17">
         <v>1</v>
@@ -10422,16 +10427,16 @@
         <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G150" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H150" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>588</v>
@@ -10470,10 +10475,10 @@
       </c>
       <c r="H151" s="10"/>
       <c r="I151" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="J151" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K151" s="23" t="s">
         <v>590</v>
@@ -10482,7 +10487,7 @@
         <v>257</v>
       </c>
       <c r="M151" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N151" s="23" t="s">
         <v>263</v>
@@ -10490,7 +10495,7 @@
     </row>
     <row r="152" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B152" s="3">
         <v>1</v>
@@ -10505,16 +10510,16 @@
         <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G152" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H152" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J152" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>1003</v>
       </c>
       <c r="K152" s="2" t="s">
         <v>278</v>
@@ -10529,7 +10534,7 @@
     </row>
     <row r="153" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B153" s="3">
         <v>1</v>
@@ -10544,16 +10549,16 @@
         <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G153" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="J153" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>588</v>
@@ -10570,7 +10575,7 @@
     </row>
     <row r="154" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B154" s="3">
         <v>1</v>
@@ -10585,22 +10590,22 @@
         <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G154" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H154" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I154" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J154" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="J154" s="2" t="s">
+      <c r="K154" s="2" t="s">
         <v>1009</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>1010</v>
       </c>
       <c r="L154" s="2" t="s">
         <v>292</v>
@@ -10614,7 +10619,7 @@
     </row>
     <row r="155" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B155" s="3">
         <v>1</v>
@@ -10629,17 +10634,17 @@
         <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G155" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I155" s="32"/>
       <c r="J155" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>505</v>
@@ -10656,7 +10661,7 @@
     </row>
     <row r="156" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B156" s="3">
         <v>1</v>
@@ -10671,17 +10676,17 @@
         <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G156" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H156" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I156" s="32"/>
       <c r="J156" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>598</v>
@@ -10698,7 +10703,7 @@
     </row>
     <row r="157" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B157" s="3">
         <v>1</v>
@@ -10713,20 +10718,20 @@
         <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G157" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="I157" s="32"/>
       <c r="J157" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K157" s="2" t="s">
         <v>1092</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>1093</v>
       </c>
       <c r="L157" s="2" t="s">
         <v>292</v>
@@ -10740,7 +10745,7 @@
     </row>
     <row r="158" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B158" s="3">
         <v>1</v>
@@ -10755,17 +10760,17 @@
         <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G158" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H158" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="I158" s="32"/>
       <c r="J158" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>588</v>
@@ -10782,7 +10787,7 @@
     </row>
     <row r="159" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B159" s="3">
         <v>1</v>
@@ -10797,17 +10802,17 @@
         <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G159" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="I159" s="32"/>
       <c r="J159" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K159" s="2" t="s">
         <v>598</v>
@@ -10824,7 +10829,7 @@
     </row>
     <row r="160" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B160" s="3">
         <v>1</v>
@@ -10839,17 +10844,17 @@
         <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G160" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H160" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="I160" s="32"/>
       <c r="J160" s="15" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="K160" s="15" t="s">
         <v>274</v>
@@ -10866,7 +10871,7 @@
     </row>
     <row r="161" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B161" s="3">
         <v>1</v>
@@ -10881,17 +10886,17 @@
         <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G161" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I161" s="32"/>
       <c r="J161" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>278</v>
@@ -10906,7 +10911,7 @@
     </row>
     <row r="162" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B162" s="3">
         <v>1</v>
@@ -10921,7 +10926,7 @@
         <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G162" s="10" t="s">
         <v>10</v>
@@ -10929,7 +10934,7 @@
       <c r="H162" s="10"/>
       <c r="I162" s="32"/>
       <c r="J162" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>598</v>
@@ -10946,7 +10951,7 @@
     </row>
     <row r="163" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B163" s="3">
         <v>1</v>
@@ -10961,7 +10966,7 @@
         <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G163" s="10" t="s">
         <v>10</v>
@@ -10969,16 +10974,16 @@
       <c r="H163" s="10"/>
       <c r="I163" s="32"/>
       <c r="J163" s="15" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="K163" s="21" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L163" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M163" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M163" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N163" s="21" t="s">
         <v>264</v>
@@ -10986,7 +10991,7 @@
     </row>
     <row r="164" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B164" s="3">
         <v>1</v>
@@ -11001,7 +11006,7 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G164" s="10" t="s">
         <v>10</v>
@@ -11009,7 +11014,7 @@
       <c r="H164" s="10"/>
       <c r="I164" s="32"/>
       <c r="J164" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="K164" s="2" t="s">
         <v>592</v>
@@ -11018,7 +11023,7 @@
         <v>501</v>
       </c>
       <c r="M164" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>264</v>
@@ -11026,7 +11031,7 @@
     </row>
     <row r="165" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B165" s="3">
         <v>1</v>
@@ -11041,7 +11046,7 @@
         <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G165" s="10" t="s">
         <v>10</v>
@@ -11068,7 +11073,7 @@
     </row>
     <row r="166" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B166" s="3">
         <v>1</v>
@@ -11083,17 +11088,17 @@
         <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G166" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H166" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I166" s="32"/>
       <c r="J166" s="13" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="K166" s="2" t="s">
         <v>588</v>
@@ -11110,7 +11115,7 @@
     </row>
     <row r="167" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B167" s="3">
         <v>1</v>
@@ -11125,17 +11130,17 @@
         <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G167" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I167" s="32"/>
       <c r="J167" s="15" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K167" s="15" t="s">
         <v>274</v>
@@ -11152,7 +11157,7 @@
     </row>
     <row r="168" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B168" s="3">
         <v>1</v>
@@ -11167,20 +11172,20 @@
         <v>19</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G168" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H168" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I168" s="32"/>
       <c r="J168" s="2" t="s">
         <v>497</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="L168" s="2" t="s">
         <v>292</v>
@@ -11194,7 +11199,7 @@
     </row>
     <row r="169" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B169" s="3">
         <v>1</v>
@@ -11209,17 +11214,17 @@
         <v>8</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G169" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I169" s="32"/>
       <c r="J169" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K169" s="2" t="s">
         <v>598</v>
@@ -11236,7 +11241,7 @@
     </row>
     <row r="170" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B170" s="3">
         <v>1</v>
@@ -11251,17 +11256,17 @@
         <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G170" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H170" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I170" s="32"/>
       <c r="J170" s="13" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="K170" s="2" t="s">
         <v>588</v>
@@ -11278,7 +11283,7 @@
     </row>
     <row r="171" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B171" s="3">
         <v>1</v>
@@ -11293,19 +11298,19 @@
         <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G171" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I171" s="32" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="J171" s="14" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="K171" s="14" t="s">
         <v>280</v>
@@ -11322,7 +11327,7 @@
     </row>
     <row r="172" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B172" s="3">
         <v>1</v>
@@ -11337,17 +11342,17 @@
         <v>19</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G172" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H172" s="10" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="I172" s="32"/>
       <c r="J172" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K172" s="2" t="s">
         <v>592</v>
@@ -11356,7 +11361,7 @@
         <v>501</v>
       </c>
       <c r="M172" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N172" s="2" t="s">
         <v>264</v>
@@ -11364,7 +11369,7 @@
     </row>
     <row r="173" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B173" s="3">
         <v>1</v>
@@ -11379,17 +11384,17 @@
         <v>19</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G173" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="I173" s="32"/>
       <c r="J173" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>596</v>
@@ -11398,7 +11403,7 @@
         <v>256</v>
       </c>
       <c r="M173" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N173" s="2" t="s">
         <v>263</v>
@@ -11406,7 +11411,7 @@
     </row>
     <row r="174" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B174" s="3">
         <v>1</v>
@@ -11421,17 +11426,17 @@
         <v>19</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G174" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H174" s="10" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="I174" s="32"/>
       <c r="J174" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="K174" s="2" t="s">
         <v>598</v>
@@ -11448,7 +11453,7 @@
     </row>
     <row r="175" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B175" s="3">
         <v>1</v>
@@ -11463,17 +11468,17 @@
         <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G175" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="I175" s="32"/>
       <c r="J175" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="K175" s="15" t="s">
         <v>274</v>
@@ -11490,7 +11495,7 @@
     </row>
     <row r="176" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B176" s="3">
         <v>1</v>
@@ -11505,17 +11510,17 @@
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G176" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H176" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I176" s="32"/>
       <c r="J176" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="K176" s="2" t="s">
         <v>537</v>
@@ -11524,7 +11529,7 @@
         <v>257</v>
       </c>
       <c r="M176" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N176" s="2" t="s">
         <v>263</v>
@@ -11532,7 +11537,7 @@
     </row>
     <row r="177" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B177" s="3">
         <v>1</v>
@@ -11547,26 +11552,26 @@
         <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G177" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I177" s="32"/>
       <c r="J177" s="21" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K177" s="21" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L177" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M177" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M177" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N177" s="21" t="s">
         <v>264</v>
@@ -11574,7 +11579,7 @@
     </row>
     <row r="178" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B178" s="3">
         <v>1</v>
@@ -11589,7 +11594,7 @@
         <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G178" s="10" t="s">
         <v>10</v>
@@ -11597,7 +11602,7 @@
       <c r="H178" s="10"/>
       <c r="I178" s="32"/>
       <c r="J178" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="K178" s="23" t="s">
         <v>590</v>
@@ -11606,7 +11611,7 @@
         <v>257</v>
       </c>
       <c r="M178" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N178" s="23" t="s">
         <v>263</v>
@@ -11647,7 +11652,7 @@
         <v>501</v>
       </c>
       <c r="M179" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>264</v>
@@ -11715,7 +11720,7 @@
         <v>123</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>594</v>
@@ -11727,7 +11732,7 @@
         <v>257</v>
       </c>
       <c r="M181" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>263</v>
@@ -11756,7 +11761,7 @@
         <v>123</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>595</v>
@@ -11768,7 +11773,7 @@
         <v>256</v>
       </c>
       <c r="M182" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>263</v>
@@ -11776,7 +11781,7 @@
     </row>
     <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B183" s="4">
         <v>1</v>
@@ -11791,14 +11796,14 @@
         <v>8</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H183" s="4"/>
       <c r="J183" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K183" s="2" t="s">
         <v>598</v>
@@ -11887,7 +11892,7 @@
         <v>257</v>
       </c>
       <c r="M185" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>263</v>
@@ -11967,7 +11972,7 @@
         <v>256</v>
       </c>
       <c r="M187" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>263</v>
@@ -12008,7 +12013,7 @@
         <v>270</v>
       </c>
       <c r="M188" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N188" s="2" t="s">
         <v>263</v>
@@ -12016,7 +12021,7 @@
     </row>
     <row r="189" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
@@ -12031,7 +12036,7 @@
         <v>22</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>123</v>
@@ -12040,7 +12045,7 @@
         <v>209</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K189" s="2" t="s">
         <v>278</v>
@@ -12055,7 +12060,7 @@
     </row>
     <row r="190" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B190" s="4">
         <v>1</v>
@@ -12070,7 +12075,7 @@
         <v>22</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>123</v>
@@ -12079,7 +12084,7 @@
         <v>209</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="K190" s="14" t="s">
         <v>280</v>
@@ -12129,7 +12134,7 @@
         <v>260</v>
       </c>
       <c r="M191" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N191" s="2" t="s">
         <v>264</v>
@@ -12137,7 +12142,7 @@
     </row>
     <row r="192" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
@@ -12152,7 +12157,7 @@
         <v>22</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>123</v>
@@ -12166,7 +12171,7 @@
     </row>
     <row r="193" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B193" s="4">
         <v>1</v>
@@ -12181,16 +12186,16 @@
         <v>8</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="K193" s="2" t="s">
         <v>537</v>
@@ -12199,7 +12204,7 @@
         <v>257</v>
       </c>
       <c r="M193" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N193" s="2" t="s">
         <v>263</v>
@@ -12207,7 +12212,7 @@
     </row>
     <row r="194" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
@@ -12222,16 +12227,16 @@
         <v>8</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="K194" s="2" t="s">
         <v>588</v>
@@ -12248,7 +12253,7 @@
     </row>
     <row r="195" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B195" s="4">
         <v>1</v>
@@ -12263,16 +12268,16 @@
         <v>8</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>505</v>
@@ -12289,7 +12294,7 @@
     </row>
     <row r="196" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B196" s="4">
         <v>1</v>
@@ -12304,16 +12309,16 @@
         <v>8</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="K196" s="2" t="s">
         <v>278</v>
@@ -12328,7 +12333,7 @@
     </row>
     <row r="197" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B197" s="4">
         <v>1</v>
@@ -12343,16 +12348,16 @@
         <v>8</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H197" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J197" s="2" t="s">
         <v>1059</v>
-      </c>
-      <c r="J197" s="2" t="s">
-        <v>1060</v>
       </c>
       <c r="K197" s="2" t="s">
         <v>616</v>
@@ -12390,7 +12395,7 @@
         <v>123</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>605</v>
@@ -12451,7 +12456,7 @@
     </row>
     <row r="200" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B200" s="4">
         <v>1</v>
@@ -12466,7 +12471,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>123</v>
@@ -12475,10 +12480,10 @@
         <v>162</v>
       </c>
       <c r="I200" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>598</v>
@@ -12495,7 +12500,7 @@
     </row>
     <row r="201" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B201" s="4">
         <v>1</v>
@@ -12510,7 +12515,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>123</v>
@@ -12649,7 +12654,7 @@
         <v>501</v>
       </c>
       <c r="M204" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N204" s="2" t="s">
         <v>264</v>
@@ -12688,7 +12693,7 @@
         <v>257</v>
       </c>
       <c r="M205" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N205" s="2" t="s">
         <v>263</v>
@@ -12768,7 +12773,7 @@
         <v>270</v>
       </c>
       <c r="M207" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N207" s="2" t="s">
         <v>263</v>
@@ -12850,7 +12855,7 @@
         <v>501</v>
       </c>
       <c r="M209" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N209" s="2" t="s">
         <v>264</v>
@@ -12858,7 +12863,7 @@
     </row>
     <row r="210" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
@@ -12873,13 +12878,13 @@
         <v>22</v>
       </c>
       <c r="F210" s="8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
@@ -12889,7 +12894,7 @@
     </row>
     <row r="211" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B211" s="4">
         <v>1</v>
@@ -12904,19 +12909,19 @@
         <v>22</v>
       </c>
       <c r="F211" s="8" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I211" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>598</v>
@@ -12933,7 +12938,7 @@
     </row>
     <row r="212" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B212" s="4">
         <v>1</v>
@@ -12948,25 +12953,25 @@
         <v>22</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="J212" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K212" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="L212" s="2" t="s">
         <v>501</v>
       </c>
       <c r="M212" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N212" s="2" t="s">
         <v>264</v>
@@ -13015,7 +13020,7 @@
     </row>
     <row r="214" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B214" s="4">
         <v>1</v>
@@ -13030,16 +13035,16 @@
         <v>22</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K214" s="2" t="s">
         <v>622</v>
@@ -13056,7 +13061,7 @@
     </row>
     <row r="215" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B215" s="4">
         <v>1</v>
@@ -13071,16 +13076,16 @@
         <v>22</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H215" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J215" s="12" t="s">
         <v>1078</v>
-      </c>
-      <c r="J215" s="12" t="s">
-        <v>1079</v>
       </c>
       <c r="K215" s="12" t="s">
         <v>288</v>
@@ -13089,7 +13094,7 @@
         <v>258</v>
       </c>
       <c r="M215" s="28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N215" s="12" t="s">
         <v>264</v>
@@ -13118,7 +13123,7 @@
         <v>123</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>724</v>
@@ -13130,7 +13135,7 @@
         <v>269</v>
       </c>
       <c r="M216" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N216" s="2" t="s">
         <v>264</v>
@@ -13220,7 +13225,7 @@
     </row>
     <row r="219" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B219" s="4">
         <v>1</v>
@@ -13235,7 +13240,7 @@
         <v>8</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>123</v>
@@ -13244,10 +13249,10 @@
         <v>173</v>
       </c>
       <c r="J219" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="K219" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="K219" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="L219" s="2" t="s">
         <v>271</v>
@@ -13324,7 +13329,7 @@
         <v>176</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>669</v>
@@ -13333,7 +13338,7 @@
         <v>501</v>
       </c>
       <c r="M221" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N221" s="2" t="s">
         <v>264</v>
@@ -13356,7 +13361,7 @@
         <v>22</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>123</v>
@@ -13365,7 +13370,7 @@
         <v>176</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K222" s="2" t="s">
         <v>580</v>
@@ -13374,7 +13379,7 @@
         <v>257</v>
       </c>
       <c r="M222" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N222" s="2" t="s">
         <v>263</v>
@@ -13406,7 +13411,7 @@
         <v>176</v>
       </c>
       <c r="J223" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K223" s="2" t="s">
         <v>598</v>
@@ -13522,7 +13527,7 @@
         <v>123</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>623</v>
@@ -13575,7 +13580,7 @@
         <v>257</v>
       </c>
       <c r="M227" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N227" s="2" t="s">
         <v>263</v>
@@ -13655,7 +13660,7 @@
         <v>501</v>
       </c>
       <c r="M229" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N229" s="2" t="s">
         <v>264</v>
@@ -13721,7 +13726,7 @@
         <v>123</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>630</v>
@@ -13741,7 +13746,7 @@
     </row>
     <row r="232" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B232" s="4">
         <v>1</v>
@@ -13756,16 +13761,16 @@
         <v>19</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K232" s="2" t="s">
         <v>598</v>
@@ -13803,7 +13808,7 @@
         <v>123</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>631</v>
@@ -13815,7 +13820,7 @@
         <v>260</v>
       </c>
       <c r="M233" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N233" s="2" t="s">
         <v>264</v>
@@ -13844,7 +13849,7 @@
         <v>123</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>633</v>
@@ -13864,7 +13869,7 @@
     </row>
     <row r="235" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B235" s="4">
         <v>1</v>
@@ -13879,7 +13884,7 @@
         <v>22</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>123</v>
@@ -13888,10 +13893,10 @@
         <v>176</v>
       </c>
       <c r="I235" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K235" s="2" t="s">
         <v>632</v>
@@ -13900,7 +13905,7 @@
         <v>260</v>
       </c>
       <c r="M235" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N235" s="2" t="s">
         <v>264</v>
@@ -13941,7 +13946,7 @@
         <v>501</v>
       </c>
       <c r="M236" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N236" s="2" t="s">
         <v>264</v>
@@ -14101,7 +14106,7 @@
         <v>257</v>
       </c>
       <c r="M240" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N240" s="2" t="s">
         <v>263</v>
@@ -14140,7 +14145,7 @@
         <v>257</v>
       </c>
       <c r="M241" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N241" s="2" t="s">
         <v>263</v>
@@ -14187,7 +14192,7 @@
     </row>
     <row r="243" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B243" s="4">
         <v>1</v>
@@ -14202,14 +14207,14 @@
         <v>22</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H243" s="4"/>
       <c r="J243" s="14" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="K243" s="14" t="s">
         <v>280</v>
@@ -14298,7 +14303,7 @@
         <v>501</v>
       </c>
       <c r="M245" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N245" s="2" t="s">
         <v>264</v>
@@ -14417,7 +14422,7 @@
         <v>501</v>
       </c>
       <c r="M248" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N248" s="2" t="s">
         <v>264</v>
@@ -14522,7 +14527,7 @@
         <v>123</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>654</v>
@@ -14614,7 +14619,7 @@
         <v>501</v>
       </c>
       <c r="M253" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N253" s="2" t="s">
         <v>264</v>
@@ -14694,7 +14699,7 @@
         <v>257</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N255" s="2" t="s">
         <v>263</v>
@@ -14741,7 +14746,7 @@
     </row>
     <row r="257" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B257" s="4">
         <v>1</v>
@@ -14756,16 +14761,16 @@
         <v>8</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J257" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="K257" s="2" t="s">
         <v>662</v>
@@ -14782,7 +14787,7 @@
     </row>
     <row r="258" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B258" s="4">
         <v>1</v>
@@ -14797,16 +14802,16 @@
         <v>8</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J258" s="14" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="K258" s="14" t="s">
         <v>280</v>
@@ -14862,7 +14867,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B260" s="4">
         <v>1</v>
@@ -14877,16 +14882,16 @@
         <v>22</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K260" s="2" t="s">
         <v>588</v>
@@ -14903,7 +14908,7 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B261" s="4">
         <v>1</v>
@@ -14918,16 +14923,16 @@
         <v>22</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="K261" s="2" t="s">
         <v>537</v>
@@ -14936,7 +14941,7 @@
         <v>257</v>
       </c>
       <c r="M261" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N261" s="2" t="s">
         <v>263</v>
@@ -14944,7 +14949,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B262" s="4">
         <v>1</v>
@@ -14959,16 +14964,16 @@
         <v>22</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K262" s="2" t="s">
         <v>604</v>
@@ -14977,7 +14982,7 @@
         <v>260</v>
       </c>
       <c r="M262" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N262" s="2" t="s">
         <v>264</v>
@@ -14985,7 +14990,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
@@ -15000,16 +15005,16 @@
         <v>22</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="K263" s="2" t="s">
         <v>651</v>
@@ -15024,7 +15029,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B264" s="4">
         <v>1</v>
@@ -15039,16 +15044,16 @@
         <v>22</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="K264" s="2" t="s">
         <v>662</v>
@@ -15065,7 +15070,7 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B265" s="4">
         <v>1</v>
@@ -15080,16 +15085,16 @@
         <v>22</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="K265" s="2" t="s">
         <v>596</v>
@@ -15098,7 +15103,7 @@
         <v>256</v>
       </c>
       <c r="M265" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N265" s="2" t="s">
         <v>263</v>
@@ -15106,7 +15111,7 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B266" s="4">
         <v>1</v>
@@ -15121,16 +15126,16 @@
         <v>22</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J266" s="14" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K266" s="14" t="s">
         <v>280</v>
@@ -15147,7 +15152,7 @@
     </row>
     <row r="267" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B267" s="4">
         <v>1</v>
@@ -15162,16 +15167,16 @@
         <v>22</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H267" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="J267" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="J267" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="K267" s="2" t="s">
         <v>588</v>
@@ -15209,7 +15214,7 @@
         <v>123</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>663</v>
@@ -15221,7 +15226,7 @@
         <v>257</v>
       </c>
       <c r="M268" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N268" s="2" t="s">
         <v>263</v>
@@ -15250,7 +15255,7 @@
         <v>123</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>664</v>
@@ -15301,7 +15306,7 @@
         <v>270</v>
       </c>
       <c r="M270" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N270" s="2" t="s">
         <v>263</v>
@@ -15379,7 +15384,7 @@
         <v>256</v>
       </c>
       <c r="M272" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N272" s="2" t="s">
         <v>263</v>
@@ -15457,7 +15462,7 @@
         <v>501</v>
       </c>
       <c r="M274" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N274" s="2" t="s">
         <v>264</v>
@@ -15535,7 +15540,7 @@
         <v>257</v>
       </c>
       <c r="M276" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N276" s="2" t="s">
         <v>263</v>
@@ -15597,7 +15602,7 @@
         <v>8</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G278" s="4" t="s">
         <v>123</v>
@@ -15621,7 +15626,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B279" s="4">
         <v>1</v>
@@ -15636,16 +15641,16 @@
         <v>8</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J279" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K279" s="2" t="s">
         <v>533</v>
@@ -15654,7 +15659,7 @@
         <v>270</v>
       </c>
       <c r="M279" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N279" s="2" t="s">
         <v>263</v>
@@ -15662,7 +15667,7 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B280" s="4">
         <v>1</v>
@@ -15677,16 +15682,16 @@
         <v>8</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J280" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="K280" s="2" t="s">
         <v>588</v>
@@ -15703,7 +15708,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B281" s="4">
         <v>1</v>
@@ -15718,16 +15723,16 @@
         <v>8</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H281" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="J281" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="J281" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="K281" s="2" t="s">
         <v>598</v>
@@ -15744,7 +15749,7 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B282" s="4">
         <v>1</v>
@@ -15759,16 +15764,16 @@
         <v>8</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J282" s="14" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K282" s="14" t="s">
         <v>280</v>
@@ -15785,7 +15790,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B283" s="4">
         <v>1</v>
@@ -15800,16 +15805,16 @@
         <v>8</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J283" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K283" s="2" t="s">
         <v>638</v>
@@ -15826,7 +15831,7 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B284" s="4">
         <v>1</v>
@@ -15841,19 +15846,19 @@
         <v>8</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G284" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I284" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="J284" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="K284" s="2" t="s">
         <v>669</v>
@@ -15862,7 +15867,7 @@
         <v>501</v>
       </c>
       <c r="M284" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N284" s="2" t="s">
         <v>264</v>
@@ -15891,10 +15896,10 @@
         <v>123</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J285" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K285" s="2" t="s">
         <v>596</v>
@@ -15903,7 +15908,7 @@
         <v>256</v>
       </c>
       <c r="M285" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N285" s="2" t="s">
         <v>263</v>
@@ -15911,7 +15916,7 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B286" s="4">
         <v>1</v>
@@ -15926,7 +15931,7 @@
         <v>8</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G286" s="4" t="s">
         <v>123</v>
@@ -15968,7 +15973,7 @@
         <v>257</v>
       </c>
       <c r="M287" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N287" s="2" t="s">
         <v>263</v>
@@ -16200,7 +16205,7 @@
         <v>501</v>
       </c>
       <c r="M293" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N293" s="2" t="s">
         <v>264</v>
@@ -16358,7 +16363,7 @@
         <v>257</v>
       </c>
       <c r="M297" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N297" s="2" t="s">
         <v>263</v>
@@ -16397,7 +16402,7 @@
         <v>256</v>
       </c>
       <c r="M298" s="27" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N298" s="2" t="s">
         <v>263</v>
@@ -16475,7 +16480,7 @@
         <v>501</v>
       </c>
       <c r="M300" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N300" s="2" t="s">
         <v>264</v>
@@ -16592,7 +16597,7 @@
         <v>501</v>
       </c>
       <c r="M303" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N303" s="2" t="s">
         <v>264</v>
@@ -16695,14 +16700,14 @@
         <v>22</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G306" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>691</v>
@@ -16913,7 +16918,7 @@
         <v>257</v>
       </c>
       <c r="M311" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N311" s="2" t="s">
         <v>263</v>
@@ -16995,7 +17000,7 @@
         <v>257</v>
       </c>
       <c r="M313" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N313" s="2" t="s">
         <v>263</v>
@@ -17036,7 +17041,7 @@
         <v>257</v>
       </c>
       <c r="M314" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N314" s="2" t="s">
         <v>263</v>
@@ -17106,7 +17111,7 @@
         <v>123</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>698</v>
@@ -17286,7 +17291,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B321" s="4">
         <v>1</v>
@@ -17397,7 +17402,7 @@
         <v>257</v>
       </c>
       <c r="M323" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N323" s="2" t="s">
         <v>263</v>
@@ -17436,7 +17441,7 @@
         <v>269</v>
       </c>
       <c r="M324" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N324" s="2" t="s">
         <v>264</v>
@@ -17465,7 +17470,7 @@
         <v>123</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>706</v>
@@ -17561,7 +17566,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B328" s="4">
         <v>1</v>
@@ -17576,16 +17581,16 @@
         <v>22</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G328" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H328" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J328" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="J328" s="2" t="s">
-        <v>1104</v>
       </c>
       <c r="K328" s="2" t="s">
         <v>640</v>
@@ -17594,7 +17599,7 @@
         <v>257</v>
       </c>
       <c r="M328" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N328" s="2" t="s">
         <v>263</v>
@@ -17602,7 +17607,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B329" s="4">
         <v>1</v>
@@ -17617,16 +17622,16 @@
         <v>22</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G329" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="J329" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K329" s="14" t="s">
         <v>280</v>
@@ -17643,7 +17648,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B330" s="4">
         <v>1</v>
@@ -17658,25 +17663,25 @@
         <v>19</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G330" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="J330" s="21" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="K330" s="21" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L330" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M330" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="M330" s="31" t="s">
-        <v>1039</v>
       </c>
       <c r="N330" s="21" t="s">
         <v>264</v>
@@ -17684,7 +17689,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B331" s="4">
         <v>1</v>
@@ -17699,16 +17704,16 @@
         <v>8</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H331" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="J331" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K331" s="2" t="s">
         <v>640</v>
@@ -17717,7 +17722,7 @@
         <v>257</v>
       </c>
       <c r="M331" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N331" s="2" t="s">
         <v>263</v>
@@ -17725,7 +17730,7 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B332" s="4">
         <v>1</v>
@@ -17740,16 +17745,16 @@
         <v>8</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G332" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H332" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J332" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="J332" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="K332" s="2" t="s">
         <v>588</v>
@@ -17766,7 +17771,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B333" s="4">
         <v>1</v>
@@ -17781,16 +17786,16 @@
         <v>8</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G333" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H333" s="4" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J333" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="K333" s="2" t="s">
         <v>627</v>
@@ -17799,7 +17804,7 @@
         <v>501</v>
       </c>
       <c r="M333" s="30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N333" s="2" t="s">
         <v>264</v>
@@ -17993,6 +17998,7 @@
     <hyperlink ref="F140" r:id="rId76" xr:uid="{0941838F-7D94-4A51-80A0-CC0D68EAB643}"/>
     <hyperlink ref="F169" r:id="rId77" xr:uid="{025C175C-D52D-4A5A-83EA-FC3E86618CDC}"/>
     <hyperlink ref="F10" r:id="rId78" xr:uid="{E46A1E00-29FE-4E0F-9DA6-866319038D91}"/>
+    <hyperlink ref="I128" r:id="rId79" xr:uid="{9D222E28-C3BD-45B6-9C21-3A7571A3E40C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C83F8B-5779-467B-8B87-81526854653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D209C-FA26-4717-ADF2-FB0A79AA7ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4121,49 +4121,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF82D8B1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9F57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD253"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -12453,10 +12411,10 @@
         <v>1</v>
       </c>
       <c r="C191" s="4">
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="D191" s="4">
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>19</v>
@@ -12494,10 +12452,10 @@
         <v>1</v>
       </c>
       <c r="C192" s="4">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="D192" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>19</v>
@@ -12533,10 +12491,10 @@
         <v>1</v>
       </c>
       <c r="C193" s="4">
-        <v>6000</v>
+        <v>7100</v>
       </c>
       <c r="D193" s="4">
-        <v>3500</v>
+        <v>4400</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>8</v>
@@ -12574,10 +12532,10 @@
         <v>1</v>
       </c>
       <c r="C194" s="4">
-        <v>5500</v>
+        <v>6300</v>
       </c>
       <c r="D194" s="4">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>19</v>
@@ -12615,10 +12573,10 @@
         <v>1</v>
       </c>
       <c r="C195" s="4">
-        <v>4000</v>
+        <v>5900</v>
       </c>
       <c r="D195" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>8</v>
@@ -12654,10 +12612,10 @@
         <v>1</v>
       </c>
       <c r="C196" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D196" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>22</v>
@@ -12695,10 +12653,10 @@
         <v>1</v>
       </c>
       <c r="C197" s="4">
-        <v>5500</v>
+        <v>4300</v>
       </c>
       <c r="D197" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>22</v>
@@ -12734,10 +12692,10 @@
         <v>1</v>
       </c>
       <c r="C198" s="4">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="D198" s="4">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>22</v>
@@ -12775,10 +12733,10 @@
         <v>1</v>
       </c>
       <c r="C199" s="4">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="D199" s="4">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>22</v>
@@ -12816,10 +12774,10 @@
         <v>1</v>
       </c>
       <c r="C200" s="4">
-        <v>4000</v>
+        <v>5100</v>
       </c>
       <c r="D200" s="4">
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>22</v>
@@ -12855,10 +12813,10 @@
         <v>1</v>
       </c>
       <c r="C201" s="4">
-        <v>5000</v>
+        <v>5800</v>
       </c>
       <c r="D201" s="4">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>22</v>
@@ -12896,10 +12854,10 @@
         <v>1</v>
       </c>
       <c r="C202" s="4">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="D202" s="4">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>22</v>
@@ -12937,10 +12895,10 @@
         <v>1</v>
       </c>
       <c r="C203" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D203" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>22</v>
@@ -12966,10 +12924,10 @@
         <v>1</v>
       </c>
       <c r="C204" s="4">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="D204" s="4">
-        <v>2500</v>
+        <v>4300</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>8</v>
@@ -13007,10 +12965,10 @@
         <v>1</v>
       </c>
       <c r="C205" s="4">
-        <v>4500</v>
+        <v>3700</v>
       </c>
       <c r="D205" s="4">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>8</v>
@@ -13048,10 +13006,10 @@
         <v>1</v>
       </c>
       <c r="C206" s="4">
-        <v>5000</v>
+        <v>3900</v>
       </c>
       <c r="D206" s="4">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>8</v>
@@ -13089,10 +13047,10 @@
         <v>1</v>
       </c>
       <c r="C207" s="4">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="D207" s="4">
-        <v>2500</v>
+        <v>3700</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>8</v>
@@ -13128,10 +13086,10 @@
         <v>1</v>
       </c>
       <c r="C208" s="4">
-        <v>5500</v>
+        <v>6600</v>
       </c>
       <c r="D208" s="4">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>8</v>
@@ -13169,10 +13127,10 @@
         <v>1</v>
       </c>
       <c r="C209" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D209" s="4">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>8</v>
@@ -13210,10 +13168,10 @@
         <v>1</v>
       </c>
       <c r="C210" s="4">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="D210" s="4">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>19</v>
@@ -13251,10 +13209,10 @@
         <v>1</v>
       </c>
       <c r="C211" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D211" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>19</v>
@@ -13295,10 +13253,10 @@
         <v>1</v>
       </c>
       <c r="C212" s="4">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="D212" s="4">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>19</v>
@@ -13336,10 +13294,10 @@
         <v>1</v>
       </c>
       <c r="C213" s="4">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="D213" s="4">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>19</v>
@@ -13377,10 +13335,10 @@
         <v>1</v>
       </c>
       <c r="C214" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D214" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>19</v>
@@ -13416,10 +13374,10 @@
         <v>1</v>
       </c>
       <c r="C215" s="4">
-        <v>4500</v>
+        <v>5600</v>
       </c>
       <c r="D215" s="4">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>8</v>
@@ -13457,10 +13415,10 @@
         <v>1</v>
       </c>
       <c r="C216" s="4">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="D216" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>19</v>
@@ -13496,10 +13454,10 @@
         <v>1</v>
       </c>
       <c r="C217" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D217" s="4">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>19</v>
@@ -13537,10 +13495,10 @@
         <v>1</v>
       </c>
       <c r="C218" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D218" s="4">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>19</v>
@@ -13576,10 +13534,10 @@
         <v>1</v>
       </c>
       <c r="C219" s="4">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="D219" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>19</v>
@@ -13617,10 +13575,10 @@
         <v>1</v>
       </c>
       <c r="C220" s="4">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="D220" s="4">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>8</v>
@@ -13661,7 +13619,7 @@
         <v>3000</v>
       </c>
       <c r="D221" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>22</v>
@@ -13689,10 +13647,10 @@
         <v>1</v>
       </c>
       <c r="C222" s="4">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="D222" s="4">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>22</v>
@@ -13733,10 +13691,10 @@
         <v>1</v>
       </c>
       <c r="C223" s="4">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="D223" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>22</v>
@@ -13774,10 +13732,10 @@
         <v>1</v>
       </c>
       <c r="C224" s="4">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="D224" s="4">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="E224" s="4" t="s">
         <v>22</v>
@@ -13815,10 +13773,10 @@
         <v>1</v>
       </c>
       <c r="C225" s="4">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D225" s="4">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>22</v>
@@ -13856,10 +13814,10 @@
         <v>1</v>
       </c>
       <c r="C226" s="4">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D226" s="4">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>22</v>
@@ -13897,10 +13855,10 @@
         <v>1</v>
       </c>
       <c r="C227" s="4">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="D227" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>22</v>
@@ -13938,10 +13896,10 @@
         <v>1</v>
       </c>
       <c r="C228" s="4">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="D228" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>8</v>
@@ -13979,10 +13937,10 @@
         <v>1</v>
       </c>
       <c r="C229" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D229" s="4">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>8</v>
@@ -14020,10 +13978,10 @@
         <v>1</v>
       </c>
       <c r="C230" s="4">
-        <v>5500</v>
+        <v>6800</v>
       </c>
       <c r="D230" s="4">
-        <v>4500</v>
+        <v>4100</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>8</v>
@@ -14059,10 +14017,10 @@
         <v>1</v>
       </c>
       <c r="C231" s="4">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="D231" s="4">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>8</v>
@@ -14100,10 +14058,10 @@
         <v>1</v>
       </c>
       <c r="C232" s="4">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="D232" s="4">
-        <v>2000</v>
+        <v>3700</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>22</v>
@@ -14141,10 +14099,10 @@
         <v>1</v>
       </c>
       <c r="C233" s="4">
-        <v>3500</v>
+        <v>4600</v>
       </c>
       <c r="D233" s="4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>22</v>
@@ -14182,10 +14140,10 @@
         <v>1</v>
       </c>
       <c r="C234" s="4">
-        <v>5500</v>
+        <v>6400</v>
       </c>
       <c r="D234" s="4">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>8</v>
@@ -14223,10 +14181,10 @@
         <v>1</v>
       </c>
       <c r="C235" s="4">
-        <v>6000</v>
+        <v>7100</v>
       </c>
       <c r="D235" s="4">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>8</v>
@@ -14262,10 +14220,10 @@
         <v>1</v>
       </c>
       <c r="C236" s="4">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="D236" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>8</v>
@@ -14303,10 +14261,10 @@
         <v>1</v>
       </c>
       <c r="C237" s="4">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="D237" s="4">
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>8</v>
@@ -14344,10 +14302,10 @@
         <v>1</v>
       </c>
       <c r="C238" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D238" s="4">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>19</v>
@@ -14385,10 +14343,10 @@
         <v>1</v>
       </c>
       <c r="C239" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D239" s="4">
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>19</v>
@@ -14424,10 +14382,10 @@
         <v>1</v>
       </c>
       <c r="C240" s="4">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="D240" s="4">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="E240" s="4" t="s">
         <v>19</v>
@@ -14461,10 +14419,10 @@
         <v>1</v>
       </c>
       <c r="C241" s="4">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D241" s="4">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>8</v>
@@ -14502,10 +14460,10 @@
         <v>1</v>
       </c>
       <c r="C242" s="4">
-        <v>4000</v>
+        <v>6200</v>
       </c>
       <c r="D242" s="4">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E242" s="4" t="s">
         <v>19</v>
@@ -14543,10 +14501,10 @@
         <v>1</v>
       </c>
       <c r="C243" s="4">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="D243" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>19</v>
@@ -14584,10 +14542,10 @@
         <v>1</v>
       </c>
       <c r="C244" s="4">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="D244" s="4">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="E244" s="4" t="s">
         <v>22</v>
@@ -14625,10 +14583,10 @@
         <v>1</v>
       </c>
       <c r="C245" s="4">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="D245" s="4">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="E245" s="4" t="s">
         <v>22</v>
@@ -14669,10 +14627,10 @@
         <v>1</v>
       </c>
       <c r="C246" s="4">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="D246" s="4">
-        <v>2500</v>
+        <v>3700</v>
       </c>
       <c r="E246" s="4" t="s">
         <v>22</v>
@@ -14710,10 +14668,10 @@
         <v>1</v>
       </c>
       <c r="C247" s="4">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="D247" s="4">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>19</v>
@@ -14749,10 +14707,10 @@
         <v>1</v>
       </c>
       <c r="C248" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D248" s="4">
-        <v>2000</v>
+        <v>2900</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>19</v>
@@ -14790,10 +14748,10 @@
         <v>1</v>
       </c>
       <c r="C249" s="4">
-        <v>4500</v>
+        <v>5300</v>
       </c>
       <c r="D249" s="4">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>8</v>
@@ -14829,10 +14787,10 @@
         <v>1</v>
       </c>
       <c r="C250" s="4">
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="D250" s="4">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>19</v>
@@ -14870,10 +14828,10 @@
         <v>1</v>
       </c>
       <c r="C251" s="4">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="D251" s="4">
-        <v>3000</v>
+        <v>4300</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>8</v>
@@ -14909,10 +14867,10 @@
         <v>1</v>
       </c>
       <c r="C252" s="4">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="D252" s="4">
-        <v>2000</v>
+        <v>2900</v>
       </c>
       <c r="E252" s="4" t="s">
         <v>19</v>
@@ -14948,10 +14906,10 @@
         <v>1</v>
       </c>
       <c r="C253" s="4">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="D253" s="4">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="E253" s="4" t="s">
         <v>22</v>
@@ -14987,10 +14945,10 @@
         <v>1</v>
       </c>
       <c r="C254" s="4">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="D254" s="4">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E254" s="4" t="s">
         <v>19</v>
@@ -15028,10 +14986,10 @@
         <v>1</v>
       </c>
       <c r="C255" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D255" s="4">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E255" s="4" t="s">
         <v>8</v>
@@ -15067,10 +15025,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="4">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="D256" s="4">
-        <v>2500</v>
+        <v>4200</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>22</v>
@@ -15106,10 +15064,10 @@
         <v>1</v>
       </c>
       <c r="C257" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D257" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E257" s="4" t="s">
         <v>22</v>
@@ -15147,10 +15105,10 @@
         <v>1</v>
       </c>
       <c r="C258" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D258" s="4">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E258" s="4" t="s">
         <v>19</v>
@@ -15186,10 +15144,10 @@
         <v>1</v>
       </c>
       <c r="C259" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D259" s="4">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="E259" s="4" t="s">
         <v>19</v>
@@ -15223,10 +15181,10 @@
         <v>1</v>
       </c>
       <c r="C260" s="4">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="D260" s="4">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E260" s="4" t="s">
         <v>8</v>
@@ -15262,10 +15220,10 @@
         <v>1</v>
       </c>
       <c r="C261" s="4">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="D261" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>8</v>
@@ -15303,10 +15261,10 @@
         <v>1</v>
       </c>
       <c r="C262" s="4">
-        <v>5000</v>
+        <v>7100</v>
       </c>
       <c r="D262" s="4">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="E262" s="4" t="s">
         <v>22</v>
@@ -15342,10 +15300,10 @@
         <v>1</v>
       </c>
       <c r="C263" s="4">
-        <v>5000</v>
+        <v>5900</v>
       </c>
       <c r="D263" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>22</v>
@@ -15383,10 +15341,10 @@
         <v>1</v>
       </c>
       <c r="C264" s="4">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D264" s="4">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="E264" s="4" t="s">
         <v>8</v>
@@ -15422,10 +15380,10 @@
         <v>1</v>
       </c>
       <c r="C265" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D265" s="4">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E265" s="4" t="s">
         <v>8</v>
@@ -15463,10 +15421,10 @@
         <v>1</v>
       </c>
       <c r="C266" s="4">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="D266" s="4">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>8</v>
@@ -15502,7 +15460,7 @@
         <v>1</v>
       </c>
       <c r="C267" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D267" s="4">
         <v>2500</v>
@@ -15543,10 +15501,10 @@
         <v>1</v>
       </c>
       <c r="C268" s="4">
-        <v>4500</v>
+        <v>6800</v>
       </c>
       <c r="D268" s="4">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="E268" s="4" t="s">
         <v>8</v>
@@ -15584,10 +15542,10 @@
         <v>1</v>
       </c>
       <c r="C269" s="4">
-        <v>5500</v>
+        <v>6500</v>
       </c>
       <c r="D269" s="4">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="E269" s="4" t="s">
         <v>19</v>
@@ -15626,7 +15584,7 @@
         <v>4000</v>
       </c>
       <c r="D270" s="4">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="E270" s="4" t="s">
         <v>22</v>
@@ -15664,10 +15622,10 @@
         <v>1</v>
       </c>
       <c r="C271" s="4">
-        <v>4500</v>
+        <v>6600</v>
       </c>
       <c r="D271" s="4">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="E271" s="4" t="s">
         <v>22</v>
@@ -15705,10 +15663,10 @@
         <v>1</v>
       </c>
       <c r="C272" s="4">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="D272" s="4">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="E272" s="4" t="s">
         <v>22</v>
@@ -15746,10 +15704,10 @@
         <v>1</v>
       </c>
       <c r="C273" s="4">
-        <v>3500</v>
+        <v>4900</v>
       </c>
       <c r="D273" s="4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E273" s="4" t="s">
         <v>22</v>
@@ -15785,10 +15743,10 @@
         <v>1</v>
       </c>
       <c r="C274" s="4">
+        <v>7000</v>
+      </c>
+      <c r="D274" s="4">
         <v>4000</v>
-      </c>
-      <c r="D274" s="4">
-        <v>2000</v>
       </c>
       <c r="E274" s="4" t="s">
         <v>22</v>
@@ -15826,10 +15784,10 @@
         <v>1</v>
       </c>
       <c r="C275" s="4">
+        <v>3200</v>
+      </c>
+      <c r="D275" s="4">
         <v>2500</v>
-      </c>
-      <c r="D275" s="4">
-        <v>1000</v>
       </c>
       <c r="E275" s="4" t="s">
         <v>22</v>
@@ -15867,10 +15825,10 @@
         <v>1</v>
       </c>
       <c r="C276" s="4">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="D276" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E276" s="4" t="s">
         <v>22</v>
@@ -15908,10 +15866,10 @@
         <v>1</v>
       </c>
       <c r="C277" s="4">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="D277" s="4">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>22</v>
@@ -15949,10 +15907,10 @@
         <v>1</v>
       </c>
       <c r="C278" s="4">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="D278" s="4">
-        <v>3500</v>
+        <v>2600</v>
       </c>
       <c r="E278" s="4" t="s">
         <v>22</v>
@@ -15990,10 +15948,10 @@
         <v>1</v>
       </c>
       <c r="C279" s="4">
-        <v>5500</v>
+        <v>7100</v>
       </c>
       <c r="D279" s="4">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>22</v>
@@ -16031,10 +15989,10 @@
         <v>1</v>
       </c>
       <c r="C280" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D280" s="4">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>19</v>
@@ -16070,10 +16028,10 @@
         <v>1</v>
       </c>
       <c r="C281" s="4">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="D281" s="4">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E281" s="4" t="s">
         <v>19</v>
@@ -16109,10 +16067,10 @@
         <v>1</v>
       </c>
       <c r="C282" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D282" s="4">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="E282" s="4" t="s">
         <v>19</v>
@@ -16148,10 +16106,10 @@
         <v>1</v>
       </c>
       <c r="C283" s="4">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="D283" s="4">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="E283" s="4" t="s">
         <v>19</v>
@@ -16187,10 +16145,10 @@
         <v>1</v>
       </c>
       <c r="C284" s="4">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="D284" s="4">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E284" s="4" t="s">
         <v>19</v>
@@ -16229,7 +16187,7 @@
         <v>5000</v>
       </c>
       <c r="D285" s="4">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E285" s="4" t="s">
         <v>22</v>
@@ -16265,10 +16223,10 @@
         <v>1</v>
       </c>
       <c r="C286" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D286" s="4">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="E286" s="4" t="s">
         <v>8</v>
@@ -16307,7 +16265,7 @@
         <v>3500</v>
       </c>
       <c r="D287" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E287" s="4" t="s">
         <v>8</v>
@@ -16343,10 +16301,10 @@
         <v>1</v>
       </c>
       <c r="C288" s="4">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="D288" s="4">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E288" s="4" t="s">
         <v>8</v>
@@ -16382,10 +16340,10 @@
         <v>1</v>
       </c>
       <c r="C289" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="D289" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E289" s="4" t="s">
         <v>8</v>
@@ -16423,10 +16381,10 @@
         <v>1</v>
       </c>
       <c r="C290" s="4">
-        <v>4000</v>
+        <v>4900</v>
       </c>
       <c r="D290" s="4">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="E290" s="4" t="s">
         <v>8</v>
@@ -16464,10 +16422,10 @@
         <v>1</v>
       </c>
       <c r="C291" s="4">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="D291" s="4">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="E291" s="4" t="s">
         <v>8</v>
@@ -16505,10 +16463,10 @@
         <v>1</v>
       </c>
       <c r="C292" s="4">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="D292" s="4">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E292" s="4" t="s">
         <v>8</v>
@@ -16546,10 +16504,10 @@
         <v>1</v>
       </c>
       <c r="C293" s="4">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="D293" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E293" s="4" t="s">
         <v>8</v>
@@ -16587,10 +16545,10 @@
         <v>1</v>
       </c>
       <c r="C294" s="4">
-        <v>3500</v>
+        <v>5100</v>
       </c>
       <c r="D294" s="4">
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="E294" s="4" t="s">
         <v>8</v>
@@ -16631,10 +16589,10 @@
         <v>1</v>
       </c>
       <c r="C295" s="4">
-        <v>5000</v>
+        <v>5900</v>
       </c>
       <c r="D295" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>8</v>
@@ -16672,10 +16630,10 @@
         <v>1</v>
       </c>
       <c r="C296" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D296" s="4">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="E296" s="4" t="s">
         <v>8</v>
@@ -16698,10 +16656,10 @@
         <v>1</v>
       </c>
       <c r="C297" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D297" s="4">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="E297" s="4" t="s">
         <v>8</v>
@@ -16737,10 +16695,10 @@
         <v>1</v>
       </c>
       <c r="C298" s="4">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="D298" s="4">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="E298" s="4" t="s">
         <v>8</v>
@@ -16776,10 +16734,10 @@
         <v>1</v>
       </c>
       <c r="C299" s="4">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="D299" s="4">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E299" s="4" t="s">
         <v>8</v>
@@ -16813,10 +16771,10 @@
         <v>1</v>
       </c>
       <c r="C300" s="4">
-        <v>5000</v>
+        <v>6800</v>
       </c>
       <c r="D300" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E300" s="4" t="s">
         <v>8</v>
@@ -16852,10 +16810,10 @@
         <v>1</v>
       </c>
       <c r="C301" s="4">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="D301" s="4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E301" s="4" t="s">
         <v>8</v>
@@ -16891,10 +16849,10 @@
         <v>1</v>
       </c>
       <c r="C302" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D302" s="4">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="E302" s="4" t="s">
         <v>8</v>
@@ -16930,10 +16888,10 @@
         <v>1</v>
       </c>
       <c r="C303" s="4">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="D303" s="4">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="E303" s="4" t="s">
         <v>19</v>
@@ -16969,10 +16927,10 @@
         <v>1</v>
       </c>
       <c r="C304" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D304" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E304" s="4" t="s">
         <v>19</v>
@@ -17006,10 +16964,10 @@
         <v>1</v>
       </c>
       <c r="C305" s="4">
-        <v>5000</v>
+        <v>5800</v>
       </c>
       <c r="D305" s="4">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="E305" s="4" t="s">
         <v>8</v>
@@ -17047,10 +17005,10 @@
         <v>1</v>
       </c>
       <c r="C306" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D306" s="4">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>8</v>
@@ -17088,10 +17046,10 @@
         <v>1</v>
       </c>
       <c r="C307" s="4">
-        <v>3500</v>
+        <v>2400</v>
       </c>
       <c r="D307" s="4">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="E307" s="4" t="s">
         <v>19</v>
@@ -17127,10 +17085,10 @@
         <v>1</v>
       </c>
       <c r="C308" s="4">
-        <v>5500</v>
+        <v>6900</v>
       </c>
       <c r="D308" s="4">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="E308" s="4" t="s">
         <v>8</v>
@@ -17166,10 +17124,10 @@
         <v>1</v>
       </c>
       <c r="C309" s="4">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="D309" s="4">
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="E309" s="4" t="s">
         <v>8</v>
@@ -17205,10 +17163,10 @@
         <v>1</v>
       </c>
       <c r="C310" s="4">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="D310" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E310" s="4" t="s">
         <v>19</v>
@@ -17244,10 +17202,10 @@
         <v>1</v>
       </c>
       <c r="C311" s="4">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D311" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="E311" s="4" t="s">
         <v>19</v>
@@ -17281,10 +17239,10 @@
         <v>1</v>
       </c>
       <c r="C312" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D312" s="4">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="E312" s="4" t="s">
         <v>8</v>
@@ -17320,10 +17278,10 @@
         <v>1</v>
       </c>
       <c r="C313" s="4">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="D313" s="4">
-        <v>2000</v>
+        <v>3700</v>
       </c>
       <c r="E313" s="4" t="s">
         <v>22</v>
@@ -17361,10 +17319,10 @@
         <v>1</v>
       </c>
       <c r="C314" s="4">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="D314" s="4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E314" s="4" t="s">
         <v>22</v>
@@ -17402,10 +17360,10 @@
         <v>1</v>
       </c>
       <c r="C315" s="4">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="D315" s="4">
-        <v>2500</v>
+        <v>3700</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>22</v>
@@ -17441,10 +17399,10 @@
         <v>1</v>
       </c>
       <c r="C316" s="4">
-        <v>6000</v>
+        <v>7100</v>
       </c>
       <c r="D316" s="4">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="E316" s="4" t="s">
         <v>22</v>
@@ -17483,10 +17441,10 @@
         <v>1</v>
       </c>
       <c r="C317" s="4">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="D317" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E317" s="4" t="s">
         <v>22</v>
@@ -17522,10 +17480,10 @@
         <v>1</v>
       </c>
       <c r="C318" s="4">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="D318" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E318" s="4" t="s">
         <v>8</v>
@@ -17563,10 +17521,10 @@
         <v>1</v>
       </c>
       <c r="C319" s="4">
-        <v>5000</v>
+        <v>6700</v>
       </c>
       <c r="D319" s="4">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="E319" s="4" t="s">
         <v>8</v>
@@ -17604,10 +17562,10 @@
         <v>1</v>
       </c>
       <c r="C320" s="4">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="D320" s="4">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="E320" s="4" t="s">
         <v>8</v>
@@ -17643,10 +17601,10 @@
         <v>1</v>
       </c>
       <c r="C321" s="4">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="D321" s="4">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E321" s="4" t="s">
         <v>19</v>
@@ -17682,10 +17640,10 @@
         <v>1</v>
       </c>
       <c r="C322" s="4">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="D322" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E322" s="4" t="s">
         <v>22</v>
@@ -17723,10 +17681,10 @@
         <v>1</v>
       </c>
       <c r="C323" s="4">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="D323" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E323" s="4" t="s">
         <v>8</v>
@@ -17764,10 +17722,10 @@
         <v>1</v>
       </c>
       <c r="C324" s="4">
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="D324" s="4">
-        <v>2500</v>
+        <v>3800</v>
       </c>
       <c r="E324" s="4" t="s">
         <v>8</v>
@@ -17805,10 +17763,10 @@
         <v>1</v>
       </c>
       <c r="C325" s="4">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="D325" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E325" s="4" t="s">
         <v>8</v>
@@ -17846,10 +17804,10 @@
         <v>1</v>
       </c>
       <c r="C326" s="4">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="D326" s="4">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="E326" s="4" t="s">
         <v>19</v>
@@ -17887,10 +17845,10 @@
         <v>1</v>
       </c>
       <c r="C327" s="4">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="D327" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E327" s="4" t="s">
         <v>8</v>
@@ -17928,10 +17886,10 @@
         <v>1</v>
       </c>
       <c r="C328" s="4">
-        <v>4500</v>
+        <v>6600</v>
       </c>
       <c r="D328" s="4">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E328" s="4" t="s">
         <v>8</v>
@@ -17969,10 +17927,10 @@
         <v>1</v>
       </c>
       <c r="C329" s="4">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="D329" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>22</v>
@@ -18008,10 +17966,10 @@
         <v>1</v>
       </c>
       <c r="C330" s="4">
-        <v>4000</v>
+        <v>7100</v>
       </c>
       <c r="D330" s="4">
-        <v>2500</v>
+        <v>4100</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>22</v>
@@ -18047,10 +18005,10 @@
         <v>1</v>
       </c>
       <c r="C331" s="4">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="D331" s="4">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="E331" s="4" t="s">
         <v>22</v>
@@ -18086,10 +18044,10 @@
         <v>1</v>
       </c>
       <c r="C332" s="4">
-        <v>5500</v>
+        <v>6700</v>
       </c>
       <c r="D332" s="4">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="E332" s="4" t="s">
         <v>8</v>
@@ -18127,10 +18085,10 @@
         <v>1</v>
       </c>
       <c r="C333" s="4">
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="D333" s="4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E333" s="4" t="s">
         <v>8</v>
@@ -18166,10 +18124,10 @@
         <v>1</v>
       </c>
       <c r="C334" s="4">
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="D334" s="4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E334" s="4" t="s">
         <v>22</v>
@@ -18205,10 +18163,10 @@
         <v>1</v>
       </c>
       <c r="C335" s="4">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="D335" s="4">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="E335" s="4" t="s">
         <v>19</v>
@@ -18244,10 +18202,10 @@
         <v>1</v>
       </c>
       <c r="C336" s="4">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="D336" s="4">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E336" s="4" t="s">
         <v>8</v>
@@ -18283,10 +18241,10 @@
         <v>1</v>
       </c>
       <c r="C337" s="4">
-        <v>5000</v>
+        <v>3700</v>
       </c>
       <c r="D337" s="4">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="E337" s="4" t="s">
         <v>22</v>
@@ -18322,10 +18280,10 @@
         <v>1</v>
       </c>
       <c r="C338" s="4">
-        <v>3500</v>
+        <v>4900</v>
       </c>
       <c r="D338" s="4">
-        <v>2000</v>
+        <v>3700</v>
       </c>
       <c r="E338" s="4" t="s">
         <v>22</v>
@@ -18363,10 +18321,10 @@
         <v>1</v>
       </c>
       <c r="C339" s="4">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D339" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E339" s="4" t="s">
         <v>22</v>
@@ -18404,10 +18362,10 @@
         <v>1</v>
       </c>
       <c r="C340" s="4">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="D340" s="4">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="E340" s="4" t="s">
         <v>19</v>
@@ -18445,10 +18403,10 @@
         <v>1</v>
       </c>
       <c r="C341" s="4">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="D341" s="4">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="E341" s="4" t="s">
         <v>8</v>
@@ -18486,10 +18444,10 @@
         <v>1</v>
       </c>
       <c r="C342" s="4">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="D342" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E342" s="4" t="s">
         <v>8</v>
@@ -18527,10 +18485,10 @@
         <v>1</v>
       </c>
       <c r="C343" s="4">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="D343" s="4">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="E343" s="4" t="s">
         <v>8</v>
@@ -18568,10 +18526,10 @@
         <v>1</v>
       </c>
       <c r="C344" s="17">
-        <v>7600</v>
+        <v>6700</v>
       </c>
       <c r="D344" s="17">
-        <v>4600</v>
+        <v>4000</v>
       </c>
       <c r="E344" s="4" t="s">
         <v>8</v>
@@ -18607,10 +18565,10 @@
         <v>1</v>
       </c>
       <c r="C345" s="4">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="D345" s="4">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E345" s="4" t="s">
         <v>22</v>
@@ -18666,6 +18624,18 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C337:C343 C191:C268 C345:C1048576">
     <cfRule type="colorScale" priority="119">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C344">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -18712,58 +18682,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:N295">
-    <cfRule type="expression" dxfId="17" priority="9">
-      <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="10">
-      <formula>OR($L2="buff",$L2="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="11">
-      <formula>OR($L2="dot",$L2="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="12">
-      <formula>OR($L2="tank",$L2="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="13">
-      <formula>OR($L2="heal",$L2="heal_all",$L2="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="14">
-      <formula>OR($L2="extra_attack",$L2="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J297:N343 J345:N345">
-    <cfRule type="expression" dxfId="11" priority="71">
-      <formula>OR($L297="debuff",$L297="bonus_debuff",$L297="revive")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="72">
-      <formula>OR($L297="buff",$L297="bonus_buff")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="73">
-      <formula>OR($L297="dot",$L297="stun")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="74">
-      <formula>OR($L297="tank",$L297="shield")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="75">
-      <formula>OR($L297="heal",$L297="heal_all",$L297="life_steal")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="76">
-      <formula>OR($L297="extra_attack",$L297="aoe")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C344">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D344">
     <cfRule type="colorScale" priority="7">
       <colorScale>
@@ -18776,24 +18694,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J344:N344">
+  <conditionalFormatting sqref="J2:N295">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>OR($L2="debuff",$L2="bonus_debuff",$L2="revive")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>OR($L2="buff",$L2="bonus_buff")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>OR($L2="dot",$L2="stun")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>OR($L2="tank",$L2="shield")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="13">
+      <formula>OR($L2="heal",$L2="heal_all",$L2="life_steal")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="14">
+      <formula>OR($L2="extra_attack",$L2="aoe")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J297:N345">
     <cfRule type="expression" dxfId="5" priority="1">
-      <formula>OR($L344="debuff",$L344="bonus_debuff",$L344="revive")</formula>
+      <formula>OR($L297="debuff",$L297="bonus_debuff",$L297="revive")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="2">
-      <formula>OR($L344="buff",$L344="bonus_buff")</formula>
+      <formula>OR($L297="buff",$L297="bonus_buff")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="3">
-      <formula>OR($L344="dot",$L344="stun")</formula>
+      <formula>OR($L297="dot",$L297="stun")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="4">
-      <formula>OR($L344="tank",$L344="shield")</formula>
+      <formula>OR($L297="tank",$L297="shield")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>OR($L344="heal",$L344="heal_all",$L344="life_steal")</formula>
+      <formula>OR($L297="heal",$L297="heal_all",$L297="life_steal")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>OR($L344="extra_attack",$L344="aoe")</formula>
+      <formula>OR($L297="extra_attack",$L297="aoe")</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D209C-FA26-4717-ADF2-FB0A79AA7ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53576B54-55AC-4D51-AC4F-8F77A36CC547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -460,7 +460,7 @@
         <v>Meta</v>
       </c>
       <c r="F2" t="str">
-        <v>https://i.pinimg.com/236x/dc/1c/38/dc1c380c8da96da99a613805061c703e.jpg</v>
+        <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSl0zRb2PJC1PivsOVji8YNKJEZAiGQ4HUalBhgDzE7hQ&amp;s=10</v>
       </c>
       <c r="G2" t="str">
         <v>H</v>

--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N346"/>
+  <dimension ref="A1:N348"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1457,7 +1457,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Blue Beetle</v>
+        <v>Blue Beetle III</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>Teen Titans</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>https://i.ibb.co/Y7g24sDp/heroes-who-are-inside-a-robotic-suit-v0-3yxhxf07yl2g1.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>Armadura escarabajo</v>
@@ -15623,9 +15623,97 @@
         <v>usar</v>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Nueva_carta_jv1ij</v>
+      </c>
+      <c r="B347">
+        <v>1</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347" t="str">
+        <v/>
+      </c>
+      <c r="F347" t="str">
+        <v/>
+      </c>
+      <c r="G347" t="str">
+        <v/>
+      </c>
+      <c r="H347" t="str">
+        <v/>
+      </c>
+      <c r="I347" t="str">
+        <v/>
+      </c>
+      <c r="J347" t="str">
+        <v/>
+      </c>
+      <c r="K347" t="str">
+        <v/>
+      </c>
+      <c r="L347" t="str">
+        <v/>
+      </c>
+      <c r="M347" t="str">
+        <v/>
+      </c>
+      <c r="N347" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Blue Beetle II</v>
+      </c>
+      <c r="B348">
+        <v>1</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F348" t="str">
+        <v>https://i.ibb.co/PswgLfNB/Blue-Bettle.jpg</v>
+      </c>
+      <c r="G348" t="str">
+        <v>H</v>
+      </c>
+      <c r="H348" t="str">
+        <v>JSA</v>
+      </c>
+      <c r="I348" t="str">
+        <v/>
+      </c>
+      <c r="J348" t="str">
+        <v/>
+      </c>
+      <c r="K348" t="str">
+        <v/>
+      </c>
+      <c r="L348" t="str">
+        <v/>
+      </c>
+      <c r="M348" t="str">
+        <v/>
+      </c>
+      <c r="N348" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N346"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N348"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N348"/>
+  <dimension ref="A1:N349"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1698,7 +1698,7 @@
         <v>H</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>The Terrifics</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -2886,7 +2886,7 @@
         <v>H</v>
       </c>
       <c r="H57" t="str">
-        <v>JSA</v>
+        <v>JSA; The Terrifics</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -5218,7 +5218,7 @@
         <v>H</v>
       </c>
       <c r="H110" t="str">
-        <v/>
+        <v>The Terrifics</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -15711,9 +15711,53 @@
         <v/>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Phantom Girl IV</v>
+      </c>
+      <c r="B349">
+        <v>1</v>
+      </c>
+      <c r="C349">
+        <v>7200</v>
+      </c>
+      <c r="D349">
+        <v>4000</v>
+      </c>
+      <c r="E349" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F349" t="str">
+        <v>https://static.wikia.nocookie.net/marvel_dc/images/d/d9/Linnya_Wazzo_Prime_Earth_001.jpg/revision/latest?cb=20180305161820</v>
+      </c>
+      <c r="G349" t="str">
+        <v>H</v>
+      </c>
+      <c r="H349" t="str">
+        <v>The Terrifics</v>
+      </c>
+      <c r="I349" t="str">
+        <v/>
+      </c>
+      <c r="J349" t="str">
+        <v>Intangibilidad</v>
+      </c>
+      <c r="K349" t="str">
+        <v/>
+      </c>
+      <c r="L349" t="str">
+        <v>shield</v>
+      </c>
+      <c r="M349" t="str">
+        <v>Poder*0,5</v>
+      </c>
+      <c r="N349" t="str">
+        <v>usar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N348"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N349"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N349"/>
+  <dimension ref="A1:N356"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15755,9 +15755,317 @@
         <v>usar</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Nueva_carta_zhmo5</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350" t="str">
+        <v/>
+      </c>
+      <c r="F350" t="str">
+        <v/>
+      </c>
+      <c r="G350" t="str">
+        <v/>
+      </c>
+      <c r="H350" t="str">
+        <v/>
+      </c>
+      <c r="I350" t="str">
+        <v/>
+      </c>
+      <c r="J350" t="str">
+        <v/>
+      </c>
+      <c r="K350" t="str">
+        <v/>
+      </c>
+      <c r="L350" t="str">
+        <v/>
+      </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
+      <c r="N350" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Nueva_carta_zhqi6</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351" t="str">
+        <v/>
+      </c>
+      <c r="F351" t="str">
+        <v/>
+      </c>
+      <c r="G351" t="str">
+        <v/>
+      </c>
+      <c r="H351" t="str">
+        <v/>
+      </c>
+      <c r="I351" t="str">
+        <v/>
+      </c>
+      <c r="J351" t="str">
+        <v/>
+      </c>
+      <c r="K351" t="str">
+        <v/>
+      </c>
+      <c r="L351" t="str">
+        <v/>
+      </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
+      <c r="N351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Merlyn</v>
+      </c>
+      <c r="B352">
+        <v>1</v>
+      </c>
+      <c r="C352">
+        <v>4500</v>
+      </c>
+      <c r="D352">
+        <v>3600</v>
+      </c>
+      <c r="E352" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F352" t="str">
+        <v>https://i.ibb.co/bgzN5Bjs/Meriln.jpg</v>
+      </c>
+      <c r="G352" t="str">
+        <v>V</v>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
+        <v/>
+      </c>
+      <c r="J352" t="str">
+        <v>Flechas oscuras</v>
+      </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
+      <c r="L352" t="str">
+        <v>stun</v>
+      </c>
+      <c r="M352" t="str">
+        <v>2</v>
+      </c>
+      <c r="N352" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Count Vertigo</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353">
+        <v>4000</v>
+      </c>
+      <c r="D353">
+        <v>3800</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F353" t="str">
+        <v>https://i.ibb.co/b5S9cjGH/vertigo.jpg</v>
+      </c>
+      <c r="G353" t="str">
+        <v>V</v>
+      </c>
+      <c r="H353" t="str">
+        <v/>
+      </c>
+      <c r="I353" t="str">
+        <v/>
+      </c>
+      <c r="J353" t="str">
+        <v>Efecto vértigo</v>
+      </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
+      <c r="L353" t="str">
+        <v>bonus_debuff</v>
+      </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
+      <c r="N353" t="str">
+        <v>auto</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Komodo</v>
+      </c>
+      <c r="B354">
+        <v>1</v>
+      </c>
+      <c r="C354">
+        <v>4600</v>
+      </c>
+      <c r="D354">
+        <v>3500</v>
+      </c>
+      <c r="E354" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F354" t="str">
+        <v>https://i.ibb.co/TypzxzD/Komodo.jpg</v>
+      </c>
+      <c r="G354" t="str">
+        <v>V</v>
+      </c>
+      <c r="H354" t="str">
+        <v/>
+      </c>
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
+        <v xml:space="preserve">Traición </v>
+      </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
+      <c r="L354" t="str">
+        <v>aoe</v>
+      </c>
+      <c r="M354" t="str">
+        <v>Poder*0,5</v>
+      </c>
+      <c r="N354" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Brick</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355">
+        <v>6000</v>
+      </c>
+      <c r="D355">
+        <v>4000</v>
+      </c>
+      <c r="E355" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F355" t="str">
+        <v>https://i.ibb.co/DPqRH0sh/Malo-De-Arrow.jpg</v>
+      </c>
+      <c r="G355" t="str">
+        <v>V</v>
+      </c>
+      <c r="H355" t="str">
+        <v/>
+      </c>
+      <c r="I355" t="str">
+        <v>https://i.ibb.co/jvbJPmtH/Malo-De-Arrow2.jpg</v>
+      </c>
+      <c r="J355" t="str">
+        <v>Invulnerabilidad</v>
+      </c>
+      <c r="K355" t="str">
+        <v/>
+      </c>
+      <c r="L355" t="str">
+        <v>tank</v>
+      </c>
+      <c r="M355" t="str">
+        <v>Salud*2</v>
+      </c>
+      <c r="N355" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Cupid</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356">
+        <v>4000</v>
+      </c>
+      <c r="D356">
+        <v>3600</v>
+      </c>
+      <c r="E356" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F356" t="str">
+        <v>https://i.ibb.co/XxrhDG82/Quien-Sea-Esta-Pava.jpg</v>
+      </c>
+      <c r="G356" t="str">
+        <v>V</v>
+      </c>
+      <c r="H356" t="str">
+        <v/>
+      </c>
+      <c r="I356" t="str">
+        <v/>
+      </c>
+      <c r="J356" t="str">
+        <v>Amor enfermizo</v>
+      </c>
+      <c r="K356" t="str">
+        <v/>
+      </c>
+      <c r="L356" t="str">
+        <v>extra_attack</v>
+      </c>
+      <c r="M356" t="str">
+        <v>Poder*1</v>
+      </c>
+      <c r="N356" t="str">
+        <v>usar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N349"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N356"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N348"/>
+  <dimension ref="A1:N356"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1698,7 +1698,7 @@
         <v>H</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>The Terrifics</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -2886,7 +2886,7 @@
         <v>H</v>
       </c>
       <c r="H57" t="str">
-        <v>JSA</v>
+        <v>JSA; The Terrifics</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -5218,7 +5218,7 @@
         <v>H</v>
       </c>
       <c r="H110" t="str">
-        <v/>
+        <v>The Terrifics</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -15711,9 +15711,361 @@
         <v/>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Phantom Girl IV</v>
+      </c>
+      <c r="B349">
+        <v>1</v>
+      </c>
+      <c r="C349">
+        <v>7200</v>
+      </c>
+      <c r="D349">
+        <v>4000</v>
+      </c>
+      <c r="E349" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F349" t="str">
+        <v>https://static.wikia.nocookie.net/marvel_dc/images/d/d9/Linnya_Wazzo_Prime_Earth_001.jpg/revision/latest?cb=20180305161820</v>
+      </c>
+      <c r="G349" t="str">
+        <v>H</v>
+      </c>
+      <c r="H349" t="str">
+        <v>The Terrifics</v>
+      </c>
+      <c r="I349" t="str">
+        <v/>
+      </c>
+      <c r="J349" t="str">
+        <v>Intangibilidad</v>
+      </c>
+      <c r="K349" t="str">
+        <v/>
+      </c>
+      <c r="L349" t="str">
+        <v>shield</v>
+      </c>
+      <c r="M349" t="str">
+        <v>Poder*0,5</v>
+      </c>
+      <c r="N349" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Nueva_carta_zhmo5</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350" t="str">
+        <v/>
+      </c>
+      <c r="F350" t="str">
+        <v/>
+      </c>
+      <c r="G350" t="str">
+        <v/>
+      </c>
+      <c r="H350" t="str">
+        <v/>
+      </c>
+      <c r="I350" t="str">
+        <v/>
+      </c>
+      <c r="J350" t="str">
+        <v/>
+      </c>
+      <c r="K350" t="str">
+        <v/>
+      </c>
+      <c r="L350" t="str">
+        <v/>
+      </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
+      <c r="N350" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Nueva_carta_zhqi6</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351" t="str">
+        <v/>
+      </c>
+      <c r="F351" t="str">
+        <v/>
+      </c>
+      <c r="G351" t="str">
+        <v/>
+      </c>
+      <c r="H351" t="str">
+        <v/>
+      </c>
+      <c r="I351" t="str">
+        <v/>
+      </c>
+      <c r="J351" t="str">
+        <v/>
+      </c>
+      <c r="K351" t="str">
+        <v/>
+      </c>
+      <c r="L351" t="str">
+        <v/>
+      </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
+      <c r="N351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Merlyn</v>
+      </c>
+      <c r="B352">
+        <v>1</v>
+      </c>
+      <c r="C352">
+        <v>4500</v>
+      </c>
+      <c r="D352">
+        <v>3600</v>
+      </c>
+      <c r="E352" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F352" t="str">
+        <v>https://i.ibb.co/bgzN5Bjs/Meriln.jpg</v>
+      </c>
+      <c r="G352" t="str">
+        <v>V</v>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
+        <v/>
+      </c>
+      <c r="J352" t="str">
+        <v>Flechas oscuras</v>
+      </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
+      <c r="L352" t="str">
+        <v>stun</v>
+      </c>
+      <c r="M352" t="str">
+        <v>2</v>
+      </c>
+      <c r="N352" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Count Vertigo</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353">
+        <v>4000</v>
+      </c>
+      <c r="D353">
+        <v>3800</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F353" t="str">
+        <v>https://i.ibb.co/b5S9cjGH/vertigo.jpg</v>
+      </c>
+      <c r="G353" t="str">
+        <v>V</v>
+      </c>
+      <c r="H353" t="str">
+        <v/>
+      </c>
+      <c r="I353" t="str">
+        <v/>
+      </c>
+      <c r="J353" t="str">
+        <v>Efecto vértigo</v>
+      </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
+      <c r="L353" t="str">
+        <v>bonus_debuff</v>
+      </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
+      <c r="N353" t="str">
+        <v>auto</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Komodo</v>
+      </c>
+      <c r="B354">
+        <v>1</v>
+      </c>
+      <c r="C354">
+        <v>4600</v>
+      </c>
+      <c r="D354">
+        <v>3500</v>
+      </c>
+      <c r="E354" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F354" t="str">
+        <v>https://i.ibb.co/TypzxzD/Komodo.jpg</v>
+      </c>
+      <c r="G354" t="str">
+        <v>V</v>
+      </c>
+      <c r="H354" t="str">
+        <v/>
+      </c>
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
+        <v xml:space="preserve">Traición </v>
+      </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
+      <c r="L354" t="str">
+        <v>aoe</v>
+      </c>
+      <c r="M354" t="str">
+        <v>Poder*0,5</v>
+      </c>
+      <c r="N354" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Brick</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355">
+        <v>6000</v>
+      </c>
+      <c r="D355">
+        <v>4000</v>
+      </c>
+      <c r="E355" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F355" t="str">
+        <v>https://i.ibb.co/DPqRH0sh/Malo-De-Arrow.jpg</v>
+      </c>
+      <c r="G355" t="str">
+        <v>V</v>
+      </c>
+      <c r="H355" t="str">
+        <v/>
+      </c>
+      <c r="I355" t="str">
+        <v>https://i.ibb.co/jvbJPmtH/Malo-De-Arrow2.jpg</v>
+      </c>
+      <c r="J355" t="str">
+        <v>Invulnerabilidad</v>
+      </c>
+      <c r="K355" t="str">
+        <v/>
+      </c>
+      <c r="L355" t="str">
+        <v>tank</v>
+      </c>
+      <c r="M355" t="str">
+        <v>Salud*2</v>
+      </c>
+      <c r="N355" t="str">
+        <v>usar</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Cupid</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356">
+        <v>4000</v>
+      </c>
+      <c r="D356">
+        <v>3600</v>
+      </c>
+      <c r="E356" t="str">
+        <v>Meta</v>
+      </c>
+      <c r="F356" t="str">
+        <v>https://i.ibb.co/XxrhDG82/Quien-Sea-Esta-Pava.jpg</v>
+      </c>
+      <c r="G356" t="str">
+        <v>V</v>
+      </c>
+      <c r="H356" t="str">
+        <v/>
+      </c>
+      <c r="I356" t="str">
+        <v/>
+      </c>
+      <c r="J356" t="str">
+        <v>Amor enfermizo</v>
+      </c>
+      <c r="K356" t="str">
+        <v/>
+      </c>
+      <c r="L356" t="str">
+        <v>extra_attack</v>
+      </c>
+      <c r="M356" t="str">
+        <v>Poder*1</v>
+      </c>
+      <c r="N356" t="str">
+        <v>usar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N348"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N356"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/resources/cartas.xlsx
+++ b/public/resources/cartas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16063,9 +16063,53 @@
         <v>usar</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Cyrus Broderick</v>
+      </c>
+      <c r="B357">
+        <v>1</v>
+      </c>
+      <c r="C357">
+        <v>3800</v>
+      </c>
+      <c r="D357">
+        <v>2900</v>
+      </c>
+      <c r="E357" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="F357" t="str">
+        <v>https://comicvine.gamespot.com/a/uploads/scale_small/11114/111147698/5331772-screen%20shot%202016-07-20%20at%2011.30.01%20am.png</v>
+      </c>
+      <c r="G357" t="str">
+        <v>V</v>
+      </c>
+      <c r="H357" t="str">
+        <v/>
+      </c>
+      <c r="I357" t="str">
+        <v/>
+      </c>
+      <c r="J357" t="str">
+        <v>Puñalada trapera</v>
+      </c>
+      <c r="K357" t="str">
+        <v/>
+      </c>
+      <c r="L357" t="str">
+        <v>dot</v>
+      </c>
+      <c r="M357" t="str">
+        <v>Poder / 8</v>
+      </c>
+      <c r="N357" t="str">
+        <v>usar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N356"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N357"/>
   </ignoredErrors>
 </worksheet>
 </file>